--- a/Primera versión/Input/Encuesta_Movilidad_Version_08_08_25.xlsx
+++ b/Primera versión/Input/Encuesta_Movilidad_Version_08_08_25.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8f89820ab55adc2/Escritorio/Natura/Input/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8f89820ab55adc2/Escritorio/Natura/Primera versión/Input/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="138" documentId="8_{676B3BA6-46B2-41C2-A545-10BB88DE3D71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A321138B-2ACF-49D7-ACB2-E6CD056A9086}"/>
@@ -24,6 +24,17 @@
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -4157,41 +4168,264 @@
     <xf numFmtId="0" fontId="15" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4200,156 +4434,6 @@
     <xf numFmtId="0" fontId="17" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4361,9 +4445,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -4396,15 +4477,6 @@
     <xf numFmtId="0" fontId="15" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -4429,183 +4501,122 @@
     <xf numFmtId="0" fontId="15" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4650,6 +4661,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4659,41 +4697,14 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -4805,10 +4816,6 @@
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5027,64 +5034,64 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="170"/>
-      <c r="B1" s="171"/>
-      <c r="C1" s="171"/>
-      <c r="D1" s="171"/>
-      <c r="E1" s="171"/>
-      <c r="F1" s="171"/>
-      <c r="G1" s="171"/>
-      <c r="H1" s="171"/>
+      <c r="A1" s="317"/>
+      <c r="B1" s="227"/>
+      <c r="C1" s="227"/>
+      <c r="D1" s="227"/>
+      <c r="E1" s="227"/>
+      <c r="F1" s="227"/>
+      <c r="G1" s="227"/>
+      <c r="H1" s="227"/>
       <c r="I1" s="96"/>
       <c r="J1" s="96"/>
       <c r="K1" s="96"/>
     </row>
     <row r="2" spans="1:11" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="172" t="s">
+      <c r="A2" s="318" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="171"/>
-      <c r="C2" s="171"/>
-      <c r="D2" s="171"/>
-      <c r="E2" s="171"/>
-      <c r="F2" s="171"/>
-      <c r="G2" s="171"/>
-      <c r="H2" s="171"/>
-      <c r="I2" s="171"/>
-      <c r="J2" s="171"/>
-      <c r="K2" s="171"/>
+      <c r="B2" s="227"/>
+      <c r="C2" s="227"/>
+      <c r="D2" s="227"/>
+      <c r="E2" s="227"/>
+      <c r="F2" s="227"/>
+      <c r="G2" s="227"/>
+      <c r="H2" s="227"/>
+      <c r="I2" s="227"/>
+      <c r="J2" s="227"/>
+      <c r="K2" s="227"/>
     </row>
     <row r="3" spans="1:11" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="46" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="173" t="s">
+      <c r="B3" s="319" t="s">
         <v>457</v>
       </c>
-      <c r="C3" s="173"/>
-      <c r="D3" s="173"/>
-      <c r="E3" s="173"/>
-      <c r="F3" s="173"/>
-      <c r="G3" s="173"/>
-      <c r="H3" s="173"/>
-      <c r="I3" s="173"/>
-      <c r="J3" s="173"/>
-      <c r="K3" s="173"/>
+      <c r="C3" s="319"/>
+      <c r="D3" s="319"/>
+      <c r="E3" s="319"/>
+      <c r="F3" s="319"/>
+      <c r="G3" s="319"/>
+      <c r="H3" s="319"/>
+      <c r="I3" s="319"/>
+      <c r="J3" s="319"/>
+      <c r="K3" s="319"/>
     </row>
     <row r="4" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="174" t="s">
+      <c r="A4" s="290" t="s">
         <v>549</v>
       </c>
-      <c r="B4" s="175"/>
-      <c r="C4" s="175"/>
-      <c r="D4" s="175"/>
-      <c r="E4" s="175"/>
-      <c r="F4" s="175"/>
-      <c r="G4" s="175"/>
-      <c r="H4" s="175"/>
-      <c r="I4" s="175"/>
-      <c r="J4" s="175"/>
-      <c r="K4" s="176"/>
+      <c r="B4" s="286"/>
+      <c r="C4" s="286"/>
+      <c r="D4" s="286"/>
+      <c r="E4" s="286"/>
+      <c r="F4" s="286"/>
+      <c r="G4" s="286"/>
+      <c r="H4" s="286"/>
+      <c r="I4" s="286"/>
+      <c r="J4" s="286"/>
+      <c r="K4" s="287"/>
     </row>
     <row r="5" spans="1:11" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="47" t="s">
@@ -5122,10 +5129,10 @@
       </c>
     </row>
     <row r="6" spans="1:11" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="177" t="s">
+      <c r="A6" s="320" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="179" t="s">
+      <c r="B6" s="196" t="s">
         <v>14</v>
       </c>
       <c r="C6" s="38">
@@ -5143,8 +5150,8 @@
       <c r="K6" s="40"/>
     </row>
     <row r="7" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="178"/>
-      <c r="B7" s="180"/>
+      <c r="A7" s="206"/>
+      <c r="B7" s="207"/>
       <c r="C7" s="38">
         <v>2</v>
       </c>
@@ -5160,10 +5167,10 @@
       <c r="K7" s="40"/>
     </row>
     <row r="8" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="194" t="s">
+      <c r="A8" s="323" t="s">
         <v>550</v>
       </c>
-      <c r="B8" s="193" t="s">
+      <c r="B8" s="322" t="s">
         <v>655</v>
       </c>
       <c r="C8" s="38">
@@ -5183,8 +5190,8 @@
       <c r="K8" s="40"/>
     </row>
     <row r="9" spans="1:11" ht="48.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="178"/>
-      <c r="B9" s="178"/>
+      <c r="A9" s="206"/>
+      <c r="B9" s="206"/>
       <c r="C9" s="38">
         <v>2</v>
       </c>
@@ -5227,10 +5234,10 @@
       <c r="K10" s="40"/>
     </row>
     <row r="11" spans="1:11" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="191" t="s">
+      <c r="A11" s="313" t="s">
         <v>551</v>
       </c>
-      <c r="B11" s="179" t="s">
+      <c r="B11" s="196" t="s">
         <v>458</v>
       </c>
       <c r="C11" s="38">
@@ -5250,8 +5257,8 @@
       <c r="K11" s="40"/>
     </row>
     <row r="12" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="196"/>
-      <c r="B12" s="195"/>
+      <c r="A12" s="315"/>
+      <c r="B12" s="198"/>
       <c r="C12" s="38">
         <v>2</v>
       </c>
@@ -5267,10 +5274,10 @@
       <c r="K12" s="40"/>
     </row>
     <row r="13" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="191" t="s">
+      <c r="A13" s="313" t="s">
         <v>552</v>
       </c>
-      <c r="B13" s="179" t="s">
+      <c r="B13" s="196" t="s">
         <v>459</v>
       </c>
       <c r="C13" s="38">
@@ -5288,8 +5295,8 @@
       <c r="K13" s="40"/>
     </row>
     <row r="14" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="196"/>
-      <c r="B14" s="195"/>
+      <c r="A14" s="315"/>
+      <c r="B14" s="198"/>
       <c r="C14" s="38">
         <v>2</v>
       </c>
@@ -5307,10 +5314,10 @@
       <c r="K14" s="40"/>
     </row>
     <row r="15" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="198" t="s">
+      <c r="A15" s="316" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="179" t="s">
+      <c r="B15" s="196" t="s">
         <v>22</v>
       </c>
       <c r="C15" s="38">
@@ -5330,8 +5337,8 @@
       <c r="K15" s="40"/>
     </row>
     <row r="16" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="178"/>
-      <c r="B16" s="180"/>
+      <c r="A16" s="206"/>
+      <c r="B16" s="207"/>
       <c r="C16" s="38">
         <v>2</v>
       </c>
@@ -5395,10 +5402,10 @@
       <c r="K18" s="40"/>
     </row>
     <row r="19" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="191" t="s">
+      <c r="A19" s="313" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="179" t="s">
+      <c r="B19" s="196" t="s">
         <v>32</v>
       </c>
       <c r="C19" s="43">
@@ -5420,8 +5427,8 @@
       <c r="K19" s="40"/>
     </row>
     <row r="20" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="197"/>
-      <c r="B20" s="185"/>
+      <c r="A20" s="314"/>
+      <c r="B20" s="197"/>
       <c r="C20" s="43">
         <v>2</v>
       </c>
@@ -5437,8 +5444,8 @@
       <c r="K20" s="40"/>
     </row>
     <row r="21" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A21" s="197"/>
-      <c r="B21" s="185"/>
+      <c r="A21" s="314"/>
+      <c r="B21" s="197"/>
       <c r="C21" s="43">
         <v>3</v>
       </c>
@@ -5454,8 +5461,8 @@
       <c r="K21" s="40"/>
     </row>
     <row r="22" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A22" s="197"/>
-      <c r="B22" s="185"/>
+      <c r="A22" s="314"/>
+      <c r="B22" s="197"/>
       <c r="C22" s="43">
         <v>4</v>
       </c>
@@ -5471,8 +5478,8 @@
       <c r="K22" s="40"/>
     </row>
     <row r="23" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A23" s="197"/>
-      <c r="B23" s="185"/>
+      <c r="A23" s="314"/>
+      <c r="B23" s="197"/>
       <c r="C23" s="43">
         <v>5</v>
       </c>
@@ -5488,8 +5495,8 @@
       <c r="K23" s="40"/>
     </row>
     <row r="24" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A24" s="197"/>
-      <c r="B24" s="185"/>
+      <c r="A24" s="314"/>
+      <c r="B24" s="197"/>
       <c r="C24" s="43">
         <v>6</v>
       </c>
@@ -5505,8 +5512,8 @@
       <c r="K24" s="40"/>
     </row>
     <row r="25" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A25" s="196"/>
-      <c r="B25" s="195"/>
+      <c r="A25" s="315"/>
+      <c r="B25" s="198"/>
       <c r="C25" s="43">
         <v>99</v>
       </c>
@@ -5545,10 +5552,10 @@
       <c r="K26" s="40"/>
     </row>
     <row r="27" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A27" s="181" t="s">
+      <c r="A27" s="312" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="179" t="s">
+      <c r="B27" s="196" t="s">
         <v>46</v>
       </c>
       <c r="C27" s="43">
@@ -5570,8 +5577,8 @@
       <c r="K27" s="40"/>
     </row>
     <row r="28" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A28" s="183"/>
-      <c r="B28" s="186"/>
+      <c r="A28" s="258"/>
+      <c r="B28" s="205"/>
       <c r="C28" s="43">
         <v>2</v>
       </c>
@@ -5587,8 +5594,8 @@
       <c r="K28" s="40"/>
     </row>
     <row r="29" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="183"/>
-      <c r="B29" s="186"/>
+      <c r="A29" s="258"/>
+      <c r="B29" s="205"/>
       <c r="C29" s="43">
         <v>3</v>
       </c>
@@ -5604,8 +5611,8 @@
       <c r="K29" s="40"/>
     </row>
     <row r="30" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="183"/>
-      <c r="B30" s="186"/>
+      <c r="A30" s="258"/>
+      <c r="B30" s="205"/>
       <c r="C30" s="43">
         <v>4</v>
       </c>
@@ -5621,8 +5628,8 @@
       <c r="K30" s="40"/>
     </row>
     <row r="31" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A31" s="183"/>
-      <c r="B31" s="186"/>
+      <c r="A31" s="258"/>
+      <c r="B31" s="205"/>
       <c r="C31" s="43">
         <v>5</v>
       </c>
@@ -5638,8 +5645,8 @@
       <c r="K31" s="40"/>
     </row>
     <row r="32" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A32" s="183"/>
-      <c r="B32" s="186"/>
+      <c r="A32" s="258"/>
+      <c r="B32" s="205"/>
       <c r="C32" s="43">
         <v>6</v>
       </c>
@@ -5655,8 +5662,8 @@
       <c r="K32" s="40"/>
     </row>
     <row r="33" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A33" s="184"/>
-      <c r="B33" s="180"/>
+      <c r="A33" s="259"/>
+      <c r="B33" s="207"/>
       <c r="C33" s="43">
         <v>99</v>
       </c>
@@ -5672,10 +5679,10 @@
       <c r="K33" s="40"/>
     </row>
     <row r="34" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A34" s="187" t="s">
+      <c r="A34" s="179" t="s">
         <v>54</v>
       </c>
-      <c r="B34" s="189" t="s">
+      <c r="B34" s="308" t="s">
         <v>55</v>
       </c>
       <c r="C34" s="108">
@@ -5695,8 +5702,8 @@
       <c r="K34" s="40"/>
     </row>
     <row r="35" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A35" s="188"/>
-      <c r="B35" s="190"/>
+      <c r="A35" s="255"/>
+      <c r="B35" s="311"/>
       <c r="C35" s="108">
         <v>2</v>
       </c>
@@ -5712,10 +5719,10 @@
       <c r="K35" s="40"/>
     </row>
     <row r="36" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="181" t="s">
+      <c r="A36" s="312" t="s">
         <v>57</v>
       </c>
-      <c r="B36" s="179" t="s">
+      <c r="B36" s="196" t="s">
         <v>58</v>
       </c>
       <c r="C36" s="53">
@@ -5741,8 +5748,8 @@
       </c>
     </row>
     <row r="37" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="183"/>
-      <c r="B37" s="186"/>
+      <c r="A37" s="258"/>
+      <c r="B37" s="205"/>
       <c r="C37" s="53">
         <v>2</v>
       </c>
@@ -5758,8 +5765,8 @@
       <c r="K37" s="40"/>
     </row>
     <row r="38" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="183"/>
-      <c r="B38" s="186"/>
+      <c r="A38" s="258"/>
+      <c r="B38" s="205"/>
       <c r="C38" s="53"/>
       <c r="D38" s="114" t="s">
         <v>576</v>
@@ -5773,8 +5780,8 @@
       <c r="K38" s="40"/>
     </row>
     <row r="39" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="183"/>
-      <c r="B39" s="186"/>
+      <c r="A39" s="258"/>
+      <c r="B39" s="205"/>
       <c r="C39" s="53">
         <v>3</v>
       </c>
@@ -5790,8 +5797,8 @@
       <c r="K39" s="40"/>
     </row>
     <row r="40" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="183"/>
-      <c r="B40" s="186"/>
+      <c r="A40" s="258"/>
+      <c r="B40" s="205"/>
       <c r="C40" s="53"/>
       <c r="D40" s="114" t="s">
         <v>577</v>
@@ -5805,8 +5812,8 @@
       <c r="K40" s="40"/>
     </row>
     <row r="41" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="183"/>
-      <c r="B41" s="186"/>
+      <c r="A41" s="258"/>
+      <c r="B41" s="205"/>
       <c r="C41" s="53">
         <v>4</v>
       </c>
@@ -5822,8 +5829,8 @@
       <c r="K41" s="40"/>
     </row>
     <row r="42" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="183"/>
-      <c r="B42" s="186"/>
+      <c r="A42" s="258"/>
+      <c r="B42" s="205"/>
       <c r="C42" s="53">
         <v>8</v>
       </c>
@@ -5839,8 +5846,8 @@
       <c r="K42" s="40"/>
     </row>
     <row r="43" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="183"/>
-      <c r="B43" s="186"/>
+      <c r="A43" s="258"/>
+      <c r="B43" s="205"/>
       <c r="C43" s="53">
         <v>9</v>
       </c>
@@ -5856,8 +5863,8 @@
       <c r="K43" s="40"/>
     </row>
     <row r="44" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="183"/>
-      <c r="B44" s="186"/>
+      <c r="A44" s="258"/>
+      <c r="B44" s="205"/>
       <c r="C44" s="53">
         <v>10</v>
       </c>
@@ -5873,8 +5880,8 @@
       <c r="K44" s="40"/>
     </row>
     <row r="45" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="183"/>
-      <c r="B45" s="186"/>
+      <c r="A45" s="258"/>
+      <c r="B45" s="205"/>
       <c r="C45" s="53">
         <v>11</v>
       </c>
@@ -5890,8 +5897,8 @@
       <c r="K45" s="40"/>
     </row>
     <row r="46" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="183"/>
-      <c r="B46" s="186"/>
+      <c r="A46" s="258"/>
+      <c r="B46" s="205"/>
       <c r="C46" s="53">
         <v>12</v>
       </c>
@@ -5907,8 +5914,8 @@
       <c r="K46" s="40"/>
     </row>
     <row r="47" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="183"/>
-      <c r="B47" s="186"/>
+      <c r="A47" s="258"/>
+      <c r="B47" s="205"/>
       <c r="C47" s="53">
         <v>13</v>
       </c>
@@ -5924,8 +5931,8 @@
       <c r="K47" s="40"/>
     </row>
     <row r="48" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="183"/>
-      <c r="B48" s="186"/>
+      <c r="A48" s="258"/>
+      <c r="B48" s="205"/>
       <c r="C48" s="53">
         <v>98</v>
       </c>
@@ -5941,10 +5948,10 @@
       <c r="K48" s="40"/>
     </row>
     <row r="49" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A49" s="191" t="s">
+      <c r="A49" s="313" t="s">
         <v>69</v>
       </c>
-      <c r="B49" s="179" t="s">
+      <c r="B49" s="196" t="s">
         <v>70</v>
       </c>
       <c r="C49" s="43">
@@ -5968,8 +5975,8 @@
       <c r="K49" s="40"/>
     </row>
     <row r="50" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A50" s="192"/>
-      <c r="B50" s="186"/>
+      <c r="A50" s="204"/>
+      <c r="B50" s="205"/>
       <c r="C50" s="43">
         <v>2</v>
       </c>
@@ -5985,8 +5992,8 @@
       <c r="K50" s="40"/>
     </row>
     <row r="51" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A51" s="178"/>
-      <c r="B51" s="180"/>
+      <c r="A51" s="206"/>
+      <c r="B51" s="207"/>
       <c r="C51" s="43">
         <v>98</v>
       </c>
@@ -6002,10 +6009,10 @@
       <c r="K51" s="40"/>
     </row>
     <row r="52" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A52" s="181" t="s">
+      <c r="A52" s="312" t="s">
         <v>76</v>
       </c>
-      <c r="B52" s="179" t="s">
+      <c r="B52" s="196" t="s">
         <v>77</v>
       </c>
       <c r="C52" s="43">
@@ -6029,8 +6036,8 @@
       <c r="K52" s="40"/>
     </row>
     <row r="53" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A53" s="182"/>
-      <c r="B53" s="185"/>
+      <c r="A53" s="321"/>
+      <c r="B53" s="197"/>
       <c r="C53" s="43">
         <v>2</v>
       </c>
@@ -6048,8 +6055,8 @@
       <c r="K53" s="40"/>
     </row>
     <row r="54" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A54" s="183"/>
-      <c r="B54" s="186"/>
+      <c r="A54" s="258"/>
+      <c r="B54" s="205"/>
       <c r="C54" s="43">
         <v>3</v>
       </c>
@@ -6067,8 +6074,8 @@
       <c r="K54" s="40"/>
     </row>
     <row r="55" spans="1:11" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="183"/>
-      <c r="B55" s="186"/>
+      <c r="A55" s="258"/>
+      <c r="B55" s="205"/>
       <c r="C55" s="43">
         <v>4</v>
       </c>
@@ -6090,8 +6097,8 @@
       <c r="K55" s="40"/>
     </row>
     <row r="56" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A56" s="183"/>
-      <c r="B56" s="186"/>
+      <c r="A56" s="258"/>
+      <c r="B56" s="205"/>
       <c r="C56" s="43">
         <v>5</v>
       </c>
@@ -6107,8 +6114,8 @@
       <c r="K56" s="40"/>
     </row>
     <row r="57" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A57" s="183"/>
-      <c r="B57" s="186"/>
+      <c r="A57" s="258"/>
+      <c r="B57" s="205"/>
       <c r="C57" s="43">
         <v>6</v>
       </c>
@@ -6126,8 +6133,8 @@
       <c r="K57" s="40"/>
     </row>
     <row r="58" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A58" s="183"/>
-      <c r="B58" s="186"/>
+      <c r="A58" s="258"/>
+      <c r="B58" s="205"/>
       <c r="C58" s="43">
         <v>7</v>
       </c>
@@ -6143,8 +6150,8 @@
       <c r="K58" s="40"/>
     </row>
     <row r="59" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A59" s="184"/>
-      <c r="B59" s="180"/>
+      <c r="A59" s="259"/>
+      <c r="B59" s="207"/>
       <c r="C59" s="38">
         <v>96</v>
       </c>
@@ -6160,10 +6167,10 @@
       <c r="K59" s="40"/>
     </row>
     <row r="60" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A60" s="181" t="s">
+      <c r="A60" s="312" t="s">
         <v>90</v>
       </c>
-      <c r="B60" s="179" t="s">
+      <c r="B60" s="196" t="s">
         <v>583</v>
       </c>
       <c r="C60" s="43">
@@ -6181,8 +6188,8 @@
       <c r="K60" s="40"/>
     </row>
     <row r="61" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A61" s="183"/>
-      <c r="B61" s="186"/>
+      <c r="A61" s="258"/>
+      <c r="B61" s="205"/>
       <c r="C61" s="43">
         <v>2</v>
       </c>
@@ -6198,8 +6205,8 @@
       <c r="K61" s="40"/>
     </row>
     <row r="62" spans="1:11" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="183"/>
-      <c r="B62" s="186"/>
+      <c r="A62" s="258"/>
+      <c r="B62" s="205"/>
       <c r="C62" s="43">
         <v>3</v>
       </c>
@@ -6217,8 +6224,8 @@
       <c r="K62" s="40"/>
     </row>
     <row r="63" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A63" s="183"/>
-      <c r="B63" s="186"/>
+      <c r="A63" s="258"/>
+      <c r="B63" s="205"/>
       <c r="C63" s="43">
         <v>4</v>
       </c>
@@ -6234,8 +6241,8 @@
       <c r="K63" s="40"/>
     </row>
     <row r="64" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A64" s="183"/>
-      <c r="B64" s="186"/>
+      <c r="A64" s="258"/>
+      <c r="B64" s="205"/>
       <c r="C64" s="43">
         <v>5</v>
       </c>
@@ -6251,8 +6258,8 @@
       <c r="K64" s="40"/>
     </row>
     <row r="65" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A65" s="183"/>
-      <c r="B65" s="186"/>
+      <c r="A65" s="258"/>
+      <c r="B65" s="205"/>
       <c r="C65" s="43">
         <v>6</v>
       </c>
@@ -6268,8 +6275,8 @@
       <c r="K65" s="40"/>
     </row>
     <row r="66" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A66" s="183"/>
-      <c r="B66" s="186"/>
+      <c r="A66" s="258"/>
+      <c r="B66" s="205"/>
       <c r="C66" s="43">
         <v>7</v>
       </c>
@@ -6285,8 +6292,8 @@
       <c r="K66" s="40"/>
     </row>
     <row r="67" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="183"/>
-      <c r="B67" s="186"/>
+      <c r="A67" s="258"/>
+      <c r="B67" s="205"/>
       <c r="C67" s="43">
         <v>8</v>
       </c>
@@ -6302,8 +6309,8 @@
       <c r="K67" s="40"/>
     </row>
     <row r="68" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A68" s="184"/>
-      <c r="B68" s="180"/>
+      <c r="A68" s="259"/>
+      <c r="B68" s="207"/>
       <c r="C68" s="43">
         <v>9</v>
       </c>
@@ -6319,10 +6326,10 @@
       <c r="K68" s="40"/>
     </row>
     <row r="69" spans="1:11" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="191" t="s">
+      <c r="A69" s="313" t="s">
         <v>97</v>
       </c>
-      <c r="B69" s="179" t="s">
+      <c r="B69" s="196" t="s">
         <v>658</v>
       </c>
       <c r="C69" s="43">
@@ -6346,8 +6353,8 @@
       <c r="K69" s="40"/>
     </row>
     <row r="70" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="197"/>
-      <c r="B70" s="185"/>
+      <c r="A70" s="314"/>
+      <c r="B70" s="197"/>
       <c r="C70" s="43">
         <v>2</v>
       </c>
@@ -6363,8 +6370,8 @@
       <c r="K70" s="40"/>
     </row>
     <row r="71" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="197"/>
-      <c r="B71" s="185"/>
+      <c r="A71" s="314"/>
+      <c r="B71" s="197"/>
       <c r="C71" s="43">
         <v>3</v>
       </c>
@@ -6380,8 +6387,8 @@
       <c r="K71" s="40"/>
     </row>
     <row r="72" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="197"/>
-      <c r="B72" s="185"/>
+      <c r="A72" s="314"/>
+      <c r="B72" s="197"/>
       <c r="C72" s="43">
         <v>4</v>
       </c>
@@ -6397,8 +6404,8 @@
       <c r="K72" s="40"/>
     </row>
     <row r="73" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A73" s="197"/>
-      <c r="B73" s="185"/>
+      <c r="A73" s="314"/>
+      <c r="B73" s="197"/>
       <c r="C73" s="43">
         <v>5</v>
       </c>
@@ -6416,8 +6423,8 @@
       <c r="K73" s="40"/>
     </row>
     <row r="74" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="197"/>
-      <c r="B74" s="185"/>
+      <c r="A74" s="314"/>
+      <c r="B74" s="197"/>
       <c r="C74" s="43">
         <v>6</v>
       </c>
@@ -6439,8 +6446,8 @@
       <c r="K74" s="40"/>
     </row>
     <row r="75" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A75" s="197"/>
-      <c r="B75" s="185"/>
+      <c r="A75" s="314"/>
+      <c r="B75" s="197"/>
       <c r="C75" s="43">
         <v>7</v>
       </c>
@@ -6458,8 +6465,8 @@
       <c r="K75" s="40"/>
     </row>
     <row r="76" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A76" s="197"/>
-      <c r="B76" s="185"/>
+      <c r="A76" s="314"/>
+      <c r="B76" s="197"/>
       <c r="C76" s="43">
         <v>8</v>
       </c>
@@ -6477,8 +6484,8 @@
       <c r="K76" s="40"/>
     </row>
     <row r="77" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A77" s="197"/>
-      <c r="B77" s="185"/>
+      <c r="A77" s="314"/>
+      <c r="B77" s="197"/>
       <c r="C77" s="43">
         <v>9</v>
       </c>
@@ -6496,8 +6503,8 @@
       <c r="K77" s="40"/>
     </row>
     <row r="78" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A78" s="197"/>
-      <c r="B78" s="185"/>
+      <c r="A78" s="314"/>
+      <c r="B78" s="197"/>
       <c r="C78" s="43">
         <v>10</v>
       </c>
@@ -6515,8 +6522,8 @@
       <c r="K78" s="40"/>
     </row>
     <row r="79" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="196"/>
-      <c r="B79" s="195"/>
+      <c r="A79" s="315"/>
+      <c r="B79" s="198"/>
       <c r="C79" s="43">
         <v>11</v>
       </c>
@@ -6538,10 +6545,10 @@
       <c r="K79" s="40"/>
     </row>
     <row r="80" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A80" s="191" t="s">
+      <c r="A80" s="313" t="s">
         <v>103</v>
       </c>
-      <c r="B80" s="179" t="s">
+      <c r="B80" s="196" t="s">
         <v>659</v>
       </c>
       <c r="C80" s="43">
@@ -6559,8 +6566,8 @@
       <c r="K80" s="40"/>
     </row>
     <row r="81" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A81" s="197"/>
-      <c r="B81" s="185"/>
+      <c r="A81" s="314"/>
+      <c r="B81" s="197"/>
       <c r="C81" s="43">
         <v>2</v>
       </c>
@@ -6576,8 +6583,8 @@
       <c r="K81" s="40"/>
     </row>
     <row r="82" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A82" s="197"/>
-      <c r="B82" s="185"/>
+      <c r="A82" s="314"/>
+      <c r="B82" s="197"/>
       <c r="C82" s="43">
         <v>3</v>
       </c>
@@ -6593,8 +6600,8 @@
       <c r="K82" s="40"/>
     </row>
     <row r="83" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A83" s="197"/>
-      <c r="B83" s="185"/>
+      <c r="A83" s="314"/>
+      <c r="B83" s="197"/>
       <c r="C83" s="43">
         <v>4</v>
       </c>
@@ -6610,8 +6617,8 @@
       <c r="K83" s="40"/>
     </row>
     <row r="84" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A84" s="192"/>
-      <c r="B84" s="186"/>
+      <c r="A84" s="204"/>
+      <c r="B84" s="205"/>
       <c r="C84" s="43">
         <v>5</v>
       </c>
@@ -6627,8 +6634,8 @@
       <c r="K84" s="40"/>
     </row>
     <row r="85" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A85" s="192"/>
-      <c r="B85" s="186"/>
+      <c r="A85" s="204"/>
+      <c r="B85" s="205"/>
       <c r="C85" s="43">
         <v>6</v>
       </c>
@@ -6644,8 +6651,8 @@
       <c r="K85" s="40"/>
     </row>
     <row r="86" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A86" s="192"/>
-      <c r="B86" s="186"/>
+      <c r="A86" s="204"/>
+      <c r="B86" s="205"/>
       <c r="C86" s="43">
         <v>7</v>
       </c>
@@ -6661,8 +6668,8 @@
       <c r="K86" s="40"/>
     </row>
     <row r="87" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A87" s="192"/>
-      <c r="B87" s="186"/>
+      <c r="A87" s="204"/>
+      <c r="B87" s="205"/>
       <c r="C87" s="43">
         <v>8</v>
       </c>
@@ -6678,8 +6685,8 @@
       <c r="K87" s="40"/>
     </row>
     <row r="88" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A88" s="192"/>
-      <c r="B88" s="186"/>
+      <c r="A88" s="204"/>
+      <c r="B88" s="205"/>
       <c r="C88" s="43">
         <v>9</v>
       </c>
@@ -6695,8 +6702,8 @@
       <c r="K88" s="40"/>
     </row>
     <row r="89" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A89" s="192"/>
-      <c r="B89" s="186"/>
+      <c r="A89" s="204"/>
+      <c r="B89" s="205"/>
       <c r="C89" s="43">
         <v>10</v>
       </c>
@@ -6712,8 +6719,8 @@
       <c r="K89" s="40"/>
     </row>
     <row r="90" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A90" s="178"/>
-      <c r="B90" s="180"/>
+      <c r="A90" s="206"/>
+      <c r="B90" s="207"/>
       <c r="C90" s="43">
         <v>11</v>
       </c>
@@ -6729,10 +6736,10 @@
       <c r="K90" s="40"/>
     </row>
     <row r="91" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="187" t="s">
+      <c r="A91" s="179" t="s">
         <v>104</v>
       </c>
-      <c r="B91" s="233" t="s">
+      <c r="B91" s="256" t="s">
         <v>464</v>
       </c>
       <c r="C91" s="38">
@@ -6754,8 +6761,8 @@
       <c r="K91" s="40"/>
     </row>
     <row r="92" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A92" s="232"/>
-      <c r="B92" s="186"/>
+      <c r="A92" s="254"/>
+      <c r="B92" s="205"/>
       <c r="C92" s="38">
         <v>2</v>
       </c>
@@ -6771,8 +6778,8 @@
       <c r="K92" s="40"/>
     </row>
     <row r="93" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="232"/>
-      <c r="B93" s="186"/>
+      <c r="A93" s="254"/>
+      <c r="B93" s="205"/>
       <c r="C93" s="38">
         <v>3</v>
       </c>
@@ -6790,8 +6797,8 @@
       <c r="K93" s="40"/>
     </row>
     <row r="94" spans="1:11" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="232"/>
-      <c r="B94" s="186"/>
+      <c r="A94" s="254"/>
+      <c r="B94" s="205"/>
       <c r="C94" s="38">
         <v>4</v>
       </c>
@@ -6809,8 +6816,8 @@
       <c r="K94" s="40"/>
     </row>
     <row r="95" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A95" s="232"/>
-      <c r="B95" s="186"/>
+      <c r="A95" s="254"/>
+      <c r="B95" s="205"/>
       <c r="C95" s="38">
         <v>5</v>
       </c>
@@ -6826,8 +6833,8 @@
       <c r="K95" s="40"/>
     </row>
     <row r="96" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A96" s="232"/>
-      <c r="B96" s="186"/>
+      <c r="A96" s="254"/>
+      <c r="B96" s="205"/>
       <c r="C96" s="38">
         <v>6</v>
       </c>
@@ -6843,8 +6850,8 @@
       <c r="K96" s="40"/>
     </row>
     <row r="97" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="232"/>
-      <c r="B97" s="186"/>
+      <c r="A97" s="254"/>
+      <c r="B97" s="205"/>
       <c r="C97" s="38">
         <v>7</v>
       </c>
@@ -6862,8 +6869,8 @@
       <c r="K97" s="40"/>
     </row>
     <row r="98" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A98" s="232"/>
-      <c r="B98" s="186"/>
+      <c r="A98" s="254"/>
+      <c r="B98" s="205"/>
       <c r="C98" s="38">
         <v>8</v>
       </c>
@@ -6879,8 +6886,8 @@
       <c r="K98" s="40"/>
     </row>
     <row r="99" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A99" s="188"/>
-      <c r="B99" s="180"/>
+      <c r="A99" s="255"/>
+      <c r="B99" s="207"/>
       <c r="C99" s="38">
         <v>9</v>
       </c>
@@ -6896,10 +6903,10 @@
       <c r="K99" s="40"/>
     </row>
     <row r="100" spans="1:11" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="234" t="s">
+      <c r="A100" s="257" t="s">
         <v>120</v>
       </c>
-      <c r="B100" s="179" t="s">
+      <c r="B100" s="196" t="s">
         <v>116</v>
       </c>
       <c r="C100" s="43">
@@ -6923,8 +6930,8 @@
       <c r="K100" s="40"/>
     </row>
     <row r="101" spans="1:11" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="183"/>
-      <c r="B101" s="186"/>
+      <c r="A101" s="258"/>
+      <c r="B101" s="205"/>
       <c r="C101" s="43">
         <v>2</v>
       </c>
@@ -6944,8 +6951,8 @@
       <c r="K101" s="40"/>
     </row>
     <row r="102" spans="1:11" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="183"/>
-      <c r="B102" s="186"/>
+      <c r="A102" s="258"/>
+      <c r="B102" s="205"/>
       <c r="C102" s="43">
         <v>3</v>
       </c>
@@ -6965,8 +6972,8 @@
       <c r="K102" s="40"/>
     </row>
     <row r="103" spans="1:11" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="183"/>
-      <c r="B103" s="186"/>
+      <c r="A103" s="258"/>
+      <c r="B103" s="205"/>
       <c r="C103" s="43">
         <v>4</v>
       </c>
@@ -6986,8 +6993,8 @@
       <c r="K103" s="40"/>
     </row>
     <row r="104" spans="1:11" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="183"/>
-      <c r="B104" s="186"/>
+      <c r="A104" s="258"/>
+      <c r="B104" s="205"/>
       <c r="C104" s="43">
         <v>5</v>
       </c>
@@ -7007,8 +7014,8 @@
       <c r="K104" s="40"/>
     </row>
     <row r="105" spans="1:11" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="183"/>
-      <c r="B105" s="186"/>
+      <c r="A105" s="258"/>
+      <c r="B105" s="205"/>
       <c r="C105" s="43">
         <v>6</v>
       </c>
@@ -7028,8 +7035,8 @@
       <c r="K105" s="40"/>
     </row>
     <row r="106" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A106" s="184"/>
-      <c r="B106" s="180"/>
+      <c r="A106" s="259"/>
+      <c r="B106" s="207"/>
       <c r="C106" s="43">
         <v>98</v>
       </c>
@@ -7045,10 +7052,10 @@
       <c r="K106" s="56"/>
     </row>
     <row r="107" spans="1:11" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="234" t="s">
+      <c r="A107" s="257" t="s">
         <v>122</v>
       </c>
-      <c r="B107" s="179" t="s">
+      <c r="B107" s="196" t="s">
         <v>660</v>
       </c>
       <c r="C107" s="90">
@@ -7068,8 +7075,8 @@
       <c r="K107" s="40"/>
     </row>
     <row r="108" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A108" s="240"/>
-      <c r="B108" s="242"/>
+      <c r="A108" s="264"/>
+      <c r="B108" s="266"/>
       <c r="C108" s="43">
         <v>2</v>
       </c>
@@ -7085,8 +7092,8 @@
       <c r="K108" s="40"/>
     </row>
     <row r="109" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A109" s="240"/>
-      <c r="B109" s="242"/>
+      <c r="A109" s="264"/>
+      <c r="B109" s="266"/>
       <c r="C109" s="43">
         <v>3</v>
       </c>
@@ -7102,8 +7109,8 @@
       <c r="K109" s="40"/>
     </row>
     <row r="110" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A110" s="240"/>
-      <c r="B110" s="242"/>
+      <c r="A110" s="264"/>
+      <c r="B110" s="266"/>
       <c r="C110" s="43">
         <v>4</v>
       </c>
@@ -7119,27 +7126,27 @@
       <c r="K110" s="40"/>
     </row>
     <row r="111" spans="1:11" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="241"/>
-      <c r="B111" s="243"/>
+      <c r="A111" s="265"/>
+      <c r="B111" s="267"/>
       <c r="C111" s="43">
         <v>98</v>
       </c>
-      <c r="D111" s="244" t="s">
+      <c r="D111" s="268" t="s">
         <v>119</v>
       </c>
-      <c r="E111" s="245"/>
-      <c r="F111" s="245"/>
-      <c r="G111" s="245"/>
-      <c r="H111" s="245"/>
-      <c r="I111" s="245"/>
-      <c r="J111" s="245"/>
-      <c r="K111" s="246"/>
+      <c r="E111" s="269"/>
+      <c r="F111" s="269"/>
+      <c r="G111" s="269"/>
+      <c r="H111" s="269"/>
+      <c r="I111" s="269"/>
+      <c r="J111" s="269"/>
+      <c r="K111" s="270"/>
     </row>
     <row r="112" spans="1:11" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="235" t="s">
+      <c r="A112" s="260" t="s">
         <v>141</v>
       </c>
-      <c r="B112" s="236" t="s">
+      <c r="B112" s="261" t="s">
         <v>656</v>
       </c>
       <c r="C112" s="44">
@@ -7161,8 +7168,8 @@
       <c r="K112" s="57"/>
     </row>
     <row r="113" spans="1:11" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="178"/>
-      <c r="B113" s="237"/>
+      <c r="A113" s="206"/>
+      <c r="B113" s="262"/>
       <c r="C113" s="44">
         <v>2</v>
       </c>
@@ -7180,10 +7187,10 @@
       <c r="K113" s="57"/>
     </row>
     <row r="114" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A114" s="235" t="s">
+      <c r="A114" s="260" t="s">
         <v>505</v>
       </c>
-      <c r="B114" s="238" t="s">
+      <c r="B114" s="263" t="s">
         <v>123</v>
       </c>
       <c r="C114" s="44">
@@ -7205,8 +7212,8 @@
       <c r="K114" s="57"/>
     </row>
     <row r="115" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A115" s="192"/>
-      <c r="B115" s="186"/>
+      <c r="A115" s="204"/>
+      <c r="B115" s="205"/>
       <c r="C115" s="44">
         <v>2</v>
       </c>
@@ -7222,8 +7229,8 @@
       <c r="K115" s="57"/>
     </row>
     <row r="116" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A116" s="192"/>
-      <c r="B116" s="186"/>
+      <c r="A116" s="204"/>
+      <c r="B116" s="205"/>
       <c r="C116" s="44">
         <v>3</v>
       </c>
@@ -7239,8 +7246,8 @@
       <c r="K116" s="57"/>
     </row>
     <row r="117" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A117" s="192"/>
-      <c r="B117" s="186"/>
+      <c r="A117" s="204"/>
+      <c r="B117" s="205"/>
       <c r="C117" s="44">
         <v>4</v>
       </c>
@@ -7256,8 +7263,8 @@
       <c r="K117" s="57"/>
     </row>
     <row r="118" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A118" s="192"/>
-      <c r="B118" s="186"/>
+      <c r="A118" s="204"/>
+      <c r="B118" s="205"/>
       <c r="C118" s="44">
         <v>5</v>
       </c>
@@ -7273,8 +7280,8 @@
       <c r="K118" s="57"/>
     </row>
     <row r="119" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A119" s="192"/>
-      <c r="B119" s="186"/>
+      <c r="A119" s="204"/>
+      <c r="B119" s="205"/>
       <c r="C119" s="44">
         <v>6</v>
       </c>
@@ -7290,8 +7297,8 @@
       <c r="K119" s="57"/>
     </row>
     <row r="120" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A120" s="178"/>
-      <c r="B120" s="180"/>
+      <c r="A120" s="206"/>
+      <c r="B120" s="207"/>
       <c r="C120" s="44">
         <v>7</v>
       </c>
@@ -7307,10 +7314,10 @@
       <c r="K120" s="57"/>
     </row>
     <row r="121" spans="1:11" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="234" t="s">
+      <c r="A121" s="257" t="s">
         <v>142</v>
       </c>
-      <c r="B121" s="179" t="s">
+      <c r="B121" s="196" t="s">
         <v>657</v>
       </c>
       <c r="C121" s="38">
@@ -7334,8 +7341,8 @@
       <c r="K121" s="40"/>
     </row>
     <row r="122" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A122" s="263"/>
-      <c r="B122" s="185"/>
+      <c r="A122" s="284"/>
+      <c r="B122" s="197"/>
       <c r="C122" s="38">
         <v>2</v>
       </c>
@@ -7351,8 +7358,8 @@
       <c r="K122" s="40"/>
     </row>
     <row r="123" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A123" s="183"/>
-      <c r="B123" s="186"/>
+      <c r="A123" s="258"/>
+      <c r="B123" s="205"/>
       <c r="C123" s="38">
         <v>3</v>
       </c>
@@ -7368,8 +7375,8 @@
       <c r="K123" s="40"/>
     </row>
     <row r="124" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A124" s="183"/>
-      <c r="B124" s="186"/>
+      <c r="A124" s="258"/>
+      <c r="B124" s="205"/>
       <c r="C124" s="38">
         <v>4</v>
       </c>
@@ -7385,8 +7392,8 @@
       <c r="K124" s="40"/>
     </row>
     <row r="125" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A125" s="183"/>
-      <c r="B125" s="186"/>
+      <c r="A125" s="258"/>
+      <c r="B125" s="205"/>
       <c r="C125" s="38">
         <v>5</v>
       </c>
@@ -7402,8 +7409,8 @@
       <c r="K125" s="40"/>
     </row>
     <row r="126" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A126" s="183"/>
-      <c r="B126" s="186"/>
+      <c r="A126" s="258"/>
+      <c r="B126" s="205"/>
       <c r="C126" s="38">
         <v>6</v>
       </c>
@@ -7419,8 +7426,8 @@
       <c r="K126" s="40"/>
     </row>
     <row r="127" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A127" s="184"/>
-      <c r="B127" s="180"/>
+      <c r="A127" s="259"/>
+      <c r="B127" s="207"/>
       <c r="C127" s="38">
         <v>99</v>
       </c>
@@ -7440,10 +7447,10 @@
       <c r="K127" s="40"/>
     </row>
     <row r="128" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A128" s="259" t="s">
+      <c r="A128" s="280" t="s">
         <v>538</v>
       </c>
-      <c r="B128" s="261" t="s">
+      <c r="B128" s="282" t="s">
         <v>486</v>
       </c>
       <c r="C128" s="68">
@@ -7461,8 +7468,8 @@
       <c r="K128" s="69"/>
     </row>
     <row r="129" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A129" s="260"/>
-      <c r="B129" s="262"/>
+      <c r="A129" s="281"/>
+      <c r="B129" s="283"/>
       <c r="C129" s="68">
         <v>1</v>
       </c>
@@ -7478,8 +7485,8 @@
       <c r="K129" s="69"/>
     </row>
     <row r="130" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="260"/>
-      <c r="B130" s="262"/>
+      <c r="A130" s="281"/>
+      <c r="B130" s="283"/>
       <c r="C130" s="68">
         <v>2</v>
       </c>
@@ -7495,40 +7502,40 @@
       <c r="K130" s="69"/>
     </row>
     <row r="131" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A131" s="199" t="s">
+      <c r="A131" s="285" t="s">
         <v>546</v>
       </c>
-      <c r="B131" s="175"/>
-      <c r="C131" s="175"/>
-      <c r="D131" s="175"/>
-      <c r="E131" s="175"/>
-      <c r="F131" s="175"/>
-      <c r="G131" s="175"/>
-      <c r="H131" s="175"/>
-      <c r="I131" s="175"/>
-      <c r="J131" s="175"/>
-      <c r="K131" s="176"/>
+      <c r="B131" s="286"/>
+      <c r="C131" s="286"/>
+      <c r="D131" s="286"/>
+      <c r="E131" s="286"/>
+      <c r="F131" s="286"/>
+      <c r="G131" s="286"/>
+      <c r="H131" s="286"/>
+      <c r="I131" s="286"/>
+      <c r="J131" s="286"/>
+      <c r="K131" s="287"/>
     </row>
     <row r="132" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A132" s="209" t="s">
+      <c r="A132" s="170" t="s">
         <v>548</v>
       </c>
-      <c r="B132" s="210"/>
-      <c r="C132" s="210"/>
-      <c r="D132" s="210"/>
-      <c r="E132" s="210"/>
-      <c r="F132" s="210"/>
-      <c r="G132" s="210"/>
-      <c r="H132" s="210"/>
-      <c r="I132" s="210"/>
-      <c r="J132" s="210"/>
-      <c r="K132" s="211"/>
+      <c r="B132" s="171"/>
+      <c r="C132" s="171"/>
+      <c r="D132" s="171"/>
+      <c r="E132" s="171"/>
+      <c r="F132" s="171"/>
+      <c r="G132" s="171"/>
+      <c r="H132" s="171"/>
+      <c r="I132" s="171"/>
+      <c r="J132" s="171"/>
+      <c r="K132" s="172"/>
     </row>
     <row r="133" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A133" s="270" t="s">
+      <c r="A133" s="230" t="s">
         <v>188</v>
       </c>
-      <c r="B133" s="269" t="s">
+      <c r="B133" s="229" t="s">
         <v>398</v>
       </c>
       <c r="C133" s="74">
@@ -7546,8 +7553,8 @@
       <c r="K133" s="40"/>
     </row>
     <row r="134" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A134" s="271"/>
-      <c r="B134" s="269"/>
+      <c r="A134" s="231"/>
+      <c r="B134" s="229"/>
       <c r="C134" s="75">
         <v>2</v>
       </c>
@@ -7563,8 +7570,8 @@
       <c r="K134" s="40"/>
     </row>
     <row r="135" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A135" s="271"/>
-      <c r="B135" s="269"/>
+      <c r="A135" s="231"/>
+      <c r="B135" s="229"/>
       <c r="C135" s="75">
         <v>3</v>
       </c>
@@ -7580,8 +7587,8 @@
       <c r="K135" s="40"/>
     </row>
     <row r="136" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A136" s="272"/>
-      <c r="B136" s="269"/>
+      <c r="A136" s="232"/>
+      <c r="B136" s="229"/>
       <c r="C136" s="75">
         <v>4</v>
       </c>
@@ -7597,10 +7604,10 @@
       <c r="K136" s="40"/>
     </row>
     <row r="137" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="250" t="s">
+      <c r="A137" s="274" t="s">
         <v>190</v>
       </c>
-      <c r="B137" s="247" t="s">
+      <c r="B137" s="271" t="s">
         <v>467</v>
       </c>
       <c r="C137" s="43">
@@ -7618,8 +7625,8 @@
       <c r="K137" s="40"/>
     </row>
     <row r="138" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A138" s="251"/>
-      <c r="B138" s="248"/>
+      <c r="A138" s="275"/>
+      <c r="B138" s="272"/>
       <c r="C138" s="43">
         <v>2</v>
       </c>
@@ -7635,8 +7642,8 @@
       <c r="K138" s="40"/>
     </row>
     <row r="139" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="251"/>
-      <c r="B139" s="248"/>
+      <c r="A139" s="275"/>
+      <c r="B139" s="272"/>
       <c r="C139" s="43">
         <v>1</v>
       </c>
@@ -7652,8 +7659,8 @@
       <c r="K139" s="40"/>
     </row>
     <row r="140" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A140" s="252"/>
-      <c r="B140" s="249"/>
+      <c r="A140" s="276"/>
+      <c r="B140" s="273"/>
       <c r="C140" s="109">
         <v>2</v>
       </c>
@@ -7669,10 +7676,10 @@
       <c r="K140" s="40"/>
     </row>
     <row r="141" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A141" s="222" t="s">
+      <c r="A141" s="301" t="s">
         <v>196</v>
       </c>
-      <c r="B141" s="219" t="s">
+      <c r="B141" s="298" t="s">
         <v>380</v>
       </c>
       <c r="C141" s="71">
@@ -7692,8 +7699,8 @@
       <c r="K141" s="40"/>
     </row>
     <row r="142" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A142" s="223"/>
-      <c r="B142" s="220"/>
+      <c r="A142" s="302"/>
+      <c r="B142" s="299"/>
       <c r="C142" s="71">
         <v>2</v>
       </c>
@@ -7709,8 +7716,8 @@
       <c r="K142" s="40"/>
     </row>
     <row r="143" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A143" s="223"/>
-      <c r="B143" s="220"/>
+      <c r="A143" s="302"/>
+      <c r="B143" s="299"/>
       <c r="C143" s="71">
         <v>3</v>
       </c>
@@ -7726,8 +7733,8 @@
       <c r="K143" s="40"/>
     </row>
     <row r="144" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A144" s="223"/>
-      <c r="B144" s="220"/>
+      <c r="A144" s="302"/>
+      <c r="B144" s="299"/>
       <c r="C144" s="71">
         <v>4</v>
       </c>
@@ -7743,8 +7750,8 @@
       <c r="K144" s="40"/>
     </row>
     <row r="145" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A145" s="224"/>
-      <c r="B145" s="221"/>
+      <c r="A145" s="303"/>
+      <c r="B145" s="300"/>
       <c r="C145" s="71">
         <v>5</v>
       </c>
@@ -7760,10 +7767,10 @@
       <c r="K145" s="40"/>
     </row>
     <row r="146" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A146" s="225" t="s">
+      <c r="A146" s="304" t="s">
         <v>392</v>
       </c>
-      <c r="B146" s="219" t="s">
+      <c r="B146" s="298" t="s">
         <v>396</v>
       </c>
       <c r="C146" s="71">
@@ -7781,8 +7788,8 @@
       <c r="K146" s="40"/>
     </row>
     <row r="147" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A147" s="226"/>
-      <c r="B147" s="220"/>
+      <c r="A147" s="305"/>
+      <c r="B147" s="299"/>
       <c r="C147" s="71">
         <v>2</v>
       </c>
@@ -7798,8 +7805,8 @@
       <c r="K147" s="40"/>
     </row>
     <row r="148" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A148" s="226"/>
-      <c r="B148" s="220"/>
+      <c r="A148" s="305"/>
+      <c r="B148" s="299"/>
       <c r="C148" s="71">
         <v>3</v>
       </c>
@@ -7815,8 +7822,8 @@
       <c r="K148" s="40"/>
     </row>
     <row r="149" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A149" s="226"/>
-      <c r="B149" s="220"/>
+      <c r="A149" s="305"/>
+      <c r="B149" s="299"/>
       <c r="C149" s="71">
         <v>4</v>
       </c>
@@ -7832,8 +7839,8 @@
       <c r="K149" s="40"/>
     </row>
     <row r="150" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A150" s="227"/>
-      <c r="B150" s="221"/>
+      <c r="A150" s="306"/>
+      <c r="B150" s="300"/>
       <c r="C150" s="71">
         <v>5</v>
       </c>
@@ -7849,10 +7856,10 @@
       <c r="K150" s="40"/>
     </row>
     <row r="151" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A151" s="222" t="s">
+      <c r="A151" s="301" t="s">
         <v>197</v>
       </c>
-      <c r="B151" s="219" t="s">
+      <c r="B151" s="298" t="s">
         <v>381</v>
       </c>
       <c r="C151" s="71">
@@ -7872,8 +7879,8 @@
       <c r="K151" s="40"/>
     </row>
     <row r="152" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A152" s="223"/>
-      <c r="B152" s="220"/>
+      <c r="A152" s="302"/>
+      <c r="B152" s="299"/>
       <c r="C152" s="71">
         <v>2</v>
       </c>
@@ -7889,8 +7896,8 @@
       <c r="K152" s="40"/>
     </row>
     <row r="153" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A153" s="223"/>
-      <c r="B153" s="220"/>
+      <c r="A153" s="302"/>
+      <c r="B153" s="299"/>
       <c r="C153" s="71">
         <v>3</v>
       </c>
@@ -7906,8 +7913,8 @@
       <c r="K153" s="40"/>
     </row>
     <row r="154" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A154" s="223"/>
-      <c r="B154" s="220"/>
+      <c r="A154" s="302"/>
+      <c r="B154" s="299"/>
       <c r="C154" s="71">
         <v>4</v>
       </c>
@@ -7923,8 +7930,8 @@
       <c r="K154" s="40"/>
     </row>
     <row r="155" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A155" s="224"/>
-      <c r="B155" s="221"/>
+      <c r="A155" s="303"/>
+      <c r="B155" s="300"/>
       <c r="C155" s="71">
         <v>5</v>
       </c>
@@ -7940,10 +7947,10 @@
       <c r="K155" s="40"/>
     </row>
     <row r="156" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A156" s="225" t="s">
+      <c r="A156" s="304" t="s">
         <v>507</v>
       </c>
-      <c r="B156" s="219" t="s">
+      <c r="B156" s="298" t="s">
         <v>395</v>
       </c>
       <c r="C156" s="71">
@@ -7961,8 +7968,8 @@
       <c r="K156" s="40"/>
     </row>
     <row r="157" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A157" s="226"/>
-      <c r="B157" s="220"/>
+      <c r="A157" s="305"/>
+      <c r="B157" s="299"/>
       <c r="C157" s="71">
         <v>2</v>
       </c>
@@ -7978,8 +7985,8 @@
       <c r="K157" s="40"/>
     </row>
     <row r="158" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A158" s="226"/>
-      <c r="B158" s="220"/>
+      <c r="A158" s="305"/>
+      <c r="B158" s="299"/>
       <c r="C158" s="71">
         <v>3</v>
       </c>
@@ -7995,8 +8002,8 @@
       <c r="K158" s="40"/>
     </row>
     <row r="159" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A159" s="226"/>
-      <c r="B159" s="220"/>
+      <c r="A159" s="305"/>
+      <c r="B159" s="299"/>
       <c r="C159" s="71">
         <v>4</v>
       </c>
@@ -8012,8 +8019,8 @@
       <c r="K159" s="40"/>
     </row>
     <row r="160" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A160" s="227"/>
-      <c r="B160" s="221"/>
+      <c r="A160" s="306"/>
+      <c r="B160" s="300"/>
       <c r="C160" s="71">
         <v>5</v>
       </c>
@@ -8029,10 +8036,10 @@
       <c r="K160" s="40"/>
     </row>
     <row r="161" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A161" s="282" t="s">
+      <c r="A161" s="242" t="s">
         <v>202</v>
       </c>
-      <c r="B161" s="189" t="s">
+      <c r="B161" s="308" t="s">
         <v>611</v>
       </c>
       <c r="C161" s="38">
@@ -8052,8 +8059,8 @@
       <c r="K161" s="40"/>
     </row>
     <row r="162" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A162" s="282"/>
-      <c r="B162" s="230"/>
+      <c r="A162" s="242"/>
+      <c r="B162" s="309"/>
       <c r="C162" s="38">
         <v>2</v>
       </c>
@@ -8071,8 +8078,8 @@
       <c r="K162" s="40"/>
     </row>
     <row r="163" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A163" s="282"/>
-      <c r="B163" s="230"/>
+      <c r="A163" s="242"/>
+      <c r="B163" s="309"/>
       <c r="C163" s="38">
         <v>3</v>
       </c>
@@ -8090,8 +8097,8 @@
       <c r="K163" s="40"/>
     </row>
     <row r="164" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A164" s="192"/>
-      <c r="B164" s="231"/>
+      <c r="A164" s="204"/>
+      <c r="B164" s="310"/>
       <c r="C164" s="38">
         <v>4</v>
       </c>
@@ -8109,8 +8116,8 @@
       <c r="K164" s="40"/>
     </row>
     <row r="165" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A165" s="192"/>
-      <c r="B165" s="231"/>
+      <c r="A165" s="204"/>
+      <c r="B165" s="310"/>
       <c r="C165" s="38">
         <v>5</v>
       </c>
@@ -8128,8 +8135,8 @@
       <c r="K165" s="40"/>
     </row>
     <row r="166" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A166" s="192"/>
-      <c r="B166" s="231"/>
+      <c r="A166" s="204"/>
+      <c r="B166" s="310"/>
       <c r="C166" s="38">
         <v>6</v>
       </c>
@@ -8149,8 +8156,8 @@
       <c r="K166" s="40"/>
     </row>
     <row r="167" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A167" s="192"/>
-      <c r="B167" s="231"/>
+      <c r="A167" s="204"/>
+      <c r="B167" s="310"/>
       <c r="C167" s="38">
         <v>7</v>
       </c>
@@ -8170,8 +8177,8 @@
       <c r="K167" s="40"/>
     </row>
     <row r="168" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A168" s="192"/>
-      <c r="B168" s="231"/>
+      <c r="A168" s="204"/>
+      <c r="B168" s="310"/>
       <c r="C168" s="38">
         <v>8</v>
       </c>
@@ -8189,8 +8196,8 @@
       <c r="K168" s="40"/>
     </row>
     <row r="169" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A169" s="192"/>
-      <c r="B169" s="231"/>
+      <c r="A169" s="204"/>
+      <c r="B169" s="310"/>
       <c r="C169" s="38">
         <v>9</v>
       </c>
@@ -8208,8 +8215,8 @@
       <c r="K169" s="40"/>
     </row>
     <row r="170" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A170" s="192"/>
-      <c r="B170" s="231"/>
+      <c r="A170" s="204"/>
+      <c r="B170" s="310"/>
       <c r="C170" s="38">
         <v>10</v>
       </c>
@@ -8227,8 +8234,8 @@
       <c r="K170" s="40"/>
     </row>
     <row r="171" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A171" s="192"/>
-      <c r="B171" s="231"/>
+      <c r="A171" s="204"/>
+      <c r="B171" s="310"/>
       <c r="C171" s="38">
         <v>11</v>
       </c>
@@ -8248,8 +8255,8 @@
       <c r="K171" s="40"/>
     </row>
     <row r="172" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A172" s="192"/>
-      <c r="B172" s="231"/>
+      <c r="A172" s="204"/>
+      <c r="B172" s="310"/>
       <c r="C172" s="38">
         <v>12</v>
       </c>
@@ -8269,8 +8276,8 @@
       <c r="K172" s="40"/>
     </row>
     <row r="173" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A173" s="192"/>
-      <c r="B173" s="231"/>
+      <c r="A173" s="204"/>
+      <c r="B173" s="310"/>
       <c r="C173" s="38">
         <v>13</v>
       </c>
@@ -8290,8 +8297,8 @@
       <c r="K173" s="40"/>
     </row>
     <row r="174" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A174" s="192"/>
-      <c r="B174" s="231"/>
+      <c r="A174" s="204"/>
+      <c r="B174" s="310"/>
       <c r="C174" s="38">
         <v>14</v>
       </c>
@@ -8311,8 +8318,8 @@
       <c r="K174" s="40"/>
     </row>
     <row r="175" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A175" s="192"/>
-      <c r="B175" s="231"/>
+      <c r="A175" s="204"/>
+      <c r="B175" s="310"/>
       <c r="C175" s="38">
         <v>15</v>
       </c>
@@ -8332,8 +8339,8 @@
       <c r="K175" s="40"/>
     </row>
     <row r="176" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A176" s="192"/>
-      <c r="B176" s="231"/>
+      <c r="A176" s="204"/>
+      <c r="B176" s="310"/>
       <c r="C176" s="38">
         <v>16</v>
       </c>
@@ -8353,8 +8360,8 @@
       <c r="K176" s="40"/>
     </row>
     <row r="177" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A177" s="192"/>
-      <c r="B177" s="231"/>
+      <c r="A177" s="204"/>
+      <c r="B177" s="310"/>
       <c r="C177" s="38">
         <v>17</v>
       </c>
@@ -8372,8 +8379,8 @@
       <c r="K177" s="40"/>
     </row>
     <row r="178" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A178" s="192"/>
-      <c r="B178" s="231"/>
+      <c r="A178" s="204"/>
+      <c r="B178" s="310"/>
       <c r="C178" s="38">
         <v>18</v>
       </c>
@@ -8393,8 +8400,8 @@
       <c r="K178" s="40"/>
     </row>
     <row r="179" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A179" s="192"/>
-      <c r="B179" s="231"/>
+      <c r="A179" s="204"/>
+      <c r="B179" s="310"/>
       <c r="C179" s="38">
         <v>19</v>
       </c>
@@ -8412,8 +8419,8 @@
       <c r="K179" s="40"/>
     </row>
     <row r="180" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A180" s="192"/>
-      <c r="B180" s="231"/>
+      <c r="A180" s="204"/>
+      <c r="B180" s="310"/>
       <c r="C180" s="38">
         <v>20</v>
       </c>
@@ -8433,8 +8440,8 @@
       <c r="K180" s="40"/>
     </row>
     <row r="181" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A181" s="192"/>
-      <c r="B181" s="231"/>
+      <c r="A181" s="204"/>
+      <c r="B181" s="310"/>
       <c r="C181" s="38">
         <v>21</v>
       </c>
@@ -8454,8 +8461,8 @@
       <c r="K181" s="40"/>
     </row>
     <row r="182" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A182" s="192"/>
-      <c r="B182" s="231"/>
+      <c r="A182" s="204"/>
+      <c r="B182" s="310"/>
       <c r="C182" s="38">
         <v>22</v>
       </c>
@@ -8473,8 +8480,8 @@
       <c r="K182" s="40"/>
     </row>
     <row r="183" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A183" s="178"/>
-      <c r="B183" s="190"/>
+      <c r="A183" s="206"/>
+      <c r="B183" s="311"/>
       <c r="C183" s="38">
         <v>23</v>
       </c>
@@ -8494,10 +8501,10 @@
       <c r="K183" s="40"/>
     </row>
     <row r="184" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A184" s="253" t="s">
+      <c r="A184" s="182" t="s">
         <v>508</v>
       </c>
-      <c r="B184" s="256" t="s">
+      <c r="B184" s="277" t="s">
         <v>509</v>
       </c>
       <c r="C184" s="65">
@@ -8515,8 +8522,8 @@
       <c r="K184" s="40"/>
     </row>
     <row r="185" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A185" s="254"/>
-      <c r="B185" s="257"/>
+      <c r="A185" s="183"/>
+      <c r="B185" s="278"/>
       <c r="C185" s="107">
         <v>2</v>
       </c>
@@ -8532,8 +8539,8 @@
       <c r="K185" s="40"/>
     </row>
     <row r="186" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A186" s="254"/>
-      <c r="B186" s="257"/>
+      <c r="A186" s="183"/>
+      <c r="B186" s="278"/>
       <c r="C186" s="107">
         <v>3</v>
       </c>
@@ -8549,8 +8556,8 @@
       <c r="K186" s="40"/>
     </row>
     <row r="187" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A187" s="255"/>
-      <c r="B187" s="258"/>
+      <c r="A187" s="184"/>
+      <c r="B187" s="279"/>
       <c r="C187" s="107">
         <v>4</v>
       </c>
@@ -8566,10 +8573,10 @@
       <c r="K187" s="40"/>
     </row>
     <row r="188" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A188" s="206" t="s">
+      <c r="A188" s="187" t="s">
         <v>512</v>
       </c>
-      <c r="B188" s="279" t="s">
+      <c r="B188" s="239" t="s">
         <v>661</v>
       </c>
       <c r="C188" s="103">
@@ -8578,7 +8585,7 @@
       <c r="D188" s="104" t="s">
         <v>452</v>
       </c>
-      <c r="E188" s="212" t="s">
+      <c r="E188" s="293" t="s">
         <v>516</v>
       </c>
       <c r="F188" s="39"/>
@@ -8589,15 +8596,15 @@
       <c r="K188" s="40"/>
     </row>
     <row r="189" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A189" s="206"/>
-      <c r="B189" s="280"/>
+      <c r="A189" s="187"/>
+      <c r="B189" s="240"/>
       <c r="C189" s="103">
         <v>2</v>
       </c>
       <c r="D189" s="104" t="s">
         <v>322</v>
       </c>
-      <c r="E189" s="213"/>
+      <c r="E189" s="294"/>
       <c r="F189" s="39"/>
       <c r="G189" s="39"/>
       <c r="H189" s="40"/>
@@ -8606,15 +8613,15 @@
       <c r="K189" s="40"/>
     </row>
     <row r="190" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A190" s="206"/>
-      <c r="B190" s="280"/>
+      <c r="A190" s="187"/>
+      <c r="B190" s="240"/>
       <c r="C190" s="103">
         <v>3</v>
       </c>
       <c r="D190" s="104" t="s">
         <v>323</v>
       </c>
-      <c r="E190" s="213"/>
+      <c r="E190" s="294"/>
       <c r="F190" s="39"/>
       <c r="G190" s="39"/>
       <c r="H190" s="40"/>
@@ -8623,15 +8630,15 @@
       <c r="K190" s="40"/>
     </row>
     <row r="191" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A191" s="206"/>
-      <c r="B191" s="280"/>
+      <c r="A191" s="187"/>
+      <c r="B191" s="240"/>
       <c r="C191" s="103">
         <v>4</v>
       </c>
       <c r="D191" s="104" t="s">
         <v>324</v>
       </c>
-      <c r="E191" s="213"/>
+      <c r="E191" s="294"/>
       <c r="F191" s="39"/>
       <c r="G191" s="39"/>
       <c r="H191" s="40"/>
@@ -8640,15 +8647,15 @@
       <c r="K191" s="40"/>
     </row>
     <row r="192" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A192" s="206"/>
-      <c r="B192" s="280"/>
+      <c r="A192" s="187"/>
+      <c r="B192" s="240"/>
       <c r="C192" s="103">
         <v>5</v>
       </c>
       <c r="D192" s="104" t="s">
         <v>325</v>
       </c>
-      <c r="E192" s="213"/>
+      <c r="E192" s="294"/>
       <c r="F192" s="39"/>
       <c r="G192" s="39"/>
       <c r="H192" s="40"/>
@@ -8657,15 +8664,15 @@
       <c r="K192" s="40"/>
     </row>
     <row r="193" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A193" s="206"/>
-      <c r="B193" s="280"/>
+      <c r="A193" s="187"/>
+      <c r="B193" s="240"/>
       <c r="C193" s="103">
         <v>6</v>
       </c>
       <c r="D193" s="104" t="s">
         <v>326</v>
       </c>
-      <c r="E193" s="213"/>
+      <c r="E193" s="294"/>
       <c r="F193" s="39"/>
       <c r="G193" s="39"/>
       <c r="H193" s="40"/>
@@ -8674,15 +8681,15 @@
       <c r="K193" s="40"/>
     </row>
     <row r="194" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A194" s="206"/>
-      <c r="B194" s="280"/>
+      <c r="A194" s="187"/>
+      <c r="B194" s="240"/>
       <c r="C194" s="103">
         <v>7</v>
       </c>
       <c r="D194" s="104" t="s">
         <v>327</v>
       </c>
-      <c r="E194" s="213"/>
+      <c r="E194" s="294"/>
       <c r="F194" s="39"/>
       <c r="G194" s="39"/>
       <c r="H194" s="40"/>
@@ -8691,15 +8698,15 @@
       <c r="K194" s="40"/>
     </row>
     <row r="195" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A195" s="206"/>
-      <c r="B195" s="281"/>
+      <c r="A195" s="187"/>
+      <c r="B195" s="241"/>
       <c r="C195" s="103">
         <v>98</v>
       </c>
       <c r="D195" s="163" t="s">
         <v>315</v>
       </c>
-      <c r="E195" s="214"/>
+      <c r="E195" s="295"/>
       <c r="F195" s="39"/>
       <c r="G195" s="39"/>
       <c r="H195" s="40"/>
@@ -8708,10 +8715,10 @@
       <c r="K195" s="40"/>
     </row>
     <row r="196" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A196" s="205" t="s">
+      <c r="A196" s="203" t="s">
         <v>513</v>
       </c>
-      <c r="B196" s="273" t="s">
+      <c r="B196" s="233" t="s">
         <v>555</v>
       </c>
       <c r="C196" s="103">
@@ -8720,7 +8727,7 @@
       <c r="D196" s="104" t="s">
         <v>453</v>
       </c>
-      <c r="E196" s="212" t="s">
+      <c r="E196" s="293" t="s">
         <v>516</v>
       </c>
       <c r="F196" s="39"/>
@@ -8731,15 +8738,15 @@
       <c r="K196" s="40"/>
     </row>
     <row r="197" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A197" s="202"/>
-      <c r="B197" s="274"/>
+      <c r="A197" s="246"/>
+      <c r="B197" s="234"/>
       <c r="C197" s="103">
         <v>2</v>
       </c>
       <c r="D197" s="104" t="s">
         <v>597</v>
       </c>
-      <c r="E197" s="213"/>
+      <c r="E197" s="294"/>
       <c r="F197" s="39"/>
       <c r="G197" s="39"/>
       <c r="H197" s="40"/>
@@ -8748,15 +8755,15 @@
       <c r="K197" s="40"/>
     </row>
     <row r="198" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A198" s="202"/>
-      <c r="B198" s="274"/>
+      <c r="A198" s="246"/>
+      <c r="B198" s="234"/>
       <c r="C198" s="103">
         <v>3</v>
       </c>
       <c r="D198" s="104" t="s">
         <v>598</v>
       </c>
-      <c r="E198" s="213"/>
+      <c r="E198" s="294"/>
       <c r="F198" s="39"/>
       <c r="G198" s="39"/>
       <c r="H198" s="40"/>
@@ -8765,15 +8772,15 @@
       <c r="K198" s="40"/>
     </row>
     <row r="199" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A199" s="202"/>
-      <c r="B199" s="274"/>
+      <c r="A199" s="246"/>
+      <c r="B199" s="234"/>
       <c r="C199" s="103">
         <v>4</v>
       </c>
       <c r="D199" s="104" t="s">
         <v>599</v>
       </c>
-      <c r="E199" s="213"/>
+      <c r="E199" s="294"/>
       <c r="F199" s="39"/>
       <c r="G199" s="39"/>
       <c r="H199" s="40"/>
@@ -8782,15 +8789,15 @@
       <c r="K199" s="40"/>
     </row>
     <row r="200" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A200" s="202"/>
-      <c r="B200" s="274"/>
+      <c r="A200" s="246"/>
+      <c r="B200" s="234"/>
       <c r="C200" s="103">
         <v>5</v>
       </c>
       <c r="D200" s="104" t="s">
         <v>600</v>
       </c>
-      <c r="E200" s="213"/>
+      <c r="E200" s="294"/>
       <c r="F200" s="39"/>
       <c r="G200" s="39"/>
       <c r="H200" s="40"/>
@@ -8799,15 +8806,15 @@
       <c r="K200" s="40"/>
     </row>
     <row r="201" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A201" s="202"/>
-      <c r="B201" s="274"/>
+      <c r="A201" s="246"/>
+      <c r="B201" s="234"/>
       <c r="C201" s="103">
         <v>6</v>
       </c>
       <c r="D201" s="104" t="s">
         <v>601</v>
       </c>
-      <c r="E201" s="213"/>
+      <c r="E201" s="294"/>
       <c r="F201" s="39"/>
       <c r="G201" s="39"/>
       <c r="H201" s="40"/>
@@ -8816,15 +8823,15 @@
       <c r="K201" s="40"/>
     </row>
     <row r="202" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A202" s="202"/>
-      <c r="B202" s="275"/>
+      <c r="A202" s="246"/>
+      <c r="B202" s="235"/>
       <c r="C202" s="103">
         <v>98</v>
       </c>
       <c r="D202" s="104" t="s">
         <v>315</v>
       </c>
-      <c r="E202" s="214"/>
+      <c r="E202" s="295"/>
       <c r="F202" s="39"/>
       <c r="G202" s="39"/>
       <c r="H202" s="40"/>
@@ -8833,10 +8840,10 @@
       <c r="K202" s="40"/>
     </row>
     <row r="203" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A203" s="206" t="s">
+      <c r="A203" s="187" t="s">
         <v>514</v>
       </c>
-      <c r="B203" s="276" t="s">
+      <c r="B203" s="236" t="s">
         <v>664</v>
       </c>
       <c r="C203" s="103">
@@ -8845,7 +8852,7 @@
       <c r="D203" s="104" t="s">
         <v>452</v>
       </c>
-      <c r="E203" s="212" t="s">
+      <c r="E203" s="293" t="s">
         <v>516</v>
       </c>
       <c r="F203" s="39"/>
@@ -8856,15 +8863,15 @@
       <c r="K203" s="40"/>
     </row>
     <row r="204" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A204" s="206"/>
-      <c r="B204" s="277"/>
+      <c r="A204" s="187"/>
+      <c r="B204" s="237"/>
       <c r="C204" s="103">
         <v>3</v>
       </c>
       <c r="D204" s="104" t="s">
         <v>328</v>
       </c>
-      <c r="E204" s="213"/>
+      <c r="E204" s="294"/>
       <c r="F204" s="39"/>
       <c r="G204" s="39"/>
       <c r="H204" s="40"/>
@@ -8873,15 +8880,15 @@
       <c r="K204" s="40"/>
     </row>
     <row r="205" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A205" s="206"/>
-      <c r="B205" s="277"/>
+      <c r="A205" s="187"/>
+      <c r="B205" s="237"/>
       <c r="C205" s="103">
         <v>3</v>
       </c>
       <c r="D205" s="104" t="s">
         <v>662</v>
       </c>
-      <c r="E205" s="213"/>
+      <c r="E205" s="294"/>
       <c r="F205" s="39"/>
       <c r="G205" s="39"/>
       <c r="H205" s="40"/>
@@ -8890,15 +8897,15 @@
       <c r="K205" s="40"/>
     </row>
     <row r="206" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A206" s="206"/>
-      <c r="B206" s="277"/>
+      <c r="A206" s="187"/>
+      <c r="B206" s="237"/>
       <c r="C206" s="103">
         <v>6</v>
       </c>
       <c r="D206" s="104" t="s">
         <v>663</v>
       </c>
-      <c r="E206" s="213"/>
+      <c r="E206" s="294"/>
       <c r="F206" s="39"/>
       <c r="G206" s="39"/>
       <c r="H206" s="40"/>
@@ -8907,15 +8914,15 @@
       <c r="K206" s="40"/>
     </row>
     <row r="207" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A207" s="206"/>
-      <c r="B207" s="278"/>
+      <c r="A207" s="187"/>
+      <c r="B207" s="238"/>
       <c r="C207" s="103">
         <v>98</v>
       </c>
       <c r="D207" s="104" t="s">
         <v>315</v>
       </c>
-      <c r="E207" s="214"/>
+      <c r="E207" s="295"/>
       <c r="F207" s="39"/>
       <c r="G207" s="39"/>
       <c r="H207" s="40"/>
@@ -8924,10 +8931,10 @@
       <c r="K207" s="40"/>
     </row>
     <row r="208" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A208" s="202" t="s">
+      <c r="A208" s="246" t="s">
         <v>516</v>
       </c>
-      <c r="B208" s="179" t="s">
+      <c r="B208" s="196" t="s">
         <v>428</v>
       </c>
       <c r="C208" s="38">
@@ -8945,8 +8952,8 @@
       <c r="K208" s="40"/>
     </row>
     <row r="209" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A209" s="202"/>
-      <c r="B209" s="185"/>
+      <c r="A209" s="246"/>
+      <c r="B209" s="197"/>
       <c r="C209" s="38">
         <v>2</v>
       </c>
@@ -8962,8 +8969,8 @@
       <c r="K209" s="40"/>
     </row>
     <row r="210" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A210" s="192"/>
-      <c r="B210" s="186"/>
+      <c r="A210" s="204"/>
+      <c r="B210" s="205"/>
       <c r="C210" s="38">
         <v>3</v>
       </c>
@@ -8979,8 +8986,8 @@
       <c r="K210" s="40"/>
     </row>
     <row r="211" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A211" s="192"/>
-      <c r="B211" s="186"/>
+      <c r="A211" s="204"/>
+      <c r="B211" s="205"/>
       <c r="C211" s="38">
         <v>4</v>
       </c>
@@ -8996,8 +9003,8 @@
       <c r="K211" s="40"/>
     </row>
     <row r="212" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A212" s="192"/>
-      <c r="B212" s="186"/>
+      <c r="A212" s="204"/>
+      <c r="B212" s="205"/>
       <c r="C212" s="38">
         <v>5</v>
       </c>
@@ -9013,8 +9020,8 @@
       <c r="K212" s="40"/>
     </row>
     <row r="213" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A213" s="192"/>
-      <c r="B213" s="186"/>
+      <c r="A213" s="204"/>
+      <c r="B213" s="205"/>
       <c r="C213" s="38">
         <v>6</v>
       </c>
@@ -9030,8 +9037,8 @@
       <c r="K213" s="98"/>
     </row>
     <row r="214" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A214" s="192"/>
-      <c r="B214" s="186"/>
+      <c r="A214" s="204"/>
+      <c r="B214" s="205"/>
       <c r="C214" s="38">
         <v>7</v>
       </c>
@@ -9047,8 +9054,8 @@
       <c r="K214" s="40"/>
     </row>
     <row r="215" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A215" s="192"/>
-      <c r="B215" s="186"/>
+      <c r="A215" s="204"/>
+      <c r="B215" s="205"/>
       <c r="C215" s="38">
         <v>8</v>
       </c>
@@ -9064,8 +9071,8 @@
       <c r="K215" s="40"/>
     </row>
     <row r="216" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A216" s="192"/>
-      <c r="B216" s="186"/>
+      <c r="A216" s="204"/>
+      <c r="B216" s="205"/>
       <c r="C216" s="38"/>
       <c r="D216" s="115" t="s">
         <v>602</v>
@@ -9079,8 +9086,8 @@
       <c r="K216" s="40"/>
     </row>
     <row r="217" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A217" s="192"/>
-      <c r="B217" s="186"/>
+      <c r="A217" s="204"/>
+      <c r="B217" s="205"/>
       <c r="C217" s="38">
         <v>9</v>
       </c>
@@ -9096,8 +9103,8 @@
       <c r="K217" s="40"/>
     </row>
     <row r="218" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A218" s="192"/>
-      <c r="B218" s="186"/>
+      <c r="A218" s="204"/>
+      <c r="B218" s="205"/>
       <c r="C218" s="38">
         <v>98</v>
       </c>
@@ -9113,10 +9120,10 @@
       <c r="K218" s="56"/>
     </row>
     <row r="219" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A219" s="206" t="s">
+      <c r="A219" s="187" t="s">
         <v>515</v>
       </c>
-      <c r="B219" s="269" t="s">
+      <c r="B219" s="229" t="s">
         <v>558</v>
       </c>
       <c r="C219" s="103">
@@ -9134,8 +9141,8 @@
       <c r="K219" s="40"/>
     </row>
     <row r="220" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A220" s="206"/>
-      <c r="B220" s="269"/>
+      <c r="A220" s="187"/>
+      <c r="B220" s="229"/>
       <c r="C220" s="103">
         <v>2</v>
       </c>
@@ -9151,10 +9158,10 @@
       <c r="K220" s="40"/>
     </row>
     <row r="221" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A221" s="267" t="s">
+      <c r="A221" s="210" t="s">
         <v>517</v>
       </c>
-      <c r="B221" s="228" t="s">
+      <c r="B221" s="211" t="s">
         <v>400</v>
       </c>
       <c r="C221" s="73">
@@ -9172,8 +9179,8 @@
       <c r="K221" s="40"/>
     </row>
     <row r="222" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A222" s="267"/>
-      <c r="B222" s="228"/>
+      <c r="A222" s="210"/>
+      <c r="B222" s="211"/>
       <c r="C222" s="73">
         <v>2</v>
       </c>
@@ -9189,8 +9196,8 @@
       <c r="K222" s="40"/>
     </row>
     <row r="223" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A223" s="267"/>
-      <c r="B223" s="228"/>
+      <c r="A223" s="210"/>
+      <c r="B223" s="211"/>
       <c r="C223" s="103">
         <v>98</v>
       </c>
@@ -9206,25 +9213,25 @@
       <c r="K223" s="40"/>
     </row>
     <row r="224" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A224" s="209" t="s">
+      <c r="A224" s="170" t="s">
         <v>402</v>
       </c>
-      <c r="B224" s="210"/>
-      <c r="C224" s="210"/>
-      <c r="D224" s="210"/>
-      <c r="E224" s="210"/>
-      <c r="F224" s="210"/>
-      <c r="G224" s="210"/>
-      <c r="H224" s="210"/>
-      <c r="I224" s="210"/>
-      <c r="J224" s="210"/>
-      <c r="K224" s="211"/>
+      <c r="B224" s="171"/>
+      <c r="C224" s="171"/>
+      <c r="D224" s="171"/>
+      <c r="E224" s="171"/>
+      <c r="F224" s="171"/>
+      <c r="G224" s="171"/>
+      <c r="H224" s="171"/>
+      <c r="I224" s="171"/>
+      <c r="J224" s="171"/>
+      <c r="K224" s="172"/>
     </row>
     <row r="225" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A225" s="267" t="s">
+      <c r="A225" s="210" t="s">
         <v>521</v>
       </c>
-      <c r="B225" s="228" t="s">
+      <c r="B225" s="211" t="s">
         <v>180</v>
       </c>
       <c r="C225" s="73">
@@ -9242,8 +9249,8 @@
       <c r="K225" s="40"/>
     </row>
     <row r="226" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A226" s="171"/>
-      <c r="B226" s="268"/>
+      <c r="A226" s="227"/>
+      <c r="B226" s="228"/>
       <c r="C226" s="73">
         <v>2</v>
       </c>
@@ -9259,10 +9266,10 @@
       <c r="K226" s="40"/>
     </row>
     <row r="227" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A227" s="267" t="s">
+      <c r="A227" s="210" t="s">
         <v>522</v>
       </c>
-      <c r="B227" s="228" t="s">
+      <c r="B227" s="211" t="s">
         <v>401</v>
       </c>
       <c r="C227" s="73">
@@ -9282,8 +9289,8 @@
       <c r="K227" s="40"/>
     </row>
     <row r="228" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A228" s="171"/>
-      <c r="B228" s="268"/>
+      <c r="A228" s="227"/>
+      <c r="B228" s="228"/>
       <c r="C228" s="73">
         <v>2</v>
       </c>
@@ -9301,8 +9308,8 @@
       <c r="K228" s="40"/>
     </row>
     <row r="229" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A229" s="171"/>
-      <c r="B229" s="268"/>
+      <c r="A229" s="227"/>
+      <c r="B229" s="228"/>
       <c r="C229" s="73">
         <v>3</v>
       </c>
@@ -9320,10 +9327,10 @@
       <c r="K229" s="40"/>
     </row>
     <row r="230" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A230" s="229" t="s">
+      <c r="A230" s="307" t="s">
         <v>523</v>
       </c>
-      <c r="B230" s="228" t="s">
+      <c r="B230" s="211" t="s">
         <v>382</v>
       </c>
       <c r="C230" s="73">
@@ -9341,8 +9348,8 @@
       <c r="K230" s="40"/>
     </row>
     <row r="231" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A231" s="229"/>
-      <c r="B231" s="228"/>
+      <c r="A231" s="307"/>
+      <c r="B231" s="211"/>
       <c r="C231" s="73">
         <v>2</v>
       </c>
@@ -9358,8 +9365,8 @@
       <c r="K231" s="57"/>
     </row>
     <row r="232" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A232" s="229"/>
-      <c r="B232" s="228"/>
+      <c r="A232" s="307"/>
+      <c r="B232" s="211"/>
       <c r="C232" s="73">
         <v>3</v>
       </c>
@@ -9375,8 +9382,8 @@
       <c r="K232" s="57"/>
     </row>
     <row r="233" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A233" s="229"/>
-      <c r="B233" s="228"/>
+      <c r="A233" s="307"/>
+      <c r="B233" s="211"/>
       <c r="C233" s="73">
         <v>4</v>
       </c>
@@ -9392,8 +9399,8 @@
       <c r="K233" s="57"/>
     </row>
     <row r="234" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A234" s="229"/>
-      <c r="B234" s="228"/>
+      <c r="A234" s="307"/>
+      <c r="B234" s="211"/>
       <c r="C234" s="73">
         <v>5</v>
       </c>
@@ -9409,8 +9416,8 @@
       <c r="K234" s="57"/>
     </row>
     <row r="235" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A235" s="229"/>
-      <c r="B235" s="228"/>
+      <c r="A235" s="307"/>
+      <c r="B235" s="211"/>
       <c r="C235" s="73">
         <v>6</v>
       </c>
@@ -9426,19 +9433,19 @@
       <c r="K235" s="57"/>
     </row>
     <row r="236" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A236" s="215" t="s">
+      <c r="A236" s="296" t="s">
         <v>469</v>
       </c>
-      <c r="B236" s="216"/>
-      <c r="C236" s="216"/>
-      <c r="D236" s="216"/>
-      <c r="E236" s="217"/>
-      <c r="F236" s="217"/>
-      <c r="G236" s="217"/>
-      <c r="H236" s="217"/>
-      <c r="I236" s="217"/>
-      <c r="J236" s="217"/>
-      <c r="K236" s="218"/>
+      <c r="B236" s="297"/>
+      <c r="C236" s="297"/>
+      <c r="D236" s="297"/>
+      <c r="E236" s="174"/>
+      <c r="F236" s="174"/>
+      <c r="G236" s="174"/>
+      <c r="H236" s="174"/>
+      <c r="I236" s="174"/>
+      <c r="J236" s="174"/>
+      <c r="K236" s="175"/>
     </row>
     <row r="237" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A237" s="92" t="s">
@@ -9462,19 +9469,19 @@
       <c r="K237" s="63"/>
     </row>
     <row r="238" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A238" s="239" t="s">
+      <c r="A238" s="173" t="s">
         <v>409</v>
       </c>
-      <c r="B238" s="217"/>
-      <c r="C238" s="217"/>
-      <c r="D238" s="217"/>
-      <c r="E238" s="217"/>
-      <c r="F238" s="217"/>
-      <c r="G238" s="217"/>
-      <c r="H238" s="217"/>
-      <c r="I238" s="217"/>
-      <c r="J238" s="217"/>
-      <c r="K238" s="218"/>
+      <c r="B238" s="174"/>
+      <c r="C238" s="174"/>
+      <c r="D238" s="174"/>
+      <c r="E238" s="174"/>
+      <c r="F238" s="174"/>
+      <c r="G238" s="174"/>
+      <c r="H238" s="174"/>
+      <c r="I238" s="174"/>
+      <c r="J238" s="174"/>
+      <c r="K238" s="175"/>
     </row>
     <row r="239" spans="1:11" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="77" t="s">
@@ -9561,19 +9568,19 @@
       <c r="K242" s="63"/>
     </row>
     <row r="243" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A243" s="239" t="s">
+      <c r="A243" s="173" t="s">
         <v>410</v>
       </c>
-      <c r="B243" s="217"/>
-      <c r="C243" s="217"/>
-      <c r="D243" s="217"/>
-      <c r="E243" s="217"/>
-      <c r="F243" s="217"/>
-      <c r="G243" s="217"/>
-      <c r="H243" s="217"/>
-      <c r="I243" s="217"/>
-      <c r="J243" s="217"/>
-      <c r="K243" s="218"/>
+      <c r="B243" s="174"/>
+      <c r="C243" s="174"/>
+      <c r="D243" s="174"/>
+      <c r="E243" s="174"/>
+      <c r="F243" s="174"/>
+      <c r="G243" s="174"/>
+      <c r="H243" s="174"/>
+      <c r="I243" s="174"/>
+      <c r="J243" s="174"/>
+      <c r="K243" s="175"/>
     </row>
     <row r="244" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A244" s="78" t="s">
@@ -9597,19 +9604,19 @@
       <c r="K244" s="63"/>
     </row>
     <row r="245" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A245" s="209" t="s">
+      <c r="A245" s="170" t="s">
         <v>547</v>
       </c>
-      <c r="B245" s="210"/>
-      <c r="C245" s="210"/>
-      <c r="D245" s="210"/>
-      <c r="E245" s="210"/>
-      <c r="F245" s="210"/>
-      <c r="G245" s="210"/>
-      <c r="H245" s="210"/>
-      <c r="I245" s="210"/>
-      <c r="J245" s="210"/>
-      <c r="K245" s="211"/>
+      <c r="B245" s="171"/>
+      <c r="C245" s="171"/>
+      <c r="D245" s="171"/>
+      <c r="E245" s="171"/>
+      <c r="F245" s="171"/>
+      <c r="G245" s="171"/>
+      <c r="H245" s="171"/>
+      <c r="I245" s="171"/>
+      <c r="J245" s="171"/>
+      <c r="K245" s="172"/>
     </row>
     <row r="246" spans="1:11" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="59" t="s">
@@ -9633,10 +9640,10 @@
       <c r="K246" s="40"/>
     </row>
     <row r="247" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A247" s="205" t="s">
+      <c r="A247" s="203" t="s">
         <v>215</v>
       </c>
-      <c r="B247" s="179" t="s">
+      <c r="B247" s="196" t="s">
         <v>405</v>
       </c>
       <c r="C247" s="62">
@@ -9656,8 +9663,8 @@
       <c r="K247" s="63"/>
     </row>
     <row r="248" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A248" s="305"/>
-      <c r="B248" s="195"/>
+      <c r="A248" s="209"/>
+      <c r="B248" s="198"/>
       <c r="C248" s="62">
         <v>2</v>
       </c>
@@ -9694,10 +9701,10 @@
       <c r="K249" s="63"/>
     </row>
     <row r="250" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A250" s="267" t="s">
+      <c r="A250" s="210" t="s">
         <v>217</v>
       </c>
-      <c r="B250" s="228" t="s">
+      <c r="B250" s="211" t="s">
         <v>339</v>
       </c>
       <c r="C250" s="73">
@@ -9715,8 +9722,8 @@
       <c r="K250" s="63"/>
     </row>
     <row r="251" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A251" s="267"/>
-      <c r="B251" s="228"/>
+      <c r="A251" s="210"/>
+      <c r="B251" s="211"/>
       <c r="C251" s="73">
         <v>2</v>
       </c>
@@ -9732,8 +9739,8 @@
       <c r="K251" s="63"/>
     </row>
     <row r="252" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A252" s="267"/>
-      <c r="B252" s="228"/>
+      <c r="A252" s="210"/>
+      <c r="B252" s="211"/>
       <c r="C252" s="73">
         <v>3</v>
       </c>
@@ -9749,8 +9756,8 @@
       <c r="K252" s="63"/>
     </row>
     <row r="253" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A253" s="267"/>
-      <c r="B253" s="228"/>
+      <c r="A253" s="210"/>
+      <c r="B253" s="211"/>
       <c r="C253" s="73">
         <v>4</v>
       </c>
@@ -9766,8 +9773,8 @@
       <c r="K253" s="63"/>
     </row>
     <row r="254" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A254" s="267"/>
-      <c r="B254" s="228"/>
+      <c r="A254" s="210"/>
+      <c r="B254" s="211"/>
       <c r="C254" s="73">
         <v>5</v>
       </c>
@@ -9783,10 +9790,10 @@
       <c r="K254" s="63"/>
     </row>
     <row r="255" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A255" s="206" t="s">
+      <c r="A255" s="187" t="s">
         <v>218</v>
       </c>
-      <c r="B255" s="306" t="s">
+      <c r="B255" s="212" t="s">
         <v>692</v>
       </c>
       <c r="C255" s="65">
@@ -9804,8 +9811,8 @@
       <c r="K255" s="67"/>
     </row>
     <row r="256" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A256" s="206"/>
-      <c r="B256" s="306"/>
+      <c r="A256" s="187"/>
+      <c r="B256" s="212"/>
       <c r="C256" s="65">
         <v>2</v>
       </c>
@@ -9821,8 +9828,8 @@
       <c r="K256" s="67"/>
     </row>
     <row r="257" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A257" s="206"/>
-      <c r="B257" s="306"/>
+      <c r="A257" s="187"/>
+      <c r="B257" s="212"/>
       <c r="C257" s="65">
         <v>3</v>
       </c>
@@ -9838,8 +9845,8 @@
       <c r="K257" s="67"/>
     </row>
     <row r="258" spans="1:11" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A258" s="206"/>
-      <c r="B258" s="306"/>
+      <c r="A258" s="187"/>
+      <c r="B258" s="212"/>
       <c r="C258" s="65">
         <v>4</v>
       </c>
@@ -9855,8 +9862,8 @@
       <c r="K258" s="67"/>
     </row>
     <row r="259" spans="1:11" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A259" s="206"/>
-      <c r="B259" s="306"/>
+      <c r="A259" s="187"/>
+      <c r="B259" s="212"/>
       <c r="C259" s="65">
         <v>5</v>
       </c>
@@ -9872,10 +9879,10 @@
       <c r="K259" s="67"/>
     </row>
     <row r="260" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A260" s="205" t="s">
+      <c r="A260" s="203" t="s">
         <v>414</v>
       </c>
-      <c r="B260" s="286" t="s">
+      <c r="B260" s="208" t="s">
         <v>693</v>
       </c>
       <c r="C260" s="38">
@@ -9895,8 +9902,8 @@
       <c r="K260" s="40"/>
     </row>
     <row r="261" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A261" s="192"/>
-      <c r="B261" s="186"/>
+      <c r="A261" s="204"/>
+      <c r="B261" s="205"/>
       <c r="C261" s="38">
         <v>2</v>
       </c>
@@ -9912,8 +9919,8 @@
       <c r="K261" s="40"/>
     </row>
     <row r="262" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A262" s="192"/>
-      <c r="B262" s="186"/>
+      <c r="A262" s="204"/>
+      <c r="B262" s="205"/>
       <c r="C262" s="38">
         <v>3</v>
       </c>
@@ -9929,8 +9936,8 @@
       <c r="K262" s="40"/>
     </row>
     <row r="263" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A263" s="192"/>
-      <c r="B263" s="186"/>
+      <c r="A263" s="204"/>
+      <c r="B263" s="205"/>
       <c r="C263" s="38">
         <v>4</v>
       </c>
@@ -9946,8 +9953,8 @@
       <c r="K263" s="40"/>
     </row>
     <row r="264" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A264" s="192"/>
-      <c r="B264" s="186"/>
+      <c r="A264" s="204"/>
+      <c r="B264" s="205"/>
       <c r="C264" s="38">
         <v>5</v>
       </c>
@@ -9963,8 +9970,8 @@
       <c r="K264" s="40"/>
     </row>
     <row r="265" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A265" s="192"/>
-      <c r="B265" s="186"/>
+      <c r="A265" s="204"/>
+      <c r="B265" s="205"/>
       <c r="C265" s="38">
         <v>6</v>
       </c>
@@ -9980,8 +9987,8 @@
       <c r="K265" s="40"/>
     </row>
     <row r="266" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A266" s="192"/>
-      <c r="B266" s="186"/>
+      <c r="A266" s="204"/>
+      <c r="B266" s="205"/>
       <c r="C266" s="38">
         <v>7</v>
       </c>
@@ -9997,8 +10004,8 @@
       <c r="K266" s="40"/>
     </row>
     <row r="267" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A267" s="192"/>
-      <c r="B267" s="186"/>
+      <c r="A267" s="204"/>
+      <c r="B267" s="205"/>
       <c r="C267" s="38">
         <v>8</v>
       </c>
@@ -10014,8 +10021,8 @@
       <c r="K267" s="40"/>
     </row>
     <row r="268" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A268" s="192"/>
-      <c r="B268" s="186"/>
+      <c r="A268" s="204"/>
+      <c r="B268" s="205"/>
       <c r="C268" s="38">
         <v>9</v>
       </c>
@@ -10031,8 +10038,8 @@
       <c r="K268" s="40"/>
     </row>
     <row r="269" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A269" s="192"/>
-      <c r="B269" s="186"/>
+      <c r="A269" s="204"/>
+      <c r="B269" s="205"/>
       <c r="C269" s="38">
         <v>10</v>
       </c>
@@ -10048,8 +10055,8 @@
       <c r="K269" s="40"/>
     </row>
     <row r="270" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A270" s="192"/>
-      <c r="B270" s="186"/>
+      <c r="A270" s="204"/>
+      <c r="B270" s="205"/>
       <c r="C270" s="38">
         <v>11</v>
       </c>
@@ -10065,8 +10072,8 @@
       <c r="K270" s="40"/>
     </row>
     <row r="271" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A271" s="192"/>
-      <c r="B271" s="186"/>
+      <c r="A271" s="204"/>
+      <c r="B271" s="205"/>
       <c r="C271" s="38">
         <v>12</v>
       </c>
@@ -10086,8 +10093,8 @@
       <c r="K271" s="40"/>
     </row>
     <row r="272" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A272" s="178"/>
-      <c r="B272" s="180"/>
+      <c r="A272" s="206"/>
+      <c r="B272" s="207"/>
       <c r="C272" s="38">
         <v>99</v>
       </c>
@@ -10103,10 +10110,10 @@
       <c r="K272" s="40"/>
     </row>
     <row r="273" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A273" s="205" t="s">
+      <c r="A273" s="203" t="s">
         <v>530</v>
       </c>
-      <c r="B273" s="179" t="s">
+      <c r="B273" s="196" t="s">
         <v>559</v>
       </c>
       <c r="C273" s="38">
@@ -10126,8 +10133,8 @@
       <c r="K273" s="40"/>
     </row>
     <row r="274" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A274" s="192"/>
-      <c r="B274" s="186"/>
+      <c r="A274" s="204"/>
+      <c r="B274" s="205"/>
       <c r="C274" s="38">
         <v>2</v>
       </c>
@@ -10145,8 +10152,8 @@
       <c r="K274" s="40"/>
     </row>
     <row r="275" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A275" s="192"/>
-      <c r="B275" s="186"/>
+      <c r="A275" s="204"/>
+      <c r="B275" s="205"/>
       <c r="C275" s="38">
         <v>3</v>
       </c>
@@ -10164,8 +10171,8 @@
       <c r="K275" s="40"/>
     </row>
     <row r="276" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A276" s="192"/>
-      <c r="B276" s="186"/>
+      <c r="A276" s="204"/>
+      <c r="B276" s="205"/>
       <c r="C276" s="38">
         <v>4</v>
       </c>
@@ -10183,8 +10190,8 @@
       <c r="K276" s="40"/>
     </row>
     <row r="277" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A277" s="192"/>
-      <c r="B277" s="186"/>
+      <c r="A277" s="204"/>
+      <c r="B277" s="205"/>
       <c r="C277" s="38">
         <v>5</v>
       </c>
@@ -10202,8 +10209,8 @@
       <c r="K277" s="40"/>
     </row>
     <row r="278" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A278" s="192"/>
-      <c r="B278" s="186"/>
+      <c r="A278" s="204"/>
+      <c r="B278" s="205"/>
       <c r="C278" s="38">
         <v>6</v>
       </c>
@@ -10221,10 +10228,10 @@
       <c r="K278" s="40"/>
     </row>
     <row r="279" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A279" s="205" t="s">
+      <c r="A279" s="203" t="s">
         <v>531</v>
       </c>
-      <c r="B279" s="179" t="s">
+      <c r="B279" s="196" t="s">
         <v>235</v>
       </c>
       <c r="C279" s="38">
@@ -10244,8 +10251,8 @@
       <c r="K279" s="40"/>
     </row>
     <row r="280" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A280" s="192"/>
-      <c r="B280" s="186"/>
+      <c r="A280" s="204"/>
+      <c r="B280" s="205"/>
       <c r="C280" s="38">
         <v>3</v>
       </c>
@@ -10263,8 +10270,8 @@
       <c r="K280" s="40"/>
     </row>
     <row r="281" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A281" s="192"/>
-      <c r="B281" s="186"/>
+      <c r="A281" s="204"/>
+      <c r="B281" s="205"/>
       <c r="C281" s="38">
         <v>4</v>
       </c>
@@ -10280,8 +10287,8 @@
       <c r="K281" s="40"/>
     </row>
     <row r="282" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A282" s="192"/>
-      <c r="B282" s="186"/>
+      <c r="A282" s="204"/>
+      <c r="B282" s="205"/>
       <c r="C282" s="38">
         <v>5</v>
       </c>
@@ -10297,8 +10304,8 @@
       <c r="K282" s="40"/>
     </row>
     <row r="283" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A283" s="178"/>
-      <c r="B283" s="180"/>
+      <c r="A283" s="206"/>
+      <c r="B283" s="207"/>
       <c r="C283" s="38">
         <v>99</v>
       </c>
@@ -10314,34 +10321,34 @@
       <c r="K283" s="40"/>
     </row>
     <row r="284" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A284" s="199" t="s">
+      <c r="A284" s="285" t="s">
         <v>545</v>
       </c>
-      <c r="B284" s="175"/>
-      <c r="C284" s="175"/>
-      <c r="D284" s="175"/>
-      <c r="E284" s="175"/>
-      <c r="F284" s="175"/>
-      <c r="G284" s="175"/>
-      <c r="H284" s="175"/>
-      <c r="I284" s="175"/>
-      <c r="J284" s="175"/>
-      <c r="K284" s="176"/>
+      <c r="B284" s="286"/>
+      <c r="C284" s="286"/>
+      <c r="D284" s="286"/>
+      <c r="E284" s="286"/>
+      <c r="F284" s="286"/>
+      <c r="G284" s="286"/>
+      <c r="H284" s="286"/>
+      <c r="I284" s="286"/>
+      <c r="J284" s="286"/>
+      <c r="K284" s="287"/>
     </row>
     <row r="285" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A285" s="209" t="s">
+      <c r="A285" s="170" t="s">
         <v>544</v>
       </c>
-      <c r="B285" s="210"/>
-      <c r="C285" s="210"/>
-      <c r="D285" s="210"/>
-      <c r="E285" s="210"/>
-      <c r="F285" s="210"/>
-      <c r="G285" s="210"/>
-      <c r="H285" s="210"/>
-      <c r="I285" s="210"/>
-      <c r="J285" s="210"/>
-      <c r="K285" s="211"/>
+      <c r="B285" s="171"/>
+      <c r="C285" s="171"/>
+      <c r="D285" s="171"/>
+      <c r="E285" s="171"/>
+      <c r="F285" s="171"/>
+      <c r="G285" s="171"/>
+      <c r="H285" s="171"/>
+      <c r="I285" s="171"/>
+      <c r="J285" s="171"/>
+      <c r="K285" s="172"/>
     </row>
     <row r="286" spans="1:11" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A286" s="93" t="s">
@@ -10365,10 +10372,10 @@
       <c r="K286" s="40"/>
     </row>
     <row r="287" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A287" s="206" t="s">
+      <c r="A287" s="187" t="s">
         <v>416</v>
       </c>
-      <c r="B287" s="316" t="s">
+      <c r="B287" s="190" t="s">
         <v>669</v>
       </c>
       <c r="C287" s="60">
@@ -10386,8 +10393,8 @@
       <c r="K287" s="40"/>
     </row>
     <row r="288" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A288" s="206"/>
-      <c r="B288" s="317"/>
+      <c r="A288" s="187"/>
+      <c r="B288" s="191"/>
       <c r="C288" s="60">
         <v>2</v>
       </c>
@@ -10403,8 +10410,8 @@
       <c r="K288" s="40"/>
     </row>
     <row r="289" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A289" s="206"/>
-      <c r="B289" s="317"/>
+      <c r="A289" s="187"/>
+      <c r="B289" s="191"/>
       <c r="C289" s="60">
         <v>3</v>
       </c>
@@ -10420,8 +10427,8 @@
       <c r="K289" s="40"/>
     </row>
     <row r="290" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A290" s="206"/>
-      <c r="B290" s="317"/>
+      <c r="A290" s="187"/>
+      <c r="B290" s="191"/>
       <c r="C290" s="60">
         <v>4</v>
       </c>
@@ -10437,8 +10444,8 @@
       <c r="K290" s="40"/>
     </row>
     <row r="291" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A291" s="206"/>
-      <c r="B291" s="317"/>
+      <c r="A291" s="187"/>
+      <c r="B291" s="191"/>
       <c r="C291" s="60">
         <v>5</v>
       </c>
@@ -10454,8 +10461,8 @@
       <c r="K291" s="40"/>
     </row>
     <row r="292" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A292" s="206"/>
-      <c r="B292" s="317"/>
+      <c r="A292" s="187"/>
+      <c r="B292" s="191"/>
       <c r="C292" s="60">
         <v>6</v>
       </c>
@@ -10471,8 +10478,8 @@
       <c r="K292" s="40"/>
     </row>
     <row r="293" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A293" s="206"/>
-      <c r="B293" s="317"/>
+      <c r="A293" s="187"/>
+      <c r="B293" s="191"/>
       <c r="C293" s="60">
         <v>7</v>
       </c>
@@ -10488,8 +10495,8 @@
       <c r="K293" s="40"/>
     </row>
     <row r="294" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A294" s="206"/>
-      <c r="B294" s="317"/>
+      <c r="A294" s="187"/>
+      <c r="B294" s="191"/>
       <c r="C294" s="60">
         <v>8</v>
       </c>
@@ -10505,8 +10512,8 @@
       <c r="K294" s="40"/>
     </row>
     <row r="295" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A295" s="206"/>
-      <c r="B295" s="317"/>
+      <c r="A295" s="187"/>
+      <c r="B295" s="191"/>
       <c r="C295" s="60">
         <v>9</v>
       </c>
@@ -10522,8 +10529,8 @@
       <c r="K295" s="40"/>
     </row>
     <row r="296" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A296" s="206"/>
-      <c r="B296" s="318"/>
+      <c r="A296" s="187"/>
+      <c r="B296" s="192"/>
       <c r="C296" s="60">
         <v>99</v>
       </c>
@@ -10539,10 +10546,10 @@
       <c r="K296" s="40"/>
     </row>
     <row r="297" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A297" s="206" t="s">
+      <c r="A297" s="187" t="s">
         <v>418</v>
       </c>
-      <c r="B297" s="316" t="s">
+      <c r="B297" s="190" t="s">
         <v>670</v>
       </c>
       <c r="C297" s="60">
@@ -10560,8 +10567,8 @@
       <c r="K297" s="40"/>
     </row>
     <row r="298" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A298" s="206"/>
-      <c r="B298" s="317"/>
+      <c r="A298" s="187"/>
+      <c r="B298" s="191"/>
       <c r="C298" s="60">
         <v>2</v>
       </c>
@@ -10577,8 +10584,8 @@
       <c r="K298" s="40"/>
     </row>
     <row r="299" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A299" s="206"/>
-      <c r="B299" s="317"/>
+      <c r="A299" s="187"/>
+      <c r="B299" s="191"/>
       <c r="C299" s="60">
         <v>3</v>
       </c>
@@ -10594,8 +10601,8 @@
       <c r="K299" s="40"/>
     </row>
     <row r="300" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A300" s="206"/>
-      <c r="B300" s="317"/>
+      <c r="A300" s="187"/>
+      <c r="B300" s="191"/>
       <c r="C300" s="60"/>
       <c r="D300" s="115" t="s">
         <v>607</v>
@@ -10609,8 +10616,8 @@
       <c r="K300" s="40"/>
     </row>
     <row r="301" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A301" s="206"/>
-      <c r="B301" s="317"/>
+      <c r="A301" s="187"/>
+      <c r="B301" s="191"/>
       <c r="C301" s="60">
         <v>4</v>
       </c>
@@ -10626,8 +10633,8 @@
       <c r="K301" s="40"/>
     </row>
     <row r="302" spans="1:11" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A302" s="206"/>
-      <c r="B302" s="317"/>
+      <c r="A302" s="187"/>
+      <c r="B302" s="191"/>
       <c r="C302" s="60">
         <v>5</v>
       </c>
@@ -10643,8 +10650,8 @@
       <c r="K302" s="40"/>
     </row>
     <row r="303" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A303" s="206"/>
-      <c r="B303" s="317"/>
+      <c r="A303" s="187"/>
+      <c r="B303" s="191"/>
       <c r="C303" s="60">
         <v>6</v>
       </c>
@@ -10660,8 +10667,8 @@
       <c r="K303" s="40"/>
     </row>
     <row r="304" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A304" s="206"/>
-      <c r="B304" s="317"/>
+      <c r="A304" s="187"/>
+      <c r="B304" s="191"/>
       <c r="C304" s="60">
         <v>7</v>
       </c>
@@ -10677,8 +10684,8 @@
       <c r="K304" s="40"/>
     </row>
     <row r="305" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A305" s="206"/>
-      <c r="B305" s="317"/>
+      <c r="A305" s="187"/>
+      <c r="B305" s="191"/>
       <c r="C305" s="60">
         <v>8</v>
       </c>
@@ -10694,8 +10701,8 @@
       <c r="K305" s="40"/>
     </row>
     <row r="306" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A306" s="206"/>
-      <c r="B306" s="317"/>
+      <c r="A306" s="187"/>
+      <c r="B306" s="191"/>
       <c r="C306" s="60">
         <v>9</v>
       </c>
@@ -10711,8 +10718,8 @@
       <c r="K306" s="40"/>
     </row>
     <row r="307" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A307" s="206"/>
-      <c r="B307" s="317"/>
+      <c r="A307" s="187"/>
+      <c r="B307" s="191"/>
       <c r="C307" s="60">
         <v>10</v>
       </c>
@@ -10728,8 +10735,8 @@
       <c r="K307" s="40"/>
     </row>
     <row r="308" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A308" s="206"/>
-      <c r="B308" s="317"/>
+      <c r="A308" s="187"/>
+      <c r="B308" s="191"/>
       <c r="C308" s="60">
         <v>11</v>
       </c>
@@ -10745,8 +10752,8 @@
       <c r="K308" s="40"/>
     </row>
     <row r="309" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A309" s="206"/>
-      <c r="B309" s="318"/>
+      <c r="A309" s="187"/>
+      <c r="B309" s="192"/>
       <c r="C309" s="60">
         <v>99</v>
       </c>
@@ -10762,10 +10769,10 @@
       <c r="K309" s="40"/>
     </row>
     <row r="310" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A310" s="253" t="s">
+      <c r="A310" s="182" t="s">
         <v>240</v>
       </c>
-      <c r="B310" s="311" t="s">
+      <c r="B310" s="181" t="s">
         <v>671</v>
       </c>
       <c r="C310" s="99">
@@ -10783,8 +10790,8 @@
       <c r="K310" s="40"/>
     </row>
     <row r="311" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A311" s="254"/>
-      <c r="B311" s="311"/>
+      <c r="A311" s="183"/>
+      <c r="B311" s="181"/>
       <c r="C311" s="99">
         <v>2</v>
       </c>
@@ -10800,8 +10807,8 @@
       <c r="K311" s="40"/>
     </row>
     <row r="312" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A312" s="254"/>
-      <c r="B312" s="311"/>
+      <c r="A312" s="183"/>
+      <c r="B312" s="181"/>
       <c r="C312" s="99">
         <v>3</v>
       </c>
@@ -10817,8 +10824,8 @@
       <c r="K312" s="40"/>
     </row>
     <row r="313" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A313" s="254"/>
-      <c r="B313" s="311"/>
+      <c r="A313" s="183"/>
+      <c r="B313" s="181"/>
       <c r="C313" s="99">
         <v>4</v>
       </c>
@@ -10834,8 +10841,8 @@
       <c r="K313" s="40"/>
     </row>
     <row r="314" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A314" s="254"/>
-      <c r="B314" s="311"/>
+      <c r="A314" s="183"/>
+      <c r="B314" s="181"/>
       <c r="C314" s="99">
         <v>5</v>
       </c>
@@ -10851,8 +10858,8 @@
       <c r="K314" s="40"/>
     </row>
     <row r="315" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A315" s="254"/>
-      <c r="B315" s="311"/>
+      <c r="A315" s="183"/>
+      <c r="B315" s="181"/>
       <c r="C315" s="99">
         <v>6</v>
       </c>
@@ -10868,8 +10875,8 @@
       <c r="K315" s="40"/>
     </row>
     <row r="316" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A316" s="254"/>
-      <c r="B316" s="311"/>
+      <c r="A316" s="183"/>
+      <c r="B316" s="181"/>
       <c r="C316" s="99">
         <v>7</v>
       </c>
@@ -10885,8 +10892,8 @@
       <c r="K316" s="40"/>
     </row>
     <row r="317" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A317" s="254"/>
-      <c r="B317" s="311"/>
+      <c r="A317" s="183"/>
+      <c r="B317" s="181"/>
       <c r="C317" s="99">
         <v>8</v>
       </c>
@@ -10902,8 +10909,8 @@
       <c r="K317" s="40"/>
     </row>
     <row r="318" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A318" s="254"/>
-      <c r="B318" s="311"/>
+      <c r="A318" s="183"/>
+      <c r="B318" s="181"/>
       <c r="C318" s="99">
         <v>9</v>
       </c>
@@ -10919,8 +10926,8 @@
       <c r="K318" s="40"/>
     </row>
     <row r="319" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A319" s="254"/>
-      <c r="B319" s="311"/>
+      <c r="A319" s="183"/>
+      <c r="B319" s="181"/>
       <c r="C319" s="99">
         <v>10</v>
       </c>
@@ -10936,8 +10943,8 @@
       <c r="K319" s="40"/>
     </row>
     <row r="320" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A320" s="254"/>
-      <c r="B320" s="311"/>
+      <c r="A320" s="183"/>
+      <c r="B320" s="181"/>
       <c r="C320" s="99">
         <v>11</v>
       </c>
@@ -10953,8 +10960,8 @@
       <c r="K320" s="40"/>
     </row>
     <row r="321" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A321" s="255"/>
-      <c r="B321" s="311"/>
+      <c r="A321" s="184"/>
+      <c r="B321" s="181"/>
       <c r="C321" s="99">
         <v>99</v>
       </c>
@@ -10970,10 +10977,10 @@
       <c r="K321" s="40"/>
     </row>
     <row r="322" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A322" s="206" t="s">
+      <c r="A322" s="187" t="s">
         <v>241</v>
       </c>
-      <c r="B322" s="315" t="s">
+      <c r="B322" s="189" t="s">
         <v>614</v>
       </c>
       <c r="C322" s="60">
@@ -10995,8 +11002,8 @@
       <c r="K322" s="40"/>
     </row>
     <row r="323" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A323" s="206"/>
-      <c r="B323" s="315"/>
+      <c r="A323" s="187"/>
+      <c r="B323" s="189"/>
       <c r="C323" s="60">
         <v>2</v>
       </c>
@@ -11012,8 +11019,8 @@
       <c r="K323" s="40"/>
     </row>
     <row r="324" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A324" s="314"/>
-      <c r="B324" s="314"/>
+      <c r="A324" s="188"/>
+      <c r="B324" s="188"/>
       <c r="C324" s="60">
         <v>3</v>
       </c>
@@ -11033,8 +11040,8 @@
       <c r="K324" s="40"/>
     </row>
     <row r="325" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A325" s="314"/>
-      <c r="B325" s="314"/>
+      <c r="A325" s="188"/>
+      <c r="B325" s="188"/>
       <c r="C325" s="60">
         <v>4</v>
       </c>
@@ -11054,8 +11061,8 @@
       <c r="K325" s="40"/>
     </row>
     <row r="326" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A326" s="314"/>
-      <c r="B326" s="314"/>
+      <c r="A326" s="188"/>
+      <c r="B326" s="188"/>
       <c r="C326" s="60">
         <v>5</v>
       </c>
@@ -11075,8 +11082,8 @@
       <c r="K326" s="40"/>
     </row>
     <row r="327" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A327" s="314"/>
-      <c r="B327" s="314"/>
+      <c r="A327" s="188"/>
+      <c r="B327" s="188"/>
       <c r="C327" s="60">
         <v>6</v>
       </c>
@@ -11096,8 +11103,8 @@
       <c r="K327" s="40"/>
     </row>
     <row r="328" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A328" s="314"/>
-      <c r="B328" s="314"/>
+      <c r="A328" s="188"/>
+      <c r="B328" s="188"/>
       <c r="C328" s="60">
         <v>7</v>
       </c>
@@ -11113,8 +11120,8 @@
       <c r="K328" s="40"/>
     </row>
     <row r="329" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A329" s="314"/>
-      <c r="B329" s="314"/>
+      <c r="A329" s="188"/>
+      <c r="B329" s="188"/>
       <c r="C329" s="60">
         <v>8</v>
       </c>
@@ -11134,8 +11141,8 @@
       <c r="K329" s="40"/>
     </row>
     <row r="330" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A330" s="314"/>
-      <c r="B330" s="314"/>
+      <c r="A330" s="188"/>
+      <c r="B330" s="188"/>
       <c r="C330" s="60">
         <v>9</v>
       </c>
@@ -11155,25 +11162,25 @@
       <c r="K330" s="40"/>
     </row>
     <row r="331" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A331" s="209" t="s">
+      <c r="A331" s="170" t="s">
         <v>543</v>
       </c>
-      <c r="B331" s="210"/>
-      <c r="C331" s="210"/>
-      <c r="D331" s="210"/>
-      <c r="E331" s="210"/>
-      <c r="F331" s="210"/>
-      <c r="G331" s="210"/>
-      <c r="H331" s="210"/>
-      <c r="I331" s="210"/>
-      <c r="J331" s="210"/>
-      <c r="K331" s="211"/>
+      <c r="B331" s="171"/>
+      <c r="C331" s="171"/>
+      <c r="D331" s="171"/>
+      <c r="E331" s="171"/>
+      <c r="F331" s="171"/>
+      <c r="G331" s="171"/>
+      <c r="H331" s="171"/>
+      <c r="I331" s="171"/>
+      <c r="J331" s="171"/>
+      <c r="K331" s="172"/>
     </row>
     <row r="332" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A332" s="313" t="s">
+      <c r="A332" s="186" t="s">
         <v>419</v>
       </c>
-      <c r="B332" s="312" t="s">
+      <c r="B332" s="185" t="s">
         <v>694</v>
       </c>
       <c r="C332" s="60">
@@ -11191,8 +11198,8 @@
       <c r="K332" s="40"/>
     </row>
     <row r="333" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A333" s="313"/>
-      <c r="B333" s="312"/>
+      <c r="A333" s="186"/>
+      <c r="B333" s="185"/>
       <c r="C333" s="60">
         <v>2</v>
       </c>
@@ -11208,8 +11215,8 @@
       <c r="K333" s="40"/>
     </row>
     <row r="334" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A334" s="313"/>
-      <c r="B334" s="312"/>
+      <c r="A334" s="186"/>
+      <c r="B334" s="185"/>
       <c r="C334" s="60">
         <v>3</v>
       </c>
@@ -11225,8 +11232,8 @@
       <c r="K334" s="40"/>
     </row>
     <row r="335" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A335" s="313"/>
-      <c r="B335" s="312"/>
+      <c r="A335" s="186"/>
+      <c r="B335" s="185"/>
       <c r="C335" s="60">
         <v>4</v>
       </c>
@@ -11242,8 +11249,8 @@
       <c r="K335" s="40"/>
     </row>
     <row r="336" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A336" s="313"/>
-      <c r="B336" s="312"/>
+      <c r="A336" s="186"/>
+      <c r="B336" s="185"/>
       <c r="C336" s="60">
         <v>5</v>
       </c>
@@ -11259,8 +11266,8 @@
       <c r="K336" s="40"/>
     </row>
     <row r="337" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A337" s="313"/>
-      <c r="B337" s="312"/>
+      <c r="A337" s="186"/>
+      <c r="B337" s="185"/>
       <c r="C337" s="60">
         <v>6</v>
       </c>
@@ -11276,8 +11283,8 @@
       <c r="K337" s="40"/>
     </row>
     <row r="338" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A338" s="313"/>
-      <c r="B338" s="312"/>
+      <c r="A338" s="186"/>
+      <c r="B338" s="185"/>
       <c r="C338" s="60">
         <v>7</v>
       </c>
@@ -11293,8 +11300,8 @@
       <c r="K338" s="40"/>
     </row>
     <row r="339" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A339" s="313"/>
-      <c r="B339" s="312"/>
+      <c r="A339" s="186"/>
+      <c r="B339" s="185"/>
       <c r="C339" s="60">
         <v>8</v>
       </c>
@@ -11310,8 +11317,8 @@
       <c r="K339" s="40"/>
     </row>
     <row r="340" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A340" s="313"/>
-      <c r="B340" s="312"/>
+      <c r="A340" s="186"/>
+      <c r="B340" s="185"/>
       <c r="C340" s="60">
         <v>9</v>
       </c>
@@ -11327,8 +11334,8 @@
       <c r="K340" s="40"/>
     </row>
     <row r="341" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A341" s="313"/>
-      <c r="B341" s="312"/>
+      <c r="A341" s="186"/>
+      <c r="B341" s="185"/>
       <c r="C341" s="60">
         <v>10</v>
       </c>
@@ -11344,8 +11351,8 @@
       <c r="K341" s="40"/>
     </row>
     <row r="342" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A342" s="313"/>
-      <c r="B342" s="312"/>
+      <c r="A342" s="186"/>
+      <c r="B342" s="185"/>
       <c r="C342" s="60">
         <v>11</v>
       </c>
@@ -11361,8 +11368,8 @@
       <c r="K342" s="40"/>
     </row>
     <row r="343" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A343" s="313"/>
-      <c r="B343" s="312"/>
+      <c r="A343" s="186"/>
+      <c r="B343" s="185"/>
       <c r="C343" s="60">
         <v>12</v>
       </c>
@@ -11378,8 +11385,8 @@
       <c r="K343" s="40"/>
     </row>
     <row r="344" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A344" s="313"/>
-      <c r="B344" s="312"/>
+      <c r="A344" s="186"/>
+      <c r="B344" s="185"/>
       <c r="C344" s="60">
         <v>13</v>
       </c>
@@ -11395,8 +11402,8 @@
       <c r="K344" s="40"/>
     </row>
     <row r="345" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A345" s="313"/>
-      <c r="B345" s="312"/>
+      <c r="A345" s="186"/>
+      <c r="B345" s="185"/>
       <c r="C345" s="60">
         <v>14</v>
       </c>
@@ -11412,8 +11419,8 @@
       <c r="K345" s="40"/>
     </row>
     <row r="346" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A346" s="313"/>
-      <c r="B346" s="312"/>
+      <c r="A346" s="186"/>
+      <c r="B346" s="185"/>
       <c r="C346" s="60">
         <v>15</v>
       </c>
@@ -11429,8 +11436,8 @@
       <c r="K346" s="40"/>
     </row>
     <row r="347" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A347" s="313"/>
-      <c r="B347" s="312"/>
+      <c r="A347" s="186"/>
+      <c r="B347" s="185"/>
       <c r="C347" s="60">
         <v>16</v>
       </c>
@@ -11446,8 +11453,8 @@
       <c r="K347" s="40"/>
     </row>
     <row r="348" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A348" s="313"/>
-      <c r="B348" s="312"/>
+      <c r="A348" s="186"/>
+      <c r="B348" s="185"/>
       <c r="C348" s="60">
         <v>17</v>
       </c>
@@ -11463,8 +11470,8 @@
       <c r="K348" s="40"/>
     </row>
     <row r="349" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A349" s="313"/>
-      <c r="B349" s="312"/>
+      <c r="A349" s="186"/>
+      <c r="B349" s="185"/>
       <c r="C349" s="60">
         <v>18</v>
       </c>
@@ -11480,8 +11487,8 @@
       <c r="K349" s="40"/>
     </row>
     <row r="350" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A350" s="313"/>
-      <c r="B350" s="312"/>
+      <c r="A350" s="186"/>
+      <c r="B350" s="185"/>
       <c r="C350" s="60">
         <v>19</v>
       </c>
@@ -11497,8 +11504,8 @@
       <c r="K350" s="40"/>
     </row>
     <row r="351" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A351" s="313"/>
-      <c r="B351" s="312"/>
+      <c r="A351" s="186"/>
+      <c r="B351" s="185"/>
       <c r="C351" s="60">
         <v>20</v>
       </c>
@@ -11514,8 +11521,8 @@
       <c r="K351" s="40"/>
     </row>
     <row r="352" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A352" s="313"/>
-      <c r="B352" s="312"/>
+      <c r="A352" s="186"/>
+      <c r="B352" s="185"/>
       <c r="C352" s="60">
         <v>21</v>
       </c>
@@ -11531,8 +11538,8 @@
       <c r="K352" s="40"/>
     </row>
     <row r="353" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A353" s="313"/>
-      <c r="B353" s="312"/>
+      <c r="A353" s="186"/>
+      <c r="B353" s="185"/>
       <c r="C353" s="60">
         <v>22</v>
       </c>
@@ -11548,8 +11555,8 @@
       <c r="K353" s="40"/>
     </row>
     <row r="354" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A354" s="313"/>
-      <c r="B354" s="312"/>
+      <c r="A354" s="186"/>
+      <c r="B354" s="185"/>
       <c r="C354" s="60">
         <v>23</v>
       </c>
@@ -11565,8 +11572,8 @@
       <c r="K354" s="40"/>
     </row>
     <row r="355" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A355" s="313"/>
-      <c r="B355" s="312"/>
+      <c r="A355" s="186"/>
+      <c r="B355" s="185"/>
       <c r="C355" s="60">
         <v>99</v>
       </c>
@@ -11582,10 +11589,10 @@
       <c r="K355" s="40"/>
     </row>
     <row r="356" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A356" s="319" t="s">
+      <c r="A356" s="193" t="s">
         <v>242</v>
       </c>
-      <c r="B356" s="283" t="s">
+      <c r="B356" s="214" t="s">
         <v>695</v>
       </c>
       <c r="C356" s="124">
@@ -11603,8 +11610,8 @@
       <c r="K356" s="40"/>
     </row>
     <row r="357" spans="1:11" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A357" s="320"/>
-      <c r="B357" s="284"/>
+      <c r="A357" s="194"/>
+      <c r="B357" s="243"/>
       <c r="C357" s="124">
         <v>2</v>
       </c>
@@ -11620,8 +11627,8 @@
       <c r="K357" s="40"/>
     </row>
     <row r="358" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A358" s="320"/>
-      <c r="B358" s="284"/>
+      <c r="A358" s="194"/>
+      <c r="B358" s="243"/>
       <c r="C358" s="124">
         <v>3</v>
       </c>
@@ -11637,8 +11644,8 @@
       <c r="K358" s="40"/>
     </row>
     <row r="359" spans="1:11" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A359" s="320"/>
-      <c r="B359" s="284"/>
+      <c r="A359" s="194"/>
+      <c r="B359" s="243"/>
       <c r="C359" s="124">
         <v>4</v>
       </c>
@@ -11654,8 +11661,8 @@
       <c r="K359" s="40"/>
     </row>
     <row r="360" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A360" s="320"/>
-      <c r="B360" s="284"/>
+      <c r="A360" s="194"/>
+      <c r="B360" s="243"/>
       <c r="C360" s="124">
         <v>5</v>
       </c>
@@ -11671,8 +11678,8 @@
       <c r="K360" s="40"/>
     </row>
     <row r="361" spans="1:11" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A361" s="320"/>
-      <c r="B361" s="284"/>
+      <c r="A361" s="194"/>
+      <c r="B361" s="243"/>
       <c r="C361" s="124">
         <v>6</v>
       </c>
@@ -11688,8 +11695,8 @@
       <c r="K361" s="40"/>
     </row>
     <row r="362" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A362" s="320"/>
-      <c r="B362" s="284"/>
+      <c r="A362" s="194"/>
+      <c r="B362" s="243"/>
       <c r="C362" s="124">
         <v>7</v>
       </c>
@@ -11705,8 +11712,8 @@
       <c r="K362" s="40"/>
     </row>
     <row r="363" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A363" s="320"/>
-      <c r="B363" s="284"/>
+      <c r="A363" s="194"/>
+      <c r="B363" s="243"/>
       <c r="C363" s="124">
         <v>8</v>
       </c>
@@ -11722,8 +11729,8 @@
       <c r="K363" s="40"/>
     </row>
     <row r="364" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A364" s="321"/>
-      <c r="B364" s="285"/>
+      <c r="A364" s="195"/>
+      <c r="B364" s="244"/>
       <c r="C364" s="125">
         <v>99</v>
       </c>
@@ -11935,25 +11942,25 @@
       <c r="K375" s="57"/>
     </row>
     <row r="376" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A376" s="209" t="s">
+      <c r="A376" s="170" t="s">
         <v>542</v>
       </c>
-      <c r="B376" s="290"/>
-      <c r="C376" s="291"/>
-      <c r="D376" s="210"/>
-      <c r="E376" s="291"/>
-      <c r="F376" s="291"/>
-      <c r="G376" s="291"/>
-      <c r="H376" s="291"/>
-      <c r="I376" s="291"/>
-      <c r="J376" s="291"/>
-      <c r="K376" s="292"/>
+      <c r="B376" s="249"/>
+      <c r="C376" s="250"/>
+      <c r="D376" s="171"/>
+      <c r="E376" s="250"/>
+      <c r="F376" s="250"/>
+      <c r="G376" s="250"/>
+      <c r="H376" s="250"/>
+      <c r="I376" s="250"/>
+      <c r="J376" s="250"/>
+      <c r="K376" s="251"/>
     </row>
     <row r="377" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A377" s="296" t="s">
+      <c r="A377" s="215" t="s">
         <v>422</v>
       </c>
-      <c r="B377" s="295" t="s">
+      <c r="B377" s="213" t="s">
         <v>672</v>
       </c>
       <c r="C377" s="65">
@@ -11971,8 +11978,8 @@
       <c r="K377" s="69"/>
     </row>
     <row r="378" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A378" s="296"/>
-      <c r="B378" s="295"/>
+      <c r="A378" s="215"/>
+      <c r="B378" s="213"/>
       <c r="C378" s="65">
         <v>2</v>
       </c>
@@ -11988,8 +11995,8 @@
       <c r="K378" s="69"/>
     </row>
     <row r="379" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A379" s="296"/>
-      <c r="B379" s="295"/>
+      <c r="A379" s="215"/>
+      <c r="B379" s="213"/>
       <c r="C379" s="65">
         <v>3</v>
       </c>
@@ -12005,8 +12012,8 @@
       <c r="K379" s="69"/>
     </row>
     <row r="380" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A380" s="296"/>
-      <c r="B380" s="295"/>
+      <c r="A380" s="215"/>
+      <c r="B380" s="213"/>
       <c r="C380" s="65">
         <v>4</v>
       </c>
@@ -12022,8 +12029,8 @@
       <c r="K380" s="69"/>
     </row>
     <row r="381" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A381" s="296"/>
-      <c r="B381" s="295"/>
+      <c r="A381" s="215"/>
+      <c r="B381" s="213"/>
       <c r="C381" s="65">
         <v>5</v>
       </c>
@@ -12039,8 +12046,8 @@
       <c r="K381" s="69"/>
     </row>
     <row r="382" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A382" s="296"/>
-      <c r="B382" s="295"/>
+      <c r="A382" s="215"/>
+      <c r="B382" s="213"/>
       <c r="C382" s="65">
         <v>6</v>
       </c>
@@ -12056,8 +12063,8 @@
       <c r="K382" s="69"/>
     </row>
     <row r="383" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A383" s="296"/>
-      <c r="B383" s="295"/>
+      <c r="A383" s="215"/>
+      <c r="B383" s="213"/>
       <c r="C383" s="65">
         <v>98</v>
       </c>
@@ -12073,8 +12080,8 @@
       <c r="K383" s="69"/>
     </row>
     <row r="384" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A384" s="296"/>
-      <c r="B384" s="283"/>
+      <c r="A384" s="215"/>
+      <c r="B384" s="214"/>
       <c r="C384" s="105">
         <v>99</v>
       </c>
@@ -12090,10 +12097,10 @@
       <c r="K384" s="69"/>
     </row>
     <row r="385" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A385" s="298" t="s">
+      <c r="A385" s="217" t="s">
         <v>424</v>
       </c>
-      <c r="B385" s="297" t="s">
+      <c r="B385" s="216" t="s">
         <v>493</v>
       </c>
       <c r="C385" s="65">
@@ -12111,8 +12118,8 @@
       <c r="K385" s="69"/>
     </row>
     <row r="386" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A386" s="299"/>
-      <c r="B386" s="297"/>
+      <c r="A386" s="218"/>
+      <c r="B386" s="216"/>
       <c r="C386" s="65">
         <v>2</v>
       </c>
@@ -12128,8 +12135,8 @@
       <c r="K386" s="69"/>
     </row>
     <row r="387" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A387" s="299"/>
-      <c r="B387" s="297"/>
+      <c r="A387" s="218"/>
+      <c r="B387" s="216"/>
       <c r="C387" s="65">
         <v>3</v>
       </c>
@@ -12145,8 +12152,8 @@
       <c r="K387" s="69"/>
     </row>
     <row r="388" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A388" s="299"/>
-      <c r="B388" s="297"/>
+      <c r="A388" s="218"/>
+      <c r="B388" s="216"/>
       <c r="C388" s="65">
         <v>4</v>
       </c>
@@ -12162,8 +12169,8 @@
       <c r="K388" s="69"/>
     </row>
     <row r="389" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A389" s="300"/>
-      <c r="B389" s="297"/>
+      <c r="A389" s="219"/>
+      <c r="B389" s="216"/>
       <c r="C389" s="65">
         <v>5</v>
       </c>
@@ -12179,10 +12186,10 @@
       <c r="K389" s="69"/>
     </row>
     <row r="390" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A390" s="298" t="s">
+      <c r="A390" s="217" t="s">
         <v>425</v>
       </c>
-      <c r="B390" s="301" t="s">
+      <c r="B390" s="220" t="s">
         <v>674</v>
       </c>
       <c r="C390" s="65">
@@ -12200,8 +12207,8 @@
       <c r="K390" s="69"/>
     </row>
     <row r="391" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A391" s="299"/>
-      <c r="B391" s="302"/>
+      <c r="A391" s="218"/>
+      <c r="B391" s="221"/>
       <c r="C391" s="73">
         <v>2</v>
       </c>
@@ -12219,8 +12226,8 @@
       <c r="K391" s="69"/>
     </row>
     <row r="392" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A392" s="299"/>
-      <c r="B392" s="302"/>
+      <c r="A392" s="218"/>
+      <c r="B392" s="221"/>
       <c r="C392" s="73">
         <v>3</v>
       </c>
@@ -12236,8 +12243,8 @@
       <c r="K392" s="69"/>
     </row>
     <row r="393" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A393" s="299"/>
-      <c r="B393" s="302"/>
+      <c r="A393" s="218"/>
+      <c r="B393" s="221"/>
       <c r="C393" s="73">
         <v>4</v>
       </c>
@@ -12253,8 +12260,8 @@
       <c r="K393" s="69"/>
     </row>
     <row r="394" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A394" s="299"/>
-      <c r="B394" s="302"/>
+      <c r="A394" s="218"/>
+      <c r="B394" s="221"/>
       <c r="C394" s="73">
         <v>6</v>
       </c>
@@ -12272,8 +12279,8 @@
       <c r="K394" s="69"/>
     </row>
     <row r="395" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A395" s="299"/>
-      <c r="B395" s="302"/>
+      <c r="A395" s="218"/>
+      <c r="B395" s="221"/>
       <c r="C395" s="73">
         <v>7</v>
       </c>
@@ -12291,8 +12298,8 @@
       <c r="K395" s="69"/>
     </row>
     <row r="396" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A396" s="299"/>
-      <c r="B396" s="302"/>
+      <c r="A396" s="218"/>
+      <c r="B396" s="221"/>
       <c r="C396" s="73">
         <v>8</v>
       </c>
@@ -12310,8 +12317,8 @@
       <c r="K396" s="69"/>
     </row>
     <row r="397" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A397" s="299"/>
-      <c r="B397" s="302"/>
+      <c r="A397" s="218"/>
+      <c r="B397" s="221"/>
       <c r="C397" s="73">
         <v>11</v>
       </c>
@@ -12327,8 +12334,8 @@
       <c r="K397" s="69"/>
     </row>
     <row r="398" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A398" s="299"/>
-      <c r="B398" s="302"/>
+      <c r="A398" s="218"/>
+      <c r="B398" s="221"/>
       <c r="C398" s="73">
         <v>12</v>
       </c>
@@ -12344,8 +12351,8 @@
       <c r="K398" s="69"/>
     </row>
     <row r="399" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A399" s="299"/>
-      <c r="B399" s="302"/>
+      <c r="A399" s="218"/>
+      <c r="B399" s="221"/>
       <c r="C399" s="73">
         <v>13</v>
       </c>
@@ -12361,8 +12368,8 @@
       <c r="K399" s="69"/>
     </row>
     <row r="400" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A400" s="299"/>
-      <c r="B400" s="302"/>
+      <c r="A400" s="218"/>
+      <c r="B400" s="221"/>
       <c r="C400" s="73">
         <v>14</v>
       </c>
@@ -12378,8 +12385,8 @@
       <c r="K400" s="69"/>
     </row>
     <row r="401" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A401" s="299"/>
-      <c r="B401" s="302"/>
+      <c r="A401" s="218"/>
+      <c r="B401" s="221"/>
       <c r="C401" s="73">
         <v>15</v>
       </c>
@@ -12395,8 +12402,8 @@
       <c r="K401" s="69"/>
     </row>
     <row r="402" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A402" s="299"/>
-      <c r="B402" s="302"/>
+      <c r="A402" s="218"/>
+      <c r="B402" s="221"/>
       <c r="C402" s="73">
         <v>16</v>
       </c>
@@ -12412,8 +12419,8 @@
       <c r="K402" s="69"/>
     </row>
     <row r="403" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A403" s="299"/>
-      <c r="B403" s="302"/>
+      <c r="A403" s="218"/>
+      <c r="B403" s="221"/>
       <c r="C403" s="73">
         <v>18</v>
       </c>
@@ -12429,8 +12436,8 @@
       <c r="K403" s="69"/>
     </row>
     <row r="404" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A404" s="299"/>
-      <c r="B404" s="302"/>
+      <c r="A404" s="218"/>
+      <c r="B404" s="221"/>
       <c r="C404" s="73">
         <v>20</v>
       </c>
@@ -12446,8 +12453,8 @@
       <c r="K404" s="69"/>
     </row>
     <row r="405" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A405" s="299"/>
-      <c r="B405" s="302"/>
+      <c r="A405" s="218"/>
+      <c r="B405" s="221"/>
       <c r="C405" s="73">
         <v>23</v>
       </c>
@@ -12463,8 +12470,8 @@
       <c r="K405" s="69"/>
     </row>
     <row r="406" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A406" s="299"/>
-      <c r="B406" s="302"/>
+      <c r="A406" s="218"/>
+      <c r="B406" s="221"/>
       <c r="C406" s="73">
         <v>24</v>
       </c>
@@ -12480,10 +12487,10 @@
       <c r="K406" s="69"/>
     </row>
     <row r="407" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A407" s="303" t="s">
+      <c r="A407" s="222" t="s">
         <v>243</v>
       </c>
-      <c r="B407" s="301" t="s">
+      <c r="B407" s="220" t="s">
         <v>623</v>
       </c>
       <c r="C407" s="73">
@@ -12503,8 +12510,8 @@
       <c r="K407" s="69"/>
     </row>
     <row r="408" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A408" s="304"/>
-      <c r="B408" s="302"/>
+      <c r="A408" s="223"/>
+      <c r="B408" s="221"/>
       <c r="C408" s="73">
         <v>1</v>
       </c>
@@ -12522,8 +12529,8 @@
       <c r="K408" s="69"/>
     </row>
     <row r="409" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A409" s="304"/>
-      <c r="B409" s="302"/>
+      <c r="A409" s="223"/>
+      <c r="B409" s="221"/>
       <c r="C409" s="73">
         <v>2</v>
       </c>
@@ -12539,8 +12546,8 @@
       <c r="K409" s="69"/>
     </row>
     <row r="410" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A410" s="304"/>
-      <c r="B410" s="302"/>
+      <c r="A410" s="223"/>
+      <c r="B410" s="221"/>
       <c r="C410" s="73">
         <v>3</v>
       </c>
@@ -12556,8 +12563,8 @@
       <c r="K410" s="69"/>
     </row>
     <row r="411" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A411" s="304"/>
-      <c r="B411" s="302"/>
+      <c r="A411" s="223"/>
+      <c r="B411" s="221"/>
       <c r="C411" s="65">
         <v>4</v>
       </c>
@@ -12573,8 +12580,8 @@
       <c r="K411" s="69"/>
     </row>
     <row r="412" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A412" s="304"/>
-      <c r="B412" s="302"/>
+      <c r="A412" s="223"/>
+      <c r="B412" s="221"/>
       <c r="C412" s="65">
         <v>5</v>
       </c>
@@ -12590,8 +12597,8 @@
       <c r="K412" s="69"/>
     </row>
     <row r="413" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A413" s="304"/>
-      <c r="B413" s="302"/>
+      <c r="A413" s="223"/>
+      <c r="B413" s="221"/>
       <c r="C413" s="65">
         <v>6</v>
       </c>
@@ -12607,8 +12614,8 @@
       <c r="K413" s="69"/>
     </row>
     <row r="414" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A414" s="304"/>
-      <c r="B414" s="302"/>
+      <c r="A414" s="223"/>
+      <c r="B414" s="221"/>
       <c r="C414" s="65">
         <v>7</v>
       </c>
@@ -12624,8 +12631,8 @@
       <c r="K414" s="69"/>
     </row>
     <row r="415" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A415" s="304"/>
-      <c r="B415" s="302"/>
+      <c r="A415" s="223"/>
+      <c r="B415" s="221"/>
       <c r="C415" s="65">
         <v>8</v>
       </c>
@@ -12641,8 +12648,8 @@
       <c r="K415" s="69"/>
     </row>
     <row r="416" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A416" s="304"/>
-      <c r="B416" s="302"/>
+      <c r="A416" s="223"/>
+      <c r="B416" s="221"/>
       <c r="C416" s="65">
         <v>9</v>
       </c>
@@ -12658,8 +12665,8 @@
       <c r="K416" s="69"/>
     </row>
     <row r="417" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A417" s="304"/>
-      <c r="B417" s="302"/>
+      <c r="A417" s="223"/>
+      <c r="B417" s="221"/>
       <c r="C417" s="65">
         <v>10</v>
       </c>
@@ -12675,8 +12682,8 @@
       <c r="K417" s="69"/>
     </row>
     <row r="418" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A418" s="304"/>
-      <c r="B418" s="302"/>
+      <c r="A418" s="223"/>
+      <c r="B418" s="221"/>
       <c r="C418" s="65">
         <v>11</v>
       </c>
@@ -12692,8 +12699,8 @@
       <c r="K418" s="69"/>
     </row>
     <row r="419" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A419" s="304"/>
-      <c r="B419" s="302"/>
+      <c r="A419" s="223"/>
+      <c r="B419" s="221"/>
       <c r="C419" s="65">
         <v>12</v>
       </c>
@@ -12709,8 +12716,8 @@
       <c r="K419" s="69"/>
     </row>
     <row r="420" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A420" s="304"/>
-      <c r="B420" s="302"/>
+      <c r="A420" s="223"/>
+      <c r="B420" s="221"/>
       <c r="C420" s="65">
         <v>13</v>
       </c>
@@ -12726,8 +12733,8 @@
       <c r="K420" s="69"/>
     </row>
     <row r="421" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A421" s="304"/>
-      <c r="B421" s="302"/>
+      <c r="A421" s="223"/>
+      <c r="B421" s="221"/>
       <c r="C421" s="65">
         <v>14</v>
       </c>
@@ -12743,8 +12750,8 @@
       <c r="K421" s="69"/>
     </row>
     <row r="422" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A422" s="304"/>
-      <c r="B422" s="302"/>
+      <c r="A422" s="223"/>
+      <c r="B422" s="221"/>
       <c r="C422" s="65">
         <v>15</v>
       </c>
@@ -12760,25 +12767,25 @@
       <c r="K422" s="69"/>
     </row>
     <row r="423" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A423" s="288" t="s">
+      <c r="A423" s="247" t="s">
         <v>541</v>
       </c>
-      <c r="B423" s="293"/>
-      <c r="C423" s="293"/>
-      <c r="D423" s="293"/>
-      <c r="E423" s="293"/>
-      <c r="F423" s="293"/>
-      <c r="G423" s="293"/>
-      <c r="H423" s="293"/>
-      <c r="I423" s="293"/>
-      <c r="J423" s="293"/>
-      <c r="K423" s="294"/>
+      <c r="B423" s="252"/>
+      <c r="C423" s="252"/>
+      <c r="D423" s="252"/>
+      <c r="E423" s="252"/>
+      <c r="F423" s="252"/>
+      <c r="G423" s="252"/>
+      <c r="H423" s="252"/>
+      <c r="I423" s="252"/>
+      <c r="J423" s="252"/>
+      <c r="K423" s="253"/>
     </row>
     <row r="424" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A424" s="206" t="s">
+      <c r="A424" s="187" t="s">
         <v>426</v>
       </c>
-      <c r="B424" s="297" t="s">
+      <c r="B424" s="216" t="s">
         <v>651</v>
       </c>
       <c r="C424" s="65">
@@ -12796,8 +12803,8 @@
       <c r="K424" s="57"/>
     </row>
     <row r="425" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A425" s="206"/>
-      <c r="B425" s="297"/>
+      <c r="A425" s="187"/>
+      <c r="B425" s="216"/>
       <c r="C425" s="65">
         <v>2</v>
       </c>
@@ -12813,8 +12820,8 @@
       <c r="K425" s="57"/>
     </row>
     <row r="426" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A426" s="206"/>
-      <c r="B426" s="297"/>
+      <c r="A426" s="187"/>
+      <c r="B426" s="216"/>
       <c r="C426" s="65">
         <v>3</v>
       </c>
@@ -12830,8 +12837,8 @@
       <c r="K426" s="57"/>
     </row>
     <row r="427" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A427" s="206"/>
-      <c r="B427" s="297"/>
+      <c r="A427" s="187"/>
+      <c r="B427" s="216"/>
       <c r="C427" s="65">
         <v>4</v>
       </c>
@@ -12847,8 +12854,8 @@
       <c r="K427" s="57"/>
     </row>
     <row r="428" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A428" s="206"/>
-      <c r="B428" s="297"/>
+      <c r="A428" s="187"/>
+      <c r="B428" s="216"/>
       <c r="C428" s="65">
         <v>5</v>
       </c>
@@ -12864,8 +12871,8 @@
       <c r="K428" s="57"/>
     </row>
     <row r="429" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A429" s="206"/>
-      <c r="B429" s="297"/>
+      <c r="A429" s="187"/>
+      <c r="B429" s="216"/>
       <c r="C429" s="65">
         <v>6</v>
       </c>
@@ -12881,8 +12888,8 @@
       <c r="K429" s="57"/>
     </row>
     <row r="430" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A430" s="206"/>
-      <c r="B430" s="297"/>
+      <c r="A430" s="187"/>
+      <c r="B430" s="216"/>
       <c r="C430" s="65">
         <v>99</v>
       </c>
@@ -12898,19 +12905,19 @@
       <c r="K430" s="57"/>
     </row>
     <row r="431" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A431" s="288" t="s">
+      <c r="A431" s="247" t="s">
         <v>540</v>
       </c>
-      <c r="B431" s="289"/>
-      <c r="C431" s="289"/>
-      <c r="D431" s="289"/>
-      <c r="E431" s="210"/>
-      <c r="F431" s="210"/>
-      <c r="G431" s="210"/>
-      <c r="H431" s="210"/>
-      <c r="I431" s="210"/>
-      <c r="J431" s="210"/>
-      <c r="K431" s="211"/>
+      <c r="B431" s="248"/>
+      <c r="C431" s="248"/>
+      <c r="D431" s="248"/>
+      <c r="E431" s="171"/>
+      <c r="F431" s="171"/>
+      <c r="G431" s="171"/>
+      <c r="H431" s="171"/>
+      <c r="I431" s="171"/>
+      <c r="J431" s="171"/>
+      <c r="K431" s="172"/>
     </row>
     <row r="432" spans="1:11" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A432" s="59" t="s">
@@ -12955,25 +12962,25 @@
       <c r="K433" s="40"/>
     </row>
     <row r="434" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A434" s="174" t="s">
+      <c r="A434" s="290" t="s">
         <v>539</v>
       </c>
-      <c r="B434" s="203"/>
-      <c r="C434" s="203"/>
-      <c r="D434" s="203"/>
-      <c r="E434" s="203"/>
-      <c r="F434" s="203"/>
-      <c r="G434" s="203"/>
-      <c r="H434" s="203"/>
-      <c r="I434" s="203"/>
-      <c r="J434" s="203"/>
-      <c r="K434" s="204"/>
+      <c r="B434" s="291"/>
+      <c r="C434" s="291"/>
+      <c r="D434" s="291"/>
+      <c r="E434" s="291"/>
+      <c r="F434" s="291"/>
+      <c r="G434" s="291"/>
+      <c r="H434" s="291"/>
+      <c r="I434" s="291"/>
+      <c r="J434" s="291"/>
+      <c r="K434" s="292"/>
     </row>
     <row r="435" spans="1:11" ht="85.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A435" s="205" t="s">
+      <c r="A435" s="203" t="s">
         <v>534</v>
       </c>
-      <c r="B435" s="286" t="s">
+      <c r="B435" s="208" t="s">
         <v>699</v>
       </c>
       <c r="C435" s="38">
@@ -12997,8 +13004,8 @@
       <c r="K435" s="40"/>
     </row>
     <row r="436" spans="1:11" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A436" s="202"/>
-      <c r="B436" s="287"/>
+      <c r="A436" s="246"/>
+      <c r="B436" s="245"/>
       <c r="C436" s="76">
         <v>2</v>
       </c>
@@ -13014,8 +13021,8 @@
       <c r="K436" s="40"/>
     </row>
     <row r="437" spans="1:11" ht="172.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A437" s="202"/>
-      <c r="B437" s="287"/>
+      <c r="A437" s="246"/>
+      <c r="B437" s="245"/>
       <c r="C437" s="76">
         <v>98</v>
       </c>
@@ -13031,10 +13038,10 @@
       <c r="K437" s="40"/>
     </row>
     <row r="438" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A438" s="187" t="s">
+      <c r="A438" s="179" t="s">
         <v>536</v>
       </c>
-      <c r="B438" s="207" t="s">
+      <c r="B438" s="200" t="s">
         <v>686</v>
       </c>
       <c r="C438" s="38">
@@ -13044,10 +13051,10 @@
         <v>691</v>
       </c>
       <c r="E438" s="40"/>
-      <c r="F438" s="307" t="s">
+      <c r="F438" s="176" t="s">
         <v>169</v>
       </c>
-      <c r="G438" s="307" t="s">
+      <c r="G438" s="176" t="s">
         <v>170</v>
       </c>
       <c r="H438" s="40"/>
@@ -13056,8 +13063,8 @@
       <c r="K438" s="40"/>
     </row>
     <row r="439" spans="1:11" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A439" s="322"/>
-      <c r="B439" s="323"/>
+      <c r="A439" s="199"/>
+      <c r="B439" s="201"/>
       <c r="C439" s="38">
         <v>2</v>
       </c>
@@ -13067,8 +13074,8 @@
       <c r="E439" s="140" t="s">
         <v>652</v>
       </c>
-      <c r="F439" s="308"/>
-      <c r="G439" s="308" t="s">
+      <c r="F439" s="177"/>
+      <c r="G439" s="177" t="s">
         <v>170</v>
       </c>
       <c r="H439" s="40"/>
@@ -13077,8 +13084,8 @@
       <c r="K439" s="40"/>
     </row>
     <row r="440" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A440" s="322"/>
-      <c r="B440" s="323"/>
+      <c r="A440" s="199"/>
+      <c r="B440" s="201"/>
       <c r="C440" s="38">
         <v>2</v>
       </c>
@@ -13086,8 +13093,8 @@
         <v>244</v>
       </c>
       <c r="E440" s="40"/>
-      <c r="F440" s="308"/>
-      <c r="G440" s="308" t="s">
+      <c r="F440" s="177"/>
+      <c r="G440" s="177" t="s">
         <v>170</v>
       </c>
       <c r="H440" s="40"/>
@@ -13096,8 +13103,8 @@
       <c r="K440" s="40"/>
     </row>
     <row r="441" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A441" s="322"/>
-      <c r="B441" s="323"/>
+      <c r="A441" s="199"/>
+      <c r="B441" s="201"/>
       <c r="C441" s="38">
         <v>3</v>
       </c>
@@ -13105,16 +13112,16 @@
         <v>681</v>
       </c>
       <c r="E441" s="40"/>
-      <c r="F441" s="308"/>
-      <c r="G441" s="308"/>
+      <c r="F441" s="177"/>
+      <c r="G441" s="177"/>
       <c r="H441" s="40"/>
       <c r="I441" s="40"/>
       <c r="J441" s="40"/>
       <c r="K441" s="40"/>
     </row>
     <row r="442" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A442" s="322"/>
-      <c r="B442" s="323"/>
+      <c r="A442" s="199"/>
+      <c r="B442" s="201"/>
       <c r="C442" s="38">
         <v>4</v>
       </c>
@@ -13122,16 +13129,16 @@
         <v>684</v>
       </c>
       <c r="E442" s="40"/>
-      <c r="F442" s="308"/>
-      <c r="G442" s="308"/>
+      <c r="F442" s="177"/>
+      <c r="G442" s="177"/>
       <c r="H442" s="40"/>
       <c r="I442" s="40"/>
       <c r="J442" s="40"/>
       <c r="K442" s="40"/>
     </row>
     <row r="443" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A443" s="322"/>
-      <c r="B443" s="323"/>
+      <c r="A443" s="199"/>
+      <c r="B443" s="201"/>
       <c r="C443" s="38">
         <v>5</v>
       </c>
@@ -13139,16 +13146,16 @@
         <v>685</v>
       </c>
       <c r="E443" s="40"/>
-      <c r="F443" s="308"/>
-      <c r="G443" s="308"/>
+      <c r="F443" s="177"/>
+      <c r="G443" s="177"/>
       <c r="H443" s="40"/>
       <c r="I443" s="40"/>
       <c r="J443" s="40"/>
       <c r="K443" s="40"/>
     </row>
     <row r="444" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A444" s="322"/>
-      <c r="B444" s="323"/>
+      <c r="A444" s="199"/>
+      <c r="B444" s="201"/>
       <c r="C444" s="38">
         <v>6</v>
       </c>
@@ -13156,8 +13163,8 @@
         <v>682</v>
       </c>
       <c r="E444" s="40"/>
-      <c r="F444" s="308"/>
-      <c r="G444" s="308" t="s">
+      <c r="F444" s="177"/>
+      <c r="G444" s="177" t="s">
         <v>170</v>
       </c>
       <c r="H444" s="40"/>
@@ -13166,8 +13173,8 @@
       <c r="K444" s="40"/>
     </row>
     <row r="445" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A445" s="322"/>
-      <c r="B445" s="323"/>
+      <c r="A445" s="199"/>
+      <c r="B445" s="201"/>
       <c r="C445" s="38">
         <v>7</v>
       </c>
@@ -13175,8 +13182,8 @@
         <v>683</v>
       </c>
       <c r="E445" s="40"/>
-      <c r="F445" s="308"/>
-      <c r="G445" s="308" t="s">
+      <c r="F445" s="177"/>
+      <c r="G445" s="177" t="s">
         <v>170</v>
       </c>
       <c r="H445" s="40"/>
@@ -13185,8 +13192,8 @@
       <c r="K445" s="40"/>
     </row>
     <row r="446" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A446" s="322"/>
-      <c r="B446" s="323"/>
+      <c r="A446" s="199"/>
+      <c r="B446" s="201"/>
       <c r="C446" s="38">
         <v>8</v>
       </c>
@@ -13194,8 +13201,8 @@
         <v>245</v>
       </c>
       <c r="E446" s="40"/>
-      <c r="F446" s="308"/>
-      <c r="G446" s="308" t="s">
+      <c r="F446" s="177"/>
+      <c r="G446" s="177" t="s">
         <v>170</v>
       </c>
       <c r="H446" s="40"/>
@@ -13204,8 +13211,8 @@
       <c r="K446" s="40"/>
     </row>
     <row r="447" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A447" s="322"/>
-      <c r="B447" s="323"/>
+      <c r="A447" s="199"/>
+      <c r="B447" s="201"/>
       <c r="C447" s="38">
         <v>9</v>
       </c>
@@ -13213,8 +13220,8 @@
         <v>246</v>
       </c>
       <c r="E447" s="40"/>
-      <c r="F447" s="308"/>
-      <c r="G447" s="308" t="s">
+      <c r="F447" s="177"/>
+      <c r="G447" s="177" t="s">
         <v>170</v>
       </c>
       <c r="H447" s="40"/>
@@ -13223,8 +13230,8 @@
       <c r="K447" s="40"/>
     </row>
     <row r="448" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A448" s="322"/>
-      <c r="B448" s="323"/>
+      <c r="A448" s="199"/>
+      <c r="B448" s="201"/>
       <c r="C448" s="38">
         <v>10</v>
       </c>
@@ -13232,8 +13239,8 @@
         <v>247</v>
       </c>
       <c r="E448" s="40"/>
-      <c r="F448" s="308"/>
-      <c r="G448" s="308" t="s">
+      <c r="F448" s="177"/>
+      <c r="G448" s="177" t="s">
         <v>170</v>
       </c>
       <c r="H448" s="40"/>
@@ -13242,8 +13249,8 @@
       <c r="K448" s="40"/>
     </row>
     <row r="449" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A449" s="322"/>
-      <c r="B449" s="323"/>
+      <c r="A449" s="199"/>
+      <c r="B449" s="201"/>
       <c r="C449" s="38">
         <v>11</v>
       </c>
@@ -13251,8 +13258,8 @@
         <v>248</v>
       </c>
       <c r="E449" s="40"/>
-      <c r="F449" s="308"/>
-      <c r="G449" s="308" t="s">
+      <c r="F449" s="177"/>
+      <c r="G449" s="177" t="s">
         <v>170</v>
       </c>
       <c r="H449" s="40"/>
@@ -13261,8 +13268,8 @@
       <c r="K449" s="40"/>
     </row>
     <row r="450" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A450" s="322"/>
-      <c r="B450" s="323"/>
+      <c r="A450" s="199"/>
+      <c r="B450" s="201"/>
       <c r="C450" s="38">
         <v>12</v>
       </c>
@@ -13270,8 +13277,8 @@
         <v>249</v>
       </c>
       <c r="E450" s="40"/>
-      <c r="F450" s="308"/>
-      <c r="G450" s="308" t="s">
+      <c r="F450" s="177"/>
+      <c r="G450" s="177" t="s">
         <v>170</v>
       </c>
       <c r="H450" s="40"/>
@@ -13280,8 +13287,8 @@
       <c r="K450" s="40"/>
     </row>
     <row r="451" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A451" s="322"/>
-      <c r="B451" s="323"/>
+      <c r="A451" s="199"/>
+      <c r="B451" s="201"/>
       <c r="C451" s="38">
         <v>13</v>
       </c>
@@ -13289,8 +13296,8 @@
         <v>250</v>
       </c>
       <c r="E451" s="40"/>
-      <c r="F451" s="308"/>
-      <c r="G451" s="308" t="s">
+      <c r="F451" s="177"/>
+      <c r="G451" s="177" t="s">
         <v>170</v>
       </c>
       <c r="H451" s="40"/>
@@ -13299,8 +13306,8 @@
       <c r="K451" s="40"/>
     </row>
     <row r="452" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A452" s="322"/>
-      <c r="B452" s="323"/>
+      <c r="A452" s="199"/>
+      <c r="B452" s="201"/>
       <c r="C452" s="38">
         <v>14</v>
       </c>
@@ -13308,8 +13315,8 @@
         <v>251</v>
       </c>
       <c r="E452" s="40"/>
-      <c r="F452" s="308"/>
-      <c r="G452" s="308" t="s">
+      <c r="F452" s="177"/>
+      <c r="G452" s="177" t="s">
         <v>170</v>
       </c>
       <c r="H452" s="40"/>
@@ -13318,8 +13325,8 @@
       <c r="K452" s="40"/>
     </row>
     <row r="453" spans="1:11" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A453" s="322"/>
-      <c r="B453" s="323"/>
+      <c r="A453" s="199"/>
+      <c r="B453" s="201"/>
       <c r="C453" s="38">
         <v>16</v>
       </c>
@@ -13327,8 +13334,8 @@
         <v>654</v>
       </c>
       <c r="E453" s="40"/>
-      <c r="F453" s="308"/>
-      <c r="G453" s="308" t="s">
+      <c r="F453" s="177"/>
+      <c r="G453" s="177" t="s">
         <v>170</v>
       </c>
       <c r="H453" s="40"/>
@@ -13337,8 +13344,8 @@
       <c r="K453" s="40"/>
     </row>
     <row r="454" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A454" s="322"/>
-      <c r="B454" s="323"/>
+      <c r="A454" s="199"/>
+      <c r="B454" s="201"/>
       <c r="C454" s="38">
         <v>15</v>
       </c>
@@ -13346,8 +13353,8 @@
         <v>687</v>
       </c>
       <c r="E454" s="40"/>
-      <c r="F454" s="308"/>
-      <c r="G454" s="308" t="s">
+      <c r="F454" s="177"/>
+      <c r="G454" s="177" t="s">
         <v>170</v>
       </c>
       <c r="H454" s="40"/>
@@ -13356,8 +13363,8 @@
       <c r="K454" s="40"/>
     </row>
     <row r="455" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A455" s="322"/>
-      <c r="B455" s="323"/>
+      <c r="A455" s="199"/>
+      <c r="B455" s="201"/>
       <c r="C455" s="38">
         <v>16</v>
       </c>
@@ -13365,8 +13372,8 @@
         <v>252</v>
       </c>
       <c r="E455" s="40"/>
-      <c r="F455" s="308"/>
-      <c r="G455" s="308" t="s">
+      <c r="F455" s="177"/>
+      <c r="G455" s="177" t="s">
         <v>170</v>
       </c>
       <c r="H455" s="40"/>
@@ -13375,8 +13382,8 @@
       <c r="K455" s="40"/>
     </row>
     <row r="456" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A456" s="322"/>
-      <c r="B456" s="323"/>
+      <c r="A456" s="199"/>
+      <c r="B456" s="201"/>
       <c r="C456" s="38">
         <v>17</v>
       </c>
@@ -13384,8 +13391,8 @@
         <v>253</v>
       </c>
       <c r="E456" s="40"/>
-      <c r="F456" s="308"/>
-      <c r="G456" s="308" t="s">
+      <c r="F456" s="177"/>
+      <c r="G456" s="177" t="s">
         <v>170</v>
       </c>
       <c r="H456" s="40"/>
@@ -13394,8 +13401,8 @@
       <c r="K456" s="40"/>
     </row>
     <row r="457" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A457" s="322"/>
-      <c r="B457" s="323"/>
+      <c r="A457" s="199"/>
+      <c r="B457" s="201"/>
       <c r="C457" s="38">
         <v>18</v>
       </c>
@@ -13403,8 +13410,8 @@
         <v>254</v>
       </c>
       <c r="E457" s="40"/>
-      <c r="F457" s="308"/>
-      <c r="G457" s="308" t="s">
+      <c r="F457" s="177"/>
+      <c r="G457" s="177" t="s">
         <v>170</v>
       </c>
       <c r="H457" s="40"/>
@@ -13413,8 +13420,8 @@
       <c r="K457" s="40"/>
     </row>
     <row r="458" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A458" s="322"/>
-      <c r="B458" s="323"/>
+      <c r="A458" s="199"/>
+      <c r="B458" s="201"/>
       <c r="C458" s="38">
         <v>19</v>
       </c>
@@ -13422,8 +13429,8 @@
         <v>255</v>
       </c>
       <c r="E458" s="40"/>
-      <c r="F458" s="308"/>
-      <c r="G458" s="308" t="s">
+      <c r="F458" s="177"/>
+      <c r="G458" s="177" t="s">
         <v>170</v>
       </c>
       <c r="H458" s="40"/>
@@ -13432,8 +13439,8 @@
       <c r="K458" s="40"/>
     </row>
     <row r="459" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A459" s="310"/>
-      <c r="B459" s="208"/>
+      <c r="A459" s="180"/>
+      <c r="B459" s="202"/>
       <c r="C459" s="148">
         <v>99</v>
       </c>
@@ -13441,8 +13448,8 @@
         <v>626</v>
       </c>
       <c r="E459" s="131"/>
-      <c r="F459" s="309"/>
-      <c r="G459" s="309" t="s">
+      <c r="F459" s="178"/>
+      <c r="G459" s="178" t="s">
         <v>170</v>
       </c>
       <c r="H459" s="40"/>
@@ -13451,10 +13458,10 @@
       <c r="K459" s="40"/>
     </row>
     <row r="460" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A460" s="187" t="s">
+      <c r="A460" s="179" t="s">
         <v>624</v>
       </c>
-      <c r="B460" s="179" t="s">
+      <c r="B460" s="196" t="s">
         <v>256</v>
       </c>
       <c r="C460" s="38">
@@ -13472,8 +13479,8 @@
       <c r="K460" s="40"/>
     </row>
     <row r="461" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A461" s="322"/>
-      <c r="B461" s="185"/>
+      <c r="A461" s="199"/>
+      <c r="B461" s="197"/>
       <c r="C461" s="38">
         <v>2</v>
       </c>
@@ -13489,8 +13496,8 @@
       <c r="K461" s="40"/>
     </row>
     <row r="462" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A462" s="322"/>
-      <c r="B462" s="185"/>
+      <c r="A462" s="199"/>
+      <c r="B462" s="197"/>
       <c r="C462" s="38">
         <v>3</v>
       </c>
@@ -13506,8 +13513,8 @@
       <c r="K462" s="40"/>
     </row>
     <row r="463" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A463" s="322"/>
-      <c r="B463" s="185"/>
+      <c r="A463" s="199"/>
+      <c r="B463" s="197"/>
       <c r="C463" s="38">
         <v>4</v>
       </c>
@@ -13523,8 +13530,8 @@
       <c r="K463" s="40"/>
     </row>
     <row r="464" spans="1:11" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A464" s="322"/>
-      <c r="B464" s="185"/>
+      <c r="A464" s="199"/>
+      <c r="B464" s="197"/>
       <c r="C464" s="38">
         <v>5</v>
       </c>
@@ -13540,8 +13547,8 @@
       <c r="K464" s="40"/>
     </row>
     <row r="465" spans="1:11" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A465" s="322"/>
-      <c r="B465" s="185"/>
+      <c r="A465" s="199"/>
+      <c r="B465" s="197"/>
       <c r="C465" s="38">
         <v>6</v>
       </c>
@@ -13561,8 +13568,8 @@
       <c r="K465" s="40"/>
     </row>
     <row r="466" spans="1:11" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A466" s="322"/>
-      <c r="B466" s="185"/>
+      <c r="A466" s="199"/>
+      <c r="B466" s="197"/>
       <c r="C466" s="38">
         <v>7</v>
       </c>
@@ -13578,8 +13585,8 @@
       <c r="K466" s="40"/>
     </row>
     <row r="467" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A467" s="322"/>
-      <c r="B467" s="185"/>
+      <c r="A467" s="199"/>
+      <c r="B467" s="197"/>
       <c r="C467" s="38">
         <v>8</v>
       </c>
@@ -13595,8 +13602,8 @@
       <c r="K467" s="40"/>
     </row>
     <row r="468" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A468" s="322"/>
-      <c r="B468" s="185"/>
+      <c r="A468" s="199"/>
+      <c r="B468" s="197"/>
       <c r="C468" s="38">
         <v>99</v>
       </c>
@@ -13616,8 +13623,8 @@
       <c r="K468" s="40"/>
     </row>
     <row r="469" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A469" s="310"/>
-      <c r="B469" s="195"/>
+      <c r="A469" s="180"/>
+      <c r="B469" s="198"/>
       <c r="C469" s="55">
         <v>98</v>
       </c>
@@ -13633,10 +13640,10 @@
       <c r="K469" s="40"/>
     </row>
     <row r="470" spans="1:11" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A470" s="187" t="s">
+      <c r="A470" s="179" t="s">
         <v>625</v>
       </c>
-      <c r="B470" s="207" t="s">
+      <c r="B470" s="200" t="s">
         <v>698</v>
       </c>
       <c r="C470" s="76">
@@ -13654,8 +13661,8 @@
       <c r="K470" s="40"/>
     </row>
     <row r="471" spans="1:11" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A471" s="310"/>
-      <c r="B471" s="208"/>
+      <c r="A471" s="180"/>
+      <c r="B471" s="202"/>
       <c r="C471" s="76">
         <v>2</v>
       </c>
@@ -13671,25 +13678,25 @@
       <c r="K471" s="40"/>
     </row>
     <row r="472" spans="1:11" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A472" s="199" t="s">
+      <c r="A472" s="285" t="s">
         <v>420</v>
       </c>
-      <c r="B472" s="200"/>
-      <c r="C472" s="200"/>
-      <c r="D472" s="200"/>
-      <c r="E472" s="200"/>
-      <c r="F472" s="200"/>
-      <c r="G472" s="200"/>
-      <c r="H472" s="200"/>
-      <c r="I472" s="200"/>
-      <c r="J472" s="200"/>
-      <c r="K472" s="201"/>
+      <c r="B472" s="288"/>
+      <c r="C472" s="288"/>
+      <c r="D472" s="288"/>
+      <c r="E472" s="288"/>
+      <c r="F472" s="288"/>
+      <c r="G472" s="288"/>
+      <c r="H472" s="288"/>
+      <c r="I472" s="288"/>
+      <c r="J472" s="288"/>
+      <c r="K472" s="289"/>
     </row>
     <row r="473" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A473" s="264" t="s">
+      <c r="A473" s="224" t="s">
         <v>537</v>
       </c>
-      <c r="B473" s="266" t="s">
+      <c r="B473" s="226" t="s">
         <v>263</v>
       </c>
       <c r="C473" s="68">
@@ -13709,8 +13716,8 @@
       <c r="K473" s="67"/>
     </row>
     <row r="474" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A474" s="265"/>
-      <c r="B474" s="266"/>
+      <c r="A474" s="225"/>
+      <c r="B474" s="226"/>
       <c r="C474" s="68">
         <v>1</v>
       </c>
@@ -13726,8 +13733,8 @@
       <c r="K474" s="67"/>
     </row>
     <row r="475" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A475" s="265"/>
-      <c r="B475" s="266"/>
+      <c r="A475" s="225"/>
+      <c r="B475" s="226"/>
       <c r="C475" s="68">
         <v>2</v>
       </c>
@@ -13743,8 +13750,8 @@
       <c r="K475" s="67"/>
     </row>
     <row r="476" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A476" s="265"/>
-      <c r="B476" s="266"/>
+      <c r="A476" s="225"/>
+      <c r="B476" s="226"/>
       <c r="C476" s="68">
         <v>3</v>
       </c>
@@ -13760,8 +13767,8 @@
       <c r="K476" s="67"/>
     </row>
     <row r="477" spans="1:11" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A477" s="265"/>
-      <c r="B477" s="266"/>
+      <c r="A477" s="225"/>
+      <c r="B477" s="226"/>
       <c r="C477" s="68">
         <v>99</v>
       </c>
@@ -13779,6 +13786,127 @@
     <row r="478" spans="1:11" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="145">
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A2:K2"/>
+    <mergeCell ref="B3:K3"/>
+    <mergeCell ref="A4:K4"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A52:A59"/>
+    <mergeCell ref="B52:B59"/>
+    <mergeCell ref="A27:A33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="A36:A48"/>
+    <mergeCell ref="B36:B48"/>
+    <mergeCell ref="A49:A51"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A60:A68"/>
+    <mergeCell ref="B60:B68"/>
+    <mergeCell ref="A69:A79"/>
+    <mergeCell ref="B69:B79"/>
+    <mergeCell ref="A80:A90"/>
+    <mergeCell ref="B80:B90"/>
+    <mergeCell ref="B49:B51"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="B27:B33"/>
+    <mergeCell ref="B19:B25"/>
+    <mergeCell ref="A19:A25"/>
+    <mergeCell ref="A472:K472"/>
+    <mergeCell ref="A208:A218"/>
+    <mergeCell ref="B208:B218"/>
+    <mergeCell ref="A284:K284"/>
+    <mergeCell ref="A434:K434"/>
+    <mergeCell ref="A196:A202"/>
+    <mergeCell ref="A203:A207"/>
+    <mergeCell ref="B470:B471"/>
+    <mergeCell ref="A132:K132"/>
+    <mergeCell ref="E188:E195"/>
+    <mergeCell ref="E196:E202"/>
+    <mergeCell ref="E203:E207"/>
+    <mergeCell ref="A236:K236"/>
+    <mergeCell ref="B141:B145"/>
+    <mergeCell ref="A141:A145"/>
+    <mergeCell ref="A151:A155"/>
+    <mergeCell ref="B151:B155"/>
+    <mergeCell ref="A146:A150"/>
+    <mergeCell ref="B146:B150"/>
+    <mergeCell ref="A156:A160"/>
+    <mergeCell ref="B156:B160"/>
+    <mergeCell ref="B230:B235"/>
+    <mergeCell ref="A230:A235"/>
+    <mergeCell ref="B161:B183"/>
+    <mergeCell ref="A91:A99"/>
+    <mergeCell ref="B91:B99"/>
+    <mergeCell ref="A100:A106"/>
+    <mergeCell ref="B100:B106"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="A114:A120"/>
+    <mergeCell ref="B114:B120"/>
+    <mergeCell ref="A243:K243"/>
+    <mergeCell ref="A107:A111"/>
+    <mergeCell ref="B107:B111"/>
+    <mergeCell ref="D111:K111"/>
+    <mergeCell ref="B137:B140"/>
+    <mergeCell ref="A137:A140"/>
+    <mergeCell ref="A184:A187"/>
+    <mergeCell ref="B184:B187"/>
+    <mergeCell ref="A128:A130"/>
+    <mergeCell ref="B128:B130"/>
+    <mergeCell ref="A121:A127"/>
+    <mergeCell ref="B121:B127"/>
+    <mergeCell ref="A131:K131"/>
+    <mergeCell ref="A473:A477"/>
+    <mergeCell ref="B473:B477"/>
+    <mergeCell ref="A227:A229"/>
+    <mergeCell ref="B227:B229"/>
+    <mergeCell ref="A221:A223"/>
+    <mergeCell ref="B221:B223"/>
+    <mergeCell ref="B133:B136"/>
+    <mergeCell ref="A133:A136"/>
+    <mergeCell ref="B219:B220"/>
+    <mergeCell ref="A219:A220"/>
+    <mergeCell ref="A224:K224"/>
+    <mergeCell ref="A188:A195"/>
+    <mergeCell ref="B196:B202"/>
+    <mergeCell ref="B203:B207"/>
+    <mergeCell ref="B188:B195"/>
+    <mergeCell ref="A225:A226"/>
+    <mergeCell ref="B225:B226"/>
+    <mergeCell ref="A161:A183"/>
+    <mergeCell ref="B356:B364"/>
+    <mergeCell ref="B435:B437"/>
+    <mergeCell ref="A435:A437"/>
+    <mergeCell ref="A431:K431"/>
+    <mergeCell ref="A376:K376"/>
+    <mergeCell ref="A423:K423"/>
+    <mergeCell ref="B377:B384"/>
+    <mergeCell ref="A377:A384"/>
+    <mergeCell ref="B385:B389"/>
+    <mergeCell ref="A385:A389"/>
+    <mergeCell ref="B424:B430"/>
+    <mergeCell ref="A424:A430"/>
+    <mergeCell ref="B390:B406"/>
+    <mergeCell ref="A390:A406"/>
+    <mergeCell ref="B407:B422"/>
+    <mergeCell ref="A407:A422"/>
+    <mergeCell ref="A279:A283"/>
+    <mergeCell ref="B279:B283"/>
+    <mergeCell ref="A260:A272"/>
+    <mergeCell ref="B260:B272"/>
+    <mergeCell ref="A247:A248"/>
+    <mergeCell ref="B247:B248"/>
+    <mergeCell ref="A250:A254"/>
+    <mergeCell ref="B250:B254"/>
+    <mergeCell ref="A255:A259"/>
+    <mergeCell ref="B255:B259"/>
     <mergeCell ref="A245:K245"/>
     <mergeCell ref="A238:K238"/>
     <mergeCell ref="F438:F459"/>
@@ -13803,127 +13931,6 @@
     <mergeCell ref="A438:A459"/>
     <mergeCell ref="A273:A278"/>
     <mergeCell ref="B273:B278"/>
-    <mergeCell ref="A279:A283"/>
-    <mergeCell ref="B279:B283"/>
-    <mergeCell ref="A260:A272"/>
-    <mergeCell ref="B260:B272"/>
-    <mergeCell ref="A247:A248"/>
-    <mergeCell ref="B247:B248"/>
-    <mergeCell ref="A250:A254"/>
-    <mergeCell ref="B250:B254"/>
-    <mergeCell ref="A255:A259"/>
-    <mergeCell ref="B255:B259"/>
-    <mergeCell ref="B377:B384"/>
-    <mergeCell ref="A377:A384"/>
-    <mergeCell ref="B385:B389"/>
-    <mergeCell ref="A385:A389"/>
-    <mergeCell ref="B424:B430"/>
-    <mergeCell ref="A424:A430"/>
-    <mergeCell ref="B390:B406"/>
-    <mergeCell ref="A390:A406"/>
-    <mergeCell ref="B407:B422"/>
-    <mergeCell ref="A407:A422"/>
-    <mergeCell ref="A473:A477"/>
-    <mergeCell ref="B473:B477"/>
-    <mergeCell ref="A227:A229"/>
-    <mergeCell ref="B227:B229"/>
-    <mergeCell ref="A221:A223"/>
-    <mergeCell ref="B221:B223"/>
-    <mergeCell ref="B133:B136"/>
-    <mergeCell ref="A133:A136"/>
-    <mergeCell ref="B219:B220"/>
-    <mergeCell ref="A219:A220"/>
-    <mergeCell ref="A224:K224"/>
-    <mergeCell ref="A188:A195"/>
-    <mergeCell ref="B196:B202"/>
-    <mergeCell ref="B203:B207"/>
-    <mergeCell ref="B188:B195"/>
-    <mergeCell ref="A225:A226"/>
-    <mergeCell ref="B225:B226"/>
-    <mergeCell ref="A161:A183"/>
-    <mergeCell ref="B356:B364"/>
-    <mergeCell ref="B435:B437"/>
-    <mergeCell ref="A435:A437"/>
-    <mergeCell ref="A431:K431"/>
-    <mergeCell ref="A376:K376"/>
-    <mergeCell ref="A423:K423"/>
-    <mergeCell ref="A91:A99"/>
-    <mergeCell ref="B91:B99"/>
-    <mergeCell ref="A100:A106"/>
-    <mergeCell ref="B100:B106"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="A114:A120"/>
-    <mergeCell ref="B114:B120"/>
-    <mergeCell ref="A243:K243"/>
-    <mergeCell ref="A107:A111"/>
-    <mergeCell ref="B107:B111"/>
-    <mergeCell ref="D111:K111"/>
-    <mergeCell ref="B137:B140"/>
-    <mergeCell ref="A137:A140"/>
-    <mergeCell ref="A184:A187"/>
-    <mergeCell ref="B184:B187"/>
-    <mergeCell ref="A128:A130"/>
-    <mergeCell ref="B128:B130"/>
-    <mergeCell ref="A121:A127"/>
-    <mergeCell ref="B121:B127"/>
-    <mergeCell ref="A131:K131"/>
-    <mergeCell ref="A472:K472"/>
-    <mergeCell ref="A208:A218"/>
-    <mergeCell ref="B208:B218"/>
-    <mergeCell ref="A284:K284"/>
-    <mergeCell ref="A434:K434"/>
-    <mergeCell ref="A196:A202"/>
-    <mergeCell ref="A203:A207"/>
-    <mergeCell ref="B470:B471"/>
-    <mergeCell ref="A132:K132"/>
-    <mergeCell ref="E188:E195"/>
-    <mergeCell ref="E196:E202"/>
-    <mergeCell ref="E203:E207"/>
-    <mergeCell ref="A236:K236"/>
-    <mergeCell ref="B141:B145"/>
-    <mergeCell ref="A141:A145"/>
-    <mergeCell ref="A151:A155"/>
-    <mergeCell ref="B151:B155"/>
-    <mergeCell ref="A146:A150"/>
-    <mergeCell ref="B146:B150"/>
-    <mergeCell ref="A156:A160"/>
-    <mergeCell ref="B156:B160"/>
-    <mergeCell ref="B230:B235"/>
-    <mergeCell ref="A230:A235"/>
-    <mergeCell ref="B161:B183"/>
-    <mergeCell ref="A60:A68"/>
-    <mergeCell ref="B60:B68"/>
-    <mergeCell ref="A69:A79"/>
-    <mergeCell ref="B69:B79"/>
-    <mergeCell ref="A80:A90"/>
-    <mergeCell ref="B80:B90"/>
-    <mergeCell ref="B49:B51"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="B27:B33"/>
-    <mergeCell ref="B19:B25"/>
-    <mergeCell ref="A19:A25"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A2:K2"/>
-    <mergeCell ref="B3:K3"/>
-    <mergeCell ref="A4:K4"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A52:A59"/>
-    <mergeCell ref="B52:B59"/>
-    <mergeCell ref="A27:A33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="A36:A48"/>
-    <mergeCell ref="B36:B48"/>
-    <mergeCell ref="A49:A51"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="A13:A14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -15021,13 +15028,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="345" t="s">
+      <c r="A1" s="339" t="s">
         <v>337</v>
       </c>
-      <c r="B1" s="345"/>
-      <c r="C1" s="345"/>
-      <c r="D1" s="345"/>
-      <c r="E1" s="345"/>
+      <c r="B1" s="339"/>
+      <c r="C1" s="339"/>
+      <c r="D1" s="339"/>
+      <c r="E1" s="339"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
@@ -15047,10 +15054,10 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="342" t="s">
+      <c r="A3" s="344" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="342" t="s">
+      <c r="B3" s="344" t="s">
         <v>203</v>
       </c>
       <c r="C3" s="21">
@@ -15064,8 +15071,8 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="348"/>
-      <c r="B4" s="348"/>
+      <c r="A4" s="345"/>
+      <c r="B4" s="345"/>
       <c r="C4" s="21">
         <v>2</v>
       </c>
@@ -15075,8 +15082,8 @@
       <c r="E4" s="23"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="348"/>
-      <c r="B5" s="348"/>
+      <c r="A5" s="345"/>
+      <c r="B5" s="345"/>
       <c r="C5" s="21">
         <v>3</v>
       </c>
@@ -15086,8 +15093,8 @@
       <c r="E5" s="23"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="348"/>
-      <c r="B6" s="348"/>
+      <c r="A6" s="345"/>
+      <c r="B6" s="345"/>
       <c r="C6" s="21">
         <v>4</v>
       </c>
@@ -15097,8 +15104,8 @@
       <c r="E6" s="23"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="348"/>
-      <c r="B7" s="348"/>
+      <c r="A7" s="345"/>
+      <c r="B7" s="345"/>
       <c r="C7" s="21">
         <v>5</v>
       </c>
@@ -15108,8 +15115,8 @@
       <c r="E7" s="23"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="349"/>
-      <c r="B8" s="349"/>
+      <c r="A8" s="346"/>
+      <c r="B8" s="346"/>
       <c r="C8" s="21">
         <v>6</v>
       </c>
@@ -15134,10 +15141,10 @@
       <c r="E9" s="23"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="342" t="s">
+      <c r="A10" s="344" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="342" t="s">
+      <c r="B10" s="344" t="s">
         <v>212</v>
       </c>
       <c r="C10" s="26">
@@ -15151,8 +15158,8 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="348"/>
-      <c r="B11" s="348"/>
+      <c r="A11" s="345"/>
+      <c r="B11" s="345"/>
       <c r="C11" s="26">
         <v>2</v>
       </c>
@@ -15162,8 +15169,8 @@
       <c r="E11" s="27"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="348"/>
-      <c r="B12" s="348"/>
+      <c r="A12" s="345"/>
+      <c r="B12" s="345"/>
       <c r="C12" s="26">
         <v>3</v>
       </c>
@@ -15173,8 +15180,8 @@
       <c r="E12" s="27"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="348"/>
-      <c r="B13" s="348"/>
+      <c r="A13" s="345"/>
+      <c r="B13" s="345"/>
       <c r="C13" s="26">
         <v>4</v>
       </c>
@@ -15184,8 +15191,8 @@
       <c r="E13" s="27"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="348"/>
-      <c r="B14" s="348"/>
+      <c r="A14" s="345"/>
+      <c r="B14" s="345"/>
       <c r="C14" s="26">
         <v>5</v>
       </c>
@@ -15195,8 +15202,8 @@
       <c r="E14" s="27"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="348"/>
-      <c r="B15" s="348"/>
+      <c r="A15" s="345"/>
+      <c r="B15" s="345"/>
       <c r="C15" s="26">
         <v>6</v>
       </c>
@@ -15224,7 +15231,7 @@
       <c r="A17" s="333" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="344" t="s">
+      <c r="B17" s="340" t="s">
         <v>339</v>
       </c>
       <c r="C17" s="15">
@@ -15237,7 +15244,7 @@
     </row>
     <row r="18" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="333"/>
-      <c r="B18" s="344"/>
+      <c r="B18" s="340"/>
       <c r="C18" s="15">
         <v>2</v>
       </c>
@@ -15248,7 +15255,7 @@
     </row>
     <row r="19" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="333"/>
-      <c r="B19" s="344"/>
+      <c r="B19" s="340"/>
       <c r="C19" s="15">
         <v>3</v>
       </c>
@@ -15259,7 +15266,7 @@
     </row>
     <row r="20" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="333"/>
-      <c r="B20" s="344"/>
+      <c r="B20" s="340"/>
       <c r="C20" s="15">
         <v>4</v>
       </c>
@@ -15270,7 +15277,7 @@
     </row>
     <row r="21" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="333"/>
-      <c r="B21" s="344"/>
+      <c r="B21" s="340"/>
       <c r="C21" s="15">
         <v>5</v>
       </c>
@@ -15280,13 +15287,13 @@
       <c r="E21" s="19"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="350" t="s">
+      <c r="A22" s="347" t="s">
         <v>336</v>
       </c>
-      <c r="B22" s="350"/>
-      <c r="C22" s="350"/>
-      <c r="D22" s="350"/>
-      <c r="E22" s="350"/>
+      <c r="B22" s="347"/>
+      <c r="C22" s="347"/>
+      <c r="D22" s="347"/>
+      <c r="E22" s="347"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
@@ -15306,10 +15313,10 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="342" t="s">
+      <c r="A24" s="344" t="s">
         <v>345</v>
       </c>
-      <c r="B24" s="342" t="s">
+      <c r="B24" s="344" t="s">
         <v>389</v>
       </c>
       <c r="C24" s="24">
@@ -15321,8 +15328,8 @@
       <c r="E24" s="34"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="343"/>
-      <c r="B25" s="343"/>
+      <c r="A25" s="342"/>
+      <c r="B25" s="342"/>
       <c r="C25" s="24">
         <v>2</v>
       </c>
@@ -15332,8 +15339,8 @@
       <c r="E25" s="34"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="343"/>
-      <c r="B26" s="343"/>
+      <c r="A26" s="342"/>
+      <c r="B26" s="342"/>
       <c r="C26" s="24">
         <v>3</v>
       </c>
@@ -15343,8 +15350,8 @@
       <c r="E26" s="34"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="343"/>
-      <c r="B27" s="343"/>
+      <c r="A27" s="342"/>
+      <c r="B27" s="342"/>
       <c r="C27" s="24">
         <v>4</v>
       </c>
@@ -15354,8 +15361,8 @@
       <c r="E27" s="34"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="343"/>
-      <c r="B28" s="343"/>
+      <c r="A28" s="342"/>
+      <c r="B28" s="342"/>
       <c r="C28" s="24">
         <v>5</v>
       </c>
@@ -15365,8 +15372,8 @@
       <c r="E28" s="34"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="343"/>
-      <c r="B29" s="343"/>
+      <c r="A29" s="342"/>
+      <c r="B29" s="342"/>
       <c r="C29" s="24">
         <v>6</v>
       </c>
@@ -15376,8 +15383,8 @@
       <c r="E29" s="34"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="343"/>
-      <c r="B30" s="343"/>
+      <c r="A30" s="342"/>
+      <c r="B30" s="342"/>
       <c r="C30" s="24">
         <v>7</v>
       </c>
@@ -15387,8 +15394,8 @@
       <c r="E30" s="34"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="343"/>
-      <c r="B31" s="343"/>
+      <c r="A31" s="342"/>
+      <c r="B31" s="342"/>
       <c r="C31" s="24">
         <v>8</v>
       </c>
@@ -15398,8 +15405,8 @@
       <c r="E31" s="34"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="343"/>
-      <c r="B32" s="343"/>
+      <c r="A32" s="342"/>
+      <c r="B32" s="342"/>
       <c r="C32" s="24">
         <v>9</v>
       </c>
@@ -15409,8 +15416,8 @@
       <c r="E32" s="34"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="343"/>
-      <c r="B33" s="343"/>
+      <c r="A33" s="342"/>
+      <c r="B33" s="342"/>
       <c r="C33" s="24">
         <v>10</v>
       </c>
@@ -15420,8 +15427,8 @@
       <c r="E33" s="34"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="343"/>
-      <c r="B34" s="343"/>
+      <c r="A34" s="342"/>
+      <c r="B34" s="342"/>
       <c r="C34" s="24">
         <v>11</v>
       </c>
@@ -15431,10 +15438,10 @@
       <c r="E34" s="34"/>
     </row>
     <row r="35" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="346" t="s">
+      <c r="A35" s="341" t="s">
         <v>346</v>
       </c>
-      <c r="B35" s="346" t="s">
+      <c r="B35" s="341" t="s">
         <v>350</v>
       </c>
       <c r="C35" s="24">
@@ -15446,8 +15453,8 @@
       <c r="E35" s="34"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="343"/>
-      <c r="B36" s="343"/>
+      <c r="A36" s="342"/>
+      <c r="B36" s="342"/>
       <c r="C36" s="24">
         <v>2</v>
       </c>
@@ -15457,8 +15464,8 @@
       <c r="E36" s="34"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="347"/>
-      <c r="B37" s="347"/>
+      <c r="A37" s="343"/>
+      <c r="B37" s="343"/>
       <c r="C37" s="24">
         <v>3</v>
       </c>
@@ -15468,10 +15475,10 @@
       <c r="E37" s="34"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="342" t="s">
+      <c r="A38" s="344" t="s">
         <v>347</v>
       </c>
-      <c r="B38" s="342" t="s">
+      <c r="B38" s="344" t="s">
         <v>390</v>
       </c>
       <c r="C38" s="24">
@@ -15483,8 +15490,8 @@
       <c r="E38" s="34"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="343"/>
-      <c r="B39" s="343"/>
+      <c r="A39" s="342"/>
+      <c r="B39" s="342"/>
       <c r="C39" s="24">
         <v>2</v>
       </c>
@@ -15494,8 +15501,8 @@
       <c r="E39" s="34"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="343"/>
-      <c r="B40" s="343"/>
+      <c r="A40" s="342"/>
+      <c r="B40" s="342"/>
       <c r="C40" s="24">
         <v>3</v>
       </c>
@@ -15505,8 +15512,8 @@
       <c r="E40" s="34"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="343"/>
-      <c r="B41" s="343"/>
+      <c r="A41" s="342"/>
+      <c r="B41" s="342"/>
       <c r="C41" s="24">
         <v>4</v>
       </c>
@@ -15516,8 +15523,8 @@
       <c r="E41" s="34"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="343"/>
-      <c r="B42" s="343"/>
+      <c r="A42" s="342"/>
+      <c r="B42" s="342"/>
       <c r="C42" s="24">
         <v>5</v>
       </c>
@@ -15527,8 +15534,8 @@
       <c r="E42" s="34"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="343"/>
-      <c r="B43" s="343"/>
+      <c r="A43" s="342"/>
+      <c r="B43" s="342"/>
       <c r="C43" s="24">
         <v>6</v>
       </c>
@@ -15538,10 +15545,10 @@
       <c r="E43" s="34"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="342" t="s">
+      <c r="A44" s="344" t="s">
         <v>348</v>
       </c>
-      <c r="B44" s="342" t="s">
+      <c r="B44" s="344" t="s">
         <v>391</v>
       </c>
       <c r="C44" s="24"/>
@@ -15549,29 +15556,29 @@
       <c r="E44" s="34"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="343"/>
-      <c r="B45" s="343"/>
+      <c r="A45" s="342"/>
+      <c r="B45" s="342"/>
       <c r="C45" s="24"/>
       <c r="D45" s="24"/>
       <c r="E45" s="34"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="343"/>
-      <c r="B46" s="343"/>
+      <c r="A46" s="342"/>
+      <c r="B46" s="342"/>
       <c r="C46" s="24"/>
       <c r="D46" s="24"/>
       <c r="E46" s="34"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="343"/>
-      <c r="B47" s="343"/>
+      <c r="A47" s="342"/>
+      <c r="B47" s="342"/>
       <c r="C47" s="24"/>
       <c r="D47" s="24"/>
       <c r="E47" s="34"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="343"/>
-      <c r="B48" s="343"/>
+      <c r="A48" s="342"/>
+      <c r="B48" s="342"/>
       <c r="C48" s="29"/>
       <c r="D48" s="29"/>
       <c r="E48" s="36"/>
@@ -15590,10 +15597,10 @@
       <c r="E49" s="17"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="344" t="s">
+      <c r="A50" s="340" t="s">
         <v>368</v>
       </c>
-      <c r="B50" s="344" t="s">
+      <c r="B50" s="340" t="s">
         <v>216</v>
       </c>
       <c r="C50" s="32">
@@ -15605,8 +15612,8 @@
       <c r="E50" s="17"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="344"/>
-      <c r="B51" s="344"/>
+      <c r="A51" s="340"/>
+      <c r="B51" s="340"/>
       <c r="C51" s="32">
         <v>2</v>
       </c>
@@ -15616,8 +15623,8 @@
       <c r="E51" s="17"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="344"/>
-      <c r="B52" s="344"/>
+      <c r="A52" s="340"/>
+      <c r="B52" s="340"/>
       <c r="C52" s="32">
         <v>3</v>
       </c>
@@ -15627,8 +15634,8 @@
       <c r="E52" s="17"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="344"/>
-      <c r="B53" s="344"/>
+      <c r="A53" s="340"/>
+      <c r="B53" s="340"/>
       <c r="C53" s="32">
         <v>4</v>
       </c>
@@ -15638,8 +15645,8 @@
       <c r="E53" s="17"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="344"/>
-      <c r="B54" s="344"/>
+      <c r="A54" s="340"/>
+      <c r="B54" s="340"/>
       <c r="C54" s="32">
         <v>5</v>
       </c>
@@ -15649,10 +15656,10 @@
       <c r="E54" s="17"/>
     </row>
     <row r="55" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="339" t="s">
+      <c r="A55" s="348" t="s">
         <v>374</v>
       </c>
-      <c r="B55" s="339" t="s">
+      <c r="B55" s="348" t="s">
         <v>375</v>
       </c>
       <c r="C55" s="32">
@@ -15664,8 +15671,8 @@
       <c r="E55" s="17"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="340"/>
-      <c r="B56" s="340"/>
+      <c r="A56" s="349"/>
+      <c r="B56" s="349"/>
       <c r="C56" s="32">
         <v>2</v>
       </c>
@@ -15675,8 +15682,8 @@
       <c r="E56" s="12"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="341"/>
-      <c r="B57" s="341"/>
+      <c r="A57" s="350"/>
+      <c r="B57" s="350"/>
       <c r="C57" s="32">
         <v>3</v>
       </c>
@@ -15687,6 +15694,16 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="A55:A57"/>
+    <mergeCell ref="A24:A34"/>
+    <mergeCell ref="B24:B34"/>
+    <mergeCell ref="A38:A43"/>
+    <mergeCell ref="B38:B43"/>
+    <mergeCell ref="A44:A48"/>
+    <mergeCell ref="B44:B48"/>
+    <mergeCell ref="A50:A54"/>
+    <mergeCell ref="B50:B54"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B17:B21"/>
     <mergeCell ref="A17:A21"/>
@@ -15697,16 +15714,6 @@
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="B10:B15"/>
     <mergeCell ref="A22:E22"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="A55:A57"/>
-    <mergeCell ref="A24:A34"/>
-    <mergeCell ref="B24:B34"/>
-    <mergeCell ref="A38:A43"/>
-    <mergeCell ref="B38:B43"/>
-    <mergeCell ref="A44:A48"/>
-    <mergeCell ref="B44:B48"/>
-    <mergeCell ref="A50:A54"/>
-    <mergeCell ref="B50:B54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -15742,7 +15749,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="353" t="s">
+      <c r="A3" s="351" t="s">
         <v>298</v>
       </c>
       <c r="B3" s="354" t="s">
@@ -15754,10 +15761,10 @@
       <c r="D3" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E3" s="352"/>
+      <c r="E3" s="353"/>
     </row>
     <row r="4" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="353"/>
+      <c r="A4" s="351"/>
       <c r="B4" s="331"/>
       <c r="C4" s="5">
         <v>2</v>
@@ -15765,10 +15772,10 @@
       <c r="D4" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E4" s="352"/>
+      <c r="E4" s="353"/>
     </row>
     <row r="5" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="353"/>
+      <c r="A5" s="351"/>
       <c r="B5" s="331"/>
       <c r="C5" s="5">
         <v>3</v>
@@ -15776,10 +15783,10 @@
       <c r="D5" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="E5" s="352"/>
+      <c r="E5" s="353"/>
     </row>
     <row r="6" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="353"/>
+      <c r="A6" s="351"/>
       <c r="B6" s="331"/>
       <c r="C6" s="5">
         <v>4</v>
@@ -15787,10 +15794,10 @@
       <c r="D6" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="E6" s="352"/>
+      <c r="E6" s="353"/>
     </row>
     <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="353"/>
+      <c r="A7" s="351"/>
       <c r="B7" s="331"/>
       <c r="C7" s="5">
         <v>5</v>
@@ -15798,10 +15805,10 @@
       <c r="D7" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E7" s="352"/>
+      <c r="E7" s="353"/>
     </row>
     <row r="8" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="353"/>
+      <c r="A8" s="351"/>
       <c r="B8" s="331"/>
       <c r="C8" s="5">
         <v>6</v>
@@ -15809,10 +15816,10 @@
       <c r="D8" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E8" s="352"/>
+      <c r="E8" s="353"/>
     </row>
     <row r="9" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="353"/>
+      <c r="A9" s="351"/>
       <c r="B9" s="331"/>
       <c r="C9" s="5">
         <v>7</v>
@@ -15820,10 +15827,10 @@
       <c r="D9" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="E9" s="352"/>
+      <c r="E9" s="353"/>
     </row>
     <row r="10" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="353"/>
+      <c r="A10" s="351"/>
       <c r="B10" s="331"/>
       <c r="C10" s="5">
         <v>8</v>
@@ -15831,10 +15838,10 @@
       <c r="D10" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="E10" s="352"/>
+      <c r="E10" s="353"/>
     </row>
     <row r="11" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="353"/>
+      <c r="A11" s="351"/>
       <c r="B11" s="331"/>
       <c r="C11" s="5">
         <v>9</v>
@@ -15842,10 +15849,10 @@
       <c r="D11" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="E11" s="352"/>
+      <c r="E11" s="353"/>
     </row>
     <row r="12" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="352" t="s">
+      <c r="A12" s="353" t="s">
         <v>300</v>
       </c>
       <c r="B12" s="355" t="s">
@@ -15860,7 +15867,7 @@
       <c r="E12" s="7"/>
     </row>
     <row r="13" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="352"/>
+      <c r="A13" s="353"/>
       <c r="B13" s="355"/>
       <c r="C13" s="5">
         <v>2</v>
@@ -15876,7 +15883,7 @@
       <c r="A14" s="328" t="s">
         <v>295</v>
       </c>
-      <c r="B14" s="351" t="s">
+      <c r="B14" s="352" t="s">
         <v>379</v>
       </c>
       <c r="C14" s="6"/>
@@ -15889,7 +15896,7 @@
     </row>
     <row r="15" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="328"/>
-      <c r="B15" s="351"/>
+      <c r="B15" s="352"/>
       <c r="C15" s="6"/>
       <c r="D15" s="1" t="s">
         <v>290</v>
@@ -15900,7 +15907,7 @@
     </row>
     <row r="16" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="328"/>
-      <c r="B16" s="351"/>
+      <c r="B16" s="352"/>
       <c r="C16" s="6"/>
       <c r="D16" s="1" t="s">
         <v>291</v>
@@ -15911,7 +15918,7 @@
     </row>
     <row r="17" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="328"/>
-      <c r="B17" s="351"/>
+      <c r="B17" s="352"/>
       <c r="C17" s="6"/>
       <c r="D17" s="1" t="s">
         <v>292</v>
@@ -15922,7 +15929,7 @@
     </row>
     <row r="18" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="328"/>
-      <c r="B18" s="351"/>
+      <c r="B18" s="352"/>
       <c r="C18" s="6"/>
       <c r="D18" s="1" t="s">
         <v>299</v>
@@ -15932,7 +15939,7 @@
       </c>
     </row>
     <row r="19" spans="1:5" ht="64.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="353" t="s">
+      <c r="A19" s="351" t="s">
         <v>305</v>
       </c>
       <c r="B19" s="328" t="s">
@@ -15947,7 +15954,7 @@
       <c r="E19" s="6"/>
     </row>
     <row r="20" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="353"/>
+      <c r="A20" s="351"/>
       <c r="B20" s="328"/>
       <c r="C20" s="6">
         <v>2</v>
@@ -15958,7 +15965,7 @@
       <c r="E20" s="6"/>
     </row>
     <row r="21" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="353"/>
+      <c r="A21" s="351"/>
       <c r="B21" s="328"/>
       <c r="C21" s="6">
         <v>3</v>
@@ -15969,7 +15976,7 @@
       <c r="E21" s="6"/>
     </row>
     <row r="22" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="353"/>
+      <c r="A22" s="351"/>
       <c r="B22" s="328"/>
       <c r="C22" s="6">
         <v>4</v>
@@ -15980,7 +15987,7 @@
       <c r="E22" s="6"/>
     </row>
     <row r="23" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="353" t="s">
+      <c r="A23" s="351" t="s">
         <v>306</v>
       </c>
       <c r="B23" s="328" t="s">
@@ -15995,7 +16002,7 @@
       <c r="E23" s="6"/>
     </row>
     <row r="24" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="353"/>
+      <c r="A24" s="351"/>
       <c r="B24" s="328"/>
       <c r="C24" s="6">
         <v>2</v>
@@ -16006,7 +16013,7 @@
       <c r="E24" s="6"/>
     </row>
     <row r="25" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="353"/>
+      <c r="A25" s="351"/>
       <c r="B25" s="328"/>
       <c r="C25" s="6">
         <v>3</v>
@@ -16017,7 +16024,7 @@
       <c r="E25" s="6"/>
     </row>
     <row r="26" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="353"/>
+      <c r="A26" s="351"/>
       <c r="B26" s="328"/>
       <c r="C26" s="6">
         <v>4</v>
@@ -16028,7 +16035,7 @@
       <c r="E26" s="6"/>
     </row>
     <row r="27" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="353" t="s">
+      <c r="A27" s="351" t="s">
         <v>307</v>
       </c>
       <c r="B27" s="328" t="s">
@@ -16043,7 +16050,7 @@
       <c r="E27" s="6"/>
     </row>
     <row r="28" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="353"/>
+      <c r="A28" s="351"/>
       <c r="B28" s="328"/>
       <c r="C28" s="6">
         <v>2</v>
@@ -16054,7 +16061,7 @@
       <c r="E28" s="6"/>
     </row>
     <row r="29" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="353"/>
+      <c r="A29" s="351"/>
       <c r="B29" s="328"/>
       <c r="C29" s="6">
         <v>3</v>
@@ -16065,7 +16072,7 @@
       <c r="E29" s="6"/>
     </row>
     <row r="30" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="353"/>
+      <c r="A30" s="351"/>
       <c r="B30" s="328"/>
       <c r="C30" s="6">
         <v>4</v>
@@ -16076,7 +16083,7 @@
       <c r="E30" s="6"/>
     </row>
     <row r="31" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="353" t="s">
+      <c r="A31" s="351" t="s">
         <v>308</v>
       </c>
       <c r="B31" s="328" t="s">
@@ -16091,7 +16098,7 @@
       <c r="E31" s="6"/>
     </row>
     <row r="32" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="353"/>
+      <c r="A32" s="351"/>
       <c r="B32" s="328"/>
       <c r="C32" s="6">
         <v>2</v>
@@ -16102,7 +16109,7 @@
       <c r="E32" s="6"/>
     </row>
     <row r="33" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="353"/>
+      <c r="A33" s="351"/>
       <c r="B33" s="328"/>
       <c r="C33" s="6">
         <v>3</v>
@@ -16113,7 +16120,7 @@
       <c r="E33" s="6"/>
     </row>
     <row r="34" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="353"/>
+      <c r="A34" s="351"/>
       <c r="B34" s="328"/>
       <c r="C34" s="6">
         <v>4</v>
@@ -16124,7 +16131,7 @@
       <c r="E34" s="6"/>
     </row>
     <row r="35" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="353" t="s">
+      <c r="A35" s="351" t="s">
         <v>309</v>
       </c>
       <c r="B35" s="328" t="s">
@@ -16139,7 +16146,7 @@
       <c r="E35" s="6"/>
     </row>
     <row r="36" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="353"/>
+      <c r="A36" s="351"/>
       <c r="B36" s="328"/>
       <c r="C36" s="6">
         <v>2</v>
@@ -16150,7 +16157,7 @@
       <c r="E36" s="6"/>
     </row>
     <row r="37" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="353"/>
+      <c r="A37" s="351"/>
       <c r="B37" s="328"/>
       <c r="C37" s="6">
         <v>3</v>
@@ -16161,7 +16168,7 @@
       <c r="E37" s="6"/>
     </row>
     <row r="38" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="353"/>
+      <c r="A38" s="351"/>
       <c r="B38" s="328"/>
       <c r="C38" s="6">
         <v>4</v>
@@ -16173,6 +16180,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B14:B18"/>
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="E3:E11"/>
+    <mergeCell ref="A3:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B3:B11"/>
+    <mergeCell ref="B12:B13"/>
     <mergeCell ref="A35:A38"/>
     <mergeCell ref="B35:B38"/>
     <mergeCell ref="A19:A22"/>
@@ -16182,14 +16197,6 @@
     <mergeCell ref="B27:B30"/>
     <mergeCell ref="A31:A34"/>
     <mergeCell ref="B31:B34"/>
-    <mergeCell ref="B14:B18"/>
-    <mergeCell ref="A14:A18"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="E3:E11"/>
-    <mergeCell ref="A3:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B3:B11"/>
-    <mergeCell ref="B12:B13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -16643,15 +16650,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <AppVersion xmlns="08ce7a00-5569-4b3f-b1aa-ca7c736aa64b" xsi:nil="true"/>
@@ -16704,6 +16702,15 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7BE2177-65AC-4334-A59B-38104E0010B1}">
   <ds:schemaRefs>
@@ -16724,14 +16731,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03C45617-08BA-4BE5-A3D7-5F2E216E6EBC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1CDA93A-2C81-40FB-BDF2-C8B81B42A0B5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -16746,4 +16745,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03C45617-08BA-4BE5-A3D7-5F2E216E6EBC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Primera versión/Input/Encuesta_Movilidad_Version_08_08_25.xlsx
+++ b/Primera versión/Input/Encuesta_Movilidad_Version_08_08_25.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8f89820ab55adc2/Escritorio/Natura/Primera versión/Input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="139" documentId="8_{676B3BA6-46B2-41C2-A545-10BB88DE3D71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BFD5D30A-F86D-4482-9E46-C3AC14C50062}"/>
+  <xr:revisionPtr revIDLastSave="143" documentId="8_{676B3BA6-46B2-41C2-A545-10BB88DE3D71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{794D2020-F5A8-4111-9219-9C262FDCD48F}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="6108" yWindow="3708" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="5760" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
@@ -4096,41 +4096,264 @@
     <xf numFmtId="0" fontId="15" fillId="16" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -4139,156 +4362,6 @@
     <xf numFmtId="0" fontId="17" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4300,9 +4373,6 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="17" fillId="15" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -4335,15 +4405,6 @@
     <xf numFmtId="0" fontId="15" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -4368,183 +4429,122 @@
     <xf numFmtId="0" fontId="15" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="17" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4589,6 +4589,33 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4598,41 +4625,14 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -4744,6 +4744,10 @@
     <xdr:clientData fLocksWithSheet="0"/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4961,60 +4965,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="146"/>
-      <c r="B1" s="147"/>
-      <c r="C1" s="147"/>
-      <c r="D1" s="147"/>
-      <c r="E1" s="147"/>
-      <c r="F1" s="147"/>
-      <c r="G1" s="147"/>
+      <c r="A1" s="293"/>
+      <c r="B1" s="203"/>
+      <c r="C1" s="203"/>
+      <c r="D1" s="203"/>
+      <c r="E1" s="203"/>
+      <c r="F1" s="203"/>
+      <c r="G1" s="203"/>
       <c r="H1" s="84"/>
       <c r="I1" s="84"/>
       <c r="J1" s="84"/>
     </row>
     <row r="2" spans="1:10" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="148" t="s">
+      <c r="A2" s="294" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="147"/>
-      <c r="C2" s="147"/>
-      <c r="D2" s="147"/>
-      <c r="E2" s="147"/>
-      <c r="F2" s="147"/>
-      <c r="G2" s="147"/>
-      <c r="H2" s="147"/>
-      <c r="I2" s="147"/>
-      <c r="J2" s="147"/>
+      <c r="B2" s="203"/>
+      <c r="C2" s="203"/>
+      <c r="D2" s="203"/>
+      <c r="E2" s="203"/>
+      <c r="F2" s="203"/>
+      <c r="G2" s="203"/>
+      <c r="H2" s="203"/>
+      <c r="I2" s="203"/>
+      <c r="J2" s="203"/>
     </row>
     <row r="3" spans="1:10" ht="45.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="44" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="149" t="s">
+      <c r="B3" s="295" t="s">
         <v>457</v>
       </c>
-      <c r="C3" s="149"/>
-      <c r="D3" s="149"/>
-      <c r="E3" s="149"/>
-      <c r="F3" s="149"/>
-      <c r="G3" s="149"/>
-      <c r="H3" s="149"/>
-      <c r="I3" s="149"/>
-      <c r="J3" s="149"/>
+      <c r="C3" s="295"/>
+      <c r="D3" s="295"/>
+      <c r="E3" s="295"/>
+      <c r="F3" s="295"/>
+      <c r="G3" s="295"/>
+      <c r="H3" s="295"/>
+      <c r="I3" s="295"/>
+      <c r="J3" s="295"/>
     </row>
     <row r="4" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="150" t="s">
+      <c r="A4" s="266" t="s">
         <v>549</v>
       </c>
-      <c r="B4" s="151"/>
-      <c r="C4" s="151"/>
-      <c r="D4" s="151"/>
-      <c r="E4" s="151"/>
-      <c r="F4" s="151"/>
-      <c r="G4" s="151"/>
-      <c r="H4" s="151"/>
-      <c r="I4" s="151"/>
-      <c r="J4" s="152"/>
+      <c r="B4" s="262"/>
+      <c r="C4" s="262"/>
+      <c r="D4" s="262"/>
+      <c r="E4" s="262"/>
+      <c r="F4" s="262"/>
+      <c r="G4" s="262"/>
+      <c r="H4" s="262"/>
+      <c r="I4" s="262"/>
+      <c r="J4" s="263"/>
     </row>
     <row r="5" spans="1:10" ht="51" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="45" t="s">
@@ -5049,10 +5053,10 @@
       </c>
     </row>
     <row r="6" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="153" t="s">
+      <c r="A6" s="296" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="155" t="s">
+      <c r="B6" s="172" t="s">
         <v>14</v>
       </c>
       <c r="C6" s="43" t="s">
@@ -5067,8 +5071,8 @@
       <c r="J6" s="40"/>
     </row>
     <row r="7" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A7" s="154"/>
-      <c r="B7" s="156"/>
+      <c r="A7" s="182"/>
+      <c r="B7" s="183"/>
       <c r="C7" s="43" t="s">
         <v>16</v>
       </c>
@@ -5081,10 +5085,10 @@
       <c r="J7" s="40"/>
     </row>
     <row r="8" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="170" t="s">
+      <c r="A8" s="299" t="s">
         <v>550</v>
       </c>
-      <c r="B8" s="169" t="s">
+      <c r="B8" s="298" t="s">
         <v>655</v>
       </c>
       <c r="C8" s="43" t="s">
@@ -5101,8 +5105,8 @@
       <c r="J8" s="40"/>
     </row>
     <row r="9" spans="1:10" ht="48.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="154"/>
-      <c r="B9" s="154"/>
+      <c r="A9" s="182"/>
+      <c r="B9" s="182"/>
       <c r="C9" s="43" t="s">
         <v>25</v>
       </c>
@@ -5139,10 +5143,10 @@
       <c r="J10" s="40"/>
     </row>
     <row r="11" spans="1:10" ht="45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="167" t="s">
+      <c r="A11" s="289" t="s">
         <v>551</v>
       </c>
-      <c r="B11" s="155" t="s">
+      <c r="B11" s="172" t="s">
         <v>458</v>
       </c>
       <c r="C11" s="43" t="s">
@@ -5159,8 +5163,8 @@
       <c r="J11" s="40"/>
     </row>
     <row r="12" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="172"/>
-      <c r="B12" s="171"/>
+      <c r="A12" s="291"/>
+      <c r="B12" s="174"/>
       <c r="C12" s="43" t="s">
         <v>25</v>
       </c>
@@ -5173,10 +5177,10 @@
       <c r="J12" s="40"/>
     </row>
     <row r="13" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A13" s="167" t="s">
+      <c r="A13" s="289" t="s">
         <v>552</v>
       </c>
-      <c r="B13" s="155" t="s">
+      <c r="B13" s="172" t="s">
         <v>459</v>
       </c>
       <c r="C13" s="43" t="s">
@@ -5191,8 +5195,8 @@
       <c r="J13" s="40"/>
     </row>
     <row r="14" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="172"/>
-      <c r="B14" s="171"/>
+      <c r="A14" s="291"/>
+      <c r="B14" s="174"/>
       <c r="C14" s="43" t="s">
         <v>25</v>
       </c>
@@ -5207,10 +5211,10 @@
       <c r="J14" s="40"/>
     </row>
     <row r="15" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="174" t="s">
+      <c r="A15" s="292" t="s">
         <v>21</v>
       </c>
-      <c r="B15" s="155" t="s">
+      <c r="B15" s="172" t="s">
         <v>22</v>
       </c>
       <c r="C15" s="43" t="s">
@@ -5227,8 +5231,8 @@
       <c r="J15" s="40"/>
     </row>
     <row r="16" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A16" s="154"/>
-      <c r="B16" s="156"/>
+      <c r="A16" s="182"/>
+      <c r="B16" s="183"/>
       <c r="C16" s="127" t="s">
         <v>25</v>
       </c>
@@ -5283,10 +5287,10 @@
       <c r="J18" s="40"/>
     </row>
     <row r="19" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="167" t="s">
+      <c r="A19" s="289" t="s">
         <v>31</v>
       </c>
-      <c r="B19" s="155" t="s">
+      <c r="B19" s="172" t="s">
         <v>32</v>
       </c>
       <c r="C19" s="127" t="s">
@@ -5305,8 +5309,8 @@
       <c r="J19" s="40"/>
     </row>
     <row r="20" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A20" s="173"/>
-      <c r="B20" s="161"/>
+      <c r="A20" s="290"/>
+      <c r="B20" s="173"/>
       <c r="C20" s="127" t="s">
         <v>36</v>
       </c>
@@ -5319,8 +5323,8 @@
       <c r="J20" s="40"/>
     </row>
     <row r="21" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A21" s="173"/>
-      <c r="B21" s="161"/>
+      <c r="A21" s="290"/>
+      <c r="B21" s="173"/>
       <c r="C21" s="127" t="s">
         <v>37</v>
       </c>
@@ -5333,8 +5337,8 @@
       <c r="J21" s="40"/>
     </row>
     <row r="22" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A22" s="173"/>
-      <c r="B22" s="161"/>
+      <c r="A22" s="290"/>
+      <c r="B22" s="173"/>
       <c r="C22" s="127" t="s">
         <v>38</v>
       </c>
@@ -5347,8 +5351,8 @@
       <c r="J22" s="40"/>
     </row>
     <row r="23" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A23" s="173"/>
-      <c r="B23" s="161"/>
+      <c r="A23" s="290"/>
+      <c r="B23" s="173"/>
       <c r="C23" s="127" t="s">
         <v>39</v>
       </c>
@@ -5361,8 +5365,8 @@
       <c r="J23" s="40"/>
     </row>
     <row r="24" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A24" s="173"/>
-      <c r="B24" s="161"/>
+      <c r="A24" s="290"/>
+      <c r="B24" s="173"/>
       <c r="C24" s="127" t="s">
         <v>40</v>
       </c>
@@ -5375,8 +5379,8 @@
       <c r="J24" s="40"/>
     </row>
     <row r="25" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A25" s="172"/>
-      <c r="B25" s="171"/>
+      <c r="A25" s="291"/>
+      <c r="B25" s="174"/>
       <c r="C25" s="127" t="s">
         <v>41</v>
       </c>
@@ -5409,10 +5413,10 @@
       <c r="J26" s="40"/>
     </row>
     <row r="27" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A27" s="157" t="s">
+      <c r="A27" s="288" t="s">
         <v>45</v>
       </c>
-      <c r="B27" s="155" t="s">
+      <c r="B27" s="172" t="s">
         <v>46</v>
       </c>
       <c r="C27" s="43" t="s">
@@ -5431,8 +5435,8 @@
       <c r="J27" s="40"/>
     </row>
     <row r="28" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A28" s="159"/>
-      <c r="B28" s="162"/>
+      <c r="A28" s="234"/>
+      <c r="B28" s="181"/>
       <c r="C28" s="43" t="s">
         <v>50</v>
       </c>
@@ -5445,8 +5449,8 @@
       <c r="J28" s="40"/>
     </row>
     <row r="29" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="159"/>
-      <c r="B29" s="162"/>
+      <c r="A29" s="234"/>
+      <c r="B29" s="181"/>
       <c r="C29" s="43" t="s">
         <v>271</v>
       </c>
@@ -5459,8 +5463,8 @@
       <c r="J29" s="40"/>
     </row>
     <row r="30" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A30" s="159"/>
-      <c r="B30" s="162"/>
+      <c r="A30" s="234"/>
+      <c r="B30" s="181"/>
       <c r="C30" s="43" t="s">
         <v>51</v>
       </c>
@@ -5473,8 +5477,8 @@
       <c r="J30" s="40"/>
     </row>
     <row r="31" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A31" s="159"/>
-      <c r="B31" s="162"/>
+      <c r="A31" s="234"/>
+      <c r="B31" s="181"/>
       <c r="C31" s="43" t="s">
         <v>52</v>
       </c>
@@ -5487,8 +5491,8 @@
       <c r="J31" s="40"/>
     </row>
     <row r="32" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A32" s="159"/>
-      <c r="B32" s="162"/>
+      <c r="A32" s="234"/>
+      <c r="B32" s="181"/>
       <c r="C32" s="43" t="s">
         <v>53</v>
       </c>
@@ -5501,8 +5505,8 @@
       <c r="J32" s="40"/>
     </row>
     <row r="33" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A33" s="160"/>
-      <c r="B33" s="156"/>
+      <c r="A33" s="235"/>
+      <c r="B33" s="183"/>
       <c r="C33" s="43" t="s">
         <v>473</v>
       </c>
@@ -5515,10 +5519,10 @@
       <c r="J33" s="40"/>
     </row>
     <row r="34" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A34" s="163" t="s">
+      <c r="A34" s="155" t="s">
         <v>54</v>
       </c>
-      <c r="B34" s="165" t="s">
+      <c r="B34" s="284" t="s">
         <v>55</v>
       </c>
       <c r="C34" s="129" t="s">
@@ -5535,8 +5539,8 @@
       <c r="J34" s="40"/>
     </row>
     <row r="35" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A35" s="164"/>
-      <c r="B35" s="166"/>
+      <c r="A35" s="231"/>
+      <c r="B35" s="287"/>
       <c r="C35" s="129" t="s">
         <v>25</v>
       </c>
@@ -5549,10 +5553,10 @@
       <c r="J35" s="40"/>
     </row>
     <row r="36" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="157" t="s">
+      <c r="A36" s="288" t="s">
         <v>57</v>
       </c>
-      <c r="B36" s="155" t="s">
+      <c r="B36" s="172" t="s">
         <v>58</v>
       </c>
       <c r="C36" s="95" t="s">
@@ -5575,8 +5579,8 @@
       </c>
     </row>
     <row r="37" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="159"/>
-      <c r="B37" s="162"/>
+      <c r="A37" s="234"/>
+      <c r="B37" s="181"/>
       <c r="C37" s="96" t="s">
         <v>64</v>
       </c>
@@ -5589,8 +5593,8 @@
       <c r="J37" s="40"/>
     </row>
     <row r="38" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="159"/>
-      <c r="B38" s="162"/>
+      <c r="A38" s="234"/>
+      <c r="B38" s="181"/>
       <c r="C38" s="96" t="s">
         <v>576</v>
       </c>
@@ -5603,8 +5607,8 @@
       <c r="J38" s="40"/>
     </row>
     <row r="39" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="159"/>
-      <c r="B39" s="162"/>
+      <c r="A39" s="234"/>
+      <c r="B39" s="181"/>
       <c r="C39" s="96" t="s">
         <v>575</v>
       </c>
@@ -5617,8 +5621,8 @@
       <c r="J39" s="40"/>
     </row>
     <row r="40" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="159"/>
-      <c r="B40" s="162"/>
+      <c r="A40" s="234"/>
+      <c r="B40" s="181"/>
       <c r="C40" s="96" t="s">
         <v>577</v>
       </c>
@@ -5631,8 +5635,8 @@
       <c r="J40" s="40"/>
     </row>
     <row r="41" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="159"/>
-      <c r="B41" s="162"/>
+      <c r="A41" s="234"/>
+      <c r="B41" s="181"/>
       <c r="C41" s="96" t="s">
         <v>578</v>
       </c>
@@ -5645,8 +5649,8 @@
       <c r="J41" s="40"/>
     </row>
     <row r="42" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="159"/>
-      <c r="B42" s="162"/>
+      <c r="A42" s="234"/>
+      <c r="B42" s="181"/>
       <c r="C42" s="96" t="s">
         <v>581</v>
       </c>
@@ -5659,8 +5663,8 @@
       <c r="J42" s="40"/>
     </row>
     <row r="43" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="159"/>
-      <c r="B43" s="162"/>
+      <c r="A43" s="234"/>
+      <c r="B43" s="181"/>
       <c r="C43" s="96" t="s">
         <v>580</v>
       </c>
@@ -5673,8 +5677,8 @@
       <c r="J43" s="40"/>
     </row>
     <row r="44" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="159"/>
-      <c r="B44" s="162"/>
+      <c r="A44" s="234"/>
+      <c r="B44" s="181"/>
       <c r="C44" s="96" t="s">
         <v>579</v>
       </c>
@@ -5687,8 +5691,8 @@
       <c r="J44" s="40"/>
     </row>
     <row r="45" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A45" s="159"/>
-      <c r="B45" s="162"/>
+      <c r="A45" s="234"/>
+      <c r="B45" s="181"/>
       <c r="C45" s="96" t="s">
         <v>65</v>
       </c>
@@ -5701,8 +5705,8 @@
       <c r="J45" s="40"/>
     </row>
     <row r="46" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="159"/>
-      <c r="B46" s="162"/>
+      <c r="A46" s="234"/>
+      <c r="B46" s="181"/>
       <c r="C46" s="96" t="s">
         <v>66</v>
       </c>
@@ -5715,8 +5719,8 @@
       <c r="J46" s="40"/>
     </row>
     <row r="47" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="159"/>
-      <c r="B47" s="162"/>
+      <c r="A47" s="234"/>
+      <c r="B47" s="181"/>
       <c r="C47" s="96" t="s">
         <v>67</v>
       </c>
@@ -5729,8 +5733,8 @@
       <c r="J47" s="40"/>
     </row>
     <row r="48" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="159"/>
-      <c r="B48" s="162"/>
+      <c r="A48" s="234"/>
+      <c r="B48" s="181"/>
       <c r="C48" s="96" t="s">
         <v>68</v>
       </c>
@@ -5743,10 +5747,10 @@
       <c r="J48" s="40"/>
     </row>
     <row r="49" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A49" s="167" t="s">
+      <c r="A49" s="289" t="s">
         <v>69</v>
       </c>
-      <c r="B49" s="155" t="s">
+      <c r="B49" s="172" t="s">
         <v>70</v>
       </c>
       <c r="C49" s="43" t="s">
@@ -5767,8 +5771,8 @@
       <c r="J49" s="40"/>
     </row>
     <row r="50" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A50" s="168"/>
-      <c r="B50" s="162"/>
+      <c r="A50" s="180"/>
+      <c r="B50" s="181"/>
       <c r="C50" s="43" t="s">
         <v>25</v>
       </c>
@@ -5781,8 +5785,8 @@
       <c r="J50" s="40"/>
     </row>
     <row r="51" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A51" s="154"/>
-      <c r="B51" s="156"/>
+      <c r="A51" s="182"/>
+      <c r="B51" s="183"/>
       <c r="C51" s="43" t="s">
         <v>75</v>
       </c>
@@ -5795,10 +5799,10 @@
       <c r="J51" s="40"/>
     </row>
     <row r="52" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A52" s="157" t="s">
+      <c r="A52" s="288" t="s">
         <v>76</v>
       </c>
-      <c r="B52" s="155" t="s">
+      <c r="B52" s="172" t="s">
         <v>77</v>
       </c>
       <c r="C52" s="43" t="s">
@@ -5819,8 +5823,8 @@
       <c r="J52" s="40"/>
     </row>
     <row r="53" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A53" s="158"/>
-      <c r="B53" s="161"/>
+      <c r="A53" s="297"/>
+      <c r="B53" s="173"/>
       <c r="C53" s="43" t="s">
         <v>78</v>
       </c>
@@ -5835,8 +5839,8 @@
       <c r="J53" s="40"/>
     </row>
     <row r="54" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A54" s="159"/>
-      <c r="B54" s="162"/>
+      <c r="A54" s="234"/>
+      <c r="B54" s="181"/>
       <c r="C54" s="43" t="s">
         <v>82</v>
       </c>
@@ -5851,8 +5855,8 @@
       <c r="J54" s="40"/>
     </row>
     <row r="55" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="159"/>
-      <c r="B55" s="162"/>
+      <c r="A55" s="234"/>
+      <c r="B55" s="181"/>
       <c r="C55" s="43" t="s">
         <v>688</v>
       </c>
@@ -5871,8 +5875,8 @@
       <c r="J55" s="40"/>
     </row>
     <row r="56" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A56" s="159"/>
-      <c r="B56" s="162"/>
+      <c r="A56" s="234"/>
+      <c r="B56" s="181"/>
       <c r="C56" s="43" t="s">
         <v>462</v>
       </c>
@@ -5885,8 +5889,8 @@
       <c r="J56" s="40"/>
     </row>
     <row r="57" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A57" s="159"/>
-      <c r="B57" s="162"/>
+      <c r="A57" s="234"/>
+      <c r="B57" s="181"/>
       <c r="C57" s="43" t="s">
         <v>87</v>
       </c>
@@ -5901,8 +5905,8 @@
       <c r="J57" s="40"/>
     </row>
     <row r="58" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A58" s="159"/>
-      <c r="B58" s="162"/>
+      <c r="A58" s="234"/>
+      <c r="B58" s="181"/>
       <c r="C58" s="43" t="s">
         <v>272</v>
       </c>
@@ -5915,8 +5919,8 @@
       <c r="J58" s="40"/>
     </row>
     <row r="59" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A59" s="160"/>
-      <c r="B59" s="156"/>
+      <c r="A59" s="235"/>
+      <c r="B59" s="183"/>
       <c r="C59" s="43" t="s">
         <v>89</v>
       </c>
@@ -5929,10 +5933,10 @@
       <c r="J59" s="40"/>
     </row>
     <row r="60" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A60" s="157" t="s">
+      <c r="A60" s="288" t="s">
         <v>90</v>
       </c>
-      <c r="B60" s="155" t="s">
+      <c r="B60" s="172" t="s">
         <v>583</v>
       </c>
       <c r="C60" s="43" t="s">
@@ -5947,8 +5951,8 @@
       <c r="J60" s="40"/>
     </row>
     <row r="61" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A61" s="159"/>
-      <c r="B61" s="162"/>
+      <c r="A61" s="234"/>
+      <c r="B61" s="181"/>
       <c r="C61" s="43" t="s">
         <v>273</v>
       </c>
@@ -5961,8 +5965,8 @@
       <c r="J61" s="40"/>
     </row>
     <row r="62" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="159"/>
-      <c r="B62" s="162"/>
+      <c r="A62" s="234"/>
+      <c r="B62" s="181"/>
       <c r="C62" s="43" t="s">
         <v>394</v>
       </c>
@@ -5977,8 +5981,8 @@
       <c r="J62" s="40"/>
     </row>
     <row r="63" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A63" s="159"/>
-      <c r="B63" s="162"/>
+      <c r="A63" s="234"/>
+      <c r="B63" s="181"/>
       <c r="C63" s="43" t="s">
         <v>91</v>
       </c>
@@ -5991,8 +5995,8 @@
       <c r="J63" s="40"/>
     </row>
     <row r="64" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A64" s="159"/>
-      <c r="B64" s="162"/>
+      <c r="A64" s="234"/>
+      <c r="B64" s="181"/>
       <c r="C64" s="43" t="s">
         <v>92</v>
       </c>
@@ -6005,8 +6009,8 @@
       <c r="J64" s="40"/>
     </row>
     <row r="65" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A65" s="159"/>
-      <c r="B65" s="162"/>
+      <c r="A65" s="234"/>
+      <c r="B65" s="181"/>
       <c r="C65" s="43" t="s">
         <v>93</v>
       </c>
@@ -6019,8 +6023,8 @@
       <c r="J65" s="40"/>
     </row>
     <row r="66" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A66" s="159"/>
-      <c r="B66" s="162"/>
+      <c r="A66" s="234"/>
+      <c r="B66" s="181"/>
       <c r="C66" s="43" t="s">
         <v>94</v>
       </c>
@@ -6033,8 +6037,8 @@
       <c r="J66" s="40"/>
     </row>
     <row r="67" spans="1:10" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="159"/>
-      <c r="B67" s="162"/>
+      <c r="A67" s="234"/>
+      <c r="B67" s="181"/>
       <c r="C67" s="43" t="s">
         <v>95</v>
       </c>
@@ -6047,8 +6051,8 @@
       <c r="J67" s="40"/>
     </row>
     <row r="68" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A68" s="160"/>
-      <c r="B68" s="156"/>
+      <c r="A68" s="235"/>
+      <c r="B68" s="183"/>
       <c r="C68" s="43" t="s">
         <v>96</v>
       </c>
@@ -6061,10 +6065,10 @@
       <c r="J68" s="40"/>
     </row>
     <row r="69" spans="1:10" ht="30.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A69" s="167" t="s">
+      <c r="A69" s="289" t="s">
         <v>97</v>
       </c>
-      <c r="B69" s="155" t="s">
+      <c r="B69" s="172" t="s">
         <v>658</v>
       </c>
       <c r="C69" s="43" t="s">
@@ -6085,8 +6089,8 @@
       <c r="J69" s="40"/>
     </row>
     <row r="70" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="173"/>
-      <c r="B70" s="161"/>
+      <c r="A70" s="290"/>
+      <c r="B70" s="173"/>
       <c r="C70" s="43" t="s">
         <v>584</v>
       </c>
@@ -6099,8 +6103,8 @@
       <c r="J70" s="40"/>
     </row>
     <row r="71" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A71" s="173"/>
-      <c r="B71" s="161"/>
+      <c r="A71" s="290"/>
+      <c r="B71" s="173"/>
       <c r="C71" s="43" t="s">
         <v>585</v>
       </c>
@@ -6113,8 +6117,8 @@
       <c r="J71" s="40"/>
     </row>
     <row r="72" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="173"/>
-      <c r="B72" s="161"/>
+      <c r="A72" s="290"/>
+      <c r="B72" s="173"/>
       <c r="C72" s="43" t="s">
         <v>586</v>
       </c>
@@ -6127,8 +6131,8 @@
       <c r="J72" s="40"/>
     </row>
     <row r="73" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A73" s="173"/>
-      <c r="B73" s="161"/>
+      <c r="A73" s="290"/>
+      <c r="B73" s="173"/>
       <c r="C73" s="43" t="s">
         <v>274</v>
       </c>
@@ -6143,8 +6147,8 @@
       <c r="J73" s="40"/>
     </row>
     <row r="74" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A74" s="173"/>
-      <c r="B74" s="161"/>
+      <c r="A74" s="290"/>
+      <c r="B74" s="173"/>
       <c r="C74" s="43" t="s">
         <v>275</v>
       </c>
@@ -6163,8 +6167,8 @@
       <c r="J74" s="40"/>
     </row>
     <row r="75" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A75" s="173"/>
-      <c r="B75" s="161"/>
+      <c r="A75" s="290"/>
+      <c r="B75" s="173"/>
       <c r="C75" s="43" t="s">
         <v>276</v>
       </c>
@@ -6179,8 +6183,8 @@
       <c r="J75" s="40"/>
     </row>
     <row r="76" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A76" s="173"/>
-      <c r="B76" s="161"/>
+      <c r="A76" s="290"/>
+      <c r="B76" s="173"/>
       <c r="C76" s="43" t="s">
         <v>277</v>
       </c>
@@ -6195,8 +6199,8 @@
       <c r="J76" s="40"/>
     </row>
     <row r="77" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A77" s="173"/>
-      <c r="B77" s="161"/>
+      <c r="A77" s="290"/>
+      <c r="B77" s="173"/>
       <c r="C77" s="43" t="s">
         <v>278</v>
       </c>
@@ -6211,8 +6215,8 @@
       <c r="J77" s="40"/>
     </row>
     <row r="78" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A78" s="173"/>
-      <c r="B78" s="161"/>
+      <c r="A78" s="290"/>
+      <c r="B78" s="173"/>
       <c r="C78" s="43" t="s">
         <v>279</v>
       </c>
@@ -6227,8 +6231,8 @@
       <c r="J78" s="40"/>
     </row>
     <row r="79" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A79" s="172"/>
-      <c r="B79" s="171"/>
+      <c r="A79" s="291"/>
+      <c r="B79" s="174"/>
       <c r="C79" s="43" t="s">
         <v>280</v>
       </c>
@@ -6247,10 +6251,10 @@
       <c r="J79" s="40"/>
     </row>
     <row r="80" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A80" s="167" t="s">
+      <c r="A80" s="289" t="s">
         <v>103</v>
       </c>
-      <c r="B80" s="155" t="s">
+      <c r="B80" s="172" t="s">
         <v>659</v>
       </c>
       <c r="C80" s="43" t="s">
@@ -6265,8 +6269,8 @@
       <c r="J80" s="40"/>
     </row>
     <row r="81" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A81" s="173"/>
-      <c r="B81" s="161"/>
+      <c r="A81" s="290"/>
+      <c r="B81" s="173"/>
       <c r="C81" s="43" t="s">
         <v>455</v>
       </c>
@@ -6279,8 +6283,8 @@
       <c r="J81" s="40"/>
     </row>
     <row r="82" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A82" s="173"/>
-      <c r="B82" s="161"/>
+      <c r="A82" s="290"/>
+      <c r="B82" s="173"/>
       <c r="C82" s="43" t="s">
         <v>456</v>
       </c>
@@ -6293,8 +6297,8 @@
       <c r="J82" s="40"/>
     </row>
     <row r="83" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A83" s="173"/>
-      <c r="B83" s="161"/>
+      <c r="A83" s="290"/>
+      <c r="B83" s="173"/>
       <c r="C83" s="43" t="s">
         <v>553</v>
       </c>
@@ -6307,8 +6311,8 @@
       <c r="J83" s="40"/>
     </row>
     <row r="84" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A84" s="168"/>
-      <c r="B84" s="162"/>
+      <c r="A84" s="180"/>
+      <c r="B84" s="181"/>
       <c r="C84" s="43" t="s">
         <v>274</v>
       </c>
@@ -6321,8 +6325,8 @@
       <c r="J84" s="40"/>
     </row>
     <row r="85" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A85" s="168"/>
-      <c r="B85" s="162"/>
+      <c r="A85" s="180"/>
+      <c r="B85" s="181"/>
       <c r="C85" s="43" t="s">
         <v>275</v>
       </c>
@@ -6335,8 +6339,8 @@
       <c r="J85" s="40"/>
     </row>
     <row r="86" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A86" s="168"/>
-      <c r="B86" s="162"/>
+      <c r="A86" s="180"/>
+      <c r="B86" s="181"/>
       <c r="C86" s="43" t="s">
         <v>276</v>
       </c>
@@ -6349,8 +6353,8 @@
       <c r="J86" s="40"/>
     </row>
     <row r="87" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A87" s="168"/>
-      <c r="B87" s="162"/>
+      <c r="A87" s="180"/>
+      <c r="B87" s="181"/>
       <c r="C87" s="43" t="s">
         <v>277</v>
       </c>
@@ -6363,8 +6367,8 @@
       <c r="J87" s="40"/>
     </row>
     <row r="88" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A88" s="168"/>
-      <c r="B88" s="162"/>
+      <c r="A88" s="180"/>
+      <c r="B88" s="181"/>
       <c r="C88" s="43" t="s">
         <v>278</v>
       </c>
@@ -6377,8 +6381,8 @@
       <c r="J88" s="40"/>
     </row>
     <row r="89" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A89" s="168"/>
-      <c r="B89" s="162"/>
+      <c r="A89" s="180"/>
+      <c r="B89" s="181"/>
       <c r="C89" s="43" t="s">
         <v>279</v>
       </c>
@@ -6391,8 +6395,8 @@
       <c r="J89" s="40"/>
     </row>
     <row r="90" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A90" s="154"/>
-      <c r="B90" s="156"/>
+      <c r="A90" s="182"/>
+      <c r="B90" s="183"/>
       <c r="C90" s="43" t="s">
         <v>280</v>
       </c>
@@ -6405,10 +6409,10 @@
       <c r="J90" s="40"/>
     </row>
     <row r="91" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A91" s="163" t="s">
+      <c r="A91" s="155" t="s">
         <v>104</v>
       </c>
-      <c r="B91" s="209" t="s">
+      <c r="B91" s="232" t="s">
         <v>464</v>
       </c>
       <c r="C91" s="43" t="s">
@@ -6427,8 +6431,8 @@
       <c r="J91" s="40"/>
     </row>
     <row r="92" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A92" s="208"/>
-      <c r="B92" s="162"/>
+      <c r="A92" s="230"/>
+      <c r="B92" s="181"/>
       <c r="C92" s="43" t="s">
         <v>108</v>
       </c>
@@ -6441,8 +6445,8 @@
       <c r="J92" s="40"/>
     </row>
     <row r="93" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A93" s="208"/>
-      <c r="B93" s="162"/>
+      <c r="A93" s="230"/>
+      <c r="B93" s="181"/>
       <c r="C93" s="43" t="s">
         <v>109</v>
       </c>
@@ -6457,8 +6461,8 @@
       <c r="J93" s="40"/>
     </row>
     <row r="94" spans="1:10" ht="20.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A94" s="208"/>
-      <c r="B94" s="162"/>
+      <c r="A94" s="230"/>
+      <c r="B94" s="181"/>
       <c r="C94" s="130" t="s">
         <v>678</v>
       </c>
@@ -6473,8 +6477,8 @@
       <c r="J94" s="40"/>
     </row>
     <row r="95" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A95" s="208"/>
-      <c r="B95" s="162"/>
+      <c r="A95" s="230"/>
+      <c r="B95" s="181"/>
       <c r="C95" s="43" t="s">
         <v>111</v>
       </c>
@@ -6487,8 +6491,8 @@
       <c r="J95" s="40"/>
     </row>
     <row r="96" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A96" s="208"/>
-      <c r="B96" s="162"/>
+      <c r="A96" s="230"/>
+      <c r="B96" s="181"/>
       <c r="C96" s="43" t="s">
         <v>112</v>
       </c>
@@ -6501,8 +6505,8 @@
       <c r="J96" s="40"/>
     </row>
     <row r="97" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A97" s="208"/>
-      <c r="B97" s="162"/>
+      <c r="A97" s="230"/>
+      <c r="B97" s="181"/>
       <c r="C97" s="43" t="s">
         <v>113</v>
       </c>
@@ -6517,8 +6521,8 @@
       <c r="J97" s="40"/>
     </row>
     <row r="98" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A98" s="208"/>
-      <c r="B98" s="162"/>
+      <c r="A98" s="230"/>
+      <c r="B98" s="181"/>
       <c r="C98" s="43" t="s">
         <v>114</v>
       </c>
@@ -6531,8 +6535,8 @@
       <c r="J98" s="40"/>
     </row>
     <row r="99" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A99" s="164"/>
-      <c r="B99" s="156"/>
+      <c r="A99" s="231"/>
+      <c r="B99" s="183"/>
       <c r="C99" s="43" t="s">
         <v>115</v>
       </c>
@@ -6545,10 +6549,10 @@
       <c r="J99" s="40"/>
     </row>
     <row r="100" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="210" t="s">
+      <c r="A100" s="233" t="s">
         <v>120</v>
       </c>
-      <c r="B100" s="155" t="s">
+      <c r="B100" s="172" t="s">
         <v>116</v>
       </c>
       <c r="C100" s="131">
@@ -6569,8 +6573,8 @@
       <c r="J100" s="40"/>
     </row>
     <row r="101" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A101" s="159"/>
-      <c r="B101" s="162"/>
+      <c r="A101" s="234"/>
+      <c r="B101" s="181"/>
       <c r="C101" s="131">
         <v>2</v>
       </c>
@@ -6587,8 +6591,8 @@
       <c r="J101" s="40"/>
     </row>
     <row r="102" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A102" s="159"/>
-      <c r="B102" s="162"/>
+      <c r="A102" s="234"/>
+      <c r="B102" s="181"/>
       <c r="C102" s="131">
         <v>3</v>
       </c>
@@ -6605,8 +6609,8 @@
       <c r="J102" s="40"/>
     </row>
     <row r="103" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A103" s="159"/>
-      <c r="B103" s="162"/>
+      <c r="A103" s="234"/>
+      <c r="B103" s="181"/>
       <c r="C103" s="131">
         <v>4</v>
       </c>
@@ -6623,8 +6627,8 @@
       <c r="J103" s="40"/>
     </row>
     <row r="104" spans="1:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A104" s="159"/>
-      <c r="B104" s="162"/>
+      <c r="A104" s="234"/>
+      <c r="B104" s="181"/>
       <c r="C104" s="131">
         <v>5</v>
       </c>
@@ -6641,8 +6645,8 @@
       <c r="J104" s="40"/>
     </row>
     <row r="105" spans="1:10" ht="12" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A105" s="159"/>
-      <c r="B105" s="162"/>
+      <c r="A105" s="234"/>
+      <c r="B105" s="181"/>
       <c r="C105" s="131">
         <v>6</v>
       </c>
@@ -6659,8 +6663,8 @@
       <c r="J105" s="40"/>
     </row>
     <row r="106" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A106" s="160"/>
-      <c r="B106" s="156"/>
+      <c r="A106" s="235"/>
+      <c r="B106" s="183"/>
       <c r="C106" s="127" t="s">
         <v>119</v>
       </c>
@@ -6673,10 +6677,10 @@
       <c r="J106" s="52"/>
     </row>
     <row r="107" spans="1:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="210" t="s">
+      <c r="A107" s="233" t="s">
         <v>122</v>
       </c>
-      <c r="B107" s="155" t="s">
+      <c r="B107" s="172" t="s">
         <v>660</v>
       </c>
       <c r="C107" s="62" t="s">
@@ -6693,8 +6697,8 @@
       <c r="J107" s="40"/>
     </row>
     <row r="108" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A108" s="216"/>
-      <c r="B108" s="218"/>
+      <c r="A108" s="240"/>
+      <c r="B108" s="242"/>
       <c r="C108" s="103" t="s">
         <v>199</v>
       </c>
@@ -6707,8 +6711,8 @@
       <c r="J108" s="40"/>
     </row>
     <row r="109" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A109" s="216"/>
-      <c r="B109" s="218"/>
+      <c r="A109" s="240"/>
+      <c r="B109" s="242"/>
       <c r="C109" s="43" t="s">
         <v>200</v>
       </c>
@@ -6721,8 +6725,8 @@
       <c r="J109" s="40"/>
     </row>
     <row r="110" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A110" s="216"/>
-      <c r="B110" s="218"/>
+      <c r="A110" s="240"/>
+      <c r="B110" s="242"/>
       <c r="C110" s="43" t="s">
         <v>201</v>
       </c>
@@ -6735,24 +6739,24 @@
       <c r="J110" s="40"/>
     </row>
     <row r="111" spans="1:10" ht="28.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="217"/>
-      <c r="B111" s="219"/>
-      <c r="C111" s="220" t="s">
+      <c r="A111" s="241"/>
+      <c r="B111" s="243"/>
+      <c r="C111" s="244" t="s">
         <v>119</v>
       </c>
-      <c r="D111" s="221"/>
-      <c r="E111" s="221"/>
-      <c r="F111" s="221"/>
-      <c r="G111" s="221"/>
-      <c r="H111" s="221"/>
-      <c r="I111" s="221"/>
-      <c r="J111" s="222"/>
+      <c r="D111" s="245"/>
+      <c r="E111" s="245"/>
+      <c r="F111" s="245"/>
+      <c r="G111" s="245"/>
+      <c r="H111" s="245"/>
+      <c r="I111" s="245"/>
+      <c r="J111" s="246"/>
     </row>
     <row r="112" spans="1:10" ht="57" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="211" t="s">
+      <c r="A112" s="236" t="s">
         <v>141</v>
       </c>
-      <c r="B112" s="212" t="s">
+      <c r="B112" s="237" t="s">
         <v>656</v>
       </c>
       <c r="C112" s="43" t="s">
@@ -6771,8 +6775,8 @@
       <c r="J112" s="53"/>
     </row>
     <row r="113" spans="1:10" ht="52.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A113" s="154"/>
-      <c r="B113" s="213"/>
+      <c r="A113" s="182"/>
+      <c r="B113" s="238"/>
       <c r="C113" s="43" t="s">
         <v>25</v>
       </c>
@@ -6787,10 +6791,10 @@
       <c r="J113" s="53"/>
     </row>
     <row r="114" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A114" s="211" t="s">
+      <c r="A114" s="236" t="s">
         <v>505</v>
       </c>
-      <c r="B114" s="214" t="s">
+      <c r="B114" s="239" t="s">
         <v>123</v>
       </c>
       <c r="C114" s="43" t="s">
@@ -6809,8 +6813,8 @@
       <c r="J114" s="53"/>
     </row>
     <row r="115" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A115" s="168"/>
-      <c r="B115" s="162"/>
+      <c r="A115" s="180"/>
+      <c r="B115" s="181"/>
       <c r="C115" s="43" t="s">
         <v>127</v>
       </c>
@@ -6823,8 +6827,8 @@
       <c r="J115" s="53"/>
     </row>
     <row r="116" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A116" s="168"/>
-      <c r="B116" s="162"/>
+      <c r="A116" s="180"/>
+      <c r="B116" s="181"/>
       <c r="C116" s="43" t="s">
         <v>128</v>
       </c>
@@ -6837,8 +6841,8 @@
       <c r="J116" s="53"/>
     </row>
     <row r="117" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A117" s="168"/>
-      <c r="B117" s="162"/>
+      <c r="A117" s="180"/>
+      <c r="B117" s="181"/>
       <c r="C117" s="43" t="s">
         <v>129</v>
       </c>
@@ -6851,8 +6855,8 @@
       <c r="J117" s="53"/>
     </row>
     <row r="118" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A118" s="168"/>
-      <c r="B118" s="162"/>
+      <c r="A118" s="180"/>
+      <c r="B118" s="181"/>
       <c r="C118" s="43" t="s">
         <v>130</v>
       </c>
@@ -6865,8 +6869,8 @@
       <c r="J118" s="53"/>
     </row>
     <row r="119" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A119" s="168"/>
-      <c r="B119" s="162"/>
+      <c r="A119" s="180"/>
+      <c r="B119" s="181"/>
       <c r="C119" s="43" t="s">
         <v>131</v>
       </c>
@@ -6879,8 +6883,8 @@
       <c r="J119" s="53"/>
     </row>
     <row r="120" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A120" s="154"/>
-      <c r="B120" s="156"/>
+      <c r="A120" s="182"/>
+      <c r="B120" s="183"/>
       <c r="C120" s="43" t="s">
         <v>132</v>
       </c>
@@ -6893,10 +6897,10 @@
       <c r="J120" s="53"/>
     </row>
     <row r="121" spans="1:10" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A121" s="210" t="s">
+      <c r="A121" s="233" t="s">
         <v>142</v>
       </c>
-      <c r="B121" s="155" t="s">
+      <c r="B121" s="172" t="s">
         <v>657</v>
       </c>
       <c r="C121" s="43" t="s">
@@ -6917,8 +6921,8 @@
       <c r="J121" s="40"/>
     </row>
     <row r="122" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A122" s="239"/>
-      <c r="B122" s="161"/>
+      <c r="A122" s="260"/>
+      <c r="B122" s="173"/>
       <c r="C122" s="43" t="s">
         <v>589</v>
       </c>
@@ -6931,8 +6935,8 @@
       <c r="J122" s="40"/>
     </row>
     <row r="123" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A123" s="159"/>
-      <c r="B123" s="162"/>
+      <c r="A123" s="234"/>
+      <c r="B123" s="181"/>
       <c r="C123" s="43" t="s">
         <v>136</v>
       </c>
@@ -6945,8 +6949,8 @@
       <c r="J123" s="40"/>
     </row>
     <row r="124" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A124" s="159"/>
-      <c r="B124" s="162"/>
+      <c r="A124" s="234"/>
+      <c r="B124" s="181"/>
       <c r="C124" s="43" t="s">
         <v>137</v>
       </c>
@@ -6959,8 +6963,8 @@
       <c r="J124" s="40"/>
     </row>
     <row r="125" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A125" s="159"/>
-      <c r="B125" s="162"/>
+      <c r="A125" s="234"/>
+      <c r="B125" s="181"/>
       <c r="C125" s="43" t="s">
         <v>138</v>
       </c>
@@ -6973,8 +6977,8 @@
       <c r="J125" s="40"/>
     </row>
     <row r="126" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A126" s="159"/>
-      <c r="B126" s="162"/>
+      <c r="A126" s="234"/>
+      <c r="B126" s="181"/>
       <c r="C126" s="43" t="s">
         <v>590</v>
       </c>
@@ -6987,8 +6991,8 @@
       <c r="J126" s="40"/>
     </row>
     <row r="127" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A127" s="160"/>
-      <c r="B127" s="156"/>
+      <c r="A127" s="235"/>
+      <c r="B127" s="183"/>
       <c r="C127" s="94" t="s">
         <v>465</v>
       </c>
@@ -7005,10 +7009,10 @@
       <c r="J127" s="40"/>
     </row>
     <row r="128" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A128" s="235" t="s">
+      <c r="A128" s="256" t="s">
         <v>538</v>
       </c>
-      <c r="B128" s="237" t="s">
+      <c r="B128" s="258" t="s">
         <v>486</v>
       </c>
       <c r="C128" s="139" t="s">
@@ -7023,8 +7027,8 @@
       <c r="J128" s="62"/>
     </row>
     <row r="129" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A129" s="236"/>
-      <c r="B129" s="238"/>
+      <c r="A129" s="257"/>
+      <c r="B129" s="259"/>
       <c r="C129" s="139" t="s">
         <v>23</v>
       </c>
@@ -7037,8 +7041,8 @@
       <c r="J129" s="62"/>
     </row>
     <row r="130" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A130" s="236"/>
-      <c r="B130" s="238"/>
+      <c r="A130" s="257"/>
+      <c r="B130" s="259"/>
       <c r="C130" s="139" t="s">
         <v>25</v>
       </c>
@@ -7051,38 +7055,38 @@
       <c r="J130" s="62"/>
     </row>
     <row r="131" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A131" s="175" t="s">
+      <c r="A131" s="261" t="s">
         <v>546</v>
       </c>
-      <c r="B131" s="151"/>
-      <c r="C131" s="151"/>
-      <c r="D131" s="151"/>
-      <c r="E131" s="151"/>
-      <c r="F131" s="151"/>
-      <c r="G131" s="151"/>
-      <c r="H131" s="151"/>
-      <c r="I131" s="151"/>
-      <c r="J131" s="152"/>
+      <c r="B131" s="262"/>
+      <c r="C131" s="262"/>
+      <c r="D131" s="262"/>
+      <c r="E131" s="262"/>
+      <c r="F131" s="262"/>
+      <c r="G131" s="262"/>
+      <c r="H131" s="262"/>
+      <c r="I131" s="262"/>
+      <c r="J131" s="263"/>
     </row>
     <row r="132" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A132" s="185" t="s">
+      <c r="A132" s="146" t="s">
         <v>548</v>
       </c>
-      <c r="B132" s="186"/>
-      <c r="C132" s="186"/>
-      <c r="D132" s="186"/>
-      <c r="E132" s="186"/>
-      <c r="F132" s="186"/>
-      <c r="G132" s="186"/>
-      <c r="H132" s="186"/>
-      <c r="I132" s="186"/>
-      <c r="J132" s="187"/>
+      <c r="B132" s="147"/>
+      <c r="C132" s="147"/>
+      <c r="D132" s="147"/>
+      <c r="E132" s="147"/>
+      <c r="F132" s="147"/>
+      <c r="G132" s="147"/>
+      <c r="H132" s="147"/>
+      <c r="I132" s="147"/>
+      <c r="J132" s="148"/>
     </row>
     <row r="133" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A133" s="246" t="s">
+      <c r="A133" s="206" t="s">
         <v>188</v>
       </c>
-      <c r="B133" s="245" t="s">
+      <c r="B133" s="205" t="s">
         <v>398</v>
       </c>
       <c r="C133" s="97" t="s">
@@ -7097,8 +7101,8 @@
       <c r="J133" s="40"/>
     </row>
     <row r="134" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A134" s="247"/>
-      <c r="B134" s="245"/>
+      <c r="A134" s="207"/>
+      <c r="B134" s="205"/>
       <c r="C134" s="98" t="s">
         <v>591</v>
       </c>
@@ -7111,8 +7115,8 @@
       <c r="J134" s="40"/>
     </row>
     <row r="135" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A135" s="247"/>
-      <c r="B135" s="245"/>
+      <c r="A135" s="207"/>
+      <c r="B135" s="205"/>
       <c r="C135" s="98" t="s">
         <v>399</v>
       </c>
@@ -7125,8 +7129,8 @@
       <c r="J135" s="40"/>
     </row>
     <row r="136" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A136" s="248"/>
-      <c r="B136" s="245"/>
+      <c r="A136" s="208"/>
+      <c r="B136" s="205"/>
       <c r="C136" s="98" t="s">
         <v>592</v>
       </c>
@@ -7139,10 +7143,10 @@
       <c r="J136" s="40"/>
     </row>
     <row r="137" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A137" s="226" t="s">
+      <c r="A137" s="250" t="s">
         <v>190</v>
       </c>
-      <c r="B137" s="223" t="s">
+      <c r="B137" s="247" t="s">
         <v>467</v>
       </c>
       <c r="C137" s="97" t="s">
@@ -7157,8 +7161,8 @@
       <c r="J137" s="40"/>
     </row>
     <row r="138" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A138" s="227"/>
-      <c r="B138" s="224"/>
+      <c r="A138" s="251"/>
+      <c r="B138" s="248"/>
       <c r="C138" s="97" t="s">
         <v>593</v>
       </c>
@@ -7171,8 +7175,8 @@
       <c r="J138" s="40"/>
     </row>
     <row r="139" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A139" s="227"/>
-      <c r="B139" s="224"/>
+      <c r="A139" s="251"/>
+      <c r="B139" s="248"/>
       <c r="C139" s="97" t="s">
         <v>466</v>
       </c>
@@ -7185,8 +7189,8 @@
       <c r="J139" s="40"/>
     </row>
     <row r="140" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A140" s="228"/>
-      <c r="B140" s="225"/>
+      <c r="A140" s="252"/>
+      <c r="B140" s="249"/>
       <c r="C140" s="99" t="s">
         <v>594</v>
       </c>
@@ -7199,10 +7203,10 @@
       <c r="J140" s="40"/>
     </row>
     <row r="141" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A141" s="198" t="s">
+      <c r="A141" s="277" t="s">
         <v>196</v>
       </c>
-      <c r="B141" s="195" t="s">
+      <c r="B141" s="274" t="s">
         <v>380</v>
       </c>
       <c r="C141" s="100">
@@ -7219,8 +7223,8 @@
       <c r="J141" s="40"/>
     </row>
     <row r="142" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A142" s="199"/>
-      <c r="B142" s="196"/>
+      <c r="A142" s="278"/>
+      <c r="B142" s="275"/>
       <c r="C142" s="100">
         <v>1</v>
       </c>
@@ -7233,8 +7237,8 @@
       <c r="J142" s="40"/>
     </row>
     <row r="143" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A143" s="199"/>
-      <c r="B143" s="196"/>
+      <c r="A143" s="278"/>
+      <c r="B143" s="275"/>
       <c r="C143" s="100">
         <v>2</v>
       </c>
@@ -7247,8 +7251,8 @@
       <c r="J143" s="40"/>
     </row>
     <row r="144" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A144" s="199"/>
-      <c r="B144" s="196"/>
+      <c r="A144" s="278"/>
+      <c r="B144" s="275"/>
       <c r="C144" s="100">
         <v>3</v>
       </c>
@@ -7261,8 +7265,8 @@
       <c r="J144" s="40"/>
     </row>
     <row r="145" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A145" s="200"/>
-      <c r="B145" s="197"/>
+      <c r="A145" s="279"/>
+      <c r="B145" s="276"/>
       <c r="C145" s="100" t="s">
         <v>596</v>
       </c>
@@ -7275,10 +7279,10 @@
       <c r="J145" s="40"/>
     </row>
     <row r="146" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A146" s="201" t="s">
+      <c r="A146" s="280" t="s">
         <v>392</v>
       </c>
-      <c r="B146" s="195" t="s">
+      <c r="B146" s="274" t="s">
         <v>396</v>
       </c>
       <c r="C146" s="100">
@@ -7293,8 +7297,8 @@
       <c r="J146" s="40"/>
     </row>
     <row r="147" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A147" s="202"/>
-      <c r="B147" s="196"/>
+      <c r="A147" s="281"/>
+      <c r="B147" s="275"/>
       <c r="C147" s="100">
         <v>1</v>
       </c>
@@ -7307,8 +7311,8 @@
       <c r="J147" s="40"/>
     </row>
     <row r="148" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A148" s="202"/>
-      <c r="B148" s="196"/>
+      <c r="A148" s="281"/>
+      <c r="B148" s="275"/>
       <c r="C148" s="100">
         <v>2</v>
       </c>
@@ -7321,8 +7325,8 @@
       <c r="J148" s="40"/>
     </row>
     <row r="149" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A149" s="202"/>
-      <c r="B149" s="196"/>
+      <c r="A149" s="281"/>
+      <c r="B149" s="275"/>
       <c r="C149" s="100">
         <v>3</v>
       </c>
@@ -7335,8 +7339,8 @@
       <c r="J149" s="40"/>
     </row>
     <row r="150" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A150" s="203"/>
-      <c r="B150" s="197"/>
+      <c r="A150" s="282"/>
+      <c r="B150" s="276"/>
       <c r="C150" s="100" t="s">
         <v>596</v>
       </c>
@@ -7349,10 +7353,10 @@
       <c r="J150" s="40"/>
     </row>
     <row r="151" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A151" s="198" t="s">
+      <c r="A151" s="277" t="s">
         <v>197</v>
       </c>
-      <c r="B151" s="195" t="s">
+      <c r="B151" s="274" t="s">
         <v>381</v>
       </c>
       <c r="C151" s="100">
@@ -7369,8 +7373,8 @@
       <c r="J151" s="40"/>
     </row>
     <row r="152" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A152" s="199"/>
-      <c r="B152" s="196"/>
+      <c r="A152" s="278"/>
+      <c r="B152" s="275"/>
       <c r="C152" s="100">
         <v>1</v>
       </c>
@@ -7383,8 +7387,8 @@
       <c r="J152" s="40"/>
     </row>
     <row r="153" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A153" s="199"/>
-      <c r="B153" s="196"/>
+      <c r="A153" s="278"/>
+      <c r="B153" s="275"/>
       <c r="C153" s="100">
         <v>2</v>
       </c>
@@ -7397,8 +7401,8 @@
       <c r="J153" s="40"/>
     </row>
     <row r="154" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A154" s="199"/>
-      <c r="B154" s="196"/>
+      <c r="A154" s="278"/>
+      <c r="B154" s="275"/>
       <c r="C154" s="100">
         <v>3</v>
       </c>
@@ -7411,8 +7415,8 @@
       <c r="J154" s="40"/>
     </row>
     <row r="155" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A155" s="200"/>
-      <c r="B155" s="197"/>
+      <c r="A155" s="279"/>
+      <c r="B155" s="276"/>
       <c r="C155" s="100" t="s">
         <v>596</v>
       </c>
@@ -7425,10 +7429,10 @@
       <c r="J155" s="40"/>
     </row>
     <row r="156" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A156" s="201" t="s">
+      <c r="A156" s="280" t="s">
         <v>507</v>
       </c>
-      <c r="B156" s="195" t="s">
+      <c r="B156" s="274" t="s">
         <v>395</v>
       </c>
       <c r="C156" s="100">
@@ -7443,8 +7447,8 @@
       <c r="J156" s="40"/>
     </row>
     <row r="157" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A157" s="202"/>
-      <c r="B157" s="196"/>
+      <c r="A157" s="281"/>
+      <c r="B157" s="275"/>
       <c r="C157" s="100">
         <v>1</v>
       </c>
@@ -7457,8 +7461,8 @@
       <c r="J157" s="40"/>
     </row>
     <row r="158" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A158" s="202"/>
-      <c r="B158" s="196"/>
+      <c r="A158" s="281"/>
+      <c r="B158" s="275"/>
       <c r="C158" s="100">
         <v>2</v>
       </c>
@@ -7471,8 +7475,8 @@
       <c r="J158" s="40"/>
     </row>
     <row r="159" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A159" s="202"/>
-      <c r="B159" s="196"/>
+      <c r="A159" s="281"/>
+      <c r="B159" s="275"/>
       <c r="C159" s="100">
         <v>3</v>
       </c>
@@ -7485,8 +7489,8 @@
       <c r="J159" s="40"/>
     </row>
     <row r="160" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A160" s="203"/>
-      <c r="B160" s="197"/>
+      <c r="A160" s="282"/>
+      <c r="B160" s="276"/>
       <c r="C160" s="100" t="s">
         <v>596</v>
       </c>
@@ -7499,10 +7503,10 @@
       <c r="J160" s="40"/>
     </row>
     <row r="161" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A161" s="258" t="s">
+      <c r="A161" s="218" t="s">
         <v>202</v>
       </c>
-      <c r="B161" s="165" t="s">
+      <c r="B161" s="284" t="s">
         <v>611</v>
       </c>
       <c r="C161" s="97" t="s">
@@ -7519,8 +7523,8 @@
       <c r="J161" s="40"/>
     </row>
     <row r="162" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A162" s="258"/>
-      <c r="B162" s="206"/>
+      <c r="A162" s="218"/>
+      <c r="B162" s="285"/>
       <c r="C162" s="92" t="s">
         <v>454</v>
       </c>
@@ -7535,8 +7539,8 @@
       <c r="J162" s="40"/>
     </row>
     <row r="163" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A163" s="258"/>
-      <c r="B163" s="206"/>
+      <c r="A163" s="218"/>
+      <c r="B163" s="285"/>
       <c r="C163" s="92" t="s">
         <v>482</v>
       </c>
@@ -7551,8 +7555,8 @@
       <c r="J163" s="40"/>
     </row>
     <row r="164" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A164" s="168"/>
-      <c r="B164" s="207"/>
+      <c r="A164" s="180"/>
+      <c r="B164" s="286"/>
       <c r="C164" s="97" t="s">
         <v>554</v>
       </c>
@@ -7567,8 +7571,8 @@
       <c r="J164" s="40"/>
     </row>
     <row r="165" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A165" s="168"/>
-      <c r="B165" s="207"/>
+      <c r="A165" s="180"/>
+      <c r="B165" s="286"/>
       <c r="C165" s="92" t="s">
         <v>149</v>
       </c>
@@ -7583,8 +7587,8 @@
       <c r="J165" s="40"/>
     </row>
     <row r="166" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A166" s="168"/>
-      <c r="B166" s="207"/>
+      <c r="A166" s="180"/>
+      <c r="B166" s="286"/>
       <c r="C166" s="92" t="s">
         <v>150</v>
       </c>
@@ -7601,8 +7605,8 @@
       <c r="J166" s="40"/>
     </row>
     <row r="167" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A167" s="168"/>
-      <c r="B167" s="207"/>
+      <c r="A167" s="180"/>
+      <c r="B167" s="286"/>
       <c r="C167" s="97" t="s">
         <v>620</v>
       </c>
@@ -7619,8 +7623,8 @@
       <c r="J167" s="40"/>
     </row>
     <row r="168" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A168" s="168"/>
-      <c r="B168" s="207"/>
+      <c r="A168" s="180"/>
+      <c r="B168" s="286"/>
       <c r="C168" s="97" t="s">
         <v>153</v>
       </c>
@@ -7635,8 +7639,8 @@
       <c r="J168" s="40"/>
     </row>
     <row r="169" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A169" s="168"/>
-      <c r="B169" s="207"/>
+      <c r="A169" s="180"/>
+      <c r="B169" s="286"/>
       <c r="C169" s="97" t="s">
         <v>154</v>
       </c>
@@ -7651,8 +7655,8 @@
       <c r="J169" s="40"/>
     </row>
     <row r="170" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A170" s="168"/>
-      <c r="B170" s="207"/>
+      <c r="A170" s="180"/>
+      <c r="B170" s="286"/>
       <c r="C170" s="97" t="s">
         <v>155</v>
       </c>
@@ -7667,8 +7671,8 @@
       <c r="J170" s="40"/>
     </row>
     <row r="171" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A171" s="168"/>
-      <c r="B171" s="207"/>
+      <c r="A171" s="180"/>
+      <c r="B171" s="286"/>
       <c r="C171" s="92" t="s">
         <v>621</v>
       </c>
@@ -7685,8 +7689,8 @@
       <c r="J171" s="40"/>
     </row>
     <row r="172" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A172" s="168"/>
-      <c r="B172" s="207"/>
+      <c r="A172" s="180"/>
+      <c r="B172" s="286"/>
       <c r="C172" s="92" t="s">
         <v>157</v>
       </c>
@@ -7703,8 +7707,8 @@
       <c r="J172" s="40"/>
     </row>
     <row r="173" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A173" s="168"/>
-      <c r="B173" s="207"/>
+      <c r="A173" s="180"/>
+      <c r="B173" s="286"/>
       <c r="C173" s="92" t="s">
         <v>629</v>
       </c>
@@ -7721,8 +7725,8 @@
       <c r="J173" s="40"/>
     </row>
     <row r="174" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A174" s="168"/>
-      <c r="B174" s="207"/>
+      <c r="A174" s="180"/>
+      <c r="B174" s="286"/>
       <c r="C174" s="92" t="s">
         <v>159</v>
       </c>
@@ -7739,8 +7743,8 @@
       <c r="J174" s="40"/>
     </row>
     <row r="175" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A175" s="168"/>
-      <c r="B175" s="207"/>
+      <c r="A175" s="180"/>
+      <c r="B175" s="286"/>
       <c r="C175" s="92" t="s">
         <v>160</v>
       </c>
@@ -7757,8 +7761,8 @@
       <c r="J175" s="40"/>
     </row>
     <row r="176" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A176" s="168"/>
-      <c r="B176" s="207"/>
+      <c r="A176" s="180"/>
+      <c r="B176" s="286"/>
       <c r="C176" s="92" t="s">
         <v>161</v>
       </c>
@@ -7775,8 +7779,8 @@
       <c r="J176" s="40"/>
     </row>
     <row r="177" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A177" s="168"/>
-      <c r="B177" s="207"/>
+      <c r="A177" s="180"/>
+      <c r="B177" s="286"/>
       <c r="C177" s="92" t="s">
         <v>162</v>
       </c>
@@ -7791,8 +7795,8 @@
       <c r="J177" s="40"/>
     </row>
     <row r="178" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A178" s="168"/>
-      <c r="B178" s="207"/>
+      <c r="A178" s="180"/>
+      <c r="B178" s="286"/>
       <c r="C178" s="92" t="s">
         <v>163</v>
       </c>
@@ -7809,8 +7813,8 @@
       <c r="J178" s="40"/>
     </row>
     <row r="179" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A179" s="168"/>
-      <c r="B179" s="207"/>
+      <c r="A179" s="180"/>
+      <c r="B179" s="286"/>
       <c r="C179" s="92" t="s">
         <v>510</v>
       </c>
@@ -7825,8 +7829,8 @@
       <c r="J179" s="40"/>
     </row>
     <row r="180" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A180" s="168"/>
-      <c r="B180" s="207"/>
+      <c r="A180" s="180"/>
+      <c r="B180" s="286"/>
       <c r="C180" s="92" t="s">
         <v>165</v>
       </c>
@@ -7843,8 +7847,8 @@
       <c r="J180" s="40"/>
     </row>
     <row r="181" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A181" s="168"/>
-      <c r="B181" s="207"/>
+      <c r="A181" s="180"/>
+      <c r="B181" s="286"/>
       <c r="C181" s="92" t="s">
         <v>166</v>
       </c>
@@ -7861,8 +7865,8 @@
       <c r="J181" s="40"/>
     </row>
     <row r="182" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A182" s="168"/>
-      <c r="B182" s="207"/>
+      <c r="A182" s="180"/>
+      <c r="B182" s="286"/>
       <c r="C182" s="92" t="s">
         <v>167</v>
       </c>
@@ -7877,8 +7881,8 @@
       <c r="J182" s="40"/>
     </row>
     <row r="183" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A183" s="154"/>
-      <c r="B183" s="166"/>
+      <c r="A183" s="182"/>
+      <c r="B183" s="287"/>
       <c r="C183" s="92" t="s">
         <v>168</v>
       </c>
@@ -7895,10 +7899,10 @@
       <c r="J183" s="40"/>
     </row>
     <row r="184" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A184" s="229" t="s">
+      <c r="A184" s="158" t="s">
         <v>508</v>
       </c>
-      <c r="B184" s="232" t="s">
+      <c r="B184" s="253" t="s">
         <v>509</v>
       </c>
       <c r="C184" s="106" t="s">
@@ -7913,8 +7917,8 @@
       <c r="J184" s="40"/>
     </row>
     <row r="185" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A185" s="230"/>
-      <c r="B185" s="233"/>
+      <c r="A185" s="159"/>
+      <c r="B185" s="254"/>
       <c r="C185" s="101" t="s">
         <v>510</v>
       </c>
@@ -7927,8 +7931,8 @@
       <c r="J185" s="40"/>
     </row>
     <row r="186" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A186" s="230"/>
-      <c r="B186" s="233"/>
+      <c r="A186" s="159"/>
+      <c r="B186" s="254"/>
       <c r="C186" s="101" t="s">
         <v>168</v>
       </c>
@@ -7941,8 +7945,8 @@
       <c r="J186" s="40"/>
     </row>
     <row r="187" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A187" s="231"/>
-      <c r="B187" s="234"/>
+      <c r="A187" s="160"/>
+      <c r="B187" s="255"/>
       <c r="C187" s="101" t="s">
         <v>511</v>
       </c>
@@ -7955,16 +7959,16 @@
       <c r="J187" s="40"/>
     </row>
     <row r="188" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A188" s="182" t="s">
+      <c r="A188" s="163" t="s">
         <v>512</v>
       </c>
-      <c r="B188" s="255" t="s">
+      <c r="B188" s="215" t="s">
         <v>661</v>
       </c>
       <c r="C188" s="90" t="s">
         <v>452</v>
       </c>
-      <c r="D188" s="188" t="s">
+      <c r="D188" s="269" t="s">
         <v>516</v>
       </c>
       <c r="E188" s="39"/>
@@ -7975,12 +7979,12 @@
       <c r="J188" s="40"/>
     </row>
     <row r="189" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A189" s="182"/>
-      <c r="B189" s="256"/>
+      <c r="A189" s="163"/>
+      <c r="B189" s="216"/>
       <c r="C189" s="90" t="s">
         <v>322</v>
       </c>
-      <c r="D189" s="189"/>
+      <c r="D189" s="270"/>
       <c r="E189" s="39"/>
       <c r="F189" s="39"/>
       <c r="G189" s="40"/>
@@ -7989,12 +7993,12 @@
       <c r="J189" s="40"/>
     </row>
     <row r="190" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A190" s="182"/>
-      <c r="B190" s="256"/>
+      <c r="A190" s="163"/>
+      <c r="B190" s="216"/>
       <c r="C190" s="90" t="s">
         <v>323</v>
       </c>
-      <c r="D190" s="189"/>
+      <c r="D190" s="270"/>
       <c r="E190" s="39"/>
       <c r="F190" s="39"/>
       <c r="G190" s="40"/>
@@ -8003,12 +8007,12 @@
       <c r="J190" s="40"/>
     </row>
     <row r="191" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A191" s="182"/>
-      <c r="B191" s="256"/>
+      <c r="A191" s="163"/>
+      <c r="B191" s="216"/>
       <c r="C191" s="90" t="s">
         <v>324</v>
       </c>
-      <c r="D191" s="189"/>
+      <c r="D191" s="270"/>
       <c r="E191" s="39"/>
       <c r="F191" s="39"/>
       <c r="G191" s="40"/>
@@ -8017,12 +8021,12 @@
       <c r="J191" s="40"/>
     </row>
     <row r="192" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A192" s="182"/>
-      <c r="B192" s="256"/>
+      <c r="A192" s="163"/>
+      <c r="B192" s="216"/>
       <c r="C192" s="90" t="s">
         <v>325</v>
       </c>
-      <c r="D192" s="189"/>
+      <c r="D192" s="270"/>
       <c r="E192" s="39"/>
       <c r="F192" s="39"/>
       <c r="G192" s="40"/>
@@ -8031,12 +8035,12 @@
       <c r="J192" s="40"/>
     </row>
     <row r="193" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A193" s="182"/>
-      <c r="B193" s="256"/>
+      <c r="A193" s="163"/>
+      <c r="B193" s="216"/>
       <c r="C193" s="90" t="s">
         <v>326</v>
       </c>
-      <c r="D193" s="189"/>
+      <c r="D193" s="270"/>
       <c r="E193" s="39"/>
       <c r="F193" s="39"/>
       <c r="G193" s="40"/>
@@ -8045,12 +8049,12 @@
       <c r="J193" s="40"/>
     </row>
     <row r="194" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A194" s="182"/>
-      <c r="B194" s="256"/>
+      <c r="A194" s="163"/>
+      <c r="B194" s="216"/>
       <c r="C194" s="90" t="s">
         <v>327</v>
       </c>
-      <c r="D194" s="189"/>
+      <c r="D194" s="270"/>
       <c r="E194" s="39"/>
       <c r="F194" s="39"/>
       <c r="G194" s="40"/>
@@ -8059,12 +8063,12 @@
       <c r="J194" s="40"/>
     </row>
     <row r="195" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A195" s="182"/>
-      <c r="B195" s="257"/>
+      <c r="A195" s="163"/>
+      <c r="B195" s="217"/>
       <c r="C195" s="140" t="s">
         <v>315</v>
       </c>
-      <c r="D195" s="190"/>
+      <c r="D195" s="271"/>
       <c r="E195" s="39"/>
       <c r="F195" s="39"/>
       <c r="G195" s="40"/>
@@ -8073,16 +8077,16 @@
       <c r="J195" s="40"/>
     </row>
     <row r="196" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A196" s="181" t="s">
+      <c r="A196" s="179" t="s">
         <v>513</v>
       </c>
-      <c r="B196" s="249" t="s">
+      <c r="B196" s="209" t="s">
         <v>555</v>
       </c>
       <c r="C196" s="90" t="s">
         <v>453</v>
       </c>
-      <c r="D196" s="188" t="s">
+      <c r="D196" s="269" t="s">
         <v>516</v>
       </c>
       <c r="E196" s="39"/>
@@ -8093,12 +8097,12 @@
       <c r="J196" s="40"/>
     </row>
     <row r="197" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A197" s="178"/>
-      <c r="B197" s="250"/>
+      <c r="A197" s="222"/>
+      <c r="B197" s="210"/>
       <c r="C197" s="90" t="s">
         <v>597</v>
       </c>
-      <c r="D197" s="189"/>
+      <c r="D197" s="270"/>
       <c r="E197" s="39"/>
       <c r="F197" s="39"/>
       <c r="G197" s="40"/>
@@ -8107,12 +8111,12 @@
       <c r="J197" s="40"/>
     </row>
     <row r="198" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A198" s="178"/>
-      <c r="B198" s="250"/>
+      <c r="A198" s="222"/>
+      <c r="B198" s="210"/>
       <c r="C198" s="90" t="s">
         <v>598</v>
       </c>
-      <c r="D198" s="189"/>
+      <c r="D198" s="270"/>
       <c r="E198" s="39"/>
       <c r="F198" s="39"/>
       <c r="G198" s="40"/>
@@ -8121,12 +8125,12 @@
       <c r="J198" s="40"/>
     </row>
     <row r="199" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A199" s="178"/>
-      <c r="B199" s="250"/>
+      <c r="A199" s="222"/>
+      <c r="B199" s="210"/>
       <c r="C199" s="90" t="s">
         <v>599</v>
       </c>
-      <c r="D199" s="189"/>
+      <c r="D199" s="270"/>
       <c r="E199" s="39"/>
       <c r="F199" s="39"/>
       <c r="G199" s="40"/>
@@ -8135,12 +8139,12 @@
       <c r="J199" s="40"/>
     </row>
     <row r="200" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A200" s="178"/>
-      <c r="B200" s="250"/>
+      <c r="A200" s="222"/>
+      <c r="B200" s="210"/>
       <c r="C200" s="90" t="s">
         <v>600</v>
       </c>
-      <c r="D200" s="189"/>
+      <c r="D200" s="270"/>
       <c r="E200" s="39"/>
       <c r="F200" s="39"/>
       <c r="G200" s="40"/>
@@ -8149,12 +8153,12 @@
       <c r="J200" s="40"/>
     </row>
     <row r="201" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A201" s="178"/>
-      <c r="B201" s="250"/>
+      <c r="A201" s="222"/>
+      <c r="B201" s="210"/>
       <c r="C201" s="90" t="s">
         <v>601</v>
       </c>
-      <c r="D201" s="189"/>
+      <c r="D201" s="270"/>
       <c r="E201" s="39"/>
       <c r="F201" s="39"/>
       <c r="G201" s="40"/>
@@ -8163,12 +8167,12 @@
       <c r="J201" s="40"/>
     </row>
     <row r="202" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A202" s="178"/>
-      <c r="B202" s="251"/>
+      <c r="A202" s="222"/>
+      <c r="B202" s="211"/>
       <c r="C202" s="90" t="s">
         <v>315</v>
       </c>
-      <c r="D202" s="190"/>
+      <c r="D202" s="271"/>
       <c r="E202" s="39"/>
       <c r="F202" s="39"/>
       <c r="G202" s="40"/>
@@ -8177,16 +8181,16 @@
       <c r="J202" s="40"/>
     </row>
     <row r="203" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A203" s="182" t="s">
+      <c r="A203" s="163" t="s">
         <v>514</v>
       </c>
-      <c r="B203" s="252" t="s">
+      <c r="B203" s="212" t="s">
         <v>664</v>
       </c>
       <c r="C203" s="90" t="s">
         <v>452</v>
       </c>
-      <c r="D203" s="188" t="s">
+      <c r="D203" s="269" t="s">
         <v>516</v>
       </c>
       <c r="E203" s="39"/>
@@ -8197,12 +8201,12 @@
       <c r="J203" s="40"/>
     </row>
     <row r="204" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A204" s="182"/>
-      <c r="B204" s="253"/>
+      <c r="A204" s="163"/>
+      <c r="B204" s="213"/>
       <c r="C204" s="90" t="s">
         <v>328</v>
       </c>
-      <c r="D204" s="189"/>
+      <c r="D204" s="270"/>
       <c r="E204" s="39"/>
       <c r="F204" s="39"/>
       <c r="G204" s="40"/>
@@ -8211,12 +8215,12 @@
       <c r="J204" s="40"/>
     </row>
     <row r="205" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A205" s="182"/>
-      <c r="B205" s="253"/>
+      <c r="A205" s="163"/>
+      <c r="B205" s="213"/>
       <c r="C205" s="90" t="s">
         <v>662</v>
       </c>
-      <c r="D205" s="189"/>
+      <c r="D205" s="270"/>
       <c r="E205" s="39"/>
       <c r="F205" s="39"/>
       <c r="G205" s="40"/>
@@ -8225,12 +8229,12 @@
       <c r="J205" s="40"/>
     </row>
     <row r="206" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A206" s="182"/>
-      <c r="B206" s="253"/>
+      <c r="A206" s="163"/>
+      <c r="B206" s="213"/>
       <c r="C206" s="90" t="s">
         <v>663</v>
       </c>
-      <c r="D206" s="189"/>
+      <c r="D206" s="270"/>
       <c r="E206" s="39"/>
       <c r="F206" s="39"/>
       <c r="G206" s="40"/>
@@ -8239,12 +8243,12 @@
       <c r="J206" s="40"/>
     </row>
     <row r="207" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A207" s="182"/>
-      <c r="B207" s="254"/>
+      <c r="A207" s="163"/>
+      <c r="B207" s="214"/>
       <c r="C207" s="90" t="s">
         <v>315</v>
       </c>
-      <c r="D207" s="190"/>
+      <c r="D207" s="271"/>
       <c r="E207" s="39"/>
       <c r="F207" s="39"/>
       <c r="G207" s="40"/>
@@ -8253,10 +8257,10 @@
       <c r="J207" s="40"/>
     </row>
     <row r="208" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A208" s="178" t="s">
+      <c r="A208" s="222" t="s">
         <v>516</v>
       </c>
-      <c r="B208" s="155" t="s">
+      <c r="B208" s="172" t="s">
         <v>428</v>
       </c>
       <c r="C208" s="94" t="s">
@@ -8271,8 +8275,8 @@
       <c r="J208" s="40"/>
     </row>
     <row r="209" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A209" s="178"/>
-      <c r="B209" s="161"/>
+      <c r="A209" s="222"/>
+      <c r="B209" s="173"/>
       <c r="C209" s="94" t="s">
         <v>556</v>
       </c>
@@ -8285,8 +8289,8 @@
       <c r="J209" s="40"/>
     </row>
     <row r="210" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A210" s="168"/>
-      <c r="B210" s="162"/>
+      <c r="A210" s="180"/>
+      <c r="B210" s="181"/>
       <c r="C210" s="94" t="s">
         <v>171</v>
       </c>
@@ -8299,8 +8303,8 @@
       <c r="J210" s="40"/>
     </row>
     <row r="211" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A211" s="168"/>
-      <c r="B211" s="162"/>
+      <c r="A211" s="180"/>
+      <c r="B211" s="181"/>
       <c r="C211" s="43" t="s">
         <v>172</v>
       </c>
@@ -8313,8 +8317,8 @@
       <c r="J211" s="40"/>
     </row>
     <row r="212" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A212" s="168"/>
-      <c r="B212" s="162"/>
+      <c r="A212" s="180"/>
+      <c r="B212" s="181"/>
       <c r="C212" s="43" t="s">
         <v>173</v>
       </c>
@@ -8327,8 +8331,8 @@
       <c r="J212" s="40"/>
     </row>
     <row r="213" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A213" s="168"/>
-      <c r="B213" s="162"/>
+      <c r="A213" s="180"/>
+      <c r="B213" s="181"/>
       <c r="C213" s="97" t="s">
         <v>174</v>
       </c>
@@ -8341,8 +8345,8 @@
       <c r="J213" s="86"/>
     </row>
     <row r="214" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A214" s="168"/>
-      <c r="B214" s="162"/>
+      <c r="A214" s="180"/>
+      <c r="B214" s="181"/>
       <c r="C214" s="97" t="s">
         <v>175</v>
       </c>
@@ -8355,8 +8359,8 @@
       <c r="J214" s="40"/>
     </row>
     <row r="215" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A215" s="168"/>
-      <c r="B215" s="162"/>
+      <c r="A215" s="180"/>
+      <c r="B215" s="181"/>
       <c r="C215" s="97" t="s">
         <v>603</v>
       </c>
@@ -8369,8 +8373,8 @@
       <c r="J215" s="40"/>
     </row>
     <row r="216" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A216" s="168"/>
-      <c r="B216" s="162"/>
+      <c r="A216" s="180"/>
+      <c r="B216" s="181"/>
       <c r="C216" s="97" t="s">
         <v>602</v>
       </c>
@@ -8383,8 +8387,8 @@
       <c r="J216" s="40"/>
     </row>
     <row r="217" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A217" s="168"/>
-      <c r="B217" s="162"/>
+      <c r="A217" s="180"/>
+      <c r="B217" s="181"/>
       <c r="C217" s="43" t="s">
         <v>176</v>
       </c>
@@ -8397,8 +8401,8 @@
       <c r="J217" s="40"/>
     </row>
     <row r="218" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A218" s="168"/>
-      <c r="B218" s="162"/>
+      <c r="A218" s="180"/>
+      <c r="B218" s="181"/>
       <c r="C218" s="43" t="s">
         <v>119</v>
       </c>
@@ -8411,10 +8415,10 @@
       <c r="J218" s="52"/>
     </row>
     <row r="219" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A219" s="182" t="s">
+      <c r="A219" s="163" t="s">
         <v>515</v>
       </c>
-      <c r="B219" s="245" t="s">
+      <c r="B219" s="205" t="s">
         <v>558</v>
       </c>
       <c r="C219" s="97" t="s">
@@ -8429,8 +8433,8 @@
       <c r="J219" s="40"/>
     </row>
     <row r="220" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A220" s="182"/>
-      <c r="B220" s="245"/>
+      <c r="A220" s="163"/>
+      <c r="B220" s="205"/>
       <c r="C220" s="43" t="s">
         <v>119</v>
       </c>
@@ -8443,10 +8447,10 @@
       <c r="J220" s="40"/>
     </row>
     <row r="221" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A221" s="243" t="s">
+      <c r="A221" s="186" t="s">
         <v>517</v>
       </c>
-      <c r="B221" s="204" t="s">
+      <c r="B221" s="187" t="s">
         <v>400</v>
       </c>
       <c r="C221" s="43" t="s">
@@ -8461,8 +8465,8 @@
       <c r="J221" s="40"/>
     </row>
     <row r="222" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A222" s="243"/>
-      <c r="B222" s="204"/>
+      <c r="A222" s="186"/>
+      <c r="B222" s="187"/>
       <c r="C222" s="43" t="s">
         <v>333</v>
       </c>
@@ -8475,8 +8479,8 @@
       <c r="J222" s="40"/>
     </row>
     <row r="223" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A223" s="243"/>
-      <c r="B223" s="204"/>
+      <c r="A223" s="186"/>
+      <c r="B223" s="187"/>
       <c r="C223" s="127" t="s">
         <v>119</v>
       </c>
@@ -8489,24 +8493,24 @@
       <c r="J223" s="40"/>
     </row>
     <row r="224" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A224" s="185" t="s">
+      <c r="A224" s="146" t="s">
         <v>402</v>
       </c>
-      <c r="B224" s="186"/>
-      <c r="C224" s="186"/>
-      <c r="D224" s="186"/>
-      <c r="E224" s="186"/>
-      <c r="F224" s="186"/>
-      <c r="G224" s="186"/>
-      <c r="H224" s="186"/>
-      <c r="I224" s="186"/>
-      <c r="J224" s="187"/>
+      <c r="B224" s="147"/>
+      <c r="C224" s="147"/>
+      <c r="D224" s="147"/>
+      <c r="E224" s="147"/>
+      <c r="F224" s="147"/>
+      <c r="G224" s="147"/>
+      <c r="H224" s="147"/>
+      <c r="I224" s="147"/>
+      <c r="J224" s="148"/>
     </row>
     <row r="225" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A225" s="243" t="s">
+      <c r="A225" s="186" t="s">
         <v>521</v>
       </c>
-      <c r="B225" s="204" t="s">
+      <c r="B225" s="187" t="s">
         <v>180</v>
       </c>
       <c r="C225" s="132" t="s">
@@ -8521,8 +8525,8 @@
       <c r="J225" s="40"/>
     </row>
     <row r="226" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A226" s="147"/>
-      <c r="B226" s="244"/>
+      <c r="A226" s="203"/>
+      <c r="B226" s="204"/>
       <c r="C226" s="132" t="s">
         <v>610</v>
       </c>
@@ -8535,10 +8539,10 @@
       <c r="J226" s="40"/>
     </row>
     <row r="227" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A227" s="243" t="s">
+      <c r="A227" s="186" t="s">
         <v>522</v>
       </c>
-      <c r="B227" s="204" t="s">
+      <c r="B227" s="187" t="s">
         <v>401</v>
       </c>
       <c r="C227" s="132" t="s">
@@ -8555,8 +8559,8 @@
       <c r="J227" s="40"/>
     </row>
     <row r="228" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A228" s="147"/>
-      <c r="B228" s="244"/>
+      <c r="A228" s="203"/>
+      <c r="B228" s="204"/>
       <c r="C228" s="132" t="s">
         <v>185</v>
       </c>
@@ -8571,8 +8575,8 @@
       <c r="J228" s="40"/>
     </row>
     <row r="229" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A229" s="147"/>
-      <c r="B229" s="244"/>
+      <c r="A229" s="203"/>
+      <c r="B229" s="204"/>
       <c r="C229" s="132" t="s">
         <v>186</v>
       </c>
@@ -8587,10 +8591,10 @@
       <c r="J229" s="40"/>
     </row>
     <row r="230" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A230" s="205" t="s">
+      <c r="A230" s="283" t="s">
         <v>523</v>
       </c>
-      <c r="B230" s="204" t="s">
+      <c r="B230" s="187" t="s">
         <v>382</v>
       </c>
       <c r="C230" s="102">
@@ -8605,8 +8609,8 @@
       <c r="J230" s="40"/>
     </row>
     <row r="231" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A231" s="205"/>
-      <c r="B231" s="204"/>
+      <c r="A231" s="283"/>
+      <c r="B231" s="187"/>
       <c r="C231" s="102">
         <v>2</v>
       </c>
@@ -8619,8 +8623,8 @@
       <c r="J231" s="53"/>
     </row>
     <row r="232" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A232" s="205"/>
-      <c r="B232" s="204"/>
+      <c r="A232" s="283"/>
+      <c r="B232" s="187"/>
       <c r="C232" s="102">
         <v>3</v>
       </c>
@@ -8633,8 +8637,8 @@
       <c r="J232" s="53"/>
     </row>
     <row r="233" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A233" s="205"/>
-      <c r="B233" s="204"/>
+      <c r="A233" s="283"/>
+      <c r="B233" s="187"/>
       <c r="C233" s="102">
         <v>4</v>
       </c>
@@ -8647,8 +8651,8 @@
       <c r="J233" s="53"/>
     </row>
     <row r="234" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A234" s="205"/>
-      <c r="B234" s="204"/>
+      <c r="A234" s="283"/>
+      <c r="B234" s="187"/>
       <c r="C234" s="102">
         <v>5</v>
       </c>
@@ -8661,8 +8665,8 @@
       <c r="J234" s="53"/>
     </row>
     <row r="235" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A235" s="205"/>
-      <c r="B235" s="204"/>
+      <c r="A235" s="283"/>
+      <c r="B235" s="187"/>
       <c r="C235" s="102" t="s">
         <v>595</v>
       </c>
@@ -8675,18 +8679,18 @@
       <c r="J235" s="53"/>
     </row>
     <row r="236" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A236" s="191" t="s">
+      <c r="A236" s="272" t="s">
         <v>469</v>
       </c>
-      <c r="B236" s="192"/>
-      <c r="C236" s="192"/>
-      <c r="D236" s="193"/>
-      <c r="E236" s="193"/>
-      <c r="F236" s="193"/>
-      <c r="G236" s="193"/>
-      <c r="H236" s="193"/>
-      <c r="I236" s="193"/>
-      <c r="J236" s="194"/>
+      <c r="B236" s="273"/>
+      <c r="C236" s="273"/>
+      <c r="D236" s="150"/>
+      <c r="E236" s="150"/>
+      <c r="F236" s="150"/>
+      <c r="G236" s="150"/>
+      <c r="H236" s="150"/>
+      <c r="I236" s="150"/>
+      <c r="J236" s="151"/>
     </row>
     <row r="237" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A237" s="80" t="s">
@@ -8707,18 +8711,18 @@
       <c r="J237" s="58"/>
     </row>
     <row r="238" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A238" s="215" t="s">
+      <c r="A238" s="149" t="s">
         <v>409</v>
       </c>
-      <c r="B238" s="193"/>
-      <c r="C238" s="193"/>
-      <c r="D238" s="193"/>
-      <c r="E238" s="193"/>
-      <c r="F238" s="193"/>
-      <c r="G238" s="193"/>
-      <c r="H238" s="193"/>
-      <c r="I238" s="193"/>
-      <c r="J238" s="194"/>
+      <c r="B238" s="150"/>
+      <c r="C238" s="150"/>
+      <c r="D238" s="150"/>
+      <c r="E238" s="150"/>
+      <c r="F238" s="150"/>
+      <c r="G238" s="150"/>
+      <c r="H238" s="150"/>
+      <c r="I238" s="150"/>
+      <c r="J238" s="151"/>
     </row>
     <row r="239" spans="1:10" ht="63.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A239" s="66" t="s">
@@ -8793,18 +8797,18 @@
       <c r="J242" s="58"/>
     </row>
     <row r="243" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A243" s="215" t="s">
+      <c r="A243" s="149" t="s">
         <v>410</v>
       </c>
-      <c r="B243" s="193"/>
-      <c r="C243" s="193"/>
-      <c r="D243" s="193"/>
-      <c r="E243" s="193"/>
-      <c r="F243" s="193"/>
-      <c r="G243" s="193"/>
-      <c r="H243" s="193"/>
-      <c r="I243" s="193"/>
-      <c r="J243" s="194"/>
+      <c r="B243" s="150"/>
+      <c r="C243" s="150"/>
+      <c r="D243" s="150"/>
+      <c r="E243" s="150"/>
+      <c r="F243" s="150"/>
+      <c r="G243" s="150"/>
+      <c r="H243" s="150"/>
+      <c r="I243" s="150"/>
+      <c r="J243" s="151"/>
     </row>
     <row r="244" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
       <c r="A244" s="67" t="s">
@@ -8825,18 +8829,18 @@
       <c r="J244" s="58"/>
     </row>
     <row r="245" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A245" s="185" t="s">
+      <c r="A245" s="146" t="s">
         <v>547</v>
       </c>
-      <c r="B245" s="186"/>
-      <c r="C245" s="186"/>
-      <c r="D245" s="186"/>
-      <c r="E245" s="186"/>
-      <c r="F245" s="186"/>
-      <c r="G245" s="186"/>
-      <c r="H245" s="186"/>
-      <c r="I245" s="186"/>
-      <c r="J245" s="187"/>
+      <c r="B245" s="147"/>
+      <c r="C245" s="147"/>
+      <c r="D245" s="147"/>
+      <c r="E245" s="147"/>
+      <c r="F245" s="147"/>
+      <c r="G245" s="147"/>
+      <c r="H245" s="147"/>
+      <c r="I245" s="147"/>
+      <c r="J245" s="148"/>
     </row>
     <row r="246" spans="1:10" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A246" s="55" t="s">
@@ -8857,10 +8861,10 @@
       <c r="J246" s="40"/>
     </row>
     <row r="247" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A247" s="181" t="s">
+      <c r="A247" s="179" t="s">
         <v>215</v>
       </c>
-      <c r="B247" s="155" t="s">
+      <c r="B247" s="172" t="s">
         <v>405</v>
       </c>
       <c r="C247" s="43" t="s">
@@ -8877,8 +8881,8 @@
       <c r="J247" s="58"/>
     </row>
     <row r="248" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A248" s="281"/>
-      <c r="B248" s="171"/>
+      <c r="A248" s="185"/>
+      <c r="B248" s="174"/>
       <c r="C248" s="43" t="s">
         <v>333</v>
       </c>
@@ -8909,10 +8913,10 @@
       <c r="J249" s="58"/>
     </row>
     <row r="250" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A250" s="243" t="s">
+      <c r="A250" s="186" t="s">
         <v>217</v>
       </c>
-      <c r="B250" s="204" t="s">
+      <c r="B250" s="187" t="s">
         <v>339</v>
       </c>
       <c r="C250" s="106" t="s">
@@ -8927,8 +8931,8 @@
       <c r="J250" s="58"/>
     </row>
     <row r="251" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A251" s="243"/>
-      <c r="B251" s="204"/>
+      <c r="A251" s="186"/>
+      <c r="B251" s="187"/>
       <c r="C251" s="106" t="s">
         <v>341</v>
       </c>
@@ -8941,8 +8945,8 @@
       <c r="J251" s="58"/>
     </row>
     <row r="252" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A252" s="243"/>
-      <c r="B252" s="204"/>
+      <c r="A252" s="186"/>
+      <c r="B252" s="187"/>
       <c r="C252" s="106" t="s">
         <v>342</v>
       </c>
@@ -8955,8 +8959,8 @@
       <c r="J252" s="58"/>
     </row>
     <row r="253" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A253" s="243"/>
-      <c r="B253" s="204"/>
+      <c r="A253" s="186"/>
+      <c r="B253" s="187"/>
       <c r="C253" s="106" t="s">
         <v>343</v>
       </c>
@@ -8969,8 +8973,8 @@
       <c r="J253" s="58"/>
     </row>
     <row r="254" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A254" s="243"/>
-      <c r="B254" s="204"/>
+      <c r="A254" s="186"/>
+      <c r="B254" s="187"/>
       <c r="C254" s="106" t="s">
         <v>470</v>
       </c>
@@ -8983,10 +8987,10 @@
       <c r="J254" s="58"/>
     </row>
     <row r="255" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A255" s="182" t="s">
+      <c r="A255" s="163" t="s">
         <v>218</v>
       </c>
-      <c r="B255" s="282" t="s">
+      <c r="B255" s="188" t="s">
         <v>692</v>
       </c>
       <c r="C255" s="90" t="s">
@@ -9001,8 +9005,8 @@
       <c r="J255" s="61"/>
     </row>
     <row r="256" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A256" s="182"/>
-      <c r="B256" s="282"/>
+      <c r="A256" s="163"/>
+      <c r="B256" s="188"/>
       <c r="C256" s="90" t="s">
         <v>370</v>
       </c>
@@ -9015,8 +9019,8 @@
       <c r="J256" s="61"/>
     </row>
     <row r="257" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A257" s="182"/>
-      <c r="B257" s="282"/>
+      <c r="A257" s="163"/>
+      <c r="B257" s="188"/>
       <c r="C257" s="90" t="s">
         <v>371</v>
       </c>
@@ -9029,8 +9033,8 @@
       <c r="J257" s="61"/>
     </row>
     <row r="258" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A258" s="182"/>
-      <c r="B258" s="282"/>
+      <c r="A258" s="163"/>
+      <c r="B258" s="188"/>
       <c r="C258" s="90" t="s">
         <v>372</v>
       </c>
@@ -9043,8 +9047,8 @@
       <c r="J258" s="61"/>
     </row>
     <row r="259" spans="1:10" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A259" s="182"/>
-      <c r="B259" s="282"/>
+      <c r="A259" s="163"/>
+      <c r="B259" s="188"/>
       <c r="C259" s="90" t="s">
         <v>373</v>
       </c>
@@ -9057,10 +9061,10 @@
       <c r="J259" s="61"/>
     </row>
     <row r="260" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A260" s="181" t="s">
+      <c r="A260" s="179" t="s">
         <v>414</v>
       </c>
-      <c r="B260" s="262" t="s">
+      <c r="B260" s="184" t="s">
         <v>693</v>
       </c>
       <c r="C260" s="43" t="s">
@@ -9077,8 +9081,8 @@
       <c r="J260" s="40"/>
     </row>
     <row r="261" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A261" s="168"/>
-      <c r="B261" s="162"/>
+      <c r="A261" s="180"/>
+      <c r="B261" s="181"/>
       <c r="C261" s="43" t="s">
         <v>356</v>
       </c>
@@ -9091,8 +9095,8 @@
       <c r="J261" s="40"/>
     </row>
     <row r="262" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A262" s="168"/>
-      <c r="B262" s="162"/>
+      <c r="A262" s="180"/>
+      <c r="B262" s="181"/>
       <c r="C262" s="43" t="s">
         <v>219</v>
       </c>
@@ -9105,8 +9109,8 @@
       <c r="J262" s="40"/>
     </row>
     <row r="263" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A263" s="168"/>
-      <c r="B263" s="162"/>
+      <c r="A263" s="180"/>
+      <c r="B263" s="181"/>
       <c r="C263" s="43" t="s">
         <v>220</v>
       </c>
@@ -9119,8 +9123,8 @@
       <c r="J263" s="40"/>
     </row>
     <row r="264" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A264" s="168"/>
-      <c r="B264" s="162"/>
+      <c r="A264" s="180"/>
+      <c r="B264" s="181"/>
       <c r="C264" s="43" t="s">
         <v>221</v>
       </c>
@@ -9133,8 +9137,8 @@
       <c r="J264" s="40"/>
     </row>
     <row r="265" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A265" s="168"/>
-      <c r="B265" s="162"/>
+      <c r="A265" s="180"/>
+      <c r="B265" s="181"/>
       <c r="C265" s="43" t="s">
         <v>222</v>
       </c>
@@ -9147,8 +9151,8 @@
       <c r="J265" s="40"/>
     </row>
     <row r="266" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A266" s="168"/>
-      <c r="B266" s="162"/>
+      <c r="A266" s="180"/>
+      <c r="B266" s="181"/>
       <c r="C266" s="43" t="s">
         <v>223</v>
       </c>
@@ -9161,8 +9165,8 @@
       <c r="J266" s="40"/>
     </row>
     <row r="267" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A267" s="168"/>
-      <c r="B267" s="162"/>
+      <c r="A267" s="180"/>
+      <c r="B267" s="181"/>
       <c r="C267" s="43" t="s">
         <v>224</v>
       </c>
@@ -9175,8 +9179,8 @@
       <c r="J267" s="40"/>
     </row>
     <row r="268" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A268" s="168"/>
-      <c r="B268" s="162"/>
+      <c r="A268" s="180"/>
+      <c r="B268" s="181"/>
       <c r="C268" s="43" t="s">
         <v>225</v>
       </c>
@@ -9189,8 +9193,8 @@
       <c r="J268" s="40"/>
     </row>
     <row r="269" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A269" s="168"/>
-      <c r="B269" s="162"/>
+      <c r="A269" s="180"/>
+      <c r="B269" s="181"/>
       <c r="C269" s="43" t="s">
         <v>226</v>
       </c>
@@ -9203,8 +9207,8 @@
       <c r="J269" s="40"/>
     </row>
     <row r="270" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A270" s="168"/>
-      <c r="B270" s="162"/>
+      <c r="A270" s="180"/>
+      <c r="B270" s="181"/>
       <c r="C270" s="43" t="s">
         <v>227</v>
       </c>
@@ -9217,8 +9221,8 @@
       <c r="J270" s="40"/>
     </row>
     <row r="271" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A271" s="168"/>
-      <c r="B271" s="162"/>
+      <c r="A271" s="180"/>
+      <c r="B271" s="181"/>
       <c r="C271" s="43" t="s">
         <v>228</v>
       </c>
@@ -9235,8 +9239,8 @@
       <c r="J271" s="40"/>
     </row>
     <row r="272" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A272" s="154"/>
-      <c r="B272" s="156"/>
+      <c r="A272" s="182"/>
+      <c r="B272" s="183"/>
       <c r="C272" s="43" t="s">
         <v>229</v>
       </c>
@@ -9249,10 +9253,10 @@
       <c r="J272" s="40"/>
     </row>
     <row r="273" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A273" s="181" t="s">
+      <c r="A273" s="179" t="s">
         <v>530</v>
       </c>
-      <c r="B273" s="155" t="s">
+      <c r="B273" s="172" t="s">
         <v>559</v>
       </c>
       <c r="C273" s="43" t="s">
@@ -9269,8 +9273,8 @@
       <c r="J273" s="40"/>
     </row>
     <row r="274" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A274" s="168"/>
-      <c r="B274" s="162"/>
+      <c r="A274" s="180"/>
+      <c r="B274" s="181"/>
       <c r="C274" s="43" t="s">
         <v>231</v>
       </c>
@@ -9285,8 +9289,8 @@
       <c r="J274" s="40"/>
     </row>
     <row r="275" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A275" s="168"/>
-      <c r="B275" s="162"/>
+      <c r="A275" s="180"/>
+      <c r="B275" s="181"/>
       <c r="C275" s="43" t="s">
         <v>232</v>
       </c>
@@ -9301,8 +9305,8 @@
       <c r="J275" s="40"/>
     </row>
     <row r="276" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A276" s="168"/>
-      <c r="B276" s="162"/>
+      <c r="A276" s="180"/>
+      <c r="B276" s="181"/>
       <c r="C276" s="43" t="s">
         <v>233</v>
       </c>
@@ -9317,8 +9321,8 @@
       <c r="J276" s="40"/>
     </row>
     <row r="277" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A277" s="168"/>
-      <c r="B277" s="162"/>
+      <c r="A277" s="180"/>
+      <c r="B277" s="181"/>
       <c r="C277" s="43" t="s">
         <v>234</v>
       </c>
@@ -9333,8 +9337,8 @@
       <c r="J277" s="40"/>
     </row>
     <row r="278" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A278" s="168"/>
-      <c r="B278" s="162"/>
+      <c r="A278" s="180"/>
+      <c r="B278" s="181"/>
       <c r="C278" s="43" t="s">
         <v>354</v>
       </c>
@@ -9349,10 +9353,10 @@
       <c r="J278" s="40"/>
     </row>
     <row r="279" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A279" s="181" t="s">
+      <c r="A279" s="179" t="s">
         <v>531</v>
       </c>
-      <c r="B279" s="155" t="s">
+      <c r="B279" s="172" t="s">
         <v>235</v>
       </c>
       <c r="C279" s="43" t="s">
@@ -9369,8 +9373,8 @@
       <c r="J279" s="40"/>
     </row>
     <row r="280" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A280" s="168"/>
-      <c r="B280" s="162"/>
+      <c r="A280" s="180"/>
+      <c r="B280" s="181"/>
       <c r="C280" s="43" t="s">
         <v>237</v>
       </c>
@@ -9385,8 +9389,8 @@
       <c r="J280" s="40"/>
     </row>
     <row r="281" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A281" s="168"/>
-      <c r="B281" s="162"/>
+      <c r="A281" s="180"/>
+      <c r="B281" s="181"/>
       <c r="C281" s="43" t="s">
         <v>471</v>
       </c>
@@ -9399,8 +9403,8 @@
       <c r="J281" s="40"/>
     </row>
     <row r="282" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A282" s="168"/>
-      <c r="B282" s="162"/>
+      <c r="A282" s="180"/>
+      <c r="B282" s="181"/>
       <c r="C282" s="43" t="s">
         <v>238</v>
       </c>
@@ -9413,8 +9417,8 @@
       <c r="J282" s="40"/>
     </row>
     <row r="283" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A283" s="154"/>
-      <c r="B283" s="156"/>
+      <c r="A283" s="182"/>
+      <c r="B283" s="183"/>
       <c r="C283" s="43" t="s">
         <v>239</v>
       </c>
@@ -9427,32 +9431,32 @@
       <c r="J283" s="40"/>
     </row>
     <row r="284" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A284" s="175" t="s">
+      <c r="A284" s="261" t="s">
         <v>545</v>
       </c>
-      <c r="B284" s="151"/>
-      <c r="C284" s="151"/>
-      <c r="D284" s="151"/>
-      <c r="E284" s="151"/>
-      <c r="F284" s="151"/>
-      <c r="G284" s="151"/>
-      <c r="H284" s="151"/>
-      <c r="I284" s="151"/>
-      <c r="J284" s="152"/>
+      <c r="B284" s="262"/>
+      <c r="C284" s="262"/>
+      <c r="D284" s="262"/>
+      <c r="E284" s="262"/>
+      <c r="F284" s="262"/>
+      <c r="G284" s="262"/>
+      <c r="H284" s="262"/>
+      <c r="I284" s="262"/>
+      <c r="J284" s="263"/>
     </row>
     <row r="285" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A285" s="185" t="s">
+      <c r="A285" s="146" t="s">
         <v>544</v>
       </c>
-      <c r="B285" s="186"/>
-      <c r="C285" s="186"/>
-      <c r="D285" s="186"/>
-      <c r="E285" s="186"/>
-      <c r="F285" s="186"/>
-      <c r="G285" s="186"/>
-      <c r="H285" s="186"/>
-      <c r="I285" s="186"/>
-      <c r="J285" s="187"/>
+      <c r="B285" s="147"/>
+      <c r="C285" s="147"/>
+      <c r="D285" s="147"/>
+      <c r="E285" s="147"/>
+      <c r="F285" s="147"/>
+      <c r="G285" s="147"/>
+      <c r="H285" s="147"/>
+      <c r="I285" s="147"/>
+      <c r="J285" s="148"/>
     </row>
     <row r="286" spans="1:10" ht="57.6" x14ac:dyDescent="0.3">
       <c r="A286" s="81" t="s">
@@ -9473,10 +9477,10 @@
       <c r="J286" s="40"/>
     </row>
     <row r="287" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A287" s="182" t="s">
+      <c r="A287" s="163" t="s">
         <v>416</v>
       </c>
-      <c r="B287" s="292" t="s">
+      <c r="B287" s="166" t="s">
         <v>669</v>
       </c>
       <c r="C287" s="43" t="s">
@@ -9491,8 +9495,8 @@
       <c r="J287" s="40"/>
     </row>
     <row r="288" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A288" s="182"/>
-      <c r="B288" s="293"/>
+      <c r="A288" s="163"/>
+      <c r="B288" s="167"/>
       <c r="C288" s="43" t="s">
         <v>560</v>
       </c>
@@ -9505,8 +9509,8 @@
       <c r="J288" s="40"/>
     </row>
     <row r="289" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A289" s="182"/>
-      <c r="B289" s="293"/>
+      <c r="A289" s="163"/>
+      <c r="B289" s="167"/>
       <c r="C289" s="43" t="s">
         <v>562</v>
       </c>
@@ -9519,8 +9523,8 @@
       <c r="J289" s="40"/>
     </row>
     <row r="290" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A290" s="182"/>
-      <c r="B290" s="293"/>
+      <c r="A290" s="163"/>
+      <c r="B290" s="167"/>
       <c r="C290" s="43" t="s">
         <v>449</v>
       </c>
@@ -9533,8 +9537,8 @@
       <c r="J290" s="40"/>
     </row>
     <row r="291" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A291" s="182"/>
-      <c r="B291" s="293"/>
+      <c r="A291" s="163"/>
+      <c r="B291" s="167"/>
       <c r="C291" s="43" t="s">
         <v>450</v>
       </c>
@@ -9547,8 +9551,8 @@
       <c r="J291" s="40"/>
     </row>
     <row r="292" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A292" s="182"/>
-      <c r="B292" s="293"/>
+      <c r="A292" s="163"/>
+      <c r="B292" s="167"/>
       <c r="C292" s="43" t="s">
         <v>568</v>
       </c>
@@ -9561,8 +9565,8 @@
       <c r="J292" s="40"/>
     </row>
     <row r="293" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A293" s="182"/>
-      <c r="B293" s="293"/>
+      <c r="A293" s="163"/>
+      <c r="B293" s="167"/>
       <c r="C293" s="43" t="s">
         <v>451</v>
       </c>
@@ -9575,8 +9579,8 @@
       <c r="J293" s="40"/>
     </row>
     <row r="294" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A294" s="182"/>
-      <c r="B294" s="293"/>
+      <c r="A294" s="163"/>
+      <c r="B294" s="167"/>
       <c r="C294" s="43" t="s">
         <v>618</v>
       </c>
@@ -9589,8 +9593,8 @@
       <c r="J294" s="40"/>
     </row>
     <row r="295" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A295" s="182"/>
-      <c r="B295" s="293"/>
+      <c r="A295" s="163"/>
+      <c r="B295" s="167"/>
       <c r="C295" s="43" t="s">
         <v>563</v>
       </c>
@@ -9603,8 +9607,8 @@
       <c r="J295" s="40"/>
     </row>
     <row r="296" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A296" s="182"/>
-      <c r="B296" s="294"/>
+      <c r="A296" s="163"/>
+      <c r="B296" s="168"/>
       <c r="C296" s="43" t="s">
         <v>41</v>
       </c>
@@ -9617,10 +9621,10 @@
       <c r="J296" s="40"/>
     </row>
     <row r="297" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A297" s="182" t="s">
+      <c r="A297" s="163" t="s">
         <v>418</v>
       </c>
-      <c r="B297" s="292" t="s">
+      <c r="B297" s="166" t="s">
         <v>670</v>
       </c>
       <c r="C297" s="43" t="s">
@@ -9635,8 +9639,8 @@
       <c r="J297" s="40"/>
     </row>
     <row r="298" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A298" s="182"/>
-      <c r="B298" s="293"/>
+      <c r="A298" s="163"/>
+      <c r="B298" s="167"/>
       <c r="C298" s="43" t="s">
         <v>564</v>
       </c>
@@ -9649,8 +9653,8 @@
       <c r="J298" s="40"/>
     </row>
     <row r="299" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A299" s="182"/>
-      <c r="B299" s="293"/>
+      <c r="A299" s="163"/>
+      <c r="B299" s="167"/>
       <c r="C299" s="97" t="s">
         <v>606</v>
       </c>
@@ -9663,8 +9667,8 @@
       <c r="J299" s="40"/>
     </row>
     <row r="300" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A300" s="182"/>
-      <c r="B300" s="293"/>
+      <c r="A300" s="163"/>
+      <c r="B300" s="167"/>
       <c r="C300" s="97" t="s">
         <v>607</v>
       </c>
@@ -9677,8 +9681,8 @@
       <c r="J300" s="40"/>
     </row>
     <row r="301" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A301" s="182"/>
-      <c r="B301" s="293"/>
+      <c r="A301" s="163"/>
+      <c r="B301" s="167"/>
       <c r="C301" s="97" t="s">
         <v>565</v>
       </c>
@@ -9691,8 +9695,8 @@
       <c r="J301" s="40"/>
     </row>
     <row r="302" spans="1:10" ht="33.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A302" s="182"/>
-      <c r="B302" s="293"/>
+      <c r="A302" s="163"/>
+      <c r="B302" s="167"/>
       <c r="C302" s="43" t="s">
         <v>474</v>
       </c>
@@ -9705,8 +9709,8 @@
       <c r="J302" s="40"/>
     </row>
     <row r="303" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A303" s="182"/>
-      <c r="B303" s="293"/>
+      <c r="A303" s="163"/>
+      <c r="B303" s="167"/>
       <c r="C303" s="43" t="s">
         <v>566</v>
       </c>
@@ -9719,8 +9723,8 @@
       <c r="J303" s="40"/>
     </row>
     <row r="304" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A304" s="182"/>
-      <c r="B304" s="293"/>
+      <c r="A304" s="163"/>
+      <c r="B304" s="167"/>
       <c r="C304" s="43" t="s">
         <v>567</v>
       </c>
@@ -9733,8 +9737,8 @@
       <c r="J304" s="40"/>
     </row>
     <row r="305" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A305" s="182"/>
-      <c r="B305" s="293"/>
+      <c r="A305" s="163"/>
+      <c r="B305" s="167"/>
       <c r="C305" s="43" t="s">
         <v>475</v>
       </c>
@@ -9747,8 +9751,8 @@
       <c r="J305" s="40"/>
     </row>
     <row r="306" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A306" s="182"/>
-      <c r="B306" s="293"/>
+      <c r="A306" s="163"/>
+      <c r="B306" s="167"/>
       <c r="C306" s="43" t="s">
         <v>476</v>
       </c>
@@ -9761,8 +9765,8 @@
       <c r="J306" s="40"/>
     </row>
     <row r="307" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A307" s="182"/>
-      <c r="B307" s="293"/>
+      <c r="A307" s="163"/>
+      <c r="B307" s="167"/>
       <c r="C307" s="43" t="s">
         <v>472</v>
       </c>
@@ -9775,8 +9779,8 @@
       <c r="J307" s="40"/>
     </row>
     <row r="308" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A308" s="182"/>
-      <c r="B308" s="293"/>
+      <c r="A308" s="163"/>
+      <c r="B308" s="167"/>
       <c r="C308" s="43" t="s">
         <v>473</v>
       </c>
@@ -9789,8 +9793,8 @@
       <c r="J308" s="40"/>
     </row>
     <row r="309" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A309" s="182"/>
-      <c r="B309" s="294"/>
+      <c r="A309" s="163"/>
+      <c r="B309" s="168"/>
       <c r="C309" s="43" t="s">
         <v>421</v>
       </c>
@@ -9803,10 +9807,10 @@
       <c r="J309" s="40"/>
     </row>
     <row r="310" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A310" s="229" t="s">
+      <c r="A310" s="158" t="s">
         <v>240</v>
       </c>
-      <c r="B310" s="287" t="s">
+      <c r="B310" s="157" t="s">
         <v>671</v>
       </c>
       <c r="C310" s="43" t="s">
@@ -9821,8 +9825,8 @@
       <c r="J310" s="40"/>
     </row>
     <row r="311" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A311" s="230"/>
-      <c r="B311" s="287"/>
+      <c r="A311" s="159"/>
+      <c r="B311" s="157"/>
       <c r="C311" s="62" t="s">
         <v>430</v>
       </c>
@@ -9835,8 +9839,8 @@
       <c r="J311" s="40"/>
     </row>
     <row r="312" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A312" s="230"/>
-      <c r="B312" s="287"/>
+      <c r="A312" s="159"/>
+      <c r="B312" s="157"/>
       <c r="C312" s="62" t="s">
         <v>569</v>
       </c>
@@ -9849,8 +9853,8 @@
       <c r="J312" s="40"/>
     </row>
     <row r="313" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A313" s="230"/>
-      <c r="B313" s="287"/>
+      <c r="A313" s="159"/>
+      <c r="B313" s="157"/>
       <c r="C313" s="62" t="s">
         <v>478</v>
       </c>
@@ -9863,8 +9867,8 @@
       <c r="J313" s="40"/>
     </row>
     <row r="314" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A314" s="230"/>
-      <c r="B314" s="287"/>
+      <c r="A314" s="159"/>
+      <c r="B314" s="157"/>
       <c r="C314" s="62" t="s">
         <v>431</v>
       </c>
@@ -9877,8 +9881,8 @@
       <c r="J314" s="40"/>
     </row>
     <row r="315" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A315" s="230"/>
-      <c r="B315" s="287"/>
+      <c r="A315" s="159"/>
+      <c r="B315" s="157"/>
       <c r="C315" s="62" t="s">
         <v>432</v>
       </c>
@@ -9891,8 +9895,8 @@
       <c r="J315" s="40"/>
     </row>
     <row r="316" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A316" s="230"/>
-      <c r="B316" s="287"/>
+      <c r="A316" s="159"/>
+      <c r="B316" s="157"/>
       <c r="C316" s="62" t="s">
         <v>433</v>
       </c>
@@ -9905,8 +9909,8 @@
       <c r="J316" s="40"/>
     </row>
     <row r="317" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A317" s="230"/>
-      <c r="B317" s="287"/>
+      <c r="A317" s="159"/>
+      <c r="B317" s="157"/>
       <c r="C317" s="62" t="s">
         <v>434</v>
       </c>
@@ -9919,8 +9923,8 @@
       <c r="J317" s="40"/>
     </row>
     <row r="318" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A318" s="230"/>
-      <c r="B318" s="287"/>
+      <c r="A318" s="159"/>
+      <c r="B318" s="157"/>
       <c r="C318" s="103" t="s">
         <v>570</v>
       </c>
@@ -9933,8 +9937,8 @@
       <c r="J318" s="40"/>
     </row>
     <row r="319" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A319" s="230"/>
-      <c r="B319" s="287"/>
+      <c r="A319" s="159"/>
+      <c r="B319" s="157"/>
       <c r="C319" s="103" t="s">
         <v>437</v>
       </c>
@@ -9947,8 +9951,8 @@
       <c r="J319" s="40"/>
     </row>
     <row r="320" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A320" s="230"/>
-      <c r="B320" s="287"/>
+      <c r="A320" s="159"/>
+      <c r="B320" s="157"/>
       <c r="C320" s="103" t="s">
         <v>436</v>
       </c>
@@ -9961,8 +9965,8 @@
       <c r="J320" s="40"/>
     </row>
     <row r="321" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A321" s="231"/>
-      <c r="B321" s="287"/>
+      <c r="A321" s="160"/>
+      <c r="B321" s="157"/>
       <c r="C321" s="43" t="s">
         <v>435</v>
       </c>
@@ -9975,10 +9979,10 @@
       <c r="J321" s="40"/>
     </row>
     <row r="322" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A322" s="182" t="s">
+      <c r="A322" s="163" t="s">
         <v>241</v>
       </c>
-      <c r="B322" s="291" t="s">
+      <c r="B322" s="165" t="s">
         <v>614</v>
       </c>
       <c r="C322" s="97" t="s">
@@ -9997,8 +10001,8 @@
       <c r="J322" s="40"/>
     </row>
     <row r="323" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A323" s="182"/>
-      <c r="B323" s="291"/>
+      <c r="A323" s="163"/>
+      <c r="B323" s="165"/>
       <c r="C323" s="97" t="s">
         <v>690</v>
       </c>
@@ -10011,8 +10015,8 @@
       <c r="J323" s="40"/>
     </row>
     <row r="324" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A324" s="290"/>
-      <c r="B324" s="290"/>
+      <c r="A324" s="164"/>
+      <c r="B324" s="164"/>
       <c r="C324" s="43" t="s">
         <v>571</v>
       </c>
@@ -10029,8 +10033,8 @@
       <c r="J324" s="40"/>
     </row>
     <row r="325" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A325" s="290"/>
-      <c r="B325" s="290"/>
+      <c r="A325" s="164"/>
+      <c r="B325" s="164"/>
       <c r="C325" s="43" t="s">
         <v>192</v>
       </c>
@@ -10047,8 +10051,8 @@
       <c r="J325" s="40"/>
     </row>
     <row r="326" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A326" s="290"/>
-      <c r="B326" s="290"/>
+      <c r="A326" s="164"/>
+      <c r="B326" s="164"/>
       <c r="C326" s="43" t="s">
         <v>572</v>
       </c>
@@ -10065,8 +10069,8 @@
       <c r="J326" s="40"/>
     </row>
     <row r="327" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A327" s="290"/>
-      <c r="B327" s="290"/>
+      <c r="A327" s="164"/>
+      <c r="B327" s="164"/>
       <c r="C327" s="43" t="s">
         <v>573</v>
       </c>
@@ -10083,8 +10087,8 @@
       <c r="J327" s="40"/>
     </row>
     <row r="328" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A328" s="290"/>
-      <c r="B328" s="290"/>
+      <c r="A328" s="164"/>
+      <c r="B328" s="164"/>
       <c r="C328" s="43" t="s">
         <v>194</v>
       </c>
@@ -10097,8 +10101,8 @@
       <c r="J328" s="40"/>
     </row>
     <row r="329" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A329" s="290"/>
-      <c r="B329" s="290"/>
+      <c r="A329" s="164"/>
+      <c r="B329" s="164"/>
       <c r="C329" s="43" t="s">
         <v>574</v>
       </c>
@@ -10115,8 +10119,8 @@
       <c r="J329" s="40"/>
     </row>
     <row r="330" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A330" s="290"/>
-      <c r="B330" s="290"/>
+      <c r="A330" s="164"/>
+      <c r="B330" s="164"/>
       <c r="C330" s="104" t="s">
         <v>479</v>
       </c>
@@ -10133,24 +10137,24 @@
       <c r="J330" s="40"/>
     </row>
     <row r="331" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A331" s="185" t="s">
+      <c r="A331" s="146" t="s">
         <v>543</v>
       </c>
-      <c r="B331" s="186"/>
-      <c r="C331" s="186"/>
-      <c r="D331" s="186"/>
-      <c r="E331" s="186"/>
-      <c r="F331" s="186"/>
-      <c r="G331" s="186"/>
-      <c r="H331" s="186"/>
-      <c r="I331" s="186"/>
-      <c r="J331" s="187"/>
+      <c r="B331" s="147"/>
+      <c r="C331" s="147"/>
+      <c r="D331" s="147"/>
+      <c r="E331" s="147"/>
+      <c r="F331" s="147"/>
+      <c r="G331" s="147"/>
+      <c r="H331" s="147"/>
+      <c r="I331" s="147"/>
+      <c r="J331" s="148"/>
     </row>
     <row r="332" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A332" s="289" t="s">
+      <c r="A332" s="162" t="s">
         <v>419</v>
       </c>
-      <c r="B332" s="288" t="s">
+      <c r="B332" s="161" t="s">
         <v>694</v>
       </c>
       <c r="C332" s="43" t="s">
@@ -10165,8 +10169,8 @@
       <c r="J332" s="40"/>
     </row>
     <row r="333" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A333" s="289"/>
-      <c r="B333" s="288"/>
+      <c r="A333" s="162"/>
+      <c r="B333" s="161"/>
       <c r="C333" s="134" t="s">
         <v>454</v>
       </c>
@@ -10179,8 +10183,8 @@
       <c r="J333" s="40"/>
     </row>
     <row r="334" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A334" s="289"/>
-      <c r="B334" s="288"/>
+      <c r="A334" s="162"/>
+      <c r="B334" s="161"/>
       <c r="C334" s="134" t="s">
         <v>481</v>
       </c>
@@ -10193,8 +10197,8 @@
       <c r="J334" s="40"/>
     </row>
     <row r="335" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A335" s="289"/>
-      <c r="B335" s="288"/>
+      <c r="A335" s="162"/>
+      <c r="B335" s="161"/>
       <c r="C335" s="97" t="s">
         <v>554</v>
       </c>
@@ -10207,8 +10211,8 @@
       <c r="J335" s="40"/>
     </row>
     <row r="336" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A336" s="289"/>
-      <c r="B336" s="288"/>
+      <c r="A336" s="162"/>
+      <c r="B336" s="161"/>
       <c r="C336" s="134" t="s">
         <v>149</v>
       </c>
@@ -10221,8 +10225,8 @@
       <c r="J336" s="40"/>
     </row>
     <row r="337" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A337" s="289"/>
-      <c r="B337" s="288"/>
+      <c r="A337" s="162"/>
+      <c r="B337" s="161"/>
       <c r="C337" s="134" t="s">
         <v>150</v>
       </c>
@@ -10235,8 +10239,8 @@
       <c r="J337" s="40"/>
     </row>
     <row r="338" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A338" s="289"/>
-      <c r="B338" s="288"/>
+      <c r="A338" s="162"/>
+      <c r="B338" s="161"/>
       <c r="C338" s="97" t="s">
         <v>620</v>
       </c>
@@ -10249,8 +10253,8 @@
       <c r="J338" s="40"/>
     </row>
     <row r="339" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A339" s="289"/>
-      <c r="B339" s="288"/>
+      <c r="A339" s="162"/>
+      <c r="B339" s="161"/>
       <c r="C339" s="43" t="s">
         <v>153</v>
       </c>
@@ -10263,8 +10267,8 @@
       <c r="J339" s="40"/>
     </row>
     <row r="340" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A340" s="289"/>
-      <c r="B340" s="288"/>
+      <c r="A340" s="162"/>
+      <c r="B340" s="161"/>
       <c r="C340" s="43" t="s">
         <v>154</v>
       </c>
@@ -10277,8 +10281,8 @@
       <c r="J340" s="40"/>
     </row>
     <row r="341" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A341" s="289"/>
-      <c r="B341" s="288"/>
+      <c r="A341" s="162"/>
+      <c r="B341" s="161"/>
       <c r="C341" s="43" t="s">
         <v>155</v>
       </c>
@@ -10291,8 +10295,8 @@
       <c r="J341" s="40"/>
     </row>
     <row r="342" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A342" s="289"/>
-      <c r="B342" s="288"/>
+      <c r="A342" s="162"/>
+      <c r="B342" s="161"/>
       <c r="C342" s="134" t="s">
         <v>156</v>
       </c>
@@ -10305,8 +10309,8 @@
       <c r="J342" s="40"/>
     </row>
     <row r="343" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A343" s="289"/>
-      <c r="B343" s="288"/>
+      <c r="A343" s="162"/>
+      <c r="B343" s="161"/>
       <c r="C343" s="134" t="s">
         <v>157</v>
       </c>
@@ -10319,8 +10323,8 @@
       <c r="J343" s="40"/>
     </row>
     <row r="344" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A344" s="289"/>
-      <c r="B344" s="288"/>
+      <c r="A344" s="162"/>
+      <c r="B344" s="161"/>
       <c r="C344" s="134" t="s">
         <v>628</v>
       </c>
@@ -10333,8 +10337,8 @@
       <c r="J344" s="40"/>
     </row>
     <row r="345" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A345" s="289"/>
-      <c r="B345" s="288"/>
+      <c r="A345" s="162"/>
+      <c r="B345" s="161"/>
       <c r="C345" s="134" t="s">
         <v>159</v>
       </c>
@@ -10347,8 +10351,8 @@
       <c r="J345" s="40"/>
     </row>
     <row r="346" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A346" s="289"/>
-      <c r="B346" s="288"/>
+      <c r="A346" s="162"/>
+      <c r="B346" s="161"/>
       <c r="C346" s="134" t="s">
         <v>160</v>
       </c>
@@ -10361,8 +10365,8 @@
       <c r="J346" s="40"/>
     </row>
     <row r="347" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A347" s="289"/>
-      <c r="B347" s="288"/>
+      <c r="A347" s="162"/>
+      <c r="B347" s="161"/>
       <c r="C347" s="134" t="s">
         <v>161</v>
       </c>
@@ -10375,8 +10379,8 @@
       <c r="J347" s="40"/>
     </row>
     <row r="348" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A348" s="289"/>
-      <c r="B348" s="288"/>
+      <c r="A348" s="162"/>
+      <c r="B348" s="161"/>
       <c r="C348" s="134" t="s">
         <v>162</v>
       </c>
@@ -10389,8 +10393,8 @@
       <c r="J348" s="40"/>
     </row>
     <row r="349" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A349" s="289"/>
-      <c r="B349" s="288"/>
+      <c r="A349" s="162"/>
+      <c r="B349" s="161"/>
       <c r="C349" s="134" t="s">
         <v>163</v>
       </c>
@@ -10403,8 +10407,8 @@
       <c r="J349" s="40"/>
     </row>
     <row r="350" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A350" s="289"/>
-      <c r="B350" s="288"/>
+      <c r="A350" s="162"/>
+      <c r="B350" s="161"/>
       <c r="C350" s="134" t="s">
         <v>164</v>
       </c>
@@ -10417,8 +10421,8 @@
       <c r="J350" s="40"/>
     </row>
     <row r="351" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A351" s="289"/>
-      <c r="B351" s="288"/>
+      <c r="A351" s="162"/>
+      <c r="B351" s="161"/>
       <c r="C351" s="134" t="s">
         <v>165</v>
       </c>
@@ -10431,8 +10435,8 @@
       <c r="J351" s="40"/>
     </row>
     <row r="352" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A352" s="289"/>
-      <c r="B352" s="288"/>
+      <c r="A352" s="162"/>
+      <c r="B352" s="161"/>
       <c r="C352" s="134" t="s">
         <v>166</v>
       </c>
@@ -10445,8 +10449,8 @@
       <c r="J352" s="40"/>
     </row>
     <row r="353" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A353" s="289"/>
-      <c r="B353" s="288"/>
+      <c r="A353" s="162"/>
+      <c r="B353" s="161"/>
       <c r="C353" s="134" t="s">
         <v>167</v>
       </c>
@@ -10459,8 +10463,8 @@
       <c r="J353" s="40"/>
     </row>
     <row r="354" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A354" s="289"/>
-      <c r="B354" s="288"/>
+      <c r="A354" s="162"/>
+      <c r="B354" s="161"/>
       <c r="C354" s="134" t="s">
         <v>168</v>
       </c>
@@ -10473,8 +10477,8 @@
       <c r="J354" s="40"/>
     </row>
     <row r="355" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A355" s="289"/>
-      <c r="B355" s="288"/>
+      <c r="A355" s="162"/>
+      <c r="B355" s="161"/>
       <c r="C355" s="134" t="s">
         <v>447</v>
       </c>
@@ -10487,10 +10491,10 @@
       <c r="J355" s="40"/>
     </row>
     <row r="356" spans="1:10" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A356" s="295" t="s">
+      <c r="A356" s="169" t="s">
         <v>242</v>
       </c>
-      <c r="B356" s="259" t="s">
+      <c r="B356" s="190" t="s">
         <v>695</v>
       </c>
       <c r="C356" s="92" t="s">
@@ -10505,8 +10509,8 @@
       <c r="J356" s="40"/>
     </row>
     <row r="357" spans="1:10" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A357" s="296"/>
-      <c r="B357" s="260"/>
+      <c r="A357" s="170"/>
+      <c r="B357" s="219"/>
       <c r="C357" s="92" t="s">
         <v>631</v>
       </c>
@@ -10519,8 +10523,8 @@
       <c r="J357" s="40"/>
     </row>
     <row r="358" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A358" s="296"/>
-      <c r="B358" s="260"/>
+      <c r="A358" s="170"/>
+      <c r="B358" s="219"/>
       <c r="C358" s="92" t="s">
         <v>388</v>
       </c>
@@ -10533,8 +10537,8 @@
       <c r="J358" s="40"/>
     </row>
     <row r="359" spans="1:10" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A359" s="296"/>
-      <c r="B359" s="260"/>
+      <c r="A359" s="170"/>
+      <c r="B359" s="219"/>
       <c r="C359" s="92" t="s">
         <v>387</v>
       </c>
@@ -10547,8 +10551,8 @@
       <c r="J359" s="40"/>
     </row>
     <row r="360" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A360" s="296"/>
-      <c r="B360" s="260"/>
+      <c r="A360" s="170"/>
+      <c r="B360" s="219"/>
       <c r="C360" s="92" t="s">
         <v>615</v>
       </c>
@@ -10561,8 +10565,8 @@
       <c r="J360" s="40"/>
     </row>
     <row r="361" spans="1:10" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A361" s="296"/>
-      <c r="B361" s="260"/>
+      <c r="A361" s="170"/>
+      <c r="B361" s="219"/>
       <c r="C361" s="92" t="s">
         <v>195</v>
       </c>
@@ -10575,8 +10579,8 @@
       <c r="J361" s="40"/>
     </row>
     <row r="362" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A362" s="296"/>
-      <c r="B362" s="260"/>
+      <c r="A362" s="170"/>
+      <c r="B362" s="219"/>
       <c r="C362" s="92" t="s">
         <v>448</v>
       </c>
@@ -10589,8 +10593,8 @@
       <c r="J362" s="40"/>
     </row>
     <row r="363" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A363" s="296"/>
-      <c r="B363" s="260"/>
+      <c r="A363" s="170"/>
+      <c r="B363" s="219"/>
       <c r="C363" s="92" t="s">
         <v>680</v>
       </c>
@@ -10603,8 +10607,8 @@
       <c r="J363" s="40"/>
     </row>
     <row r="364" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A364" s="297"/>
-      <c r="B364" s="261"/>
+      <c r="A364" s="171"/>
+      <c r="B364" s="220"/>
       <c r="C364" s="106" t="s">
         <v>619</v>
       </c>
@@ -10788,24 +10792,24 @@
       <c r="J375" s="53"/>
     </row>
     <row r="376" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A376" s="185" t="s">
+      <c r="A376" s="146" t="s">
         <v>542</v>
       </c>
-      <c r="B376" s="266"/>
-      <c r="C376" s="186"/>
-      <c r="D376" s="267"/>
-      <c r="E376" s="267"/>
-      <c r="F376" s="267"/>
-      <c r="G376" s="267"/>
-      <c r="H376" s="267"/>
-      <c r="I376" s="267"/>
-      <c r="J376" s="268"/>
+      <c r="B376" s="225"/>
+      <c r="C376" s="147"/>
+      <c r="D376" s="226"/>
+      <c r="E376" s="226"/>
+      <c r="F376" s="226"/>
+      <c r="G376" s="226"/>
+      <c r="H376" s="226"/>
+      <c r="I376" s="226"/>
+      <c r="J376" s="227"/>
     </row>
     <row r="377" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A377" s="272" t="s">
+      <c r="A377" s="191" t="s">
         <v>422</v>
       </c>
-      <c r="B377" s="271" t="s">
+      <c r="B377" s="189" t="s">
         <v>672</v>
       </c>
       <c r="C377" s="118" t="s">
@@ -10820,8 +10824,8 @@
       <c r="J377" s="62"/>
     </row>
     <row r="378" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A378" s="272"/>
-      <c r="B378" s="271"/>
+      <c r="A378" s="191"/>
+      <c r="B378" s="189"/>
       <c r="C378" s="118" t="s">
         <v>487</v>
       </c>
@@ -10834,8 +10838,8 @@
       <c r="J378" s="62"/>
     </row>
     <row r="379" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A379" s="272"/>
-      <c r="B379" s="271"/>
+      <c r="A379" s="191"/>
+      <c r="B379" s="189"/>
       <c r="C379" s="118" t="s">
         <v>488</v>
       </c>
@@ -10848,8 +10852,8 @@
       <c r="J379" s="62"/>
     </row>
     <row r="380" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A380" s="272"/>
-      <c r="B380" s="271"/>
+      <c r="A380" s="191"/>
+      <c r="B380" s="189"/>
       <c r="C380" s="118" t="s">
         <v>489</v>
       </c>
@@ -10862,8 +10866,8 @@
       <c r="J380" s="62"/>
     </row>
     <row r="381" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A381" s="272"/>
-      <c r="B381" s="271"/>
+      <c r="A381" s="191"/>
+      <c r="B381" s="189"/>
       <c r="C381" s="118" t="s">
         <v>490</v>
       </c>
@@ -10876,8 +10880,8 @@
       <c r="J381" s="62"/>
     </row>
     <row r="382" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A382" s="272"/>
-      <c r="B382" s="271"/>
+      <c r="A382" s="191"/>
+      <c r="B382" s="189"/>
       <c r="C382" s="118" t="s">
         <v>491</v>
       </c>
@@ -10890,8 +10894,8 @@
       <c r="J382" s="62"/>
     </row>
     <row r="383" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A383" s="272"/>
-      <c r="B383" s="271"/>
+      <c r="A383" s="191"/>
+      <c r="B383" s="189"/>
       <c r="C383" s="141" t="s">
         <v>492</v>
       </c>
@@ -10904,8 +10908,8 @@
       <c r="J383" s="62"/>
     </row>
     <row r="384" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A384" s="272"/>
-      <c r="B384" s="259"/>
+      <c r="A384" s="191"/>
+      <c r="B384" s="190"/>
       <c r="C384" s="141" t="s">
         <v>41</v>
       </c>
@@ -10918,10 +10922,10 @@
       <c r="J384" s="62"/>
     </row>
     <row r="385" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A385" s="274" t="s">
+      <c r="A385" s="193" t="s">
         <v>424</v>
       </c>
-      <c r="B385" s="273" t="s">
+      <c r="B385" s="192" t="s">
         <v>493</v>
       </c>
       <c r="C385" s="142" t="s">
@@ -10936,8 +10940,8 @@
       <c r="J385" s="62"/>
     </row>
     <row r="386" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A386" s="275"/>
-      <c r="B386" s="273"/>
+      <c r="A386" s="194"/>
+      <c r="B386" s="192"/>
       <c r="C386" s="142" t="s">
         <v>495</v>
       </c>
@@ -10950,8 +10954,8 @@
       <c r="J386" s="62"/>
     </row>
     <row r="387" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A387" s="275"/>
-      <c r="B387" s="273"/>
+      <c r="A387" s="194"/>
+      <c r="B387" s="192"/>
       <c r="C387" s="142" t="s">
         <v>496</v>
       </c>
@@ -10964,8 +10968,8 @@
       <c r="J387" s="62"/>
     </row>
     <row r="388" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A388" s="275"/>
-      <c r="B388" s="273"/>
+      <c r="A388" s="194"/>
+      <c r="B388" s="192"/>
       <c r="C388" s="142" t="s">
         <v>497</v>
       </c>
@@ -10978,8 +10982,8 @@
       <c r="J388" s="62"/>
     </row>
     <row r="389" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A389" s="276"/>
-      <c r="B389" s="273"/>
+      <c r="A389" s="195"/>
+      <c r="B389" s="192"/>
       <c r="C389" s="142" t="s">
         <v>498</v>
       </c>
@@ -10992,10 +10996,10 @@
       <c r="J389" s="62"/>
     </row>
     <row r="390" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A390" s="274" t="s">
+      <c r="A390" s="193" t="s">
         <v>425</v>
       </c>
-      <c r="B390" s="277" t="s">
+      <c r="B390" s="196" t="s">
         <v>674</v>
       </c>
       <c r="C390" s="128" t="s">
@@ -11010,8 +11014,8 @@
       <c r="J390" s="62"/>
     </row>
     <row r="391" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A391" s="275"/>
-      <c r="B391" s="278"/>
+      <c r="A391" s="194"/>
+      <c r="B391" s="197"/>
       <c r="C391" s="128" t="s">
         <v>647</v>
       </c>
@@ -11026,8 +11030,8 @@
       <c r="J391" s="62"/>
     </row>
     <row r="392" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A392" s="275"/>
-      <c r="B392" s="278"/>
+      <c r="A392" s="194"/>
+      <c r="B392" s="197"/>
       <c r="C392" s="143" t="s">
         <v>454</v>
       </c>
@@ -11040,8 +11044,8 @@
       <c r="J392" s="62"/>
     </row>
     <row r="393" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A393" s="275"/>
-      <c r="B393" s="278"/>
+      <c r="A393" s="194"/>
+      <c r="B393" s="197"/>
       <c r="C393" s="143" t="s">
         <v>482</v>
       </c>
@@ -11054,8 +11058,8 @@
       <c r="J393" s="62"/>
     </row>
     <row r="394" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A394" s="275"/>
-      <c r="B394" s="278"/>
+      <c r="A394" s="194"/>
+      <c r="B394" s="197"/>
       <c r="C394" s="143" t="s">
         <v>649</v>
       </c>
@@ -11070,8 +11074,8 @@
       <c r="J394" s="62"/>
     </row>
     <row r="395" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A395" s="275"/>
-      <c r="B395" s="278"/>
+      <c r="A395" s="194"/>
+      <c r="B395" s="197"/>
       <c r="C395" s="143" t="s">
         <v>650</v>
       </c>
@@ -11086,8 +11090,8 @@
       <c r="J395" s="62"/>
     </row>
     <row r="396" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A396" s="275"/>
-      <c r="B396" s="278"/>
+      <c r="A396" s="194"/>
+      <c r="B396" s="197"/>
       <c r="C396" s="143" t="s">
         <v>648</v>
       </c>
@@ -11102,8 +11106,8 @@
       <c r="J396" s="62"/>
     </row>
     <row r="397" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A397" s="275"/>
-      <c r="B397" s="278"/>
+      <c r="A397" s="194"/>
+      <c r="B397" s="197"/>
       <c r="C397" s="128" t="s">
         <v>154</v>
       </c>
@@ -11116,8 +11120,8 @@
       <c r="J397" s="62"/>
     </row>
     <row r="398" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A398" s="275"/>
-      <c r="B398" s="278"/>
+      <c r="A398" s="194"/>
+      <c r="B398" s="197"/>
       <c r="C398" s="128" t="s">
         <v>155</v>
       </c>
@@ -11130,8 +11134,8 @@
       <c r="J398" s="62"/>
     </row>
     <row r="399" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A399" s="275"/>
-      <c r="B399" s="278"/>
+      <c r="A399" s="194"/>
+      <c r="B399" s="197"/>
       <c r="C399" s="143" t="s">
         <v>621</v>
       </c>
@@ -11144,8 +11148,8 @@
       <c r="J399" s="62"/>
     </row>
     <row r="400" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A400" s="275"/>
-      <c r="B400" s="278"/>
+      <c r="A400" s="194"/>
+      <c r="B400" s="197"/>
       <c r="C400" s="143" t="s">
         <v>157</v>
       </c>
@@ -11158,8 +11162,8 @@
       <c r="J400" s="62"/>
     </row>
     <row r="401" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A401" s="275"/>
-      <c r="B401" s="278"/>
+      <c r="A401" s="194"/>
+      <c r="B401" s="197"/>
       <c r="C401" s="143" t="s">
         <v>628</v>
       </c>
@@ -11172,8 +11176,8 @@
       <c r="J401" s="62"/>
     </row>
     <row r="402" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A402" s="275"/>
-      <c r="B402" s="278"/>
+      <c r="A402" s="194"/>
+      <c r="B402" s="197"/>
       <c r="C402" s="143" t="s">
         <v>159</v>
       </c>
@@ -11186,8 +11190,8 @@
       <c r="J402" s="62"/>
     </row>
     <row r="403" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A403" s="275"/>
-      <c r="B403" s="278"/>
+      <c r="A403" s="194"/>
+      <c r="B403" s="197"/>
       <c r="C403" s="143" t="s">
         <v>161</v>
       </c>
@@ -11200,8 +11204,8 @@
       <c r="J403" s="62"/>
     </row>
     <row r="404" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A404" s="275"/>
-      <c r="B404" s="278"/>
+      <c r="A404" s="194"/>
+      <c r="B404" s="197"/>
       <c r="C404" s="143" t="s">
         <v>163</v>
       </c>
@@ -11214,8 +11218,8 @@
       <c r="J404" s="62"/>
     </row>
     <row r="405" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A405" s="275"/>
-      <c r="B405" s="278"/>
+      <c r="A405" s="194"/>
+      <c r="B405" s="197"/>
       <c r="C405" s="143" t="s">
         <v>166</v>
       </c>
@@ -11228,8 +11232,8 @@
       <c r="J405" s="62"/>
     </row>
     <row r="406" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A406" s="275"/>
-      <c r="B406" s="278"/>
+      <c r="A406" s="194"/>
+      <c r="B406" s="197"/>
       <c r="C406" s="143" t="s">
         <v>167</v>
       </c>
@@ -11242,10 +11246,10 @@
       <c r="J406" s="62"/>
     </row>
     <row r="407" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A407" s="279" t="s">
+      <c r="A407" s="198" t="s">
         <v>243</v>
       </c>
-      <c r="B407" s="277" t="s">
+      <c r="B407" s="196" t="s">
         <v>623</v>
       </c>
       <c r="C407" s="143" t="s">
@@ -11262,8 +11266,8 @@
       <c r="J407" s="62"/>
     </row>
     <row r="408" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A408" s="280"/>
-      <c r="B408" s="278"/>
+      <c r="A408" s="199"/>
+      <c r="B408" s="197"/>
       <c r="C408" s="143" t="s">
         <v>165</v>
       </c>
@@ -11278,8 +11282,8 @@
       <c r="J408" s="62"/>
     </row>
     <row r="409" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A409" s="280"/>
-      <c r="B409" s="278"/>
+      <c r="A409" s="199"/>
+      <c r="B409" s="197"/>
       <c r="C409" s="143" t="s">
         <v>166</v>
       </c>
@@ -11292,8 +11296,8 @@
       <c r="J409" s="62"/>
     </row>
     <row r="410" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A410" s="280"/>
-      <c r="B410" s="278"/>
+      <c r="A410" s="199"/>
+      <c r="B410" s="197"/>
       <c r="C410" s="143" t="s">
         <v>644</v>
       </c>
@@ -11306,8 +11310,8 @@
       <c r="J410" s="62"/>
     </row>
     <row r="411" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A411" s="280"/>
-      <c r="B411" s="278"/>
+      <c r="A411" s="199"/>
+      <c r="B411" s="197"/>
       <c r="C411" s="143" t="s">
         <v>164</v>
       </c>
@@ -11320,8 +11324,8 @@
       <c r="J411" s="62"/>
     </row>
     <row r="412" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A412" s="280"/>
-      <c r="B412" s="278"/>
+      <c r="A412" s="199"/>
+      <c r="B412" s="197"/>
       <c r="C412" s="143" t="s">
         <v>163</v>
       </c>
@@ -11334,8 +11338,8 @@
       <c r="J412" s="62"/>
     </row>
     <row r="413" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A413" s="280"/>
-      <c r="B413" s="278"/>
+      <c r="A413" s="199"/>
+      <c r="B413" s="197"/>
       <c r="C413" s="143" t="s">
         <v>621</v>
       </c>
@@ -11348,8 +11352,8 @@
       <c r="J413" s="62"/>
     </row>
     <row r="414" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A414" s="280"/>
-      <c r="B414" s="278"/>
+      <c r="A414" s="199"/>
+      <c r="B414" s="197"/>
       <c r="C414" s="143" t="s">
         <v>157</v>
       </c>
@@ -11362,8 +11366,8 @@
       <c r="J414" s="62"/>
     </row>
     <row r="415" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A415" s="280"/>
-      <c r="B415" s="278"/>
+      <c r="A415" s="199"/>
+      <c r="B415" s="197"/>
       <c r="C415" s="143" t="s">
         <v>629</v>
       </c>
@@ -11376,8 +11380,8 @@
       <c r="J415" s="62"/>
     </row>
     <row r="416" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A416" s="280"/>
-      <c r="B416" s="278"/>
+      <c r="A416" s="199"/>
+      <c r="B416" s="197"/>
       <c r="C416" s="128" t="s">
         <v>622</v>
       </c>
@@ -11390,8 +11394,8 @@
       <c r="J416" s="62"/>
     </row>
     <row r="417" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A417" s="280"/>
-      <c r="B417" s="278"/>
+      <c r="A417" s="199"/>
+      <c r="B417" s="197"/>
       <c r="C417" s="143" t="s">
         <v>454</v>
       </c>
@@ -11404,8 +11408,8 @@
       <c r="J417" s="62"/>
     </row>
     <row r="418" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A418" s="280"/>
-      <c r="B418" s="278"/>
+      <c r="A418" s="199"/>
+      <c r="B418" s="197"/>
       <c r="C418" s="143" t="s">
         <v>482</v>
       </c>
@@ -11418,8 +11422,8 @@
       <c r="J418" s="62"/>
     </row>
     <row r="419" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A419" s="280"/>
-      <c r="B419" s="278"/>
+      <c r="A419" s="199"/>
+      <c r="B419" s="197"/>
       <c r="C419" s="143" t="s">
         <v>149</v>
       </c>
@@ -11432,8 +11436,8 @@
       <c r="J419" s="62"/>
     </row>
     <row r="420" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A420" s="280"/>
-      <c r="B420" s="278"/>
+      <c r="A420" s="199"/>
+      <c r="B420" s="197"/>
       <c r="C420" s="143" t="s">
         <v>150</v>
       </c>
@@ -11446,8 +11450,8 @@
       <c r="J420" s="62"/>
     </row>
     <row r="421" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A421" s="280"/>
-      <c r="B421" s="278"/>
+      <c r="A421" s="199"/>
+      <c r="B421" s="197"/>
       <c r="C421" s="128" t="s">
         <v>154</v>
       </c>
@@ -11460,8 +11464,8 @@
       <c r="J421" s="62"/>
     </row>
     <row r="422" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A422" s="280"/>
-      <c r="B422" s="278"/>
+      <c r="A422" s="199"/>
+      <c r="B422" s="197"/>
       <c r="C422" s="128" t="s">
         <v>155</v>
       </c>
@@ -11474,24 +11478,24 @@
       <c r="J422" s="62"/>
     </row>
     <row r="423" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A423" s="264" t="s">
+      <c r="A423" s="223" t="s">
         <v>541</v>
       </c>
-      <c r="B423" s="269"/>
-      <c r="C423" s="269"/>
-      <c r="D423" s="269"/>
-      <c r="E423" s="269"/>
-      <c r="F423" s="269"/>
-      <c r="G423" s="269"/>
-      <c r="H423" s="269"/>
-      <c r="I423" s="269"/>
-      <c r="J423" s="270"/>
+      <c r="B423" s="228"/>
+      <c r="C423" s="228"/>
+      <c r="D423" s="228"/>
+      <c r="E423" s="228"/>
+      <c r="F423" s="228"/>
+      <c r="G423" s="228"/>
+      <c r="H423" s="228"/>
+      <c r="I423" s="228"/>
+      <c r="J423" s="229"/>
     </row>
     <row r="424" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A424" s="182" t="s">
+      <c r="A424" s="163" t="s">
         <v>426</v>
       </c>
-      <c r="B424" s="273" t="s">
+      <c r="B424" s="192" t="s">
         <v>651</v>
       </c>
       <c r="C424" s="62" t="s">
@@ -11506,8 +11510,8 @@
       <c r="J424" s="53"/>
     </row>
     <row r="425" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A425" s="182"/>
-      <c r="B425" s="273"/>
+      <c r="A425" s="163"/>
+      <c r="B425" s="192"/>
       <c r="C425" s="62" t="s">
         <v>500</v>
       </c>
@@ -11520,8 +11524,8 @@
       <c r="J425" s="53"/>
     </row>
     <row r="426" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A426" s="182"/>
-      <c r="B426" s="273"/>
+      <c r="A426" s="163"/>
+      <c r="B426" s="192"/>
       <c r="C426" s="62" t="s">
         <v>433</v>
       </c>
@@ -11534,8 +11538,8 @@
       <c r="J426" s="53"/>
     </row>
     <row r="427" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A427" s="182"/>
-      <c r="B427" s="273"/>
+      <c r="A427" s="163"/>
+      <c r="B427" s="192"/>
       <c r="C427" s="62" t="s">
         <v>501</v>
       </c>
@@ -11548,8 +11552,8 @@
       <c r="J427" s="53"/>
     </row>
     <row r="428" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A428" s="182"/>
-      <c r="B428" s="273"/>
+      <c r="A428" s="163"/>
+      <c r="B428" s="192"/>
       <c r="C428" s="62" t="s">
         <v>502</v>
       </c>
@@ -11562,8 +11566,8 @@
       <c r="J428" s="53"/>
     </row>
     <row r="429" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A429" s="182"/>
-      <c r="B429" s="273"/>
+      <c r="A429" s="163"/>
+      <c r="B429" s="192"/>
       <c r="C429" s="62" t="s">
         <v>503</v>
       </c>
@@ -11576,8 +11580,8 @@
       <c r="J429" s="53"/>
     </row>
     <row r="430" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A430" s="182"/>
-      <c r="B430" s="273"/>
+      <c r="A430" s="163"/>
+      <c r="B430" s="192"/>
       <c r="C430" s="62" t="s">
         <v>504</v>
       </c>
@@ -11590,18 +11594,18 @@
       <c r="J430" s="53"/>
     </row>
     <row r="431" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A431" s="264" t="s">
+      <c r="A431" s="223" t="s">
         <v>540</v>
       </c>
-      <c r="B431" s="265"/>
-      <c r="C431" s="265"/>
-      <c r="D431" s="186"/>
-      <c r="E431" s="186"/>
-      <c r="F431" s="186"/>
-      <c r="G431" s="186"/>
-      <c r="H431" s="186"/>
-      <c r="I431" s="186"/>
-      <c r="J431" s="187"/>
+      <c r="B431" s="224"/>
+      <c r="C431" s="224"/>
+      <c r="D431" s="147"/>
+      <c r="E431" s="147"/>
+      <c r="F431" s="147"/>
+      <c r="G431" s="147"/>
+      <c r="H431" s="147"/>
+      <c r="I431" s="147"/>
+      <c r="J431" s="148"/>
     </row>
     <row r="432" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A432" s="55" t="s">
@@ -11640,24 +11644,24 @@
       <c r="J433" s="40"/>
     </row>
     <row r="434" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A434" s="150" t="s">
+      <c r="A434" s="266" t="s">
         <v>539</v>
       </c>
-      <c r="B434" s="179"/>
-      <c r="C434" s="179"/>
-      <c r="D434" s="179"/>
-      <c r="E434" s="179"/>
-      <c r="F434" s="179"/>
-      <c r="G434" s="179"/>
-      <c r="H434" s="179"/>
-      <c r="I434" s="179"/>
-      <c r="J434" s="180"/>
+      <c r="B434" s="267"/>
+      <c r="C434" s="267"/>
+      <c r="D434" s="267"/>
+      <c r="E434" s="267"/>
+      <c r="F434" s="267"/>
+      <c r="G434" s="267"/>
+      <c r="H434" s="267"/>
+      <c r="I434" s="267"/>
+      <c r="J434" s="268"/>
     </row>
     <row r="435" spans="1:10" ht="85.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A435" s="181" t="s">
+      <c r="A435" s="179" t="s">
         <v>534</v>
       </c>
-      <c r="B435" s="262" t="s">
+      <c r="B435" s="184" t="s">
         <v>699</v>
       </c>
       <c r="C435" s="124" t="s">
@@ -11678,8 +11682,8 @@
       <c r="J435" s="40"/>
     </row>
     <row r="436" spans="1:10" ht="43.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A436" s="178"/>
-      <c r="B436" s="263"/>
+      <c r="A436" s="222"/>
+      <c r="B436" s="221"/>
       <c r="C436" s="62" t="s">
         <v>483</v>
       </c>
@@ -11691,9 +11695,9 @@
       <c r="I436" s="40"/>
       <c r="J436" s="40"/>
     </row>
-    <row r="437" spans="1:10" ht="172.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A437" s="178"/>
-      <c r="B437" s="263"/>
+    <row r="437" spans="1:10" ht="252.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A437" s="222"/>
+      <c r="B437" s="221"/>
       <c r="C437" s="125" t="s">
         <v>269</v>
       </c>
@@ -11706,20 +11710,20 @@
       <c r="J437" s="40"/>
     </row>
     <row r="438" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A438" s="163" t="s">
+      <c r="A438" s="155" t="s">
         <v>536</v>
       </c>
-      <c r="B438" s="183" t="s">
+      <c r="B438" s="176" t="s">
         <v>686</v>
       </c>
       <c r="C438" s="136" t="s">
         <v>691</v>
       </c>
       <c r="D438" s="40"/>
-      <c r="E438" s="283" t="s">
+      <c r="E438" s="152" t="s">
         <v>169</v>
       </c>
-      <c r="F438" s="283" t="s">
+      <c r="F438" s="152" t="s">
         <v>170</v>
       </c>
       <c r="G438" s="40"/>
@@ -11728,16 +11732,16 @@
       <c r="J438" s="40"/>
     </row>
     <row r="439" spans="1:10" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A439" s="298"/>
-      <c r="B439" s="299"/>
+      <c r="A439" s="175"/>
+      <c r="B439" s="177"/>
       <c r="C439" s="137" t="s">
         <v>653</v>
       </c>
       <c r="D439" s="119" t="s">
         <v>652</v>
       </c>
-      <c r="E439" s="284"/>
-      <c r="F439" s="284" t="s">
+      <c r="E439" s="153"/>
+      <c r="F439" s="153" t="s">
         <v>170</v>
       </c>
       <c r="G439" s="40"/>
@@ -11746,14 +11750,14 @@
       <c r="J439" s="40"/>
     </row>
     <row r="440" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A440" s="298"/>
-      <c r="B440" s="299"/>
+      <c r="A440" s="175"/>
+      <c r="B440" s="177"/>
       <c r="C440" s="136" t="s">
         <v>244</v>
       </c>
       <c r="D440" s="40"/>
-      <c r="E440" s="284"/>
-      <c r="F440" s="284" t="s">
+      <c r="E440" s="153"/>
+      <c r="F440" s="153" t="s">
         <v>170</v>
       </c>
       <c r="G440" s="40"/>
@@ -11762,56 +11766,56 @@
       <c r="J440" s="40"/>
     </row>
     <row r="441" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A441" s="298"/>
-      <c r="B441" s="299"/>
+      <c r="A441" s="175"/>
+      <c r="B441" s="177"/>
       <c r="C441" s="136" t="s">
         <v>681</v>
       </c>
       <c r="D441" s="40"/>
-      <c r="E441" s="284"/>
-      <c r="F441" s="284"/>
+      <c r="E441" s="153"/>
+      <c r="F441" s="153"/>
       <c r="G441" s="40"/>
       <c r="H441" s="40"/>
       <c r="I441" s="40"/>
       <c r="J441" s="40"/>
     </row>
     <row r="442" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A442" s="298"/>
-      <c r="B442" s="299"/>
+      <c r="A442" s="175"/>
+      <c r="B442" s="177"/>
       <c r="C442" s="136" t="s">
         <v>684</v>
       </c>
       <c r="D442" s="40"/>
-      <c r="E442" s="284"/>
-      <c r="F442" s="284"/>
+      <c r="E442" s="153"/>
+      <c r="F442" s="153"/>
       <c r="G442" s="40"/>
       <c r="H442" s="40"/>
       <c r="I442" s="40"/>
       <c r="J442" s="40"/>
     </row>
     <row r="443" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A443" s="298"/>
-      <c r="B443" s="299"/>
+      <c r="A443" s="175"/>
+      <c r="B443" s="177"/>
       <c r="C443" s="136" t="s">
         <v>685</v>
       </c>
       <c r="D443" s="40"/>
-      <c r="E443" s="284"/>
-      <c r="F443" s="284"/>
+      <c r="E443" s="153"/>
+      <c r="F443" s="153"/>
       <c r="G443" s="40"/>
       <c r="H443" s="40"/>
       <c r="I443" s="40"/>
       <c r="J443" s="40"/>
     </row>
     <row r="444" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A444" s="298"/>
-      <c r="B444" s="299"/>
+      <c r="A444" s="175"/>
+      <c r="B444" s="177"/>
       <c r="C444" s="43" t="s">
         <v>682</v>
       </c>
       <c r="D444" s="40"/>
-      <c r="E444" s="284"/>
-      <c r="F444" s="284" t="s">
+      <c r="E444" s="153"/>
+      <c r="F444" s="153" t="s">
         <v>170</v>
       </c>
       <c r="G444" s="40"/>
@@ -11820,14 +11824,14 @@
       <c r="J444" s="40"/>
     </row>
     <row r="445" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A445" s="298"/>
-      <c r="B445" s="299"/>
+      <c r="A445" s="175"/>
+      <c r="B445" s="177"/>
       <c r="C445" s="43" t="s">
         <v>683</v>
       </c>
       <c r="D445" s="40"/>
-      <c r="E445" s="284"/>
-      <c r="F445" s="284" t="s">
+      <c r="E445" s="153"/>
+      <c r="F445" s="153" t="s">
         <v>170</v>
       </c>
       <c r="G445" s="40"/>
@@ -11836,14 +11840,14 @@
       <c r="J445" s="40"/>
     </row>
     <row r="446" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A446" s="298"/>
-      <c r="B446" s="299"/>
+      <c r="A446" s="175"/>
+      <c r="B446" s="177"/>
       <c r="C446" s="43" t="s">
         <v>245</v>
       </c>
       <c r="D446" s="40"/>
-      <c r="E446" s="284"/>
-      <c r="F446" s="284" t="s">
+      <c r="E446" s="153"/>
+      <c r="F446" s="153" t="s">
         <v>170</v>
       </c>
       <c r="G446" s="40"/>
@@ -11852,14 +11856,14 @@
       <c r="J446" s="40"/>
     </row>
     <row r="447" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A447" s="298"/>
-      <c r="B447" s="299"/>
+      <c r="A447" s="175"/>
+      <c r="B447" s="177"/>
       <c r="C447" s="43" t="s">
         <v>246</v>
       </c>
       <c r="D447" s="40"/>
-      <c r="E447" s="284"/>
-      <c r="F447" s="284" t="s">
+      <c r="E447" s="153"/>
+      <c r="F447" s="153" t="s">
         <v>170</v>
       </c>
       <c r="G447" s="40"/>
@@ -11868,14 +11872,14 @@
       <c r="J447" s="40"/>
     </row>
     <row r="448" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A448" s="298"/>
-      <c r="B448" s="299"/>
+      <c r="A448" s="175"/>
+      <c r="B448" s="177"/>
       <c r="C448" s="43" t="s">
         <v>247</v>
       </c>
       <c r="D448" s="40"/>
-      <c r="E448" s="284"/>
-      <c r="F448" s="284" t="s">
+      <c r="E448" s="153"/>
+      <c r="F448" s="153" t="s">
         <v>170</v>
       </c>
       <c r="G448" s="40"/>
@@ -11884,14 +11888,14 @@
       <c r="J448" s="40"/>
     </row>
     <row r="449" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A449" s="298"/>
-      <c r="B449" s="299"/>
+      <c r="A449" s="175"/>
+      <c r="B449" s="177"/>
       <c r="C449" s="43" t="s">
         <v>248</v>
       </c>
       <c r="D449" s="40"/>
-      <c r="E449" s="284"/>
-      <c r="F449" s="284" t="s">
+      <c r="E449" s="153"/>
+      <c r="F449" s="153" t="s">
         <v>170</v>
       </c>
       <c r="G449" s="40"/>
@@ -11900,14 +11904,14 @@
       <c r="J449" s="40"/>
     </row>
     <row r="450" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A450" s="298"/>
-      <c r="B450" s="299"/>
+      <c r="A450" s="175"/>
+      <c r="B450" s="177"/>
       <c r="C450" s="43" t="s">
         <v>249</v>
       </c>
       <c r="D450" s="40"/>
-      <c r="E450" s="284"/>
-      <c r="F450" s="284" t="s">
+      <c r="E450" s="153"/>
+      <c r="F450" s="153" t="s">
         <v>170</v>
       </c>
       <c r="G450" s="40"/>
@@ -11916,14 +11920,14 @@
       <c r="J450" s="40"/>
     </row>
     <row r="451" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A451" s="298"/>
-      <c r="B451" s="299"/>
+      <c r="A451" s="175"/>
+      <c r="B451" s="177"/>
       <c r="C451" s="43" t="s">
         <v>250</v>
       </c>
       <c r="D451" s="40"/>
-      <c r="E451" s="284"/>
-      <c r="F451" s="284" t="s">
+      <c r="E451" s="153"/>
+      <c r="F451" s="153" t="s">
         <v>170</v>
       </c>
       <c r="G451" s="40"/>
@@ -11932,14 +11936,14 @@
       <c r="J451" s="40"/>
     </row>
     <row r="452" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A452" s="298"/>
-      <c r="B452" s="299"/>
+      <c r="A452" s="175"/>
+      <c r="B452" s="177"/>
       <c r="C452" s="43" t="s">
         <v>251</v>
       </c>
       <c r="D452" s="40"/>
-      <c r="E452" s="284"/>
-      <c r="F452" s="284" t="s">
+      <c r="E452" s="153"/>
+      <c r="F452" s="153" t="s">
         <v>170</v>
       </c>
       <c r="G452" s="40"/>
@@ -11948,14 +11952,14 @@
       <c r="J452" s="40"/>
     </row>
     <row r="453" spans="1:10" ht="14.4" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A453" s="298"/>
-      <c r="B453" s="299"/>
+      <c r="A453" s="175"/>
+      <c r="B453" s="177"/>
       <c r="C453" s="135" t="s">
         <v>654</v>
       </c>
       <c r="D453" s="40"/>
-      <c r="E453" s="284"/>
-      <c r="F453" s="284" t="s">
+      <c r="E453" s="153"/>
+      <c r="F453" s="153" t="s">
         <v>170</v>
       </c>
       <c r="G453" s="40"/>
@@ -11964,14 +11968,14 @@
       <c r="J453" s="40"/>
     </row>
     <row r="454" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A454" s="298"/>
-      <c r="B454" s="299"/>
+      <c r="A454" s="175"/>
+      <c r="B454" s="177"/>
       <c r="C454" s="97" t="s">
         <v>687</v>
       </c>
       <c r="D454" s="40"/>
-      <c r="E454" s="284"/>
-      <c r="F454" s="284" t="s">
+      <c r="E454" s="153"/>
+      <c r="F454" s="153" t="s">
         <v>170</v>
       </c>
       <c r="G454" s="40"/>
@@ -11980,14 +11984,14 @@
       <c r="J454" s="40"/>
     </row>
     <row r="455" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A455" s="298"/>
-      <c r="B455" s="299"/>
+      <c r="A455" s="175"/>
+      <c r="B455" s="177"/>
       <c r="C455" s="43" t="s">
         <v>252</v>
       </c>
       <c r="D455" s="40"/>
-      <c r="E455" s="284"/>
-      <c r="F455" s="284" t="s">
+      <c r="E455" s="153"/>
+      <c r="F455" s="153" t="s">
         <v>170</v>
       </c>
       <c r="G455" s="40"/>
@@ -11996,14 +12000,14 @@
       <c r="J455" s="40"/>
     </row>
     <row r="456" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A456" s="298"/>
-      <c r="B456" s="299"/>
+      <c r="A456" s="175"/>
+      <c r="B456" s="177"/>
       <c r="C456" s="43" t="s">
         <v>253</v>
       </c>
       <c r="D456" s="40"/>
-      <c r="E456" s="284"/>
-      <c r="F456" s="284" t="s">
+      <c r="E456" s="153"/>
+      <c r="F456" s="153" t="s">
         <v>170</v>
       </c>
       <c r="G456" s="40"/>
@@ -12012,14 +12016,14 @@
       <c r="J456" s="40"/>
     </row>
     <row r="457" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A457" s="298"/>
-      <c r="B457" s="299"/>
+      <c r="A457" s="175"/>
+      <c r="B457" s="177"/>
       <c r="C457" s="43" t="s">
         <v>254</v>
       </c>
       <c r="D457" s="40"/>
-      <c r="E457" s="284"/>
-      <c r="F457" s="284" t="s">
+      <c r="E457" s="153"/>
+      <c r="F457" s="153" t="s">
         <v>170</v>
       </c>
       <c r="G457" s="40"/>
@@ -12028,14 +12032,14 @@
       <c r="J457" s="40"/>
     </row>
     <row r="458" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A458" s="298"/>
-      <c r="B458" s="299"/>
+      <c r="A458" s="175"/>
+      <c r="B458" s="177"/>
       <c r="C458" s="133" t="s">
         <v>255</v>
       </c>
       <c r="D458" s="40"/>
-      <c r="E458" s="284"/>
-      <c r="F458" s="284" t="s">
+      <c r="E458" s="153"/>
+      <c r="F458" s="153" t="s">
         <v>170</v>
       </c>
       <c r="G458" s="40"/>
@@ -12044,14 +12048,14 @@
       <c r="J458" s="40"/>
     </row>
     <row r="459" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A459" s="286"/>
-      <c r="B459" s="184"/>
+      <c r="A459" s="156"/>
+      <c r="B459" s="178"/>
       <c r="C459" s="90" t="s">
         <v>626</v>
       </c>
       <c r="D459" s="110"/>
-      <c r="E459" s="285"/>
-      <c r="F459" s="285" t="s">
+      <c r="E459" s="154"/>
+      <c r="F459" s="154" t="s">
         <v>170</v>
       </c>
       <c r="G459" s="40"/>
@@ -12060,10 +12064,10 @@
       <c r="J459" s="40"/>
     </row>
     <row r="460" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A460" s="163" t="s">
+      <c r="A460" s="155" t="s">
         <v>624</v>
       </c>
-      <c r="B460" s="155" t="s">
+      <c r="B460" s="172" t="s">
         <v>256</v>
       </c>
       <c r="C460" s="138" t="s">
@@ -12078,8 +12082,8 @@
       <c r="J460" s="40"/>
     </row>
     <row r="461" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A461" s="298"/>
-      <c r="B461" s="161"/>
+      <c r="A461" s="175"/>
+      <c r="B461" s="173"/>
       <c r="C461" s="43" t="s">
         <v>258</v>
       </c>
@@ -12092,8 +12096,8 @@
       <c r="J461" s="40"/>
     </row>
     <row r="462" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A462" s="298"/>
-      <c r="B462" s="161"/>
+      <c r="A462" s="175"/>
+      <c r="B462" s="173"/>
       <c r="C462" s="43" t="s">
         <v>259</v>
       </c>
@@ -12106,8 +12110,8 @@
       <c r="J462" s="40"/>
     </row>
     <row r="463" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A463" s="298"/>
-      <c r="B463" s="161"/>
+      <c r="A463" s="175"/>
+      <c r="B463" s="173"/>
       <c r="C463" s="43" t="s">
         <v>260</v>
       </c>
@@ -12120,8 +12124,8 @@
       <c r="J463" s="40"/>
     </row>
     <row r="464" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
-      <c r="A464" s="298"/>
-      <c r="B464" s="161"/>
+      <c r="A464" s="175"/>
+      <c r="B464" s="173"/>
       <c r="C464" s="43" t="s">
         <v>429</v>
       </c>
@@ -12134,8 +12138,8 @@
       <c r="J464" s="40"/>
     </row>
     <row r="465" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A465" s="298"/>
-      <c r="B465" s="161"/>
+      <c r="A465" s="175"/>
+      <c r="B465" s="173"/>
       <c r="C465" s="104" t="s">
         <v>616</v>
       </c>
@@ -12152,8 +12156,8 @@
       <c r="J465" s="40"/>
     </row>
     <row r="466" spans="1:10" ht="29.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A466" s="298"/>
-      <c r="B466" s="161"/>
+      <c r="A466" s="175"/>
+      <c r="B466" s="173"/>
       <c r="C466" s="94" t="s">
         <v>617</v>
       </c>
@@ -12166,8 +12170,8 @@
       <c r="J466" s="40"/>
     </row>
     <row r="467" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A467" s="298"/>
-      <c r="B467" s="161"/>
+      <c r="A467" s="175"/>
+      <c r="B467" s="173"/>
       <c r="C467" s="43" t="s">
         <v>485</v>
       </c>
@@ -12180,8 +12184,8 @@
       <c r="J467" s="40"/>
     </row>
     <row r="468" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A468" s="298"/>
-      <c r="B468" s="161"/>
+      <c r="A468" s="175"/>
+      <c r="B468" s="173"/>
       <c r="C468" s="94" t="s">
         <v>627</v>
       </c>
@@ -12198,8 +12202,8 @@
       <c r="J468" s="40"/>
     </row>
     <row r="469" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A469" s="286"/>
-      <c r="B469" s="171"/>
+      <c r="A469" s="156"/>
+      <c r="B469" s="174"/>
       <c r="C469" s="94" t="s">
         <v>269</v>
       </c>
@@ -12212,10 +12216,10 @@
       <c r="J469" s="40"/>
     </row>
     <row r="470" spans="1:10" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A470" s="163" t="s">
+      <c r="A470" s="155" t="s">
         <v>625</v>
       </c>
-      <c r="B470" s="183" t="s">
+      <c r="B470" s="176" t="s">
         <v>698</v>
       </c>
       <c r="C470" s="62" t="s">
@@ -12230,8 +12234,8 @@
       <c r="J470" s="40"/>
     </row>
     <row r="471" spans="1:10" ht="24.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A471" s="286"/>
-      <c r="B471" s="184"/>
+      <c r="A471" s="156"/>
+      <c r="B471" s="178"/>
       <c r="C471" s="62" t="s">
         <v>25</v>
       </c>
@@ -12244,24 +12248,24 @@
       <c r="J471" s="40"/>
     </row>
     <row r="472" spans="1:10" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A472" s="175" t="s">
+      <c r="A472" s="261" t="s">
         <v>420</v>
       </c>
-      <c r="B472" s="176"/>
-      <c r="C472" s="176"/>
-      <c r="D472" s="176"/>
-      <c r="E472" s="176"/>
-      <c r="F472" s="176"/>
-      <c r="G472" s="176"/>
-      <c r="H472" s="176"/>
-      <c r="I472" s="176"/>
-      <c r="J472" s="177"/>
+      <c r="B472" s="264"/>
+      <c r="C472" s="264"/>
+      <c r="D472" s="264"/>
+      <c r="E472" s="264"/>
+      <c r="F472" s="264"/>
+      <c r="G472" s="264"/>
+      <c r="H472" s="264"/>
+      <c r="I472" s="264"/>
+      <c r="J472" s="265"/>
     </row>
     <row r="473" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A473" s="240" t="s">
+      <c r="A473" s="200" t="s">
         <v>537</v>
       </c>
-      <c r="B473" s="242" t="s">
+      <c r="B473" s="202" t="s">
         <v>263</v>
       </c>
       <c r="C473" s="139" t="s">
@@ -12278,8 +12282,8 @@
       <c r="J473" s="61"/>
     </row>
     <row r="474" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A474" s="241"/>
-      <c r="B474" s="242"/>
+      <c r="A474" s="201"/>
+      <c r="B474" s="202"/>
       <c r="C474" s="139" t="s">
         <v>264</v>
       </c>
@@ -12292,8 +12296,8 @@
       <c r="J474" s="61"/>
     </row>
     <row r="475" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A475" s="241"/>
-      <c r="B475" s="242"/>
+      <c r="A475" s="201"/>
+      <c r="B475" s="202"/>
       <c r="C475" s="139" t="s">
         <v>266</v>
       </c>
@@ -12306,8 +12310,8 @@
       <c r="J475" s="61"/>
     </row>
     <row r="476" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A476" s="241"/>
-      <c r="B476" s="242"/>
+      <c r="A476" s="201"/>
+      <c r="B476" s="202"/>
       <c r="C476" s="139" t="s">
         <v>267</v>
       </c>
@@ -12320,8 +12324,8 @@
       <c r="J476" s="61"/>
     </row>
     <row r="477" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
-      <c r="A477" s="241"/>
-      <c r="B477" s="242"/>
+      <c r="A477" s="201"/>
+      <c r="B477" s="202"/>
       <c r="C477" s="100" t="s">
         <v>268</v>
       </c>
@@ -12336,6 +12340,127 @@
     <row r="478" spans="1:10" ht="14.4" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="145">
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="B3:J3"/>
+    <mergeCell ref="A4:J4"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="A52:A59"/>
+    <mergeCell ref="B52:B59"/>
+    <mergeCell ref="A27:A33"/>
+    <mergeCell ref="A34:A35"/>
+    <mergeCell ref="B34:B35"/>
+    <mergeCell ref="A36:A48"/>
+    <mergeCell ref="B36:B48"/>
+    <mergeCell ref="A49:A51"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B13:B14"/>
+    <mergeCell ref="A13:A14"/>
+    <mergeCell ref="A60:A68"/>
+    <mergeCell ref="B60:B68"/>
+    <mergeCell ref="A69:A79"/>
+    <mergeCell ref="B69:B79"/>
+    <mergeCell ref="A80:A90"/>
+    <mergeCell ref="B80:B90"/>
+    <mergeCell ref="B49:B51"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
+    <mergeCell ref="B27:B33"/>
+    <mergeCell ref="B19:B25"/>
+    <mergeCell ref="A19:A25"/>
+    <mergeCell ref="A472:J472"/>
+    <mergeCell ref="A208:A218"/>
+    <mergeCell ref="B208:B218"/>
+    <mergeCell ref="A284:J284"/>
+    <mergeCell ref="A434:J434"/>
+    <mergeCell ref="A196:A202"/>
+    <mergeCell ref="A203:A207"/>
+    <mergeCell ref="B470:B471"/>
+    <mergeCell ref="A132:J132"/>
+    <mergeCell ref="D188:D195"/>
+    <mergeCell ref="D196:D202"/>
+    <mergeCell ref="D203:D207"/>
+    <mergeCell ref="A236:J236"/>
+    <mergeCell ref="B141:B145"/>
+    <mergeCell ref="A141:A145"/>
+    <mergeCell ref="A151:A155"/>
+    <mergeCell ref="B151:B155"/>
+    <mergeCell ref="A146:A150"/>
+    <mergeCell ref="B146:B150"/>
+    <mergeCell ref="A156:A160"/>
+    <mergeCell ref="B156:B160"/>
+    <mergeCell ref="B230:B235"/>
+    <mergeCell ref="A230:A235"/>
+    <mergeCell ref="B161:B183"/>
+    <mergeCell ref="A91:A99"/>
+    <mergeCell ref="B91:B99"/>
+    <mergeCell ref="A100:A106"/>
+    <mergeCell ref="B100:B106"/>
+    <mergeCell ref="A112:A113"/>
+    <mergeCell ref="B112:B113"/>
+    <mergeCell ref="A114:A120"/>
+    <mergeCell ref="B114:B120"/>
+    <mergeCell ref="A243:J243"/>
+    <mergeCell ref="A107:A111"/>
+    <mergeCell ref="B107:B111"/>
+    <mergeCell ref="C111:J111"/>
+    <mergeCell ref="B137:B140"/>
+    <mergeCell ref="A137:A140"/>
+    <mergeCell ref="A184:A187"/>
+    <mergeCell ref="B184:B187"/>
+    <mergeCell ref="A128:A130"/>
+    <mergeCell ref="B128:B130"/>
+    <mergeCell ref="A121:A127"/>
+    <mergeCell ref="B121:B127"/>
+    <mergeCell ref="A131:J131"/>
+    <mergeCell ref="A473:A477"/>
+    <mergeCell ref="B473:B477"/>
+    <mergeCell ref="A227:A229"/>
+    <mergeCell ref="B227:B229"/>
+    <mergeCell ref="A221:A223"/>
+    <mergeCell ref="B221:B223"/>
+    <mergeCell ref="B133:B136"/>
+    <mergeCell ref="A133:A136"/>
+    <mergeCell ref="B219:B220"/>
+    <mergeCell ref="A219:A220"/>
+    <mergeCell ref="A224:J224"/>
+    <mergeCell ref="A188:A195"/>
+    <mergeCell ref="B196:B202"/>
+    <mergeCell ref="B203:B207"/>
+    <mergeCell ref="B188:B195"/>
+    <mergeCell ref="A225:A226"/>
+    <mergeCell ref="B225:B226"/>
+    <mergeCell ref="A161:A183"/>
+    <mergeCell ref="B356:B364"/>
+    <mergeCell ref="B435:B437"/>
+    <mergeCell ref="A435:A437"/>
+    <mergeCell ref="A431:J431"/>
+    <mergeCell ref="A376:J376"/>
+    <mergeCell ref="A423:J423"/>
+    <mergeCell ref="B377:B384"/>
+    <mergeCell ref="A377:A384"/>
+    <mergeCell ref="B385:B389"/>
+    <mergeCell ref="A385:A389"/>
+    <mergeCell ref="B424:B430"/>
+    <mergeCell ref="A424:A430"/>
+    <mergeCell ref="B390:B406"/>
+    <mergeCell ref="A390:A406"/>
+    <mergeCell ref="B407:B422"/>
+    <mergeCell ref="A407:A422"/>
+    <mergeCell ref="A279:A283"/>
+    <mergeCell ref="B279:B283"/>
+    <mergeCell ref="A260:A272"/>
+    <mergeCell ref="B260:B272"/>
+    <mergeCell ref="A247:A248"/>
+    <mergeCell ref="B247:B248"/>
+    <mergeCell ref="A250:A254"/>
+    <mergeCell ref="B250:B254"/>
+    <mergeCell ref="A255:A259"/>
+    <mergeCell ref="B255:B259"/>
     <mergeCell ref="A245:J245"/>
     <mergeCell ref="A238:J238"/>
     <mergeCell ref="E438:E459"/>
@@ -12360,127 +12485,6 @@
     <mergeCell ref="A438:A459"/>
     <mergeCell ref="A273:A278"/>
     <mergeCell ref="B273:B278"/>
-    <mergeCell ref="A279:A283"/>
-    <mergeCell ref="B279:B283"/>
-    <mergeCell ref="A260:A272"/>
-    <mergeCell ref="B260:B272"/>
-    <mergeCell ref="A247:A248"/>
-    <mergeCell ref="B247:B248"/>
-    <mergeCell ref="A250:A254"/>
-    <mergeCell ref="B250:B254"/>
-    <mergeCell ref="A255:A259"/>
-    <mergeCell ref="B255:B259"/>
-    <mergeCell ref="B377:B384"/>
-    <mergeCell ref="A377:A384"/>
-    <mergeCell ref="B385:B389"/>
-    <mergeCell ref="A385:A389"/>
-    <mergeCell ref="B424:B430"/>
-    <mergeCell ref="A424:A430"/>
-    <mergeCell ref="B390:B406"/>
-    <mergeCell ref="A390:A406"/>
-    <mergeCell ref="B407:B422"/>
-    <mergeCell ref="A407:A422"/>
-    <mergeCell ref="A473:A477"/>
-    <mergeCell ref="B473:B477"/>
-    <mergeCell ref="A227:A229"/>
-    <mergeCell ref="B227:B229"/>
-    <mergeCell ref="A221:A223"/>
-    <mergeCell ref="B221:B223"/>
-    <mergeCell ref="B133:B136"/>
-    <mergeCell ref="A133:A136"/>
-    <mergeCell ref="B219:B220"/>
-    <mergeCell ref="A219:A220"/>
-    <mergeCell ref="A224:J224"/>
-    <mergeCell ref="A188:A195"/>
-    <mergeCell ref="B196:B202"/>
-    <mergeCell ref="B203:B207"/>
-    <mergeCell ref="B188:B195"/>
-    <mergeCell ref="A225:A226"/>
-    <mergeCell ref="B225:B226"/>
-    <mergeCell ref="A161:A183"/>
-    <mergeCell ref="B356:B364"/>
-    <mergeCell ref="B435:B437"/>
-    <mergeCell ref="A435:A437"/>
-    <mergeCell ref="A431:J431"/>
-    <mergeCell ref="A376:J376"/>
-    <mergeCell ref="A423:J423"/>
-    <mergeCell ref="A91:A99"/>
-    <mergeCell ref="B91:B99"/>
-    <mergeCell ref="A100:A106"/>
-    <mergeCell ref="B100:B106"/>
-    <mergeCell ref="A112:A113"/>
-    <mergeCell ref="B112:B113"/>
-    <mergeCell ref="A114:A120"/>
-    <mergeCell ref="B114:B120"/>
-    <mergeCell ref="A243:J243"/>
-    <mergeCell ref="A107:A111"/>
-    <mergeCell ref="B107:B111"/>
-    <mergeCell ref="C111:J111"/>
-    <mergeCell ref="B137:B140"/>
-    <mergeCell ref="A137:A140"/>
-    <mergeCell ref="A184:A187"/>
-    <mergeCell ref="B184:B187"/>
-    <mergeCell ref="A128:A130"/>
-    <mergeCell ref="B128:B130"/>
-    <mergeCell ref="A121:A127"/>
-    <mergeCell ref="B121:B127"/>
-    <mergeCell ref="A131:J131"/>
-    <mergeCell ref="A472:J472"/>
-    <mergeCell ref="A208:A218"/>
-    <mergeCell ref="B208:B218"/>
-    <mergeCell ref="A284:J284"/>
-    <mergeCell ref="A434:J434"/>
-    <mergeCell ref="A196:A202"/>
-    <mergeCell ref="A203:A207"/>
-    <mergeCell ref="B470:B471"/>
-    <mergeCell ref="A132:J132"/>
-    <mergeCell ref="D188:D195"/>
-    <mergeCell ref="D196:D202"/>
-    <mergeCell ref="D203:D207"/>
-    <mergeCell ref="A236:J236"/>
-    <mergeCell ref="B141:B145"/>
-    <mergeCell ref="A141:A145"/>
-    <mergeCell ref="A151:A155"/>
-    <mergeCell ref="B151:B155"/>
-    <mergeCell ref="A146:A150"/>
-    <mergeCell ref="B146:B150"/>
-    <mergeCell ref="A156:A160"/>
-    <mergeCell ref="B156:B160"/>
-    <mergeCell ref="B230:B235"/>
-    <mergeCell ref="A230:A235"/>
-    <mergeCell ref="B161:B183"/>
-    <mergeCell ref="A60:A68"/>
-    <mergeCell ref="B60:B68"/>
-    <mergeCell ref="A69:A79"/>
-    <mergeCell ref="B69:B79"/>
-    <mergeCell ref="A80:A90"/>
-    <mergeCell ref="B80:B90"/>
-    <mergeCell ref="B49:B51"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="B27:B33"/>
-    <mergeCell ref="B19:B25"/>
-    <mergeCell ref="A19:A25"/>
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="B3:J3"/>
-    <mergeCell ref="A4:J4"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A52:A59"/>
-    <mergeCell ref="B52:B59"/>
-    <mergeCell ref="A27:A33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="A36:A48"/>
-    <mergeCell ref="B36:B48"/>
-    <mergeCell ref="A49:A51"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="A13:A14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -13578,13 +13582,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="321" t="s">
+      <c r="A1" s="315" t="s">
         <v>337</v>
       </c>
-      <c r="B1" s="321"/>
-      <c r="C1" s="321"/>
-      <c r="D1" s="321"/>
-      <c r="E1" s="321"/>
+      <c r="B1" s="315"/>
+      <c r="C1" s="315"/>
+      <c r="D1" s="315"/>
+      <c r="E1" s="315"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="13" t="s">
@@ -13604,10 +13608,10 @@
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="318" t="s">
+      <c r="A3" s="320" t="s">
         <v>17</v>
       </c>
-      <c r="B3" s="318" t="s">
+      <c r="B3" s="320" t="s">
         <v>203</v>
       </c>
       <c r="C3" s="21">
@@ -13621,8 +13625,8 @@
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="324"/>
-      <c r="B4" s="324"/>
+      <c r="A4" s="321"/>
+      <c r="B4" s="321"/>
       <c r="C4" s="21">
         <v>2</v>
       </c>
@@ -13632,8 +13636,8 @@
       <c r="E4" s="23"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="324"/>
-      <c r="B5" s="324"/>
+      <c r="A5" s="321"/>
+      <c r="B5" s="321"/>
       <c r="C5" s="21">
         <v>3</v>
       </c>
@@ -13643,8 +13647,8 @@
       <c r="E5" s="23"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="324"/>
-      <c r="B6" s="324"/>
+      <c r="A6" s="321"/>
+      <c r="B6" s="321"/>
       <c r="C6" s="21">
         <v>4</v>
       </c>
@@ -13654,8 +13658,8 @@
       <c r="E6" s="23"/>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="324"/>
-      <c r="B7" s="324"/>
+      <c r="A7" s="321"/>
+      <c r="B7" s="321"/>
       <c r="C7" s="21">
         <v>5</v>
       </c>
@@ -13665,8 +13669,8 @@
       <c r="E7" s="23"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="325"/>
-      <c r="B8" s="325"/>
+      <c r="A8" s="322"/>
+      <c r="B8" s="322"/>
       <c r="C8" s="21">
         <v>6</v>
       </c>
@@ -13691,10 +13695,10 @@
       <c r="E9" s="23"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="318" t="s">
+      <c r="A10" s="320" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="318" t="s">
+      <c r="B10" s="320" t="s">
         <v>212</v>
       </c>
       <c r="C10" s="26">
@@ -13708,8 +13712,8 @@
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="324"/>
-      <c r="B11" s="324"/>
+      <c r="A11" s="321"/>
+      <c r="B11" s="321"/>
       <c r="C11" s="26">
         <v>2</v>
       </c>
@@ -13719,8 +13723,8 @@
       <c r="E11" s="27"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="324"/>
-      <c r="B12" s="324"/>
+      <c r="A12" s="321"/>
+      <c r="B12" s="321"/>
       <c r="C12" s="26">
         <v>3</v>
       </c>
@@ -13730,8 +13734,8 @@
       <c r="E12" s="27"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="324"/>
-      <c r="B13" s="324"/>
+      <c r="A13" s="321"/>
+      <c r="B13" s="321"/>
       <c r="C13" s="26">
         <v>4</v>
       </c>
@@ -13741,8 +13745,8 @@
       <c r="E13" s="27"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="324"/>
-      <c r="B14" s="324"/>
+      <c r="A14" s="321"/>
+      <c r="B14" s="321"/>
       <c r="C14" s="26">
         <v>5</v>
       </c>
@@ -13752,8 +13756,8 @@
       <c r="E14" s="27"/>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="324"/>
-      <c r="B15" s="324"/>
+      <c r="A15" s="321"/>
+      <c r="B15" s="321"/>
       <c r="C15" s="26">
         <v>6</v>
       </c>
@@ -13781,7 +13785,7 @@
       <c r="A17" s="309" t="s">
         <v>45</v>
       </c>
-      <c r="B17" s="320" t="s">
+      <c r="B17" s="316" t="s">
         <v>339</v>
       </c>
       <c r="C17" s="15">
@@ -13794,7 +13798,7 @@
     </row>
     <row r="18" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="309"/>
-      <c r="B18" s="320"/>
+      <c r="B18" s="316"/>
       <c r="C18" s="15">
         <v>2</v>
       </c>
@@ -13805,7 +13809,7 @@
     </row>
     <row r="19" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="309"/>
-      <c r="B19" s="320"/>
+      <c r="B19" s="316"/>
       <c r="C19" s="15">
         <v>3</v>
       </c>
@@ -13816,7 +13820,7 @@
     </row>
     <row r="20" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="309"/>
-      <c r="B20" s="320"/>
+      <c r="B20" s="316"/>
       <c r="C20" s="15">
         <v>4</v>
       </c>
@@ -13827,7 +13831,7 @@
     </row>
     <row r="21" spans="1:5" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="309"/>
-      <c r="B21" s="320"/>
+      <c r="B21" s="316"/>
       <c r="C21" s="15">
         <v>5</v>
       </c>
@@ -13837,13 +13841,13 @@
       <c r="E21" s="19"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="326" t="s">
+      <c r="A22" s="323" t="s">
         <v>336</v>
       </c>
-      <c r="B22" s="326"/>
-      <c r="C22" s="326"/>
-      <c r="D22" s="326"/>
-      <c r="E22" s="326"/>
+      <c r="B22" s="323"/>
+      <c r="C22" s="323"/>
+      <c r="D22" s="323"/>
+      <c r="E22" s="323"/>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="13" t="s">
@@ -13863,10 +13867,10 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="318" t="s">
+      <c r="A24" s="320" t="s">
         <v>345</v>
       </c>
-      <c r="B24" s="318" t="s">
+      <c r="B24" s="320" t="s">
         <v>389</v>
       </c>
       <c r="C24" s="24">
@@ -13878,8 +13882,8 @@
       <c r="E24" s="34"/>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="319"/>
-      <c r="B25" s="319"/>
+      <c r="A25" s="318"/>
+      <c r="B25" s="318"/>
       <c r="C25" s="24">
         <v>2</v>
       </c>
@@ -13889,8 +13893,8 @@
       <c r="E25" s="34"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="319"/>
-      <c r="B26" s="319"/>
+      <c r="A26" s="318"/>
+      <c r="B26" s="318"/>
       <c r="C26" s="24">
         <v>3</v>
       </c>
@@ -13900,8 +13904,8 @@
       <c r="E26" s="34"/>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="319"/>
-      <c r="B27" s="319"/>
+      <c r="A27" s="318"/>
+      <c r="B27" s="318"/>
       <c r="C27" s="24">
         <v>4</v>
       </c>
@@ -13911,8 +13915,8 @@
       <c r="E27" s="34"/>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="319"/>
-      <c r="B28" s="319"/>
+      <c r="A28" s="318"/>
+      <c r="B28" s="318"/>
       <c r="C28" s="24">
         <v>5</v>
       </c>
@@ -13922,8 +13926,8 @@
       <c r="E28" s="34"/>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="319"/>
-      <c r="B29" s="319"/>
+      <c r="A29" s="318"/>
+      <c r="B29" s="318"/>
       <c r="C29" s="24">
         <v>6</v>
       </c>
@@ -13933,8 +13937,8 @@
       <c r="E29" s="34"/>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="319"/>
-      <c r="B30" s="319"/>
+      <c r="A30" s="318"/>
+      <c r="B30" s="318"/>
       <c r="C30" s="24">
         <v>7</v>
       </c>
@@ -13944,8 +13948,8 @@
       <c r="E30" s="34"/>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="319"/>
-      <c r="B31" s="319"/>
+      <c r="A31" s="318"/>
+      <c r="B31" s="318"/>
       <c r="C31" s="24">
         <v>8</v>
       </c>
@@ -13955,8 +13959,8 @@
       <c r="E31" s="34"/>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="319"/>
-      <c r="B32" s="319"/>
+      <c r="A32" s="318"/>
+      <c r="B32" s="318"/>
       <c r="C32" s="24">
         <v>9</v>
       </c>
@@ -13966,8 +13970,8 @@
       <c r="E32" s="34"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="319"/>
-      <c r="B33" s="319"/>
+      <c r="A33" s="318"/>
+      <c r="B33" s="318"/>
       <c r="C33" s="24">
         <v>10</v>
       </c>
@@ -13977,8 +13981,8 @@
       <c r="E33" s="34"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="319"/>
-      <c r="B34" s="319"/>
+      <c r="A34" s="318"/>
+      <c r="B34" s="318"/>
       <c r="C34" s="24">
         <v>11</v>
       </c>
@@ -13988,10 +13992,10 @@
       <c r="E34" s="34"/>
     </row>
     <row r="35" spans="1:5" ht="25.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="322" t="s">
+      <c r="A35" s="317" t="s">
         <v>346</v>
       </c>
-      <c r="B35" s="322" t="s">
+      <c r="B35" s="317" t="s">
         <v>350</v>
       </c>
       <c r="C35" s="24">
@@ -14003,8 +14007,8 @@
       <c r="E35" s="34"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="319"/>
-      <c r="B36" s="319"/>
+      <c r="A36" s="318"/>
+      <c r="B36" s="318"/>
       <c r="C36" s="24">
         <v>2</v>
       </c>
@@ -14014,8 +14018,8 @@
       <c r="E36" s="34"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="323"/>
-      <c r="B37" s="323"/>
+      <c r="A37" s="319"/>
+      <c r="B37" s="319"/>
       <c r="C37" s="24">
         <v>3</v>
       </c>
@@ -14025,10 +14029,10 @@
       <c r="E37" s="34"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="318" t="s">
+      <c r="A38" s="320" t="s">
         <v>347</v>
       </c>
-      <c r="B38" s="318" t="s">
+      <c r="B38" s="320" t="s">
         <v>390</v>
       </c>
       <c r="C38" s="24">
@@ -14040,8 +14044,8 @@
       <c r="E38" s="34"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="319"/>
-      <c r="B39" s="319"/>
+      <c r="A39" s="318"/>
+      <c r="B39" s="318"/>
       <c r="C39" s="24">
         <v>2</v>
       </c>
@@ -14051,8 +14055,8 @@
       <c r="E39" s="34"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="319"/>
-      <c r="B40" s="319"/>
+      <c r="A40" s="318"/>
+      <c r="B40" s="318"/>
       <c r="C40" s="24">
         <v>3</v>
       </c>
@@ -14062,8 +14066,8 @@
       <c r="E40" s="34"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="319"/>
-      <c r="B41" s="319"/>
+      <c r="A41" s="318"/>
+      <c r="B41" s="318"/>
       <c r="C41" s="24">
         <v>4</v>
       </c>
@@ -14073,8 +14077,8 @@
       <c r="E41" s="34"/>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="319"/>
-      <c r="B42" s="319"/>
+      <c r="A42" s="318"/>
+      <c r="B42" s="318"/>
       <c r="C42" s="24">
         <v>5</v>
       </c>
@@ -14084,8 +14088,8 @@
       <c r="E42" s="34"/>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="319"/>
-      <c r="B43" s="319"/>
+      <c r="A43" s="318"/>
+      <c r="B43" s="318"/>
       <c r="C43" s="24">
         <v>6</v>
       </c>
@@ -14095,10 +14099,10 @@
       <c r="E43" s="34"/>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="318" t="s">
+      <c r="A44" s="320" t="s">
         <v>348</v>
       </c>
-      <c r="B44" s="318" t="s">
+      <c r="B44" s="320" t="s">
         <v>391</v>
       </c>
       <c r="C44" s="24"/>
@@ -14106,29 +14110,29 @@
       <c r="E44" s="34"/>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="319"/>
-      <c r="B45" s="319"/>
+      <c r="A45" s="318"/>
+      <c r="B45" s="318"/>
       <c r="C45" s="24"/>
       <c r="D45" s="24"/>
       <c r="E45" s="34"/>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="319"/>
-      <c r="B46" s="319"/>
+      <c r="A46" s="318"/>
+      <c r="B46" s="318"/>
       <c r="C46" s="24"/>
       <c r="D46" s="24"/>
       <c r="E46" s="34"/>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="319"/>
-      <c r="B47" s="319"/>
+      <c r="A47" s="318"/>
+      <c r="B47" s="318"/>
       <c r="C47" s="24"/>
       <c r="D47" s="24"/>
       <c r="E47" s="34"/>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="319"/>
-      <c r="B48" s="319"/>
+      <c r="A48" s="318"/>
+      <c r="B48" s="318"/>
       <c r="C48" s="29"/>
       <c r="D48" s="29"/>
       <c r="E48" s="36"/>
@@ -14147,10 +14151,10 @@
       <c r="E49" s="17"/>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="320" t="s">
+      <c r="A50" s="316" t="s">
         <v>368</v>
       </c>
-      <c r="B50" s="320" t="s">
+      <c r="B50" s="316" t="s">
         <v>216</v>
       </c>
       <c r="C50" s="32">
@@ -14162,8 +14166,8 @@
       <c r="E50" s="17"/>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="320"/>
-      <c r="B51" s="320"/>
+      <c r="A51" s="316"/>
+      <c r="B51" s="316"/>
       <c r="C51" s="32">
         <v>2</v>
       </c>
@@ -14173,8 +14177,8 @@
       <c r="E51" s="17"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="320"/>
-      <c r="B52" s="320"/>
+      <c r="A52" s="316"/>
+      <c r="B52" s="316"/>
       <c r="C52" s="32">
         <v>3</v>
       </c>
@@ -14184,8 +14188,8 @@
       <c r="E52" s="17"/>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="320"/>
-      <c r="B53" s="320"/>
+      <c r="A53" s="316"/>
+      <c r="B53" s="316"/>
       <c r="C53" s="32">
         <v>4</v>
       </c>
@@ -14195,8 +14199,8 @@
       <c r="E53" s="17"/>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="320"/>
-      <c r="B54" s="320"/>
+      <c r="A54" s="316"/>
+      <c r="B54" s="316"/>
       <c r="C54" s="32">
         <v>5</v>
       </c>
@@ -14206,10 +14210,10 @@
       <c r="E54" s="17"/>
     </row>
     <row r="55" spans="1:5" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="315" t="s">
+      <c r="A55" s="324" t="s">
         <v>374</v>
       </c>
-      <c r="B55" s="315" t="s">
+      <c r="B55" s="324" t="s">
         <v>375</v>
       </c>
       <c r="C55" s="32">
@@ -14221,8 +14225,8 @@
       <c r="E55" s="17"/>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="316"/>
-      <c r="B56" s="316"/>
+      <c r="A56" s="325"/>
+      <c r="B56" s="325"/>
       <c r="C56" s="32">
         <v>2</v>
       </c>
@@ -14232,8 +14236,8 @@
       <c r="E56" s="12"/>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="317"/>
-      <c r="B57" s="317"/>
+      <c r="A57" s="326"/>
+      <c r="B57" s="326"/>
       <c r="C57" s="32">
         <v>3</v>
       </c>
@@ -14244,6 +14248,16 @@
     </row>
   </sheetData>
   <mergeCells count="20">
+    <mergeCell ref="B55:B57"/>
+    <mergeCell ref="A55:A57"/>
+    <mergeCell ref="A24:A34"/>
+    <mergeCell ref="B24:B34"/>
+    <mergeCell ref="A38:A43"/>
+    <mergeCell ref="B38:B43"/>
+    <mergeCell ref="A44:A48"/>
+    <mergeCell ref="B44:B48"/>
+    <mergeCell ref="A50:A54"/>
+    <mergeCell ref="B50:B54"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="B17:B21"/>
     <mergeCell ref="A17:A21"/>
@@ -14254,16 +14268,6 @@
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="B10:B15"/>
     <mergeCell ref="A22:E22"/>
-    <mergeCell ref="B55:B57"/>
-    <mergeCell ref="A55:A57"/>
-    <mergeCell ref="A24:A34"/>
-    <mergeCell ref="B24:B34"/>
-    <mergeCell ref="A38:A43"/>
-    <mergeCell ref="B38:B43"/>
-    <mergeCell ref="A44:A48"/>
-    <mergeCell ref="B44:B48"/>
-    <mergeCell ref="A50:A54"/>
-    <mergeCell ref="B50:B54"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
@@ -14299,7 +14303,7 @@
       </c>
     </row>
     <row r="3" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A3" s="329" t="s">
+      <c r="A3" s="327" t="s">
         <v>298</v>
       </c>
       <c r="B3" s="330" t="s">
@@ -14311,10 +14315,10 @@
       <c r="D3" s="1" t="s">
         <v>105</v>
       </c>
-      <c r="E3" s="328"/>
+      <c r="E3" s="329"/>
     </row>
     <row r="4" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="329"/>
+      <c r="A4" s="327"/>
       <c r="B4" s="307"/>
       <c r="C4" s="5">
         <v>2</v>
@@ -14322,10 +14326,10 @@
       <c r="D4" s="1" t="s">
         <v>108</v>
       </c>
-      <c r="E4" s="328"/>
+      <c r="E4" s="329"/>
     </row>
     <row r="5" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="329"/>
+      <c r="A5" s="327"/>
       <c r="B5" s="307"/>
       <c r="C5" s="5">
         <v>3</v>
@@ -14333,10 +14337,10 @@
       <c r="D5" s="1" t="s">
         <v>282</v>
       </c>
-      <c r="E5" s="328"/>
+      <c r="E5" s="329"/>
     </row>
     <row r="6" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="329"/>
+      <c r="A6" s="327"/>
       <c r="B6" s="307"/>
       <c r="C6" s="5">
         <v>4</v>
@@ -14344,10 +14348,10 @@
       <c r="D6" s="1" t="s">
         <v>283</v>
       </c>
-      <c r="E6" s="328"/>
+      <c r="E6" s="329"/>
     </row>
     <row r="7" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="329"/>
+      <c r="A7" s="327"/>
       <c r="B7" s="307"/>
       <c r="C7" s="5">
         <v>5</v>
@@ -14355,10 +14359,10 @@
       <c r="D7" s="1" t="s">
         <v>284</v>
       </c>
-      <c r="E7" s="328"/>
+      <c r="E7" s="329"/>
     </row>
     <row r="8" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="329"/>
+      <c r="A8" s="327"/>
       <c r="B8" s="307"/>
       <c r="C8" s="5">
         <v>6</v>
@@ -14366,10 +14370,10 @@
       <c r="D8" s="1" t="s">
         <v>285</v>
       </c>
-      <c r="E8" s="328"/>
+      <c r="E8" s="329"/>
     </row>
     <row r="9" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="329"/>
+      <c r="A9" s="327"/>
       <c r="B9" s="307"/>
       <c r="C9" s="5">
         <v>7</v>
@@ -14377,10 +14381,10 @@
       <c r="D9" s="1" t="s">
         <v>286</v>
       </c>
-      <c r="E9" s="328"/>
+      <c r="E9" s="329"/>
     </row>
     <row r="10" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="329"/>
+      <c r="A10" s="327"/>
       <c r="B10" s="307"/>
       <c r="C10" s="5">
         <v>8</v>
@@ -14388,10 +14392,10 @@
       <c r="D10" s="1" t="s">
         <v>287</v>
       </c>
-      <c r="E10" s="328"/>
+      <c r="E10" s="329"/>
     </row>
     <row r="11" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A11" s="329"/>
+      <c r="A11" s="327"/>
       <c r="B11" s="307"/>
       <c r="C11" s="5">
         <v>9</v>
@@ -14399,10 +14403,10 @@
       <c r="D11" s="1" t="s">
         <v>288</v>
       </c>
-      <c r="E11" s="328"/>
+      <c r="E11" s="329"/>
     </row>
     <row r="12" spans="1:5" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="328" t="s">
+      <c r="A12" s="329" t="s">
         <v>300</v>
       </c>
       <c r="B12" s="331" t="s">
@@ -14417,7 +14421,7 @@
       <c r="E12" s="7"/>
     </row>
     <row r="13" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="328"/>
+      <c r="A13" s="329"/>
       <c r="B13" s="331"/>
       <c r="C13" s="5">
         <v>2</v>
@@ -14433,7 +14437,7 @@
       <c r="A14" s="304" t="s">
         <v>295</v>
       </c>
-      <c r="B14" s="327" t="s">
+      <c r="B14" s="328" t="s">
         <v>379</v>
       </c>
       <c r="C14" s="6"/>
@@ -14446,7 +14450,7 @@
     </row>
     <row r="15" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="304"/>
-      <c r="B15" s="327"/>
+      <c r="B15" s="328"/>
       <c r="C15" s="6"/>
       <c r="D15" s="1" t="s">
         <v>290</v>
@@ -14457,7 +14461,7 @@
     </row>
     <row r="16" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="304"/>
-      <c r="B16" s="327"/>
+      <c r="B16" s="328"/>
       <c r="C16" s="6"/>
       <c r="D16" s="1" t="s">
         <v>291</v>
@@ -14468,7 +14472,7 @@
     </row>
     <row r="17" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A17" s="304"/>
-      <c r="B17" s="327"/>
+      <c r="B17" s="328"/>
       <c r="C17" s="6"/>
       <c r="D17" s="1" t="s">
         <v>292</v>
@@ -14479,7 +14483,7 @@
     </row>
     <row r="18" spans="1:5" ht="37.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="304"/>
-      <c r="B18" s="327"/>
+      <c r="B18" s="328"/>
       <c r="C18" s="6"/>
       <c r="D18" s="1" t="s">
         <v>299</v>
@@ -14489,7 +14493,7 @@
       </c>
     </row>
     <row r="19" spans="1:5" ht="64.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="329" t="s">
+      <c r="A19" s="327" t="s">
         <v>305</v>
       </c>
       <c r="B19" s="304" t="s">
@@ -14504,7 +14508,7 @@
       <c r="E19" s="6"/>
     </row>
     <row r="20" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="329"/>
+      <c r="A20" s="327"/>
       <c r="B20" s="304"/>
       <c r="C20" s="6">
         <v>2</v>
@@ -14515,7 +14519,7 @@
       <c r="E20" s="6"/>
     </row>
     <row r="21" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A21" s="329"/>
+      <c r="A21" s="327"/>
       <c r="B21" s="304"/>
       <c r="C21" s="6">
         <v>3</v>
@@ -14526,7 +14530,7 @@
       <c r="E21" s="6"/>
     </row>
     <row r="22" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="329"/>
+      <c r="A22" s="327"/>
       <c r="B22" s="304"/>
       <c r="C22" s="6">
         <v>4</v>
@@ -14537,7 +14541,7 @@
       <c r="E22" s="6"/>
     </row>
     <row r="23" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A23" s="329" t="s">
+      <c r="A23" s="327" t="s">
         <v>306</v>
       </c>
       <c r="B23" s="304" t="s">
@@ -14552,7 +14556,7 @@
       <c r="E23" s="6"/>
     </row>
     <row r="24" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="329"/>
+      <c r="A24" s="327"/>
       <c r="B24" s="304"/>
       <c r="C24" s="6">
         <v>2</v>
@@ -14563,7 +14567,7 @@
       <c r="E24" s="6"/>
     </row>
     <row r="25" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="329"/>
+      <c r="A25" s="327"/>
       <c r="B25" s="304"/>
       <c r="C25" s="6">
         <v>3</v>
@@ -14574,7 +14578,7 @@
       <c r="E25" s="6"/>
     </row>
     <row r="26" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="329"/>
+      <c r="A26" s="327"/>
       <c r="B26" s="304"/>
       <c r="C26" s="6">
         <v>4</v>
@@ -14585,7 +14589,7 @@
       <c r="E26" s="6"/>
     </row>
     <row r="27" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A27" s="329" t="s">
+      <c r="A27" s="327" t="s">
         <v>307</v>
       </c>
       <c r="B27" s="304" t="s">
@@ -14600,7 +14604,7 @@
       <c r="E27" s="6"/>
     </row>
     <row r="28" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="329"/>
+      <c r="A28" s="327"/>
       <c r="B28" s="304"/>
       <c r="C28" s="6">
         <v>2</v>
@@ -14611,7 +14615,7 @@
       <c r="E28" s="6"/>
     </row>
     <row r="29" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="329"/>
+      <c r="A29" s="327"/>
       <c r="B29" s="304"/>
       <c r="C29" s="6">
         <v>3</v>
@@ -14622,7 +14626,7 @@
       <c r="E29" s="6"/>
     </row>
     <row r="30" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="329"/>
+      <c r="A30" s="327"/>
       <c r="B30" s="304"/>
       <c r="C30" s="6">
         <v>4</v>
@@ -14633,7 +14637,7 @@
       <c r="E30" s="6"/>
     </row>
     <row r="31" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="329" t="s">
+      <c r="A31" s="327" t="s">
         <v>308</v>
       </c>
       <c r="B31" s="304" t="s">
@@ -14648,7 +14652,7 @@
       <c r="E31" s="6"/>
     </row>
     <row r="32" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="329"/>
+      <c r="A32" s="327"/>
       <c r="B32" s="304"/>
       <c r="C32" s="6">
         <v>2</v>
@@ -14659,7 +14663,7 @@
       <c r="E32" s="6"/>
     </row>
     <row r="33" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="329"/>
+      <c r="A33" s="327"/>
       <c r="B33" s="304"/>
       <c r="C33" s="6">
         <v>3</v>
@@ -14670,7 +14674,7 @@
       <c r="E33" s="6"/>
     </row>
     <row r="34" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="329"/>
+      <c r="A34" s="327"/>
       <c r="B34" s="304"/>
       <c r="C34" s="6">
         <v>4</v>
@@ -14681,7 +14685,7 @@
       <c r="E34" s="6"/>
     </row>
     <row r="35" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="329" t="s">
+      <c r="A35" s="327" t="s">
         <v>309</v>
       </c>
       <c r="B35" s="304" t="s">
@@ -14696,7 +14700,7 @@
       <c r="E35" s="6"/>
     </row>
     <row r="36" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="329"/>
+      <c r="A36" s="327"/>
       <c r="B36" s="304"/>
       <c r="C36" s="6">
         <v>2</v>
@@ -14707,7 +14711,7 @@
       <c r="E36" s="6"/>
     </row>
     <row r="37" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="329"/>
+      <c r="A37" s="327"/>
       <c r="B37" s="304"/>
       <c r="C37" s="6">
         <v>3</v>
@@ -14718,7 +14722,7 @@
       <c r="E37" s="6"/>
     </row>
     <row r="38" spans="1:5" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="329"/>
+      <c r="A38" s="327"/>
       <c r="B38" s="304"/>
       <c r="C38" s="6">
         <v>4</v>
@@ -14730,6 +14734,14 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="B14:B18"/>
+    <mergeCell ref="A14:A18"/>
+    <mergeCell ref="B19:B22"/>
+    <mergeCell ref="E3:E11"/>
+    <mergeCell ref="A3:A11"/>
+    <mergeCell ref="A12:A13"/>
+    <mergeCell ref="B3:B11"/>
+    <mergeCell ref="B12:B13"/>
     <mergeCell ref="A35:A38"/>
     <mergeCell ref="B35:B38"/>
     <mergeCell ref="A19:A22"/>
@@ -14739,14 +14751,6 @@
     <mergeCell ref="B27:B30"/>
     <mergeCell ref="A31:A34"/>
     <mergeCell ref="B31:B34"/>
-    <mergeCell ref="B14:B18"/>
-    <mergeCell ref="A14:A18"/>
-    <mergeCell ref="B19:B22"/>
-    <mergeCell ref="E3:E11"/>
-    <mergeCell ref="A3:A11"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="B3:B11"/>
-    <mergeCell ref="B12:B13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -15200,15 +15204,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <AppVersion xmlns="08ce7a00-5569-4b3f-b1aa-ca7c736aa64b" xsi:nil="true"/>
@@ -15261,6 +15256,15 @@
 </p:properties>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7BE2177-65AC-4334-A59B-38104E0010B1}">
   <ds:schemaRefs>
@@ -15281,14 +15285,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03C45617-08BA-4BE5-A3D7-5F2E216E6EBC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1CDA93A-2C81-40FB-BDF2-C8B81B42A0B5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -15303,4 +15299,12 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03C45617-08BA-4BE5-A3D7-5F2E216E6EBC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/Primera versión/Input/Encuesta_Movilidad_Version_08_08_25.xlsx
+++ b/Primera versión/Input/Encuesta_Movilidad_Version_08_08_25.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f8f89820ab55adc2/Escritorio/Natura/Primera versión/Input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="143" documentId="8_{676B3BA6-46B2-41C2-A545-10BB88DE3D71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{794D2020-F5A8-4111-9219-9C262FDCD48F}"/>
+  <xr:revisionPtr revIDLastSave="144" documentId="8_{676B3BA6-46B2-41C2-A545-10BB88DE3D71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0417BA16-586F-49E7-9AF0-74C6AA700D62}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="5760" yWindow="3360" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="6456" yWindow="4056" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja 1" sheetId="1" r:id="rId1"/>
@@ -4746,10 +4746,6 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Sheets">
   <a:themeElements>
@@ -4959,7 +4955,7 @@
     <col min="3" max="3" width="50.44140625" style="107" customWidth="1"/>
     <col min="4" max="4" width="22.44140625" style="41" customWidth="1"/>
     <col min="5" max="5" width="20.44140625" style="41" customWidth="1"/>
-    <col min="6" max="6" width="23.44140625" style="41" customWidth="1"/>
+    <col min="6" max="6" width="70.109375" style="41" bestFit="1" customWidth="1"/>
     <col min="7" max="10" width="22.44140625" style="41" customWidth="1"/>
     <col min="11" max="16384" width="12.44140625" style="41"/>
   </cols>
@@ -5798,7 +5794,7 @@
       <c r="I51" s="40"/>
       <c r="J51" s="40"/>
     </row>
-    <row r="52" spans="1:10" ht="28.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" ht="14.4" x14ac:dyDescent="0.3">
       <c r="A52" s="288" t="s">
         <v>76</v>
       </c>
@@ -14757,6 +14753,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101005181076F8DBB9C489A82B37ADE714453" ma:contentTypeVersion="39" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="62545f31067f25252c10b6c76d9cb46e">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="08ce7a00-5569-4b3f-b1aa-ca7c736aa64b" xmlns:ns4="ca04e328-97a0-48bd-9e93-6fd51a4de9ff" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="ade3febc4a4334513c02f338efb26cc1" ns3:_="" ns4:_="">
     <xsd:import namespace="08ce7a00-5569-4b3f-b1aa-ca7c736aa64b"/>
@@ -15203,7 +15208,7 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <AppVersion xmlns="08ce7a00-5569-4b3f-b1aa-ca7c736aa64b" xsi:nil="true"/>
@@ -15256,16 +15261,15 @@
 </p:properties>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03C45617-08BA-4BE5-A3D7-5F2E216E6EBC}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A7BE2177-65AC-4334-A59B-38104E0010B1}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -15284,7 +15288,7 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D1CDA93A-2C81-40FB-BDF2-C8B81B42A0B5}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -15299,12 +15303,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{03C45617-08BA-4BE5-A3D7-5F2E216E6EBC}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>